--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5014387-D6E4-413B-8684-2F6625AB8AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D5A06D-D5DD-49D7-8EB7-01B0E8EB883F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="14" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051" sheetId="60" r:id="rId1"/>
@@ -53,15 +53,12 @@
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId32" roundtripDataChecksum="OIMpsSDwRNurc2ws9swRBhiMce7b/jzXJM4VYIB7AQA="/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3574" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3600" uniqueCount="474">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -576,6 +573,9 @@
     <t>PROGRAMAÇÃO ONDULADEIRA - DANPACK EMBALAGENS LTDA  —  OF: 001036</t>
   </si>
   <si>
+    <t>W55R</t>
+  </si>
+  <si>
     <t>1140x1840</t>
   </si>
   <si>
@@ -1471,6 +1471,15 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA - ABAPEL COMERCIO DE EMBALAGENS LTDA  —  OF: 001074</t>
+  </si>
+  <si>
+    <t>03/08/2026</t>
+  </si>
+  <si>
+    <t>1364x2123</t>
+  </si>
+  <si>
+    <t>1330x1913</t>
   </si>
 </sst>
 </file>
@@ -1482,7 +1491,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1531,13 +1540,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -1637,7 +1639,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1675,8 +1677,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1697,61 +1699,61 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1763,7 +1765,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1779,34 +1781,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1818,84 +1820,82 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2149,88 +2149,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
-        <v>342</v>
-      </c>
-      <c r="B1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="91" t="s">
+      <c r="A1" s="85" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="85" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2325,13 +2325,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C3" s="56" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E3" s="56" t="s">
         <v>27</v>
@@ -2340,7 +2340,7 @@
         <v>261916</v>
       </c>
       <c r="G3" s="56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H3" s="56">
         <v>500</v>
@@ -2403,7 +2403,7 @@
         <v>39</v>
       </c>
       <c r="AB3" s="51" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2411,13 +2411,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="58" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="56" t="s">
         <v>229</v>
       </c>
-      <c r="C4" s="56" t="s">
-        <v>228</v>
-      </c>
       <c r="D4" s="56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>27</v>
@@ -2426,7 +2426,7 @@
         <v>261915</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H4" s="56">
         <v>2000</v>
@@ -2489,7 +2489,7 @@
         <v>33</v>
       </c>
       <c r="AB4" s="51" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2497,13 +2497,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="58" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="56" t="s">
         <v>229</v>
       </c>
-      <c r="C5" s="56" t="s">
-        <v>228</v>
-      </c>
       <c r="D5" s="56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E5" s="56" t="s">
         <v>27</v>
@@ -2512,7 +2512,7 @@
         <v>261914</v>
       </c>
       <c r="G5" s="56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H5" s="56">
         <v>2000</v>
@@ -2575,7 +2575,7 @@
         <v>33</v>
       </c>
       <c r="AB5" s="51" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2583,13 +2583,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C6" s="56" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E6" s="56" t="s">
         <v>27</v>
@@ -2598,7 +2598,7 @@
         <v>261920</v>
       </c>
       <c r="G6" s="56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H6" s="56">
         <v>4000</v>
@@ -2661,7 +2661,7 @@
         <v>30</v>
       </c>
       <c r="AB6" s="51" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2669,13 +2669,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C7" s="56" t="s">
         <v>55</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E7" s="56" t="s">
         <v>27</v>
@@ -2684,7 +2684,7 @@
         <v>261919</v>
       </c>
       <c r="G7" s="56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H7" s="56">
         <v>1400</v>
@@ -2747,7 +2747,7 @@
         <v>39</v>
       </c>
       <c r="AB7" s="51" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2755,13 +2755,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C8" s="56" t="s">
         <v>55</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E8" s="56" t="s">
         <v>27</v>
@@ -2770,7 +2770,7 @@
         <v>261918</v>
       </c>
       <c r="G8" s="56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H8" s="56">
         <v>1400</v>
@@ -2833,7 +2833,7 @@
         <v>39</v>
       </c>
       <c r="AB8" s="51" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2841,13 +2841,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C9" s="56" t="s">
         <v>55</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E9" s="56" t="s">
         <v>27</v>
@@ -2856,7 +2856,7 @@
         <v>261917</v>
       </c>
       <c r="G9" s="56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H9" s="56">
         <v>500</v>
@@ -2919,7 +2919,7 @@
         <v>39</v>
       </c>
       <c r="AB9" s="51" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3055,88 +3055,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="86" t="s">
-        <v>256</v>
-      </c>
-      <c r="B1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="86" t="s">
+      <c r="A1" s="80" t="s">
+        <v>257</v>
+      </c>
+      <c r="B1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="80" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C3" s="65" t="s">
         <v>36</v>
@@ -3255,22 +3255,22 @@
         <v>1.9059999999999999</v>
       </c>
       <c r="K3" s="65" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L3" s="65">
         <v>1561014</v>
       </c>
       <c r="M3" s="65" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N3" s="65" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O3" s="65" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P3" s="65" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q3" s="65">
         <v>2</v>
@@ -3285,7 +3285,7 @@
         <v>58</v>
       </c>
       <c r="U3" s="65" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="V3" s="65" t="s">
         <v>28</v>
@@ -3300,7 +3300,7 @@
         <v>2</v>
       </c>
       <c r="AB3" s="65" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:28" s="32" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3308,13 +3308,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>27</v>
@@ -3323,7 +3323,7 @@
         <v>261937</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H4" s="15">
         <v>500</v>
@@ -3335,7 +3335,7 @@
         <v>1.64</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L4" s="17">
         <v>423.12</v>
@@ -3386,7 +3386,7 @@
         <v>33</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:28" s="32" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3394,13 +3394,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>27</v>
@@ -3409,7 +3409,7 @@
         <v>261932</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H5" s="15">
         <v>500</v>
@@ -3421,7 +3421,7 @@
         <v>1.21</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L5" s="17">
         <v>232.92500000000001</v>
@@ -3472,7 +3472,7 @@
         <v>39</v>
       </c>
       <c r="AB5" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:28" s="32" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3480,13 +3480,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>55</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>27</v>
@@ -3495,7 +3495,7 @@
         <v>261941</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H6" s="15">
         <v>2300</v>
@@ -3507,7 +3507,7 @@
         <v>1.07</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L6" s="17">
         <v>969.63400000000001</v>
@@ -3558,7 +3558,7 @@
         <v>30</v>
       </c>
       <c r="AB6" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:28" s="32" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3566,13 +3566,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>55</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>27</v>
@@ -3581,7 +3581,7 @@
         <v>261939</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H7" s="15">
         <v>2000</v>
@@ -3593,7 +3593,7 @@
         <v>1.61</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L7" s="17">
         <v>1738.8</v>
@@ -3644,7 +3644,7 @@
         <v>30</v>
       </c>
       <c r="AB7" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:28" s="32" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3652,13 +3652,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>27</v>
@@ -3667,7 +3667,7 @@
         <v>261934</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H8" s="15">
         <v>400</v>
@@ -3679,7 +3679,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L8" s="17">
         <v>184.8</v>
@@ -3730,7 +3730,7 @@
         <v>39</v>
       </c>
       <c r="AB8" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:28" s="32" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3738,13 +3738,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>27</v>
@@ -3753,7 +3753,7 @@
         <v>261936</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H9" s="15">
         <v>400</v>
@@ -3765,7 +3765,7 @@
         <v>1.06</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L9" s="17">
         <v>182.744</v>
@@ -3816,7 +3816,7 @@
         <v>39</v>
       </c>
       <c r="AB9" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:28" s="32" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3824,13 +3824,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>27</v>
@@ -3839,7 +3839,7 @@
         <v>261935</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H10" s="15">
         <v>400</v>
@@ -3851,7 +3851,7 @@
         <v>1.33</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L10" s="17">
         <v>233.548</v>
@@ -3902,7 +3902,7 @@
         <v>39</v>
       </c>
       <c r="AB10" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:28" s="32" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3910,13 +3910,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>27</v>
@@ -3925,7 +3925,7 @@
         <v>261933</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H11" s="15">
         <v>300</v>
@@ -3937,7 +3937,7 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L11" s="17">
         <v>134.39699999999999</v>
@@ -3988,7 +3988,7 @@
         <v>39</v>
       </c>
       <c r="AB11" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:28" s="32" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3996,13 +3996,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>55</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>27</v>
@@ -4011,7 +4011,7 @@
         <v>261938</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H12" s="15">
         <v>1000</v>
@@ -4023,7 +4023,7 @@
         <v>1.17</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L12" s="17">
         <v>485.55</v>
@@ -4074,7 +4074,7 @@
         <v>39</v>
       </c>
       <c r="AB12" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:28" s="32" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4082,7 +4082,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>36</v>
@@ -4107,22 +4107,22 @@
         <v>1.002</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L13" s="17">
         <v>1397790</v>
       </c>
       <c r="M13" s="19" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N13" s="16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P13" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q13" s="15">
         <v>2</v>
@@ -4131,13 +4131,13 @@
         <v>700</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="T13" s="15">
         <v>142</v>
       </c>
       <c r="U13" s="16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="V13" s="15" t="s">
         <v>28</v>
@@ -4154,7 +4154,7 @@
         <v>2</v>
       </c>
       <c r="AB13" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:28" s="32" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4291,88 +4291,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
-        <v>318</v>
-      </c>
-      <c r="B1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="91" t="s">
+      <c r="A1" s="85" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="85" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4467,13 +4467,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C3" s="56" t="s">
         <v>45</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E3" s="56" t="s">
         <v>27</v>
@@ -4482,7 +4482,7 @@
         <v>261959</v>
       </c>
       <c r="G3" s="56" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H3" s="56">
         <v>200</v>
@@ -4494,7 +4494,7 @@
         <v>1.403</v>
       </c>
       <c r="K3" s="56" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L3" s="53">
         <v>175.09399999999999</v>
@@ -4545,7 +4545,7 @@
         <v>33</v>
       </c>
       <c r="AB3" s="51" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
@@ -4553,13 +4553,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C4" s="56" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>27</v>
@@ -4568,7 +4568,7 @@
         <v>261961</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H4" s="56">
         <v>300</v>
@@ -4631,7 +4631,7 @@
         <v>33</v>
       </c>
       <c r="AB4" s="51" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
@@ -4639,13 +4639,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C5" s="56" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E5" s="56" t="s">
         <v>27</v>
@@ -4654,7 +4654,7 @@
         <v>261960</v>
       </c>
       <c r="G5" s="56" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H5" s="56">
         <v>200</v>
@@ -4717,7 +4717,7 @@
         <v>33</v>
       </c>
       <c r="AB5" s="51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
@@ -4725,13 +4725,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C6" s="56" t="s">
         <v>45</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E6" s="56" t="s">
         <v>27</v>
@@ -4740,7 +4740,7 @@
         <v>251958</v>
       </c>
       <c r="G6" s="56" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H6" s="56">
         <v>400</v>
@@ -4752,7 +4752,7 @@
         <v>1.383</v>
       </c>
       <c r="K6" s="56" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L6" s="53">
         <v>300.94099999999997</v>
@@ -4803,7 +4803,7 @@
         <v>33</v>
       </c>
       <c r="AB6" s="51" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
@@ -4817,7 +4817,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E7" s="56" t="s">
         <v>27</v>
@@ -4826,7 +4826,7 @@
         <v>261957</v>
       </c>
       <c r="G7" s="56" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H7" s="56">
         <v>1500</v>
@@ -4838,7 +4838,7 @@
         <v>1.2689999999999999</v>
       </c>
       <c r="K7" s="56" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L7" s="53">
         <v>940.32899999999995</v>
@@ -4889,7 +4889,7 @@
         <v>33</v>
       </c>
       <c r="AB7" s="51" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
@@ -4903,7 +4903,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E8" s="56" t="s">
         <v>27</v>
@@ -4912,7 +4912,7 @@
         <v>261958</v>
       </c>
       <c r="G8" s="56" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H8" s="56">
         <v>1500</v>
@@ -4924,7 +4924,7 @@
         <v>1.393</v>
       </c>
       <c r="K8" s="56" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L8" s="53">
         <v>940.27499999999998</v>
@@ -4975,7 +4975,7 @@
         <v>33</v>
       </c>
       <c r="AB8" s="51" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
@@ -5110,88 +5110,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="90" t="s">
-        <v>341</v>
-      </c>
-      <c r="B1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="90" t="s">
+      <c r="A1" s="84" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="84" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
         <v>261974</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H3" s="15">
         <v>320</v>
@@ -5313,7 +5313,7 @@
         <v>1.7030000000000001</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L3" s="17">
         <v>900.81899999999996</v>
@@ -5364,7 +5364,7 @@
         <v>33</v>
       </c>
       <c r="AB3" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5387,7 +5387,7 @@
         <v>261976</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H4" s="15">
         <v>600</v>
@@ -5399,7 +5399,7 @@
         <v>2.2029999999999998</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L4" s="17">
         <v>1608.6310000000001</v>
@@ -5450,7 +5450,7 @@
         <v>39</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5473,7 +5473,7 @@
         <v>261975</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H5" s="15">
         <v>150</v>
@@ -5485,7 +5485,7 @@
         <v>2.5830000000000002</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L5" s="17">
         <v>599.77300000000002</v>
@@ -5536,7 +5536,7 @@
         <v>39</v>
       </c>
       <c r="AB5" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5559,7 +5559,7 @@
         <v>261977</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H6" s="15">
         <v>500</v>
@@ -5571,7 +5571,7 @@
         <v>1.7829999999999999</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L6" s="17">
         <v>954.79600000000005</v>
@@ -5622,7 +5622,7 @@
         <v>30</v>
       </c>
       <c r="AB6" s="15" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5630,13 +5630,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>27</v>
@@ -5645,7 +5645,7 @@
         <v>261971</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H7" s="15">
         <v>150</v>
@@ -5708,7 +5708,7 @@
         <v>33</v>
       </c>
       <c r="AB7" s="15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5722,7 +5722,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>27</v>
@@ -5731,7 +5731,7 @@
         <v>261973</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H8" s="15">
         <v>2000</v>
@@ -5743,7 +5743,7 @@
         <v>1.6830000000000001</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L8" s="17">
         <v>2093.652</v>
@@ -5794,7 +5794,7 @@
         <v>54</v>
       </c>
       <c r="AB8" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5808,7 +5808,7 @@
         <v>36</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>27</v>
@@ -5817,7 +5817,7 @@
         <v>261972</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H9" s="15">
         <v>2000</v>
@@ -5829,7 +5829,7 @@
         <v>1.5429999999999999</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L9" s="17">
         <v>1762.106</v>
@@ -5880,7 +5880,7 @@
         <v>33</v>
       </c>
       <c r="AB9" s="15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5980,7 +5980,10 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A275621-EF96-4899-9847-36600E4070B0}">
-  <dimension ref="A1:AB14"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="13" customWidth="1"/>
@@ -6000,7 +6003,7 @@
     <col min="16" max="16" width="8.77734375" style="13" customWidth="1"/>
     <col min="17" max="17" width="3.21875" style="13" customWidth="1"/>
     <col min="18" max="18" width="6.44140625" style="13" customWidth="1"/>
-    <col min="19" max="19" width="6.77734375" style="13" customWidth="1"/>
+    <col min="19" max="19" width="7" style="13" customWidth="1"/>
     <col min="20" max="20" width="11.77734375" style="13" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="8.77734375" style="13" hidden="1" customWidth="1"/>
     <col min="22" max="23" width="8" style="13" customWidth="1"/>
@@ -6008,93 +6011,93 @@
     <col min="25" max="25" width="7.5546875" style="13" customWidth="1"/>
     <col min="26" max="26" width="7.6640625" style="13" customWidth="1"/>
     <col min="27" max="27" width="3.5546875" style="13" customWidth="1"/>
-    <col min="28" max="28" width="10.77734375" style="13" customWidth="1"/>
+    <col min="28" max="28" width="7.21875" style="13" customWidth="1"/>
     <col min="29" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="85" t="s">
-        <v>360</v>
-      </c>
-      <c r="B1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="85" t="s">
+      <c r="A1" s="82" t="s">
+        <v>361</v>
+      </c>
+      <c r="B1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="82" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6184,267 +6187,267 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" s="21">
+    <row r="3" spans="1:28" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="86">
         <v>1</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="21">
-        <v>261982</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="H3" s="21">
-        <v>600</v>
-      </c>
-      <c r="I3" s="24">
-        <v>1.0309999999999999</v>
-      </c>
-      <c r="J3" s="24">
-        <v>1.7609999999999999</v>
-      </c>
-      <c r="K3" s="21" t="s">
+      <c r="D3" s="86" t="s">
+        <v>471</v>
+      </c>
+      <c r="E3" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="86">
+        <v>262036</v>
+      </c>
+      <c r="G3" s="86" t="s">
+        <v>171</v>
+      </c>
+      <c r="H3" s="86">
+        <v>155</v>
+      </c>
+      <c r="I3" s="87">
+        <v>1.3440000000000001</v>
+      </c>
+      <c r="J3" s="87">
+        <v>2.1030000000000002</v>
+      </c>
+      <c r="K3" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="24">
-        <v>1089.355</v>
-      </c>
-      <c r="M3" s="25">
-        <v>1056.5999999999999</v>
-      </c>
-      <c r="N3" s="26">
-        <v>0.29349999999999998</v>
-      </c>
-      <c r="O3" s="27">
-        <v>17.61</v>
-      </c>
-      <c r="P3" s="21">
-        <v>660.1</v>
-      </c>
-      <c r="Q3" s="21">
+      <c r="L3" s="87">
+        <v>438.09699999999998</v>
+      </c>
+      <c r="M3" s="88">
+        <v>326</v>
+      </c>
+      <c r="N3" s="89">
+        <v>9.0499999999999997E-2</v>
+      </c>
+      <c r="O3" s="90">
+        <v>5.43</v>
+      </c>
+      <c r="P3" s="86">
+        <v>265.5</v>
+      </c>
+      <c r="Q3" s="86">
         <v>1</v>
       </c>
-      <c r="R3" s="21">
-        <v>1100</v>
-      </c>
-      <c r="S3" s="24">
-        <v>1.0309999999999999</v>
-      </c>
-      <c r="T3" s="21">
-        <v>69</v>
-      </c>
-      <c r="U3" s="26">
-        <v>6.2700000000000006E-2</v>
-      </c>
-      <c r="V3" s="21" t="s">
+      <c r="R3" s="86">
+        <v>1400</v>
+      </c>
+      <c r="S3" s="87">
+        <v>1.3440000000000001</v>
+      </c>
+      <c r="T3" s="86">
+        <v>56</v>
+      </c>
+      <c r="U3" s="89">
+        <v>0.04</v>
+      </c>
+      <c r="V3" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="W3" s="21" t="s">
+      <c r="W3" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="21" t="s">
+      <c r="X3" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="Y3" s="21" t="s">
+      <c r="Y3" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="Z3" s="21" t="s">
+      <c r="Z3" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="AA3" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB3" s="21" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="21">
+      <c r="AA3" s="86" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB3" s="86" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="86">
         <v>2</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="21">
-        <v>261984</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>356</v>
-      </c>
-      <c r="H4" s="21">
-        <v>310</v>
-      </c>
-      <c r="I4" s="24">
-        <v>1.272</v>
-      </c>
-      <c r="J4" s="24">
-        <v>1.335</v>
-      </c>
-      <c r="K4" s="21" t="s">
+      <c r="C4" s="86" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="86" t="s">
+        <v>471</v>
+      </c>
+      <c r="E4" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="86">
+        <v>262035</v>
+      </c>
+      <c r="G4" s="86" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4" s="86">
+        <v>155</v>
+      </c>
+      <c r="I4" s="87">
+        <v>1.31</v>
+      </c>
+      <c r="J4" s="87">
+        <v>1.893</v>
+      </c>
+      <c r="K4" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="24">
-        <v>526.41700000000003</v>
-      </c>
-      <c r="M4" s="25">
-        <v>413.8</v>
-      </c>
-      <c r="N4" s="26">
-        <v>0.115</v>
-      </c>
-      <c r="O4" s="27">
-        <v>6.9</v>
-      </c>
-      <c r="P4" s="21">
-        <v>181.6</v>
-      </c>
-      <c r="Q4" s="21">
+      <c r="L4" s="87">
+        <v>384.37400000000002</v>
+      </c>
+      <c r="M4" s="88">
+        <v>293.39999999999998</v>
+      </c>
+      <c r="N4" s="89">
+        <v>8.1500000000000003E-2</v>
+      </c>
+      <c r="O4" s="90">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="P4" s="86">
+        <v>232.9</v>
+      </c>
+      <c r="Q4" s="86">
         <v>1</v>
       </c>
-      <c r="R4" s="21">
-        <v>1300</v>
-      </c>
-      <c r="S4" s="24">
-        <v>1.272</v>
-      </c>
-      <c r="T4" s="21">
-        <v>28</v>
-      </c>
-      <c r="U4" s="26">
-        <v>2.1499999999999998E-2</v>
-      </c>
-      <c r="V4" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="X4" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="21" t="s">
+      <c r="R4" s="86">
+        <v>1350</v>
+      </c>
+      <c r="S4" s="87">
+        <v>1.31</v>
+      </c>
+      <c r="T4" s="86">
+        <v>40</v>
+      </c>
+      <c r="U4" s="89">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="V4" s="86" t="s">
+        <v>35</v>
+      </c>
+      <c r="W4" s="86" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" s="86" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y4" s="86" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z4" s="86" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA4" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="AB4" s="21" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AB4" s="86" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>163</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>27</v>
       </c>
       <c r="F5" s="21">
-        <v>261985</v>
+        <v>261982</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H5" s="21">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="I5" s="24">
-        <v>1.242</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="J5" s="24">
-        <v>2.105</v>
+        <v>1.7609999999999999</v>
       </c>
       <c r="K5" s="21" t="s">
         <v>34</v>
       </c>
       <c r="L5" s="24">
-        <v>653.60199999999998</v>
+        <v>1089.355</v>
       </c>
       <c r="M5" s="25">
-        <v>526.29999999999995</v>
+        <v>1056.5999999999999</v>
       </c>
       <c r="N5" s="26">
-        <v>0.1462</v>
+        <v>0.29349999999999998</v>
       </c>
       <c r="O5" s="27">
-        <v>8.77</v>
+        <v>17.61</v>
       </c>
       <c r="P5" s="21">
-        <v>225.5</v>
+        <v>660.1</v>
       </c>
       <c r="Q5" s="21">
         <v>1</v>
       </c>
       <c r="R5" s="21">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="S5" s="24">
-        <v>1.242</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="T5" s="21">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="U5" s="26">
-        <v>4.4600000000000001E-2</v>
+        <v>6.2700000000000006E-2</v>
       </c>
       <c r="V5" s="21" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="W5" s="21" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="X5" s="21" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Y5" s="21" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Z5" s="21" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="AA5" s="21" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="AB5" s="21" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>163</v>
@@ -6453,58 +6456,58 @@
         <v>36</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="21">
-        <v>261983</v>
+        <v>261984</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H6" s="21">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="I6" s="24">
-        <v>0.995</v>
+        <v>1.272</v>
       </c>
       <c r="J6" s="24">
-        <v>1.99</v>
+        <v>1.335</v>
       </c>
       <c r="K6" s="21" t="s">
         <v>34</v>
       </c>
       <c r="L6" s="24">
-        <v>554.41399999999999</v>
+        <v>526.41700000000003</v>
       </c>
       <c r="M6" s="25">
-        <v>557.20000000000005</v>
+        <v>413.8</v>
       </c>
       <c r="N6" s="26">
-        <v>0.15479999999999999</v>
+        <v>0.115</v>
       </c>
       <c r="O6" s="27">
-        <v>9.2899999999999991</v>
+        <v>6.9</v>
       </c>
       <c r="P6" s="21">
-        <v>191.3</v>
+        <v>181.6</v>
       </c>
       <c r="Q6" s="21">
         <v>1</v>
       </c>
       <c r="R6" s="21">
-        <v>1050</v>
+        <v>1300</v>
       </c>
       <c r="S6" s="24">
-        <v>0.995</v>
+        <v>1.272</v>
       </c>
       <c r="T6" s="21">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="U6" s="26">
-        <v>5.2400000000000002E-2</v>
+        <v>2.1499999999999998E-2</v>
       </c>
       <c r="V6" s="21" t="s">
         <v>28</v>
@@ -6525,12 +6528,12 @@
         <v>39</v>
       </c>
       <c r="AB6" s="21" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>163</v>
@@ -6539,58 +6542,58 @@
         <v>36</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="21">
-        <v>261981</v>
+        <v>261985</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="H7" s="21">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I7" s="24">
-        <v>0.92500000000000004</v>
+        <v>1.242</v>
       </c>
       <c r="J7" s="24">
-        <v>2.0470000000000002</v>
+        <v>2.105</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>354</v>
+        <v>34</v>
       </c>
       <c r="L7" s="24">
-        <v>378.69499999999999</v>
+        <v>653.60199999999998</v>
       </c>
       <c r="M7" s="25">
-        <v>409.4</v>
+        <v>526.29999999999995</v>
       </c>
       <c r="N7" s="26">
-        <v>0.1137</v>
+        <v>0.1462</v>
       </c>
       <c r="O7" s="27">
-        <v>6.82</v>
+        <v>8.77</v>
       </c>
       <c r="P7" s="21">
-        <v>130.6</v>
+        <v>225.5</v>
       </c>
       <c r="Q7" s="21">
         <v>1</v>
       </c>
       <c r="R7" s="21">
-        <v>950</v>
+        <v>1300</v>
       </c>
       <c r="S7" s="24">
-        <v>0.92500000000000004</v>
+        <v>1.242</v>
       </c>
       <c r="T7" s="21">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="U7" s="26">
-        <v>2.63E-2</v>
+        <v>4.4600000000000001E-2</v>
       </c>
       <c r="V7" s="21" t="s">
         <v>28</v>
@@ -6611,92 +6614,98 @@
         <v>39</v>
       </c>
       <c r="AB7" s="21" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>163</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="23">
-        <v>46233</v>
-      </c>
-      <c r="E8" s="21"/>
+        <v>36</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>27</v>
+      </c>
       <c r="F8" s="21">
-        <v>261999</v>
-      </c>
-      <c r="G8" s="83">
-        <v>1584</v>
+        <v>261983</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>357</v>
       </c>
       <c r="H8" s="21">
-        <v>1000</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>393</v>
+        <v>280</v>
+      </c>
+      <c r="I8" s="24">
+        <v>0.995</v>
       </c>
       <c r="J8" s="24">
-        <v>1.171</v>
+        <v>1.99</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>386</v>
+        <v>34</v>
       </c>
       <c r="L8" s="24">
-        <v>936800</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>387</v>
-      </c>
-      <c r="N8" s="26" t="s">
-        <v>388</v>
-      </c>
-      <c r="O8" s="27" t="s">
-        <v>389</v>
-      </c>
-      <c r="P8" s="21" t="s">
-        <v>390</v>
+        <v>554.41399999999999</v>
+      </c>
+      <c r="M8" s="25">
+        <v>557.20000000000005</v>
+      </c>
+      <c r="N8" s="26">
+        <v>0.15479999999999999</v>
+      </c>
+      <c r="O8" s="27">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="P8" s="21">
+        <v>191.3</v>
       </c>
       <c r="Q8" s="21">
         <v>1</v>
       </c>
       <c r="R8" s="21">
-        <v>850</v>
-      </c>
-      <c r="S8" s="24" t="s">
-        <v>385</v>
+        <v>1050</v>
+      </c>
+      <c r="S8" s="24">
+        <v>0.995</v>
       </c>
       <c r="T8" s="21">
-        <v>50</v>
-      </c>
-      <c r="U8" s="26" t="s">
-        <v>391</v>
+        <v>55</v>
+      </c>
+      <c r="U8" s="26">
+        <v>5.2400000000000002E-2</v>
       </c>
       <c r="V8" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W8" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="X8" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="Y8" s="21"/>
-      <c r="Z8" s="21"/>
-      <c r="AA8" s="21">
-        <v>2</v>
+      <c r="Y8" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="21" t="s">
+        <v>39</v>
       </c>
       <c r="AB8" s="21" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>163</v>
@@ -6705,58 +6714,58 @@
         <v>36</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="21">
-        <v>261980</v>
+        <v>261981</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H9" s="21">
         <v>200</v>
       </c>
       <c r="I9" s="24">
-        <v>0.81100000000000005</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="J9" s="24">
-        <v>1.603</v>
+        <v>2.0470000000000002</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="L9" s="24">
-        <v>260.00700000000001</v>
+        <v>378.69499999999999</v>
       </c>
       <c r="M9" s="25">
-        <v>320.60000000000002</v>
+        <v>409.4</v>
       </c>
       <c r="N9" s="26">
-        <v>8.9099999999999999E-2</v>
+        <v>0.1137</v>
       </c>
       <c r="O9" s="27">
-        <v>5.34</v>
+        <v>6.82</v>
       </c>
       <c r="P9" s="21">
-        <v>89.7</v>
+        <v>130.6</v>
       </c>
       <c r="Q9" s="21">
         <v>1</v>
       </c>
       <c r="R9" s="21">
-        <v>850</v>
+        <v>950</v>
       </c>
       <c r="S9" s="24">
-        <v>0.81100000000000005</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="T9" s="21">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="U9" s="26">
-        <v>4.5900000000000003E-2</v>
+        <v>2.63E-2</v>
       </c>
       <c r="V9" s="21" t="s">
         <v>28</v>
@@ -6777,436 +6786,602 @@
         <v>39</v>
       </c>
       <c r="AB9" s="21" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="21">
+        <v>6</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="23">
+        <v>46233</v>
+      </c>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21">
+        <v>261999</v>
+      </c>
+      <c r="G10" s="77">
+        <v>1584</v>
+      </c>
+      <c r="H10" s="21">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="J10" s="24">
+        <v>1.171</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="L10" s="24">
+        <v>936800</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>388</v>
+      </c>
+      <c r="N10" s="26" t="s">
+        <v>389</v>
+      </c>
+      <c r="O10" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="P10" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q10" s="21">
+        <v>1</v>
+      </c>
+      <c r="R10" s="21">
+        <v>850</v>
+      </c>
+      <c r="S10" s="24" t="s">
+        <v>386</v>
+      </c>
+      <c r="T10" s="21">
+        <v>50</v>
+      </c>
+      <c r="U10" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="V10" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="W10" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="X10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" s="21"/>
+      <c r="Z10" s="21"/>
+      <c r="AA10" s="21">
+        <v>2</v>
+      </c>
+      <c r="AB10" s="21" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="21">
+        <v>7</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="21">
+        <v>261980</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="H11" s="21">
+        <v>200</v>
+      </c>
+      <c r="I11" s="24">
+        <v>0.81100000000000005</v>
+      </c>
+      <c r="J11" s="24">
+        <v>1.603</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="L11" s="24">
+        <v>260.00700000000001</v>
+      </c>
+      <c r="M11" s="25">
+        <v>320.60000000000002</v>
+      </c>
+      <c r="N11" s="26">
+        <v>8.9099999999999999E-2</v>
+      </c>
+      <c r="O11" s="27">
+        <v>5.34</v>
+      </c>
+      <c r="P11" s="21">
+        <v>89.7</v>
+      </c>
+      <c r="Q11" s="21">
+        <v>1</v>
+      </c>
+      <c r="R11" s="21">
+        <v>850</v>
+      </c>
+      <c r="S11" s="24">
+        <v>0.81100000000000005</v>
+      </c>
+      <c r="T11" s="21">
+        <v>39</v>
+      </c>
+      <c r="U11" s="26">
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="V11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="W11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="X11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y11" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB11" s="21" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" s="91" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="86">
+        <v>8</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>347</v>
+      </c>
+      <c r="E12" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="86">
+        <v>261986</v>
+      </c>
+      <c r="G12" s="86" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" s="64" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
-        <v>8</v>
-      </c>
-      <c r="B10" s="76" t="s">
-        <v>312</v>
-      </c>
-      <c r="C10" s="75" t="s">
+      <c r="H12" s="86">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="87">
+        <v>0.66</v>
+      </c>
+      <c r="J12" s="87">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K12" s="86" t="s">
+        <v>345</v>
+      </c>
+      <c r="L12" s="87">
+        <v>1353</v>
+      </c>
+      <c r="M12" s="88">
+        <v>2050</v>
+      </c>
+      <c r="N12" s="89">
+        <v>0.56940000000000002</v>
+      </c>
+      <c r="O12" s="90">
+        <v>34.17</v>
+      </c>
+      <c r="P12" s="86">
+        <v>466.8</v>
+      </c>
+      <c r="Q12" s="86">
+        <v>1</v>
+      </c>
+      <c r="R12" s="86">
+        <v>700</v>
+      </c>
+      <c r="S12" s="87">
+        <v>0.66</v>
+      </c>
+      <c r="T12" s="86">
+        <v>40</v>
+      </c>
+      <c r="U12" s="89">
+        <v>5.7099999999999998E-2</v>
+      </c>
+      <c r="V12" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="W12" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="X12" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y12" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z12" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA12" s="86" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB12" s="86" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" s="91" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="86">
+        <v>9</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C13" s="86" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="75" t="s">
+      <c r="D13" s="86" t="s">
+        <v>347</v>
+      </c>
+      <c r="E13" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="86">
+        <v>261987</v>
+      </c>
+      <c r="G13" s="86" t="s">
+        <v>349</v>
+      </c>
+      <c r="H13" s="86">
+        <v>1000</v>
+      </c>
+      <c r="I13" s="87">
+        <v>0.66</v>
+      </c>
+      <c r="J13" s="87">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K13" s="86" t="s">
+        <v>345</v>
+      </c>
+      <c r="L13" s="87">
+        <v>1353</v>
+      </c>
+      <c r="M13" s="88">
+        <v>2050</v>
+      </c>
+      <c r="N13" s="89">
+        <v>0.56940000000000002</v>
+      </c>
+      <c r="O13" s="90">
+        <v>34.17</v>
+      </c>
+      <c r="P13" s="86">
+        <v>466.8</v>
+      </c>
+      <c r="Q13" s="86">
+        <v>1</v>
+      </c>
+      <c r="R13" s="86">
+        <v>700</v>
+      </c>
+      <c r="S13" s="87">
+        <v>0.66</v>
+      </c>
+      <c r="T13" s="86">
+        <v>40</v>
+      </c>
+      <c r="U13" s="89">
+        <v>5.7099999999999998E-2</v>
+      </c>
+      <c r="V13" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="W13" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="X13" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y13" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z13" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA13" s="86" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB13" s="86" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" s="91" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="86">
+        <v>10</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C14" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="86" t="s">
+        <v>347</v>
+      </c>
+      <c r="E14" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="86">
+        <v>261988</v>
+      </c>
+      <c r="G14" s="86" t="s">
         <v>346</v>
       </c>
-      <c r="E10" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="75">
-        <v>261986</v>
-      </c>
-      <c r="G10" s="75" t="s">
-        <v>349</v>
-      </c>
-      <c r="H10" s="75">
+      <c r="H14" s="86">
         <v>1000</v>
       </c>
-      <c r="I10" s="77">
+      <c r="I14" s="87">
         <v>0.66</v>
       </c>
-      <c r="J10" s="77">
+      <c r="J14" s="87">
         <v>2.0499999999999998</v>
       </c>
-      <c r="K10" s="75" t="s">
+      <c r="K14" s="86" t="s">
+        <v>345</v>
+      </c>
+      <c r="L14" s="87">
+        <v>1353</v>
+      </c>
+      <c r="M14" s="88">
+        <v>2050</v>
+      </c>
+      <c r="N14" s="89">
+        <v>0.56940000000000002</v>
+      </c>
+      <c r="O14" s="90">
+        <v>34.17</v>
+      </c>
+      <c r="P14" s="86">
+        <v>466.8</v>
+      </c>
+      <c r="Q14" s="86">
+        <v>1</v>
+      </c>
+      <c r="R14" s="86">
+        <v>700</v>
+      </c>
+      <c r="S14" s="87">
+        <v>0.66</v>
+      </c>
+      <c r="T14" s="86">
+        <v>40</v>
+      </c>
+      <c r="U14" s="89">
+        <v>5.7099999999999998E-2</v>
+      </c>
+      <c r="V14" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="W14" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="X14" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y14" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z14" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA14" s="86" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB14" s="86" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" s="91" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="86">
+        <v>11</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C15" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="86" t="s">
+        <v>347</v>
+      </c>
+      <c r="E15" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="86">
+        <v>261989</v>
+      </c>
+      <c r="G15" s="86" t="s">
+        <v>346</v>
+      </c>
+      <c r="H15" s="86">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="87">
+        <v>0.66</v>
+      </c>
+      <c r="J15" s="87">
+        <v>1.865</v>
+      </c>
+      <c r="K15" s="86" t="s">
+        <v>345</v>
+      </c>
+      <c r="L15" s="87">
+        <v>1230.9000000000001</v>
+      </c>
+      <c r="M15" s="88">
+        <v>1865</v>
+      </c>
+      <c r="N15" s="89">
+        <v>0.5181</v>
+      </c>
+      <c r="O15" s="90">
+        <v>31.08</v>
+      </c>
+      <c r="P15" s="86">
+        <v>424.7</v>
+      </c>
+      <c r="Q15" s="86">
+        <v>1</v>
+      </c>
+      <c r="R15" s="86">
+        <v>700</v>
+      </c>
+      <c r="S15" s="87">
+        <v>0.66</v>
+      </c>
+      <c r="T15" s="86">
+        <v>40</v>
+      </c>
+      <c r="U15" s="89">
+        <v>5.7099999999999998E-2</v>
+      </c>
+      <c r="V15" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="W15" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="X15" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y15" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z15" s="86" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA15" s="86" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB15" s="86" t="s">
         <v>344</v>
       </c>
-      <c r="L10" s="77">
-        <v>1353</v>
-      </c>
-      <c r="M10" s="78">
-        <v>2050</v>
-      </c>
-      <c r="N10" s="79">
-        <v>0.56940000000000002</v>
-      </c>
-      <c r="O10" s="80">
-        <v>34.17</v>
-      </c>
-      <c r="P10" s="75">
-        <v>466.8</v>
-      </c>
-      <c r="Q10" s="75">
-        <v>1</v>
-      </c>
-      <c r="R10" s="75">
-        <v>700</v>
-      </c>
-      <c r="S10" s="77">
-        <v>0.66</v>
-      </c>
-      <c r="T10" s="75">
-        <v>40</v>
-      </c>
-      <c r="U10" s="79">
-        <v>5.7099999999999998E-2</v>
-      </c>
-      <c r="V10" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="W10" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="X10" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y10" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z10" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA10" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB10" s="75" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" s="64" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21">
-        <v>9</v>
-      </c>
-      <c r="B11" s="76" t="s">
-        <v>312</v>
-      </c>
-      <c r="C11" s="75" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="75" t="s">
-        <v>346</v>
-      </c>
-      <c r="E11" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="75">
-        <v>261987</v>
-      </c>
-      <c r="G11" s="75" t="s">
-        <v>348</v>
-      </c>
-      <c r="H11" s="75">
-        <v>1000</v>
-      </c>
-      <c r="I11" s="77">
-        <v>0.66</v>
-      </c>
-      <c r="J11" s="77">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="K11" s="75" t="s">
-        <v>344</v>
-      </c>
-      <c r="L11" s="77">
-        <v>1353</v>
-      </c>
-      <c r="M11" s="78">
-        <v>2050</v>
-      </c>
-      <c r="N11" s="79">
-        <v>0.56940000000000002</v>
-      </c>
-      <c r="O11" s="80">
-        <v>34.17</v>
-      </c>
-      <c r="P11" s="75">
-        <v>466.8</v>
-      </c>
-      <c r="Q11" s="75">
-        <v>1</v>
-      </c>
-      <c r="R11" s="75">
-        <v>700</v>
-      </c>
-      <c r="S11" s="77">
-        <v>0.66</v>
-      </c>
-      <c r="T11" s="75">
-        <v>40</v>
-      </c>
-      <c r="U11" s="79">
-        <v>5.7099999999999998E-2</v>
-      </c>
-      <c r="V11" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="W11" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="X11" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y11" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z11" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA11" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB11" s="75" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" s="64" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21">
-        <v>10</v>
-      </c>
-      <c r="B12" s="76" t="s">
-        <v>312</v>
-      </c>
-      <c r="C12" s="75" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="75" t="s">
-        <v>346</v>
-      </c>
-      <c r="E12" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="75">
-        <v>261988</v>
-      </c>
-      <c r="G12" s="75" t="s">
-        <v>345</v>
-      </c>
-      <c r="H12" s="75">
-        <v>1000</v>
-      </c>
-      <c r="I12" s="77">
-        <v>0.66</v>
-      </c>
-      <c r="J12" s="77">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="K12" s="75" t="s">
-        <v>344</v>
-      </c>
-      <c r="L12" s="77">
-        <v>1353</v>
-      </c>
-      <c r="M12" s="78">
-        <v>2050</v>
-      </c>
-      <c r="N12" s="79">
-        <v>0.56940000000000002</v>
-      </c>
-      <c r="O12" s="80">
-        <v>34.17</v>
-      </c>
-      <c r="P12" s="75">
-        <v>466.8</v>
-      </c>
-      <c r="Q12" s="75">
-        <v>1</v>
-      </c>
-      <c r="R12" s="75">
-        <v>700</v>
-      </c>
-      <c r="S12" s="77">
-        <v>0.66</v>
-      </c>
-      <c r="T12" s="75">
-        <v>40</v>
-      </c>
-      <c r="U12" s="79">
-        <v>5.7099999999999998E-2</v>
-      </c>
-      <c r="V12" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="W12" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="X12" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y12" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z12" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA12" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB12" s="75" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" s="64" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21">
-        <v>11</v>
-      </c>
-      <c r="B13" s="76" t="s">
-        <v>312</v>
-      </c>
-      <c r="C13" s="75" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="75" t="s">
-        <v>346</v>
-      </c>
-      <c r="E13" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="75">
-        <v>261989</v>
-      </c>
-      <c r="G13" s="75" t="s">
-        <v>345</v>
-      </c>
-      <c r="H13" s="75">
-        <v>1000</v>
-      </c>
-      <c r="I13" s="77">
-        <v>0.66</v>
-      </c>
-      <c r="J13" s="77">
-        <v>1.865</v>
-      </c>
-      <c r="K13" s="75" t="s">
-        <v>344</v>
-      </c>
-      <c r="L13" s="77">
-        <v>1230.9000000000001</v>
-      </c>
-      <c r="M13" s="78">
-        <v>1865</v>
-      </c>
-      <c r="N13" s="79">
-        <v>0.5181</v>
-      </c>
-      <c r="O13" s="80">
-        <v>31.08</v>
-      </c>
-      <c r="P13" s="75">
-        <v>424.7</v>
-      </c>
-      <c r="Q13" s="75">
-        <v>1</v>
-      </c>
-      <c r="R13" s="75">
-        <v>700</v>
-      </c>
-      <c r="S13" s="77">
-        <v>0.66</v>
-      </c>
-      <c r="T13" s="75">
-        <v>40</v>
-      </c>
-      <c r="U13" s="79">
-        <v>5.7099999999999998E-2</v>
-      </c>
-      <c r="V13" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="W13" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="X13" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y13" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z13" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA13" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB13" s="75" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="29">
+    </row>
+    <row r="16" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="29">
         <v>5840</v>
       </c>
-      <c r="I14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="N14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" s="29">
+      <c r="I16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="P16" s="29">
         <v>3303.9</v>
       </c>
-      <c r="Q14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="R14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="S14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="T14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="U14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="V14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="W14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="X14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA14" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB14" s="29" t="s">
+      <c r="Q16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="R16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="S16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="T16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="U16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="V16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="W16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="X16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB16" s="29" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7214,7 +7389,8 @@
   <mergeCells count="1">
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins left="0.79" right="0.511811024" top="1.29" bottom="1.51" header="0.31496062000000002" footer="1.1100000000000001"/>
+  <pageSetup scale="68" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7257,88 +7433,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
-        <v>364</v>
-      </c>
-      <c r="B1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="91" t="s">
+      <c r="A1" s="85" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="85" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7428,178 +7604,178 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="81" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="81">
+    <row r="3" spans="1:28" s="75" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="75">
         <v>1</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="C3" s="81" t="s">
-        <v>195</v>
+        <v>205</v>
+      </c>
+      <c r="C3" s="75" t="s">
+        <v>196</v>
       </c>
       <c r="D3" s="59">
         <v>46234</v>
       </c>
-      <c r="F3" s="81">
+      <c r="F3" s="75">
         <v>262006</v>
       </c>
-      <c r="G3" s="81">
+      <c r="G3" s="75">
         <v>44</v>
       </c>
-      <c r="H3" s="81">
+      <c r="H3" s="75">
         <v>200</v>
       </c>
-      <c r="I3" s="81" t="s">
-        <v>408</v>
+      <c r="I3" s="75" t="s">
+        <v>409</v>
       </c>
       <c r="J3" s="60">
         <v>2500</v>
       </c>
-      <c r="K3" s="81" t="s">
-        <v>409</v>
+      <c r="K3" s="75" t="s">
+        <v>410</v>
       </c>
       <c r="L3" s="60">
         <v>393000</v>
       </c>
-      <c r="M3" s="81" t="s">
-        <v>410</v>
-      </c>
-      <c r="N3" s="81" t="s">
+      <c r="M3" s="75" t="s">
         <v>411</v>
       </c>
-      <c r="O3" s="81" t="s">
-        <v>269</v>
-      </c>
-      <c r="P3" s="81" t="s">
+      <c r="N3" s="75" t="s">
         <v>412</v>
       </c>
-      <c r="Q3" s="81">
+      <c r="O3" s="75" t="s">
+        <v>270</v>
+      </c>
+      <c r="P3" s="75" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q3" s="75">
         <v>2</v>
       </c>
-      <c r="R3" s="81">
+      <c r="R3" s="75">
         <v>1600</v>
       </c>
       <c r="S3" s="60">
         <v>1572</v>
       </c>
-      <c r="T3" s="81">
-        <v>28</v>
-      </c>
-      <c r="U3" s="81" t="s">
-        <v>413</v>
-      </c>
-      <c r="V3" s="81" t="s">
+      <c r="T3" s="75">
+        <v>28</v>
+      </c>
+      <c r="U3" s="75" t="s">
+        <v>414</v>
+      </c>
+      <c r="V3" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="W3" s="81" t="s">
+      <c r="W3" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="81" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="81" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z3" s="81" t="s">
+      <c r="X3" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="AA3" s="81">
+      <c r="AA3" s="75">
         <v>2</v>
       </c>
-      <c r="AB3" s="81" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" s="81" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="81">
+      <c r="AB3" s="75" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" s="75" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="75">
         <v>2</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="C4" s="81" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="75" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="59">
         <v>46234</v>
       </c>
-      <c r="F4" s="81">
+      <c r="F4" s="75">
         <v>262006</v>
       </c>
-      <c r="G4" s="81">
+      <c r="G4" s="75">
         <v>43</v>
       </c>
-      <c r="H4" s="81">
+      <c r="H4" s="75">
         <v>500</v>
       </c>
-      <c r="I4" s="81" t="s">
-        <v>400</v>
+      <c r="I4" s="75" t="s">
+        <v>401</v>
       </c>
       <c r="J4" s="60">
         <v>2062</v>
       </c>
-      <c r="K4" s="81" t="s">
-        <v>401</v>
+      <c r="K4" s="75" t="s">
+        <v>402</v>
       </c>
       <c r="L4" s="60">
         <v>725824</v>
       </c>
-      <c r="M4" s="81" t="s">
-        <v>402</v>
-      </c>
-      <c r="N4" s="81" t="s">
+      <c r="M4" s="75" t="s">
         <v>403</v>
       </c>
-      <c r="O4" s="81" t="s">
+      <c r="N4" s="75" t="s">
         <v>404</v>
       </c>
-      <c r="P4" s="81" t="s">
+      <c r="O4" s="75" t="s">
         <v>405</v>
       </c>
-      <c r="Q4" s="81">
+      <c r="P4" s="75" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q4" s="75">
         <v>2</v>
       </c>
-      <c r="R4" s="81">
+      <c r="R4" s="75">
         <v>1450</v>
       </c>
       <c r="S4" s="60">
         <v>1408</v>
       </c>
-      <c r="T4" s="81">
+      <c r="T4" s="75">
         <v>42</v>
       </c>
-      <c r="U4" s="81" t="s">
-        <v>406</v>
-      </c>
-      <c r="V4" s="81" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="81" t="s">
-        <v>28</v>
-      </c>
-      <c r="X4" s="81" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA4" s="81">
+      <c r="U4" s="75" t="s">
+        <v>407</v>
+      </c>
+      <c r="V4" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA4" s="75">
         <v>2</v>
       </c>
-      <c r="AB4" s="81" t="s">
-        <v>407</v>
+      <c r="AB4" s="75" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:28" s="28" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="81">
+      <c r="A5" s="75">
         <v>3</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>36</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>27</v>
@@ -7608,7 +7784,7 @@
         <v>261989</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H5" s="21">
         <v>2000</v>
@@ -7620,7 +7796,7 @@
         <v>1.3420000000000001</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L5" s="24">
         <v>1379.576</v>
@@ -7671,7 +7847,7 @@
         <v>30</v>
       </c>
       <c r="AB5" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
@@ -7804,88 +7980,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
-        <v>377</v>
-      </c>
-      <c r="B1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="87" t="s">
+      <c r="A1" s="81" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="81" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7980,7 +8156,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="68" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C3" s="68" t="s">
         <v>26</v>
@@ -8004,22 +8180,22 @@
         <v>1.228</v>
       </c>
       <c r="K3" s="68" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L3" s="60">
         <v>1009416</v>
       </c>
       <c r="M3" s="68" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N3" s="68" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O3" s="68" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P3" s="68" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q3" s="68">
         <v>2</v>
@@ -8034,7 +8210,7 @@
         <v>30</v>
       </c>
       <c r="U3" s="68" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="V3" s="68" t="s">
         <v>28</v>
@@ -8055,7 +8231,7 @@
         <v>7</v>
       </c>
       <c r="AB3" s="68" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
@@ -8063,13 +8239,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>27</v>
@@ -8078,7 +8254,7 @@
         <v>261996</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H4" s="15">
         <v>1000</v>
@@ -8090,7 +8266,7 @@
         <v>1.528</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L4" s="17">
         <v>985.56</v>
@@ -8141,7 +8317,7 @@
         <v>41</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
@@ -8149,13 +8325,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>27</v>
@@ -8164,7 +8340,7 @@
         <v>261995</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H5" s="15">
         <v>3000</v>
@@ -8176,7 +8352,7 @@
         <v>1.268</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L5" s="17">
         <v>2149.2600000000002</v>
@@ -8227,7 +8403,7 @@
         <v>65</v>
       </c>
       <c r="AB5" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
@@ -8235,13 +8411,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>27</v>
@@ -8250,7 +8426,7 @@
         <v>261994</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H6" s="15">
         <v>3300</v>
@@ -8262,7 +8438,7 @@
         <v>1.31</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L6" s="17">
         <v>1750.8150000000001</v>
@@ -8313,7 +8489,7 @@
         <v>33</v>
       </c>
       <c r="AB6" s="15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
@@ -8321,13 +8497,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>27</v>
@@ -8336,7 +8512,7 @@
         <v>261993</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H7" s="15">
         <v>350</v>
@@ -8348,7 +8524,7 @@
         <v>2.34</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L7" s="17">
         <v>1107.288</v>
@@ -8399,7 +8575,7 @@
         <v>33</v>
       </c>
       <c r="AB7" s="15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
@@ -8407,13 +8583,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C8" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>368</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>367</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>27</v>
@@ -8422,7 +8598,7 @@
         <v>261993</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H8" s="15">
         <v>900</v>
@@ -8434,7 +8610,7 @@
         <v>1.64</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L8" s="17">
         <v>1073.0519999999999</v>
@@ -8485,7 +8661,7 @@
         <v>30</v>
       </c>
       <c r="AB8" s="15" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
@@ -8493,13 +8669,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C9" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>368</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>367</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>27</v>
@@ -8508,7 +8684,7 @@
         <v>261990</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H9" s="15">
         <v>800</v>
@@ -8520,7 +8696,7 @@
         <v>1.6679999999999999</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L9" s="17">
         <v>956.76499999999999</v>
@@ -8571,7 +8747,7 @@
         <v>30</v>
       </c>
       <c r="AB9" s="15" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
@@ -8579,13 +8755,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C10" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>368</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>367</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>27</v>
@@ -8594,7 +8770,7 @@
         <v>261992</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H10" s="15">
         <v>1200</v>
@@ -8606,7 +8782,7 @@
         <v>1.19</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L10" s="17">
         <v>958.18799999999999</v>
@@ -8657,7 +8833,7 @@
         <v>32</v>
       </c>
       <c r="AB10" s="15" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
@@ -8665,13 +8841,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C11" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>368</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>367</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>27</v>
@@ -8680,7 +8856,7 @@
         <v>261991</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H11" s="15">
         <v>2500</v>
@@ -8743,7 +8919,7 @@
         <v>32</v>
       </c>
       <c r="AB11" s="15" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
@@ -8879,88 +9055,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
-        <v>399</v>
-      </c>
-      <c r="B1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="91" t="s">
+      <c r="A1" s="85" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="85" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="85" t="s">
         <v>27</v>
       </c>
     </row>
@@ -9055,13 +9231,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E3" s="56" t="s">
         <v>27</v>
@@ -9070,7 +9246,7 @@
         <v>262002</v>
       </c>
       <c r="G3" s="56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H3" s="56">
         <v>2283</v>
@@ -9133,7 +9309,7 @@
         <v>30</v>
       </c>
       <c r="AB3" s="51" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9141,13 +9317,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>27</v>
@@ -9156,7 +9332,7 @@
         <v>262001</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H4" s="56">
         <v>1662</v>
@@ -9219,7 +9395,7 @@
         <v>33</v>
       </c>
       <c r="AB4" s="51" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9227,13 +9403,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C5" s="56" t="s">
         <v>55</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E5" s="56" t="s">
         <v>27</v>
@@ -9242,7 +9418,7 @@
         <v>262005</v>
       </c>
       <c r="G5" s="56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H5" s="56">
         <v>3052</v>
@@ -9305,7 +9481,7 @@
         <v>39</v>
       </c>
       <c r="AB5" s="51" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9313,13 +9489,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C6" s="56" t="s">
         <v>55</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E6" s="56" t="s">
         <v>27</v>
@@ -9328,7 +9504,7 @@
         <v>262004</v>
       </c>
       <c r="G6" s="56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H6" s="56">
         <v>2764</v>
@@ -9391,7 +9567,7 @@
         <v>33</v>
       </c>
       <c r="AB6" s="51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9399,13 +9575,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E7" s="56" t="s">
         <v>27</v>
@@ -9414,7 +9590,7 @@
         <v>262003</v>
       </c>
       <c r="G7" s="56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H7" s="56">
         <v>1140</v>
@@ -9477,7 +9653,7 @@
         <v>33</v>
       </c>
       <c r="AB7" s="51" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9614,88 +9790,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
-        <v>436</v>
-      </c>
-      <c r="B1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="88" t="s">
+      <c r="A1" s="82" t="s">
+        <v>437</v>
+      </c>
+      <c r="B1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="82" t="s">
         <v>27</v>
       </c>
     </row>
@@ -9793,10 +9969,10 @@
         <v>140</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>27</v>
@@ -9805,7 +9981,7 @@
         <v>262012</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H3" s="21">
         <v>300</v>
@@ -9817,7 +9993,7 @@
         <v>1.855</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L3" s="24">
         <v>424.053</v>
@@ -9850,13 +10026,13 @@
         <v>1.6799999999999999E-2</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="W3" s="21" t="s">
         <v>42</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Y3" s="21" t="s">
         <v>27</v>
@@ -9868,7 +10044,7 @@
         <v>39</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9879,10 +10055,10 @@
         <v>140</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>27</v>
@@ -9891,7 +10067,7 @@
         <v>262014</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H4" s="21">
         <v>2000</v>
@@ -9903,7 +10079,7 @@
         <v>1.915</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L4" s="24">
         <v>2458.86</v>
@@ -9954,7 +10130,7 @@
         <v>54</v>
       </c>
       <c r="AB4" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9965,10 +10141,10 @@
         <v>140</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>27</v>
@@ -9977,7 +10153,7 @@
         <v>262013</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H5" s="21">
         <v>2000</v>
@@ -9989,7 +10165,7 @@
         <v>1.915</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L5" s="24">
         <v>2535.46</v>
@@ -10040,7 +10216,7 @@
         <v>54</v>
       </c>
       <c r="AB5" s="21" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10054,7 +10230,7 @@
         <v>139</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>27</v>
@@ -10063,7 +10239,7 @@
         <v>262008</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H6" s="21">
         <v>300</v>
@@ -10075,7 +10251,7 @@
         <v>1.7849999999999999</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L6" s="24">
         <v>534.42899999999997</v>
@@ -10126,7 +10302,7 @@
         <v>39</v>
       </c>
       <c r="AB6" s="21" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10140,7 +10316,7 @@
         <v>139</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>27</v>
@@ -10149,7 +10325,7 @@
         <v>262007</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H7" s="21">
         <v>1000</v>
@@ -10161,7 +10337,7 @@
         <v>0.94</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L7" s="24">
         <v>430.52</v>
@@ -10212,7 +10388,7 @@
         <v>39</v>
       </c>
       <c r="AB7" s="21" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10226,7 +10402,7 @@
         <v>139</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>27</v>
@@ -10235,7 +10411,7 @@
         <v>262009</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H8" s="21">
         <v>500</v>
@@ -10247,7 +10423,7 @@
         <v>0.875</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L8" s="24">
         <v>165.375</v>
@@ -10298,7 +10474,7 @@
         <v>39</v>
       </c>
       <c r="AB8" s="21" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10312,7 +10488,7 @@
         <v>139</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>27</v>
@@ -10321,7 +10497,7 @@
         <v>262011</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H9" s="21">
         <v>400</v>
@@ -10333,7 +10509,7 @@
         <v>1.105</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L9" s="24">
         <v>151.16399999999999</v>
@@ -10384,7 +10560,7 @@
         <v>39</v>
       </c>
       <c r="AB9" s="21" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10398,7 +10574,7 @@
         <v>139</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E10" s="21" t="s">
         <v>27</v>
@@ -10407,7 +10583,7 @@
         <v>262010</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H10" s="21">
         <v>1000</v>
@@ -10419,7 +10595,7 @@
         <v>0.83899999999999997</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L10" s="24">
         <v>271.83600000000001</v>
@@ -10470,7 +10646,7 @@
         <v>39</v>
       </c>
       <c r="AB10" s="21" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10603,88 +10779,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="32" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
-        <v>465</v>
-      </c>
-      <c r="B1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="87" t="s">
+      <c r="A1" s="81" t="s">
+        <v>466</v>
+      </c>
+      <c r="B1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="81" t="s">
         <v>27</v>
       </c>
     </row>
@@ -10779,13 +10955,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>27</v>
@@ -10794,7 +10970,7 @@
         <v>262017</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H3" s="15">
         <v>1250</v>
@@ -10857,7 +11033,7 @@
         <v>32</v>
       </c>
       <c r="AB3" s="15" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -10865,13 +11041,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>27</v>
@@ -10880,7 +11056,7 @@
         <v>262027</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H4" s="15">
         <v>200</v>
@@ -10892,7 +11068,7 @@
         <v>1.5389999999999999</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L4" s="17">
         <v>198.53100000000001</v>
@@ -10943,7 +11119,7 @@
         <v>33</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -10951,13 +11127,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>27</v>
@@ -10966,7 +11142,7 @@
         <v>262031</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H5" s="15">
         <v>400</v>
@@ -11037,13 +11213,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>27</v>
@@ -11052,7 +11228,7 @@
         <v>262030</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H6" s="15">
         <v>100</v>
@@ -11123,13 +11299,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>27</v>
@@ -11138,7 +11314,7 @@
         <v>262029</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H7" s="15">
         <v>700</v>
@@ -11150,7 +11326,7 @@
         <v>1.7190000000000001</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L7" s="17">
         <v>666.62800000000004</v>
@@ -11201,7 +11377,7 @@
         <v>33</v>
       </c>
       <c r="AB7" s="15" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -11209,13 +11385,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>27</v>
@@ -11224,7 +11400,7 @@
         <v>262015</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H8" s="15">
         <v>660</v>
@@ -11236,7 +11412,7 @@
         <v>1.7030000000000001</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L8" s="17">
         <v>629.42899999999997</v>
@@ -11287,7 +11463,7 @@
         <v>33</v>
       </c>
       <c r="AB8" s="15" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -11295,13 +11471,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>27</v>
@@ -11310,7 +11486,7 @@
         <v>262028</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H9" s="15">
         <v>150</v>
@@ -11322,7 +11498,7 @@
         <v>1.5589999999999999</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L9" s="17">
         <v>256.06599999999997</v>
@@ -11373,7 +11549,7 @@
         <v>39</v>
       </c>
       <c r="AB9" s="15" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="10" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -11381,13 +11557,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>27</v>
@@ -11396,7 +11572,7 @@
         <v>262018</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H10" s="15">
         <v>2500</v>
@@ -11408,7 +11584,7 @@
         <v>1.4990000000000001</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L10" s="17">
         <v>1626.415</v>
@@ -11459,7 +11635,7 @@
         <v>87</v>
       </c>
       <c r="AB10" s="15" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -11467,13 +11643,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>27</v>
@@ -11482,7 +11658,7 @@
         <v>262022</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H11" s="15">
         <v>250</v>
@@ -11545,7 +11721,7 @@
         <v>39</v>
       </c>
       <c r="AB11" s="15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -11553,13 +11729,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>27</v>
@@ -11568,7 +11744,7 @@
         <v>262021</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H12" s="15">
         <v>350</v>
@@ -11631,7 +11807,7 @@
         <v>39</v>
       </c>
       <c r="AB12" s="15" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -11639,13 +11815,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>27</v>
@@ -11654,7 +11830,7 @@
         <v>262026</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H13" s="15">
         <v>300</v>
@@ -11666,7 +11842,7 @@
         <v>1.649</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L13" s="17">
         <v>420</v>
@@ -11717,7 +11893,7 @@
         <v>39</v>
       </c>
       <c r="AB13" s="15" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -11725,13 +11901,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>27</v>
@@ -11740,7 +11916,7 @@
         <v>262019</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H14" s="15">
         <v>1100</v>
@@ -11752,7 +11928,7 @@
         <v>1.133</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L14" s="17">
         <v>501.01299999999998</v>
@@ -11803,7 +11979,7 @@
         <v>39</v>
       </c>
       <c r="AB14" s="15" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -11811,13 +11987,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>55</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>27</v>
@@ -11826,7 +12002,7 @@
         <v>262023</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H15" s="15">
         <v>2000</v>
@@ -11838,7 +12014,7 @@
         <v>1.649</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L15" s="17">
         <v>2618.6120000000001</v>
@@ -11889,7 +12065,7 @@
         <v>54</v>
       </c>
       <c r="AB15" s="15" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -11897,13 +12073,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>55</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>27</v>
@@ -11912,7 +12088,7 @@
         <v>262024</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H16" s="15">
         <v>1300</v>
@@ -11924,7 +12100,7 @@
         <v>1.7689999999999999</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L16" s="17">
         <v>1894.953</v>
@@ -11975,7 +12151,7 @@
         <v>32</v>
       </c>
       <c r="AB16" s="15" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -11983,13 +12159,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>55</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>27</v>
@@ -11998,7 +12174,7 @@
         <v>262020</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H17" s="15">
         <v>1200</v>
@@ -12061,7 +12237,7 @@
         <v>39</v>
       </c>
       <c r="AB17" s="15" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="18" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -12069,13 +12245,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>27</v>
@@ -12084,7 +12260,7 @@
         <v>262025</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H18" s="15">
         <v>1000</v>
@@ -12096,7 +12272,7 @@
         <v>0.79900000000000004</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L18" s="17">
         <v>287.64</v>
@@ -12147,7 +12323,7 @@
         <v>39</v>
       </c>
       <c r="AB18" s="15" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -12155,13 +12331,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>55</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>27</v>
@@ -12170,7 +12346,7 @@
         <v>262016</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H19" s="15">
         <v>1000</v>
@@ -12182,7 +12358,7 @@
         <v>0.84899999999999998</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L19" s="17">
         <v>249.60599999999999</v>
@@ -12233,7 +12409,7 @@
         <v>39</v>
       </c>
       <c r="AB19" s="15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="20" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
@@ -12366,88 +12542,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="84" t="s">
-        <v>469</v>
-      </c>
-      <c r="B1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="84" t="s">
+      <c r="A1" s="78" t="s">
+        <v>470</v>
+      </c>
+      <c r="B1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="78" t="s">
         <v>27</v>
       </c>
     </row>
@@ -12542,13 +12718,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>27</v>
@@ -12557,7 +12733,7 @@
         <v>262033</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H3" s="9">
         <v>1000</v>
@@ -12569,7 +12745,7 @@
         <v>1.04</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L3" s="6">
         <v>600.08000000000004</v>
@@ -12620,7 +12796,7 @@
         <v>33</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
@@ -12755,88 +12931,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="80" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="86" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="86" t="s">
+      <c r="B1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="80" t="s">
         <v>27</v>
       </c>
     </row>
@@ -13661,88 +13837,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="85" t="s">
+      <c r="B1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="79" t="s">
         <v>27</v>
       </c>
     </row>
@@ -15857,88 +16033,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="79" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="85" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="85" t="s">
+      <c r="B1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="79" t="s">
         <v>27</v>
       </c>
     </row>
@@ -16419,88 +16595,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="82" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="88" t="s">
+      <c r="B1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="82" t="s">
         <v>27</v>
       </c>
     </row>
@@ -17666,88 +17842,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="83" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="89" t="s">
+      <c r="B1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="83" t="s">
         <v>27</v>
       </c>
     </row>
@@ -17928,7 +18104,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C4" s="34" t="s">
         <v>45</v>
@@ -17953,22 +18129,22 @@
         <v>1.91</v>
       </c>
       <c r="K4" s="34" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L4" s="36">
         <v>618840</v>
       </c>
       <c r="M4" s="38" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N4" s="35" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P4" s="34" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q4" s="34">
         <v>1</v>
@@ -17977,13 +18153,13 @@
         <v>850</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="T4" s="34">
         <v>40</v>
       </c>
       <c r="U4" s="35" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="V4" s="34" t="s">
         <v>35</v>
@@ -18004,7 +18180,7 @@
         <v>3</v>
       </c>
       <c r="AB4" s="34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
@@ -18230,88 +18406,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="90" t="s">
-        <v>186</v>
-      </c>
-      <c r="B1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="90" t="s">
+      <c r="A1" s="84" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="84" t="s">
         <v>27</v>
       </c>
     </row>
@@ -18405,7 +18581,7 @@
       <c r="A3" s="15">
         <v>1</v>
       </c>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="76" t="s">
         <v>47</v>
       </c>
       <c r="C3" s="15" t="s">
@@ -18421,7 +18597,7 @@
         <v>261872</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H3" s="15">
         <v>8920</v>
@@ -18433,7 +18609,7 @@
         <v>1.8089999999999999</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L3" s="17">
         <v>10036.766</v>
@@ -18491,7 +18667,7 @@
       <c r="A4" s="15">
         <v>2</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="76" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -18507,7 +18683,7 @@
         <v>261871</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H4" s="15">
         <v>4460</v>
@@ -18577,7 +18753,7 @@
       <c r="A5" s="15">
         <v>3</v>
       </c>
-      <c r="B5" s="82" t="s">
+      <c r="B5" s="76" t="s">
         <v>47</v>
       </c>
       <c r="C5" s="15" t="s">
@@ -18593,7 +18769,7 @@
         <v>261877</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H5" s="15">
         <v>3400</v>
@@ -18656,14 +18832,14 @@
         <v>30</v>
       </c>
       <c r="AB5" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <v>4</v>
       </c>
-      <c r="B6" s="82" t="s">
+      <c r="B6" s="76" t="s">
         <v>47</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -18679,7 +18855,7 @@
         <v>261875</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H6" s="15">
         <v>3500</v>
@@ -18742,14 +18918,14 @@
         <v>30</v>
       </c>
       <c r="AB6" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
         <v>5</v>
       </c>
-      <c r="B7" s="82" t="s">
+      <c r="B7" s="76" t="s">
         <v>47</v>
       </c>
       <c r="C7" s="15" t="s">
@@ -18765,7 +18941,7 @@
         <v>261876</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H7" s="15">
         <v>3500</v>
@@ -18828,14 +19004,14 @@
         <v>30</v>
       </c>
       <c r="AB7" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <v>6</v>
       </c>
-      <c r="B8" s="82" t="s">
+      <c r="B8" s="76" t="s">
         <v>47</v>
       </c>
       <c r="C8" s="15" t="s">
@@ -18851,7 +19027,7 @@
         <v>261873</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H8" s="15">
         <v>2500</v>
@@ -18914,14 +19090,14 @@
         <v>30</v>
       </c>
       <c r="AB8" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15">
         <v>7</v>
       </c>
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="76" t="s">
         <v>47</v>
       </c>
       <c r="C9" s="15" t="s">
@@ -18937,7 +19113,7 @@
         <v>261874</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H9" s="15">
         <v>2500</v>
@@ -19000,7 +19176,7 @@
         <v>30</v>
       </c>
       <c r="AB9" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19138,88 +19314,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
-        <v>193</v>
-      </c>
-      <c r="B1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="87" t="s">
+      <c r="A1" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="81" t="s">
         <v>27</v>
       </c>
     </row>
@@ -19335,22 +19511,22 @@
         <v>1.621</v>
       </c>
       <c r="K3" s="65" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L3" s="65">
         <v>202139</v>
       </c>
       <c r="M3" s="65" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N3" s="65" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O3" s="65" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P3" s="65" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q3" s="65">
         <v>1</v>
@@ -19365,7 +19541,7 @@
         <v>53</v>
       </c>
       <c r="U3" s="65" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V3" s="65" t="s">
         <v>35</v>
@@ -19386,7 +19562,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="65" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:28" s="65" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19415,22 +19591,22 @@
         <v>1.246</v>
       </c>
       <c r="K4" s="65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L4" s="65">
         <v>147776</v>
       </c>
       <c r="M4" s="65" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N4" s="65" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O4" s="65" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P4" s="65" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q4" s="65">
         <v>1</v>
@@ -19445,7 +19621,7 @@
         <v>64</v>
       </c>
       <c r="U4" s="65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="V4" s="65" t="s">
         <v>35</v>
@@ -19466,7 +19642,7 @@
         <v>1</v>
       </c>
       <c r="AB4" s="65" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:28" s="65" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19495,22 +19671,22 @@
         <v>1.581</v>
       </c>
       <c r="K5" s="65" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L5" s="65">
         <v>163792</v>
       </c>
       <c r="M5" s="65" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N5" s="65" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O5" s="65" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P5" s="65" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q5" s="65">
         <v>1</v>
@@ -19525,7 +19701,7 @@
         <v>64</v>
       </c>
       <c r="U5" s="65" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="V5" s="65" t="s">
         <v>35</v>
@@ -19546,7 +19722,7 @@
         <v>1</v>
       </c>
       <c r="AB5" s="65" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:28" s="48" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19569,7 +19745,7 @@
         <v>261882</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H6" s="42">
         <v>200</v>
@@ -19655,7 +19831,7 @@
         <v>261880</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H7" s="42">
         <v>1000</v>
@@ -19741,7 +19917,7 @@
         <v>261883</v>
       </c>
       <c r="G8" s="42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H8" s="42">
         <v>600</v>
@@ -19827,7 +20003,7 @@
         <v>261878</v>
       </c>
       <c r="G9" s="42" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H9" s="42">
         <v>400</v>
@@ -19890,7 +20066,7 @@
         <v>39</v>
       </c>
       <c r="AB9" s="42" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:28" s="48" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -19913,7 +20089,7 @@
         <v>261884</v>
       </c>
       <c r="G10" s="42" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H10" s="42">
         <v>800</v>
@@ -19976,7 +20152,7 @@
         <v>33</v>
       </c>
       <c r="AB10" s="42" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:28" s="48" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20285,88 +20461,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
-        <v>213</v>
-      </c>
-      <c r="B1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="88" t="s">
+      <c r="A1" s="82" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="82" t="s">
         <v>27</v>
       </c>
     </row>
@@ -20461,10 +20637,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D3" s="59">
         <v>46226</v>
@@ -20474,34 +20650,34 @@
         <v>261921</v>
       </c>
       <c r="G3" s="40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H3" s="40">
         <v>440</v>
       </c>
       <c r="I3" s="40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J3" s="60">
         <v>2950</v>
       </c>
       <c r="K3" s="40" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L3" s="60">
         <v>902110</v>
       </c>
       <c r="M3" s="40" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N3" s="40" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O3" s="40" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P3" s="40" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q3" s="40">
         <v>2</v>
@@ -20516,7 +20692,7 @@
         <v>60</v>
       </c>
       <c r="U3" s="40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="V3" s="40" t="s">
         <v>29</v>
@@ -20537,7 +20713,7 @@
         <v>3</v>
       </c>
       <c r="AB3" s="40" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:28" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20545,10 +20721,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D4" s="59">
         <v>46226</v>
@@ -20558,13 +20734,13 @@
         <v>261912</v>
       </c>
       <c r="G4" s="61" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H4" s="40">
         <v>245</v>
       </c>
       <c r="I4" s="40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J4" s="60">
         <v>1620</v>
@@ -20576,16 +20752,16 @@
         <v>275845</v>
       </c>
       <c r="M4" s="40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N4" s="40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O4" s="40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q4" s="40">
         <v>2</v>
@@ -20600,7 +20776,7 @@
         <v>60</v>
       </c>
       <c r="U4" s="40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="V4" s="40" t="s">
         <v>29</v>
@@ -20621,7 +20797,7 @@
         <v>1</v>
       </c>
       <c r="AB4" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20629,13 +20805,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>48</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>27</v>
@@ -20644,7 +20820,7 @@
         <v>261909</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H5" s="21">
         <v>700</v>
@@ -20656,7 +20832,7 @@
         <v>1.99</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L5" s="24">
         <v>794.01</v>
@@ -20707,7 +20883,7 @@
         <v>33</v>
       </c>
       <c r="AB5" s="21" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20715,13 +20891,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>48</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>27</v>
@@ -20730,7 +20906,7 @@
         <v>261908</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H6" s="21">
         <v>1500</v>
@@ -20742,7 +20918,7 @@
         <v>1.59</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L6" s="24">
         <v>1216.3499999999999</v>
@@ -20793,7 +20969,7 @@
         <v>30</v>
       </c>
       <c r="AB6" s="21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20801,13 +20977,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>27</v>
@@ -20816,7 +20992,7 @@
         <v>261910</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H7" s="21">
         <v>600</v>
@@ -20828,7 +21004,7 @@
         <v>1.93</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L7" s="24">
         <v>1007.46</v>
@@ -20879,7 +21055,7 @@
         <v>33</v>
       </c>
       <c r="AB7" s="21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -20887,13 +21063,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>203</v>
-      </c>
       <c r="D8" s="21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>27</v>
@@ -20902,7 +21078,7 @@
         <v>261911</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H8" s="21">
         <v>400</v>
@@ -20914,7 +21090,7 @@
         <v>2.9820000000000002</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L8" s="24">
         <v>908.91399999999999</v>
@@ -20965,7 +21141,7 @@
         <v>39</v>
       </c>
       <c r="AB8" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FFD328-27AB-47DD-9CB1-2BA245E4CAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA9561A-E41C-4A17-8696-C158CF83EA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="14" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="14" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051" sheetId="60" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="Renovapel 1072 " sheetId="57" r:id="rId16"/>
     <sheet name="HARMONY EMBALAGENS 1073" sheetId="58" r:id="rId17"/>
     <sheet name="ABAPEL 1074" sheetId="63" r:id="rId18"/>
+    <sheet name="CARPEL 1078" sheetId="67" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023'!$A$1:$AB$10</definedName>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3476" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="491">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1418,6 +1419,117 @@
   </si>
   <si>
     <t>1040x2040</t>
+  </si>
+  <si>
+    <t>Z4A Embalagens</t>
+  </si>
+  <si>
+    <t>382.5</t>
+  </si>
+  <si>
+    <t>0.0531</t>
+  </si>
+  <si>
+    <t>3.19</t>
+  </si>
+  <si>
+    <t>203.8</t>
+  </si>
+  <si>
+    <t>0.0267</t>
+  </si>
+  <si>
+    <t>750x1550</t>
+  </si>
+  <si>
+    <t>1052x1280</t>
+  </si>
+  <si>
+    <t>97x150x97</t>
+  </si>
+  <si>
+    <t>0408</t>
+  </si>
+  <si>
+    <t>CARPEL</t>
+  </si>
+  <si>
+    <t>840x1780</t>
+  </si>
+  <si>
+    <t>808x1380</t>
+  </si>
+  <si>
+    <t>122x150x122</t>
+  </si>
+  <si>
+    <t>950x1220</t>
+  </si>
+  <si>
+    <t>1008x1580</t>
+  </si>
+  <si>
+    <t>172x150x172</t>
+  </si>
+  <si>
+    <t>1088x1780</t>
+  </si>
+  <si>
+    <t>1088x1410</t>
+  </si>
+  <si>
+    <t>1068x2160</t>
+  </si>
+  <si>
+    <t>187x150x187</t>
+  </si>
+  <si>
+    <t>574x2224</t>
+  </si>
+  <si>
+    <t>197x160x197</t>
+  </si>
+  <si>
+    <t>1200x2180</t>
+  </si>
+  <si>
+    <t>1160x2180</t>
+  </si>
+  <si>
+    <t>197x170x197</t>
+  </si>
+  <si>
+    <t>780x1850</t>
+  </si>
+  <si>
+    <t>840x1480</t>
+  </si>
+  <si>
+    <t>840x1820</t>
+  </si>
+  <si>
+    <t>1180x1820</t>
+  </si>
+  <si>
+    <t>1200x1862</t>
+  </si>
+  <si>
+    <t>67x480x67</t>
+  </si>
+  <si>
+    <t>920x1970</t>
+  </si>
+  <si>
+    <t>920x1520</t>
+  </si>
+  <si>
+    <t>1020x2147</t>
+  </si>
+  <si>
+    <t>157x395x157</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - CARPEL  —  OF: 001078</t>
   </si>
 </sst>
 </file>
@@ -1528,15 +1640,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1548,7 +1661,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1568,6 +1681,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0F1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1611,7 +1730,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1820,25 +1939,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1858,22 +1958,22 @@
     <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1892,6 +1992,42 @@
     <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7605,7 +7741,7 @@
         <v>182</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>334</v>
+        <v>36</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>333</v>
@@ -11479,432 +11615,432 @@
       </c>
     </row>
     <row r="3" spans="1:28" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="97">
+      <c r="A3" s="90">
         <v>1</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="97" t="s">
+      <c r="D3" s="90" t="s">
         <v>444</v>
       </c>
-      <c r="E3" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="97">
+      <c r="E3" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="90">
         <v>262040</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="90" t="s">
         <v>445</v>
       </c>
-      <c r="H3" s="97">
+      <c r="H3" s="90">
         <v>480</v>
       </c>
-      <c r="I3" s="98">
+      <c r="I3" s="91">
         <v>0.78500000000000003</v>
       </c>
-      <c r="J3" s="98">
+      <c r="J3" s="91">
         <v>1.8280000000000001</v>
       </c>
-      <c r="K3" s="97" t="s">
+      <c r="K3" s="90" t="s">
         <v>446</v>
       </c>
-      <c r="L3" s="98">
+      <c r="L3" s="91">
         <v>688.79</v>
       </c>
-      <c r="M3" s="99">
+      <c r="M3" s="92">
         <v>438.7</v>
       </c>
-      <c r="N3" s="100">
+      <c r="N3" s="93">
         <v>6.0900000000000003E-2</v>
       </c>
-      <c r="O3" s="101">
+      <c r="O3" s="94">
         <v>3.66</v>
       </c>
-      <c r="P3" s="97">
+      <c r="P3" s="90">
         <v>408.5</v>
       </c>
-      <c r="Q3" s="97">
+      <c r="Q3" s="90">
         <v>2</v>
       </c>
-      <c r="R3" s="97">
+      <c r="R3" s="90">
         <v>1600</v>
       </c>
-      <c r="S3" s="98">
+      <c r="S3" s="91">
         <v>1.57</v>
       </c>
-      <c r="T3" s="97">
+      <c r="T3" s="90">
         <v>30</v>
       </c>
-      <c r="U3" s="100">
+      <c r="U3" s="93">
         <v>1.8700000000000001E-2</v>
       </c>
-      <c r="V3" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="97" t="s">
+      <c r="V3" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="X3" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z3" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA3" s="97" t="s">
+      <c r="X3" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="AB3" s="97" t="s">
+      <c r="AB3" s="90" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="96" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="90">
+    <row r="4" spans="1:28" s="89" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="83">
         <v>1</v>
       </c>
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="90" t="s">
+      <c r="C4" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="90" t="s">
+      <c r="D4" s="83" t="s">
         <v>439</v>
       </c>
-      <c r="E4" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="90">
+      <c r="E4" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="83">
         <v>262039</v>
       </c>
-      <c r="G4" s="90" t="s">
+      <c r="G4" s="83" t="s">
         <v>440</v>
       </c>
-      <c r="H4" s="90">
+      <c r="H4" s="83">
         <v>140</v>
       </c>
-      <c r="I4" s="92">
+      <c r="I4" s="85">
+        <v>1.49</v>
+      </c>
+      <c r="J4" s="85">
+        <v>2.61</v>
+      </c>
+      <c r="K4" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="85">
+        <v>540.79200000000003</v>
+      </c>
+      <c r="M4" s="86">
+        <v>365.4</v>
+      </c>
+      <c r="N4" s="87">
+        <v>0.10150000000000001</v>
+      </c>
+      <c r="O4" s="88">
+        <v>6.09</v>
+      </c>
+      <c r="P4" s="83">
+        <v>320.7</v>
+      </c>
+      <c r="Q4" s="83">
+        <v>1</v>
+      </c>
+      <c r="R4" s="83">
+        <v>1500</v>
+      </c>
+      <c r="S4" s="85">
         <v>1.48</v>
       </c>
-      <c r="J4" s="92">
-        <v>2.61</v>
-      </c>
-      <c r="K4" s="90" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="92">
-        <v>540.79200000000003</v>
-      </c>
-      <c r="M4" s="93">
-        <v>365.4</v>
-      </c>
-      <c r="N4" s="94">
-        <v>0.10150000000000001</v>
-      </c>
-      <c r="O4" s="95">
-        <v>6.09</v>
-      </c>
-      <c r="P4" s="90">
-        <v>320.7</v>
-      </c>
-      <c r="Q4" s="90">
-        <v>1</v>
-      </c>
-      <c r="R4" s="90">
-        <v>1500</v>
-      </c>
-      <c r="S4" s="92">
-        <v>1.48</v>
-      </c>
-      <c r="T4" s="90">
+      <c r="T4" s="83">
         <v>20</v>
       </c>
-      <c r="U4" s="94">
+      <c r="U4" s="87">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="V4" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="90" t="s">
+      <c r="V4" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="X4" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z4" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA4" s="90" t="s">
+      <c r="X4" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z4" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA4" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="AB4" s="90" t="s">
+      <c r="AB4" s="83" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="83" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="84">
+    <row r="5" spans="1:28" s="76" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="77">
         <v>2</v>
       </c>
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="78" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="84" t="s">
+      <c r="C5" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="77" t="s">
         <v>439</v>
       </c>
-      <c r="E5" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="84">
+      <c r="E5" s="77" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="77">
         <v>262037</v>
       </c>
-      <c r="G5" s="84" t="s">
+      <c r="G5" s="77" t="s">
         <v>440</v>
       </c>
-      <c r="H5" s="84">
+      <c r="H5" s="77">
         <v>800</v>
       </c>
-      <c r="I5" s="86">
+      <c r="I5" s="79">
         <v>0.64200000000000002</v>
       </c>
-      <c r="J5" s="86">
+      <c r="J5" s="79">
         <v>2.2000000000000002</v>
       </c>
-      <c r="K5" s="84" t="s">
+      <c r="K5" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="86">
+      <c r="L5" s="79">
         <v>1129.92</v>
       </c>
-      <c r="M5" s="87">
+      <c r="M5" s="80">
         <v>880</v>
       </c>
-      <c r="N5" s="88">
+      <c r="N5" s="81">
         <v>0.1222</v>
       </c>
-      <c r="O5" s="89">
+      <c r="O5" s="82">
         <v>7.33</v>
       </c>
-      <c r="P5" s="84">
+      <c r="P5" s="77">
         <v>670</v>
       </c>
-      <c r="Q5" s="84">
+      <c r="Q5" s="77">
         <v>2</v>
       </c>
-      <c r="R5" s="84">
+      <c r="R5" s="77">
         <v>1350</v>
       </c>
-      <c r="S5" s="86">
+      <c r="S5" s="79">
         <v>1.284</v>
       </c>
-      <c r="T5" s="84">
+      <c r="T5" s="77">
         <v>66</v>
       </c>
-      <c r="U5" s="88">
+      <c r="U5" s="81">
         <v>4.8899999999999999E-2</v>
       </c>
-      <c r="V5" s="84" t="s">
-        <v>28</v>
-      </c>
-      <c r="W5" s="84" t="s">
+      <c r="V5" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="X5" s="84" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="84" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z5" s="84" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA5" s="84" t="s">
+      <c r="X5" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z5" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA5" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="AB5" s="84" t="s">
+      <c r="AB5" s="77" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="83" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="97">
+    <row r="6" spans="1:28" s="76" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="90">
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="97" t="s">
+      <c r="C6" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="97" t="s">
+      <c r="D6" s="90" t="s">
         <v>444</v>
       </c>
-      <c r="E6" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="97">
+      <c r="E6" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="90">
         <v>262042</v>
       </c>
-      <c r="G6" s="97" t="s">
+      <c r="G6" s="90" t="s">
         <v>445</v>
       </c>
-      <c r="H6" s="97">
+      <c r="H6" s="90">
         <v>700</v>
       </c>
-      <c r="I6" s="98">
+      <c r="I6" s="91">
         <v>0.63700000000000001</v>
       </c>
-      <c r="J6" s="98">
+      <c r="J6" s="91">
         <v>1.7450000000000001</v>
       </c>
-      <c r="K6" s="97" t="s">
+      <c r="K6" s="90" t="s">
         <v>448</v>
       </c>
-      <c r="L6" s="98">
+      <c r="L6" s="91">
         <v>778.096</v>
       </c>
-      <c r="M6" s="99">
+      <c r="M6" s="92">
         <v>610.79999999999995</v>
       </c>
-      <c r="N6" s="100">
+      <c r="N6" s="93">
         <v>8.48E-2</v>
       </c>
-      <c r="O6" s="101">
+      <c r="O6" s="94">
         <v>5.09</v>
       </c>
-      <c r="P6" s="97">
+      <c r="P6" s="90">
         <v>461.4</v>
       </c>
-      <c r="Q6" s="97">
+      <c r="Q6" s="90">
         <v>2</v>
       </c>
-      <c r="R6" s="97">
+      <c r="R6" s="90">
         <v>1300</v>
       </c>
-      <c r="S6" s="98">
+      <c r="S6" s="91">
         <v>1.274</v>
       </c>
-      <c r="T6" s="97">
+      <c r="T6" s="90">
         <v>26</v>
       </c>
-      <c r="U6" s="100">
+      <c r="U6" s="93">
         <v>0.02</v>
       </c>
-      <c r="V6" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="W6" s="97" t="s">
+      <c r="V6" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="X6" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y6" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z6" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA6" s="97" t="s">
+      <c r="X6" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z6" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA6" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="AB6" s="97" t="s">
+      <c r="AB6" s="90" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="83" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="84">
+    <row r="7" spans="1:28" s="76" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="77">
         <v>3</v>
       </c>
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="78" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="84" t="s">
+      <c r="C7" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="84" t="s">
+      <c r="D7" s="77" t="s">
         <v>439</v>
       </c>
-      <c r="E7" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="84">
+      <c r="E7" s="77" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="77">
         <v>262038</v>
       </c>
-      <c r="G7" s="84" t="s">
+      <c r="G7" s="77" t="s">
         <v>440</v>
       </c>
-      <c r="H7" s="84">
+      <c r="H7" s="77">
         <v>1100</v>
       </c>
-      <c r="I7" s="86">
+      <c r="I7" s="79">
         <v>0.59499999999999997</v>
       </c>
-      <c r="J7" s="86">
+      <c r="J7" s="79">
         <v>1.6579999999999999</v>
       </c>
-      <c r="K7" s="84" t="s">
+      <c r="K7" s="77" t="s">
         <v>442</v>
       </c>
-      <c r="L7" s="86">
+      <c r="L7" s="79">
         <v>1085.1610000000001</v>
       </c>
-      <c r="M7" s="87">
+      <c r="M7" s="80">
         <v>911.9</v>
       </c>
-      <c r="N7" s="88">
+      <c r="N7" s="81">
         <v>0.12670000000000001</v>
       </c>
-      <c r="O7" s="89">
+      <c r="O7" s="82">
         <v>7.6</v>
       </c>
-      <c r="P7" s="84">
+      <c r="P7" s="77">
         <v>643.5</v>
       </c>
-      <c r="Q7" s="84">
+      <c r="Q7" s="77">
         <v>2</v>
       </c>
-      <c r="R7" s="84">
+      <c r="R7" s="77">
         <v>1250</v>
       </c>
-      <c r="S7" s="86">
+      <c r="S7" s="79">
         <v>1.19</v>
       </c>
-      <c r="T7" s="84">
+      <c r="T7" s="77">
         <v>60</v>
       </c>
-      <c r="U7" s="88">
+      <c r="U7" s="81">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="V7" s="84" t="s">
-        <v>28</v>
-      </c>
-      <c r="W7" s="84" t="s">
+      <c r="V7" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="X7" s="84" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y7" s="84" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z7" s="84" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA7" s="84" t="s">
+      <c r="X7" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y7" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z7" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA7" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="AB7" s="84" t="s">
+      <c r="AB7" s="77" t="s">
         <v>443</v>
       </c>
     </row>
@@ -11995,174 +12131,174 @@
       </c>
     </row>
     <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="97">
+      <c r="A9" s="90">
         <v>3</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="97" t="s">
+      <c r="C9" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="97" t="s">
+      <c r="D9" s="90" t="s">
         <v>444</v>
       </c>
-      <c r="E9" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="97">
+      <c r="E9" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="90">
         <v>262043</v>
       </c>
-      <c r="G9" s="97" t="s">
+      <c r="G9" s="90" t="s">
         <v>445</v>
       </c>
-      <c r="H9" s="97">
+      <c r="H9" s="90">
         <v>1800</v>
       </c>
-      <c r="I9" s="98">
+      <c r="I9" s="91">
         <v>0.42699999999999999</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="91">
         <v>1.214</v>
       </c>
-      <c r="K9" s="97" t="s">
+      <c r="K9" s="90" t="s">
         <v>450</v>
       </c>
-      <c r="L9" s="98">
+      <c r="L9" s="91">
         <v>933.08</v>
       </c>
-      <c r="M9" s="99">
+      <c r="M9" s="92">
         <v>1092.5999999999999</v>
       </c>
-      <c r="N9" s="100">
+      <c r="N9" s="93">
         <v>0.1517</v>
       </c>
-      <c r="O9" s="101">
+      <c r="O9" s="94">
         <v>9.1</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="90">
         <v>321.89999999999998</v>
       </c>
-      <c r="Q9" s="97">
+      <c r="Q9" s="90">
         <v>2</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="90">
         <v>900</v>
       </c>
-      <c r="S9" s="98">
+      <c r="S9" s="91">
         <v>0.85399999999999998</v>
       </c>
-      <c r="T9" s="97">
+      <c r="T9" s="90">
         <v>46</v>
       </c>
-      <c r="U9" s="100">
+      <c r="U9" s="93">
         <v>5.11E-2</v>
       </c>
-      <c r="V9" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="W9" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="X9" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y9" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z9" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA9" s="97" t="s">
+      <c r="V9" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="W9" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="X9" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y9" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="AB9" s="97" t="s">
+      <c r="AB9" s="90" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="97">
+      <c r="A10" s="90">
         <v>4</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="C10" s="97" t="s">
+      <c r="C10" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="97" t="s">
+      <c r="D10" s="90" t="s">
         <v>444</v>
       </c>
-      <c r="E10" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="97">
+      <c r="E10" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="90">
         <v>262041</v>
       </c>
-      <c r="G10" s="97" t="s">
+      <c r="G10" s="90" t="s">
         <v>445</v>
       </c>
-      <c r="H10" s="97">
+      <c r="H10" s="90">
         <v>3000</v>
       </c>
-      <c r="I10" s="98">
+      <c r="I10" s="91">
         <v>0.34</v>
       </c>
-      <c r="J10" s="98">
+      <c r="J10" s="91">
         <v>1.01</v>
       </c>
-      <c r="K10" s="97" t="s">
+      <c r="K10" s="90" t="s">
         <v>452</v>
       </c>
-      <c r="L10" s="98">
+      <c r="L10" s="91">
         <v>1030.2</v>
       </c>
-      <c r="M10" s="99">
+      <c r="M10" s="92">
         <v>1515</v>
       </c>
-      <c r="N10" s="100">
+      <c r="N10" s="93">
         <v>0.2104</v>
       </c>
-      <c r="O10" s="101">
+      <c r="O10" s="94">
         <v>12.63</v>
       </c>
-      <c r="P10" s="97">
+      <c r="P10" s="90">
         <v>355.4</v>
       </c>
-      <c r="Q10" s="97">
+      <c r="Q10" s="90">
         <v>2</v>
       </c>
-      <c r="R10" s="97">
+      <c r="R10" s="90">
         <v>700</v>
       </c>
-      <c r="S10" s="98">
+      <c r="S10" s="91">
         <v>0.68</v>
       </c>
-      <c r="T10" s="97">
+      <c r="T10" s="90">
         <v>20</v>
       </c>
-      <c r="U10" s="100">
+      <c r="U10" s="93">
         <v>2.86E-2</v>
       </c>
-      <c r="V10" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="W10" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="X10" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y10" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z10" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA10" s="97" t="s">
+      <c r="V10" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="AB10" s="97" t="s">
+      <c r="AB10" s="90" t="s">
         <v>453</v>
       </c>
     </row>
@@ -12258,6 +12394,2026 @@
   </mergeCells>
   <pageMargins left="0.32" right="0.17" top="1.28" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup scale="88" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1FA60D2-9EE8-4466-8FFC-C8F46CF7934D}">
+  <dimension ref="A1:AB23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.21875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="8.33203125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="3.33203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="7.33203125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="7.44140625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.33203125" style="1" customWidth="1"/>
+    <col min="25" max="26" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="4.6640625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="12" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="75" t="s">
+        <v>490</v>
+      </c>
+      <c r="B1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="75" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="5">
+        <v>262061</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H3" s="5">
+        <v>500</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="J3" s="7">
+        <v>1.28</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="L3" s="7">
+        <v>453.76</v>
+      </c>
+      <c r="M3" s="9">
+        <v>320</v>
+      </c>
+      <c r="N3" s="6">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="O3" s="8">
+        <v>2.67</v>
+      </c>
+      <c r="P3" s="5">
+        <v>156.5</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>2</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1450</v>
+      </c>
+      <c r="S3" s="7">
+        <v>1.4179999999999999</v>
+      </c>
+      <c r="T3" s="5">
+        <v>32</v>
+      </c>
+      <c r="U3" s="6">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="5">
+        <v>262062</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H4" s="5">
+        <v>500</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="J4" s="7">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="L4" s="7">
+        <v>354.5</v>
+      </c>
+      <c r="M4" s="9">
+        <v>250</v>
+      </c>
+      <c r="N4" s="6">
+        <v>3.4700000000000002E-2</v>
+      </c>
+      <c r="O4" s="8">
+        <v>2.08</v>
+      </c>
+      <c r="P4" s="5">
+        <v>122.3</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>2</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1450</v>
+      </c>
+      <c r="S4" s="7">
+        <v>1.4179999999999999</v>
+      </c>
+      <c r="T4" s="5">
+        <v>32</v>
+      </c>
+      <c r="U4" s="6">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="5">
+        <v>262049</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2000</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0.45</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="7">
+        <v>675</v>
+      </c>
+      <c r="M5" s="9">
+        <v>500</v>
+      </c>
+      <c r="N5" s="6">
+        <v>4.6300000000000001E-2</v>
+      </c>
+      <c r="O5" s="8">
+        <v>2.78</v>
+      </c>
+      <c r="P5" s="5">
+        <v>232.9</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>3</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1400</v>
+      </c>
+      <c r="S5" s="7">
+        <v>1.35</v>
+      </c>
+      <c r="T5" s="5">
+        <v>50</v>
+      </c>
+      <c r="U5" s="6">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="5">
+        <v>262050</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2000</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0.45</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0.65</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="7">
+        <v>585</v>
+      </c>
+      <c r="M6" s="9">
+        <v>433.3</v>
+      </c>
+      <c r="N6" s="6">
+        <v>4.0099999999999997E-2</v>
+      </c>
+      <c r="O6" s="8">
+        <v>2.41</v>
+      </c>
+      <c r="P6" s="5">
+        <v>201.8</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>3</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1400</v>
+      </c>
+      <c r="S6" s="7">
+        <v>1.35</v>
+      </c>
+      <c r="T6" s="5">
+        <v>50</v>
+      </c>
+      <c r="U6" s="6">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB6" s="5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="5">
+        <v>262065</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H7" s="5">
+        <v>500</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0.59</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="L7" s="7">
+        <v>181.13</v>
+      </c>
+      <c r="M7" s="9">
+        <v>147.5</v>
+      </c>
+      <c r="N7" s="6">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="O7" s="8">
+        <v>1.23</v>
+      </c>
+      <c r="P7" s="5">
+        <v>62.5</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>2</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1250</v>
+      </c>
+      <c r="S7" s="7">
+        <v>1.228</v>
+      </c>
+      <c r="T7" s="5">
+        <v>22</v>
+      </c>
+      <c r="U7" s="6">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB7" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="5">
+        <v>262046</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="J8" s="7">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="7">
+        <v>696</v>
+      </c>
+      <c r="M8" s="9">
+        <v>580</v>
+      </c>
+      <c r="N8" s="6">
+        <v>8.0600000000000005E-2</v>
+      </c>
+      <c r="O8" s="8">
+        <v>4.83</v>
+      </c>
+      <c r="P8" s="5">
+        <v>240.1</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>2</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1250</v>
+      </c>
+      <c r="S8" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="T8" s="5">
+        <v>50</v>
+      </c>
+      <c r="U8" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB8" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>7</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="5">
+        <v>262048</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H9" s="5">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0.41</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="7">
+        <v>2460</v>
+      </c>
+      <c r="M9" s="9">
+        <v>2000</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0.1852</v>
+      </c>
+      <c r="O9" s="8">
+        <v>11.11</v>
+      </c>
+      <c r="P9" s="5">
+        <v>848.7</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>3</v>
+      </c>
+      <c r="R9" s="5">
+        <v>1250</v>
+      </c>
+      <c r="S9" s="7">
+        <v>1.23</v>
+      </c>
+      <c r="T9" s="5">
+        <v>20</v>
+      </c>
+      <c r="U9" s="6">
+        <v>1.6E-2</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB9" s="5" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="5">
+        <v>262063</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H10" s="5">
+        <v>500</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0.41</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="7">
+        <v>149.65</v>
+      </c>
+      <c r="M10" s="9">
+        <v>121.7</v>
+      </c>
+      <c r="N10" s="6">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="O10" s="8">
+        <v>0.68</v>
+      </c>
+      <c r="P10" s="5">
+        <v>51.6</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>3</v>
+      </c>
+      <c r="R10" s="5">
+        <v>1250</v>
+      </c>
+      <c r="S10" s="7">
+        <v>1.23</v>
+      </c>
+      <c r="T10" s="5">
+        <v>20</v>
+      </c>
+      <c r="U10" s="6">
+        <v>1.6E-2</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB10" s="5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="5">
+        <v>262064</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0.61</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="7">
+        <v>463.6</v>
+      </c>
+      <c r="M11" s="9">
+        <v>380</v>
+      </c>
+      <c r="N11" s="6">
+        <v>5.28E-2</v>
+      </c>
+      <c r="O11" s="8">
+        <v>3.17</v>
+      </c>
+      <c r="P11" s="5">
+        <v>159.9</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>2</v>
+      </c>
+      <c r="R11" s="5">
+        <v>1250</v>
+      </c>
+      <c r="S11" s="7">
+        <v>1.22</v>
+      </c>
+      <c r="T11" s="5">
+        <v>30</v>
+      </c>
+      <c r="U11" s="6">
+        <v>2.4E-2</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB11" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="5">
+        <v>262053</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H12" s="5">
+        <v>4000</v>
+      </c>
+      <c r="I12" s="7">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J12" s="7">
+        <v>2.16</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="L12" s="7">
+        <v>4924.8</v>
+      </c>
+      <c r="M12" s="9">
+        <v>4320</v>
+      </c>
+      <c r="N12" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="O12" s="8">
+        <v>36</v>
+      </c>
+      <c r="P12" s="5">
+        <v>1699.1</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>2</v>
+      </c>
+      <c r="R12" s="5">
+        <v>1200</v>
+      </c>
+      <c r="S12" s="7">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="T12" s="5">
+        <v>60</v>
+      </c>
+      <c r="U12" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB12" s="5" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="5">
+        <v>262052</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1500</v>
+      </c>
+      <c r="I13" s="7">
+        <v>0.59</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0.54</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="7">
+        <v>477.9</v>
+      </c>
+      <c r="M13" s="9">
+        <v>405</v>
+      </c>
+      <c r="N13" s="6">
+        <v>5.6300000000000003E-2</v>
+      </c>
+      <c r="O13" s="8">
+        <v>3.38</v>
+      </c>
+      <c r="P13" s="5">
+        <v>164.9</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>2</v>
+      </c>
+      <c r="R13" s="5">
+        <v>1200</v>
+      </c>
+      <c r="S13" s="7">
+        <v>1.18</v>
+      </c>
+      <c r="T13" s="5">
+        <v>20</v>
+      </c>
+      <c r="U13" s="6">
+        <v>1.67E-2</v>
+      </c>
+      <c r="V13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB13" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="5">
+        <v>262051</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H14" s="5">
+        <v>2000</v>
+      </c>
+      <c r="I14" s="7">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="J14" s="7">
+        <v>2.2040000000000002</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="L14" s="7">
+        <v>2442.0320000000002</v>
+      </c>
+      <c r="M14" s="9">
+        <v>2204</v>
+      </c>
+      <c r="N14" s="6">
+        <v>0.30609999999999998</v>
+      </c>
+      <c r="O14" s="8">
+        <v>18.37</v>
+      </c>
+      <c r="P14" s="5">
+        <v>842.5</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>2</v>
+      </c>
+      <c r="R14" s="5">
+        <v>1150</v>
+      </c>
+      <c r="S14" s="7">
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="T14" s="5">
+        <v>42</v>
+      </c>
+      <c r="U14" s="6">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="V14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB14" s="5" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <v>13</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="5">
+        <v>262059</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1500</v>
+      </c>
+      <c r="I15" s="7">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="J15" s="7">
+        <v>2.14</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="L15" s="7">
+        <v>1682.04</v>
+      </c>
+      <c r="M15" s="9">
+        <v>1605</v>
+      </c>
+      <c r="N15" s="6">
+        <v>0.22289999999999999</v>
+      </c>
+      <c r="O15" s="8">
+        <v>13.38</v>
+      </c>
+      <c r="P15" s="5">
+        <v>580.29999999999995</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>2</v>
+      </c>
+      <c r="R15" s="5">
+        <v>1100</v>
+      </c>
+      <c r="S15" s="7">
+        <v>1.048</v>
+      </c>
+      <c r="T15" s="5">
+        <v>52</v>
+      </c>
+      <c r="U15" s="6">
+        <v>4.7300000000000002E-2</v>
+      </c>
+      <c r="V15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB15" s="5" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <v>14</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="5">
+        <v>262056</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H16" s="5">
+        <v>500</v>
+      </c>
+      <c r="I16" s="7">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="J16" s="7">
+        <v>1.39</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="7">
+        <v>371.13</v>
+      </c>
+      <c r="M16" s="9">
+        <v>347.5</v>
+      </c>
+      <c r="N16" s="6">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="O16" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="P16" s="5">
+        <v>128</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>2</v>
+      </c>
+      <c r="R16" s="5">
+        <v>1100</v>
+      </c>
+      <c r="S16" s="7">
+        <v>1.0680000000000001</v>
+      </c>
+      <c r="T16" s="5">
+        <v>32</v>
+      </c>
+      <c r="U16" s="6">
+        <v>2.9100000000000001E-2</v>
+      </c>
+      <c r="V16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB16" s="5" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <v>15</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="5">
+        <v>262058</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H17" s="5">
+        <v>500</v>
+      </c>
+      <c r="I17" s="7">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="J17" s="7">
+        <v>1.76</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="7">
+        <v>469.92</v>
+      </c>
+      <c r="M17" s="9">
+        <v>440</v>
+      </c>
+      <c r="N17" s="6">
+        <v>6.1100000000000002E-2</v>
+      </c>
+      <c r="O17" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="P17" s="5">
+        <v>162.1</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>2</v>
+      </c>
+      <c r="R17" s="5">
+        <v>1100</v>
+      </c>
+      <c r="S17" s="7">
+        <v>1.0680000000000001</v>
+      </c>
+      <c r="T17" s="5">
+        <v>32</v>
+      </c>
+      <c r="U17" s="6">
+        <v>2.9100000000000001E-2</v>
+      </c>
+      <c r="V17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB17" s="5" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>16</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="5">
+        <v>262057</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H18" s="5">
+        <v>700</v>
+      </c>
+      <c r="I18" s="7">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="J18" s="7">
+        <v>1.56</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="L18" s="7">
+        <v>539.44799999999998</v>
+      </c>
+      <c r="M18" s="9">
+        <v>546</v>
+      </c>
+      <c r="N18" s="6">
+        <v>7.5800000000000006E-2</v>
+      </c>
+      <c r="O18" s="8">
+        <v>4.55</v>
+      </c>
+      <c r="P18" s="5">
+        <v>186.1</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>2</v>
+      </c>
+      <c r="R18" s="5">
+        <v>1050</v>
+      </c>
+      <c r="S18" s="7">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="T18" s="5">
+        <v>62</v>
+      </c>
+      <c r="U18" s="6">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="V18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB18" s="5" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <v>17</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="5">
+        <v>262060</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I19" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="J19" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="7">
+        <v>1116</v>
+      </c>
+      <c r="M19" s="9">
+        <v>1200</v>
+      </c>
+      <c r="N19" s="6">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="O19" s="8">
+        <v>20</v>
+      </c>
+      <c r="P19" s="5">
+        <v>385</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>1</v>
+      </c>
+      <c r="R19" s="5">
+        <v>950</v>
+      </c>
+      <c r="S19" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="T19" s="5">
+        <v>20</v>
+      </c>
+      <c r="U19" s="6">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="V19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB19" s="5" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <v>18</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="5">
+        <v>262055</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H20" s="5">
+        <v>2000</v>
+      </c>
+      <c r="I20" s="7">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="J20" s="7">
+        <v>1.36</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="L20" s="7">
+        <v>1071.68</v>
+      </c>
+      <c r="M20" s="9">
+        <v>1360</v>
+      </c>
+      <c r="N20" s="6">
+        <v>0.18890000000000001</v>
+      </c>
+      <c r="O20" s="8">
+        <v>11.33</v>
+      </c>
+      <c r="P20" s="5">
+        <v>369.7</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>2</v>
+      </c>
+      <c r="R20" s="5">
+        <v>850</v>
+      </c>
+      <c r="S20" s="7">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="T20" s="5">
+        <v>62</v>
+      </c>
+      <c r="U20" s="6">
+        <v>7.2900000000000006E-2</v>
+      </c>
+      <c r="V20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB20" s="5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>19</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="5">
+        <v>262047</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H21" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I21" s="7">
+        <v>0.82</v>
+      </c>
+      <c r="J21" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="7">
+        <v>721.6</v>
+      </c>
+      <c r="M21" s="9">
+        <v>880</v>
+      </c>
+      <c r="N21" s="6">
+        <v>0.24440000000000001</v>
+      </c>
+      <c r="O21" s="8">
+        <v>14.67</v>
+      </c>
+      <c r="P21" s="5">
+        <v>249</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>1</v>
+      </c>
+      <c r="R21" s="5">
+        <v>850</v>
+      </c>
+      <c r="S21" s="7">
+        <v>0.82</v>
+      </c>
+      <c r="T21" s="5">
+        <v>30</v>
+      </c>
+      <c r="U21" s="6">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="V21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB21" s="5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <v>20</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="5">
+        <v>262054</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H22" s="5">
+        <v>2000</v>
+      </c>
+      <c r="I22" s="7">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="J22" s="7">
+        <v>1.26</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="L22" s="7">
+        <v>866.88</v>
+      </c>
+      <c r="M22" s="9">
+        <v>1260</v>
+      </c>
+      <c r="N22" s="6">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="O22" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="P22" s="5">
+        <v>299.10000000000002</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>2</v>
+      </c>
+      <c r="R22" s="5">
+        <v>750</v>
+      </c>
+      <c r="S22" s="7">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="T22" s="5">
+        <v>62</v>
+      </c>
+      <c r="U22" s="6">
+        <v>8.2699999999999996E-2</v>
+      </c>
+      <c r="V22" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W22" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X22" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA22" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB22" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="19">
+        <v>34700</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P23" s="19">
+        <v>7142.2</v>
+      </c>
+      <c r="Q23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="X23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA23" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB23" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
@@ -17740,17 +19896,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" style="98" customWidth="1"/>
     <col min="2" max="2" width="9.44140625" style="1" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="98" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" style="98" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" style="98" customWidth="1"/>
     <col min="9" max="9" width="6.5546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="7.5546875" style="1" customWidth="1"/>
     <col min="11" max="11" width="13" style="1" customWidth="1"/>
@@ -17758,9 +19914,9 @@
     <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
     <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="8.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="4.33203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.77734375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="6.44140625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="4.33203125" style="98" customWidth="1"/>
+    <col min="18" max="18" width="5.77734375" style="98" customWidth="1"/>
+    <col min="19" max="19" width="6.44140625" style="98" customWidth="1"/>
     <col min="20" max="20" width="6.21875" style="1" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="7.33203125" style="1" customWidth="1"/>
@@ -17860,7 +20016,7 @@
       </c>
     </row>
     <row r="2" spans="1:28" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="95" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -17875,13 +20031,13 @@
       <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="95" t="s">
         <v>5</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -17908,13 +20064,13 @@
       <c r="P2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="95" t="s">
         <v>16</v>
       </c>
       <c r="T2" s="2" t="s">
@@ -17945,94 +20101,88 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+    <row r="3" spans="1:28" s="108" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="100">
         <v>1</v>
       </c>
-      <c r="B3" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="5">
-        <v>261872</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="H3" s="5">
-        <v>8920</v>
-      </c>
-      <c r="I3" s="7">
-        <v>0.622</v>
-      </c>
-      <c r="J3" s="7">
-        <v>1.8089999999999999</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="L3" s="7">
-        <v>10036.766</v>
-      </c>
-      <c r="M3" s="9">
-        <v>8068.1</v>
-      </c>
-      <c r="N3" s="6">
-        <v>1.1206</v>
-      </c>
-      <c r="O3" s="8">
-        <v>67.23</v>
-      </c>
-      <c r="P3" s="5">
-        <v>4290.7</v>
-      </c>
-      <c r="Q3" s="5">
+      <c r="B3" s="107" t="s">
+        <v>454</v>
+      </c>
+      <c r="C3" s="107" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="107">
+        <v>46238</v>
+      </c>
+      <c r="E3" s="107"/>
+      <c r="F3" s="100">
+        <v>262045</v>
+      </c>
+      <c r="G3" s="100">
+        <v>2054</v>
+      </c>
+      <c r="H3" s="100">
+        <v>1000</v>
+      </c>
+      <c r="I3" s="107">
+        <v>0.73</v>
+      </c>
+      <c r="J3" s="107">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="K3" s="107" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="107">
+        <v>558450</v>
+      </c>
+      <c r="M3" s="107" t="s">
+        <v>455</v>
+      </c>
+      <c r="N3" s="107" t="s">
+        <v>456</v>
+      </c>
+      <c r="O3" s="107" t="s">
+        <v>457</v>
+      </c>
+      <c r="P3" s="107" t="s">
+        <v>458</v>
+      </c>
+      <c r="Q3" s="100">
         <v>2</v>
       </c>
-      <c r="R3" s="5">
-        <v>1300</v>
-      </c>
-      <c r="S3" s="7">
-        <v>1.244</v>
-      </c>
-      <c r="T3" s="5">
-        <v>56</v>
-      </c>
-      <c r="U3" s="6">
-        <v>4.3099999999999999E-2</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB3" s="5" t="s">
-        <v>50</v>
+      <c r="R3" s="100">
+        <v>1500</v>
+      </c>
+      <c r="S3" s="100">
+        <v>1460</v>
+      </c>
+      <c r="T3" s="107">
+        <v>40</v>
+      </c>
+      <c r="U3" s="107" t="s">
+        <v>459</v>
+      </c>
+      <c r="V3" s="107" t="s">
+        <v>29</v>
+      </c>
+      <c r="W3" s="107" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="107" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y3" s="107"/>
+      <c r="Z3" s="107"/>
+      <c r="AA3" s="107">
+        <v>2</v>
+      </c>
+      <c r="AB3" s="107" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+      <c r="A4" s="47">
         <v>2</v>
       </c>
       <c r="B4" s="57" t="s">
@@ -18047,53 +20197,53 @@
       <c r="E4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="5">
-        <v>261871</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="H4" s="5">
-        <v>4460</v>
+      <c r="F4" s="96">
+        <v>261872</v>
+      </c>
+      <c r="G4" s="96" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="96">
+        <v>8920</v>
       </c>
       <c r="I4" s="7">
-        <v>0.32</v>
+        <v>0.622</v>
       </c>
       <c r="J4" s="7">
-        <v>0.86599999999999999</v>
+        <v>1.8089999999999999</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>34</v>
+        <v>177</v>
       </c>
       <c r="L4" s="7">
-        <v>1235.9549999999999</v>
+        <v>10036.766</v>
       </c>
       <c r="M4" s="9">
-        <v>1287.5</v>
+        <v>8068.1</v>
       </c>
       <c r="N4" s="6">
-        <v>0.1192</v>
+        <v>1.1206</v>
       </c>
       <c r="O4" s="8">
-        <v>7.15</v>
+        <v>67.23</v>
       </c>
       <c r="P4" s="5">
-        <v>528.4</v>
-      </c>
-      <c r="Q4" s="5">
-        <v>3</v>
-      </c>
-      <c r="R4" s="5">
-        <v>1000</v>
-      </c>
-      <c r="S4" s="7">
-        <v>0.96</v>
+        <v>4290.7</v>
+      </c>
+      <c r="Q4" s="96">
+        <v>2</v>
+      </c>
+      <c r="R4" s="96">
+        <v>1300</v>
+      </c>
+      <c r="S4" s="96">
+        <v>1.244</v>
       </c>
       <c r="T4" s="5">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U4" s="6">
-        <v>0.04</v>
+        <v>4.3099999999999999E-2</v>
       </c>
       <c r="V4" s="5" t="s">
         <v>42</v>
@@ -18111,525 +20261,611 @@
         <v>27</v>
       </c>
       <c r="AA4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="47">
+        <v>3</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="96">
+        <v>261871</v>
+      </c>
+      <c r="G5" s="96" t="s">
+        <v>176</v>
+      </c>
+      <c r="H5" s="96">
+        <v>4460</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="7">
+        <v>1235.9549999999999</v>
+      </c>
+      <c r="M5" s="9">
+        <v>1287.5</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0.1192</v>
+      </c>
+      <c r="O5" s="8">
+        <v>7.15</v>
+      </c>
+      <c r="P5" s="5">
+        <v>528.4</v>
+      </c>
+      <c r="Q5" s="96">
+        <v>3</v>
+      </c>
+      <c r="R5" s="96">
+        <v>1000</v>
+      </c>
+      <c r="S5" s="96">
+        <v>0.96</v>
+      </c>
+      <c r="T5" s="5">
+        <v>40</v>
+      </c>
+      <c r="U5" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AB5" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="76">
+    <row r="6" spans="1:28" s="106" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="100">
+        <v>4</v>
+      </c>
+      <c r="B6" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="99" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="99" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="101">
+        <v>261877</v>
+      </c>
+      <c r="G6" s="101" t="s">
+        <v>175</v>
+      </c>
+      <c r="H6" s="101">
+        <v>3400</v>
+      </c>
+      <c r="I6" s="102">
+        <v>0.4</v>
+      </c>
+      <c r="J6" s="102">
+        <v>0.9</v>
+      </c>
+      <c r="K6" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="102">
+        <v>1224</v>
+      </c>
+      <c r="M6" s="103">
+        <v>1020</v>
+      </c>
+      <c r="N6" s="104">
+        <v>9.4399999999999998E-2</v>
+      </c>
+      <c r="O6" s="105">
+        <v>5.67</v>
+      </c>
+      <c r="P6" s="99">
+        <v>446.8</v>
+      </c>
+      <c r="Q6" s="101">
         <v>3</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="R6" s="101">
+        <v>1250</v>
+      </c>
+      <c r="S6" s="101">
+        <v>1.2</v>
+      </c>
+      <c r="T6" s="99">
+        <v>50</v>
+      </c>
+      <c r="U6" s="104">
+        <v>0.04</v>
+      </c>
+      <c r="V6" s="99" t="s">
+        <v>29</v>
+      </c>
+      <c r="W6" s="99" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="99" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y6" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB6" s="99" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" s="106" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="100">
+        <v>5</v>
+      </c>
+      <c r="B7" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="76" t="s">
+      <c r="C7" s="99" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="99" t="s">
         <v>131</v>
       </c>
-      <c r="E5" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="76">
-        <v>261877</v>
-      </c>
-      <c r="G5" s="76" t="s">
-        <v>175</v>
-      </c>
-      <c r="H5" s="76">
-        <v>3400</v>
-      </c>
-      <c r="I5" s="78">
-        <v>0.4</v>
-      </c>
-      <c r="J5" s="78">
-        <v>0.9</v>
-      </c>
-      <c r="K5" s="76" t="s">
+      <c r="E7" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="101">
+        <v>261875</v>
+      </c>
+      <c r="G7" s="101" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" s="101">
+        <v>3500</v>
+      </c>
+      <c r="I7" s="102">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J7" s="102">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="K7" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="78">
-        <v>1224</v>
-      </c>
-      <c r="M5" s="79">
-        <v>1020</v>
-      </c>
-      <c r="N5" s="80">
-        <v>9.4399999999999998E-2</v>
-      </c>
-      <c r="O5" s="81">
-        <v>5.67</v>
-      </c>
-      <c r="P5" s="76">
-        <v>446.8</v>
-      </c>
-      <c r="Q5" s="76">
-        <v>3</v>
-      </c>
-      <c r="R5" s="76">
-        <v>1250</v>
-      </c>
-      <c r="S5" s="78">
-        <v>1.2</v>
-      </c>
-      <c r="T5" s="76">
+      <c r="L7" s="102">
+        <v>2410.9749999999999</v>
+      </c>
+      <c r="M7" s="103">
+        <v>2096.5</v>
+      </c>
+      <c r="N7" s="104">
+        <v>0.58240000000000003</v>
+      </c>
+      <c r="O7" s="105">
+        <v>34.94</v>
+      </c>
+      <c r="P7" s="99">
+        <v>940.3</v>
+      </c>
+      <c r="Q7" s="101">
+        <v>1</v>
+      </c>
+      <c r="R7" s="101">
+        <v>1200</v>
+      </c>
+      <c r="S7" s="101">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="T7" s="99">
         <v>50</v>
       </c>
-      <c r="U5" s="80">
+      <c r="U7" s="104">
+        <v>4.1700000000000001E-2</v>
+      </c>
+      <c r="V7" s="99" t="s">
+        <v>42</v>
+      </c>
+      <c r="W7" s="99" t="s">
+        <v>28</v>
+      </c>
+      <c r="X7" s="99" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y7" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB7" s="99" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" s="106" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="100">
+        <v>6</v>
+      </c>
+      <c r="B8" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="99" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="99" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="101">
+        <v>261876</v>
+      </c>
+      <c r="G8" s="101" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" s="101">
+        <v>3500</v>
+      </c>
+      <c r="I8" s="102">
+        <v>1.151</v>
+      </c>
+      <c r="J8" s="102">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="K8" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="102">
+        <v>2815.9209999999998</v>
+      </c>
+      <c r="M8" s="103">
+        <v>2446.5</v>
+      </c>
+      <c r="N8" s="104">
+        <v>0.67959999999999998</v>
+      </c>
+      <c r="O8" s="105">
+        <v>40.770000000000003</v>
+      </c>
+      <c r="P8" s="99">
+        <v>1098.2</v>
+      </c>
+      <c r="Q8" s="101">
+        <v>1</v>
+      </c>
+      <c r="R8" s="101">
+        <v>1200</v>
+      </c>
+      <c r="S8" s="101">
+        <v>1.151</v>
+      </c>
+      <c r="T8" s="99">
+        <v>49</v>
+      </c>
+      <c r="U8" s="104">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="V8" s="99" t="s">
+        <v>42</v>
+      </c>
+      <c r="W8" s="99" t="s">
+        <v>28</v>
+      </c>
+      <c r="X8" s="99" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y8" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB8" s="99" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" s="106" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="100">
+        <v>7</v>
+      </c>
+      <c r="B9" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="99" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="99" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="101">
+        <v>261873</v>
+      </c>
+      <c r="G9" s="101" t="s">
+        <v>169</v>
+      </c>
+      <c r="H9" s="101">
+        <v>2500</v>
+      </c>
+      <c r="I9" s="102">
+        <v>0.98</v>
+      </c>
+      <c r="J9" s="102">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="K9" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="102">
+        <v>1511.65</v>
+      </c>
+      <c r="M9" s="103">
+        <v>1542.5</v>
+      </c>
+      <c r="N9" s="104">
+        <v>0.42849999999999999</v>
+      </c>
+      <c r="O9" s="105">
+        <v>25.71</v>
+      </c>
+      <c r="P9" s="99">
+        <v>589.5</v>
+      </c>
+      <c r="Q9" s="101">
+        <v>1</v>
+      </c>
+      <c r="R9" s="101">
+        <v>1000</v>
+      </c>
+      <c r="S9" s="101">
+        <v>0.98</v>
+      </c>
+      <c r="T9" s="99">
+        <v>20</v>
+      </c>
+      <c r="U9" s="104">
+        <v>0.02</v>
+      </c>
+      <c r="V9" s="99" t="s">
+        <v>42</v>
+      </c>
+      <c r="W9" s="99" t="s">
+        <v>28</v>
+      </c>
+      <c r="X9" s="99" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y9" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB9" s="99" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" s="106" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="100">
+        <v>8</v>
+      </c>
+      <c r="B10" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="99" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="99" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="101">
+        <v>261874</v>
+      </c>
+      <c r="G10" s="101" t="s">
+        <v>167</v>
+      </c>
+      <c r="H10" s="101">
+        <v>2500</v>
+      </c>
+      <c r="I10" s="102">
+        <v>0.96</v>
+      </c>
+      <c r="J10" s="102">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="K10" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="102">
+        <v>1677.6</v>
+      </c>
+      <c r="M10" s="103">
+        <v>1747.5</v>
+      </c>
+      <c r="N10" s="104">
+        <v>0.4854</v>
+      </c>
+      <c r="O10" s="105">
+        <v>29.13</v>
+      </c>
+      <c r="P10" s="99">
+        <v>654.29999999999995</v>
+      </c>
+      <c r="Q10" s="101">
+        <v>1</v>
+      </c>
+      <c r="R10" s="101">
+        <v>1000</v>
+      </c>
+      <c r="S10" s="101">
+        <v>0.96</v>
+      </c>
+      <c r="T10" s="99">
+        <v>40</v>
+      </c>
+      <c r="U10" s="104">
         <v>0.04</v>
       </c>
-      <c r="V5" s="76" t="s">
-        <v>29</v>
-      </c>
-      <c r="W5" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="X5" s="76" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y5" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z5" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA5" s="76" t="s">
+      <c r="V10" s="99" t="s">
+        <v>42</v>
+      </c>
+      <c r="W10" s="99" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="99" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y10" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="AB5" s="76" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="76">
-        <v>4</v>
-      </c>
-      <c r="B6" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="76" t="s">
-        <v>132</v>
-      </c>
-      <c r="D6" s="76" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="76">
-        <v>261875</v>
-      </c>
-      <c r="G6" s="76" t="s">
-        <v>173</v>
-      </c>
-      <c r="H6" s="76">
-        <v>3500</v>
-      </c>
-      <c r="I6" s="78">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J6" s="78">
-        <v>0.59899999999999998</v>
-      </c>
-      <c r="K6" s="76" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="78">
-        <v>2410.9749999999999</v>
-      </c>
-      <c r="M6" s="79">
-        <v>2096.5</v>
-      </c>
-      <c r="N6" s="80">
-        <v>0.58240000000000003</v>
-      </c>
-      <c r="O6" s="81">
-        <v>34.94</v>
-      </c>
-      <c r="P6" s="76">
-        <v>940.3</v>
-      </c>
-      <c r="Q6" s="76">
-        <v>1</v>
-      </c>
-      <c r="R6" s="76">
-        <v>1200</v>
-      </c>
-      <c r="S6" s="78">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="T6" s="76">
-        <v>50</v>
-      </c>
-      <c r="U6" s="80">
-        <v>4.1700000000000001E-2</v>
-      </c>
-      <c r="V6" s="76" t="s">
-        <v>42</v>
-      </c>
-      <c r="W6" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="X6" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y6" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z6" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA6" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB6" s="76" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="76">
-        <v>5</v>
-      </c>
-      <c r="B7" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="76" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" s="76" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="76">
-        <v>261876</v>
-      </c>
-      <c r="G7" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" s="76">
-        <v>3500</v>
-      </c>
-      <c r="I7" s="78">
-        <v>1.151</v>
-      </c>
-      <c r="J7" s="78">
-        <v>0.69899999999999995</v>
-      </c>
-      <c r="K7" s="76" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="78">
-        <v>2815.9209999999998</v>
-      </c>
-      <c r="M7" s="79">
-        <v>2446.5</v>
-      </c>
-      <c r="N7" s="80">
-        <v>0.67959999999999998</v>
-      </c>
-      <c r="O7" s="81">
-        <v>40.770000000000003</v>
-      </c>
-      <c r="P7" s="76">
-        <v>1098.2</v>
-      </c>
-      <c r="Q7" s="76">
-        <v>1</v>
-      </c>
-      <c r="R7" s="76">
-        <v>1200</v>
-      </c>
-      <c r="S7" s="78">
-        <v>1.151</v>
-      </c>
-      <c r="T7" s="76">
-        <v>49</v>
-      </c>
-      <c r="U7" s="80">
-        <v>4.0800000000000003E-2</v>
-      </c>
-      <c r="V7" s="76" t="s">
-        <v>42</v>
-      </c>
-      <c r="W7" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="X7" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y7" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z7" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA7" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB7" s="76" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="76">
-        <v>6</v>
-      </c>
-      <c r="B8" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="76" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="76" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="76">
-        <v>261873</v>
-      </c>
-      <c r="G8" s="76" t="s">
-        <v>169</v>
-      </c>
-      <c r="H8" s="76">
-        <v>2500</v>
-      </c>
-      <c r="I8" s="78">
-        <v>0.98</v>
-      </c>
-      <c r="J8" s="78">
-        <v>0.61699999999999999</v>
-      </c>
-      <c r="K8" s="76" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="78">
-        <v>1511.65</v>
-      </c>
-      <c r="M8" s="79">
-        <v>1542.5</v>
-      </c>
-      <c r="N8" s="80">
-        <v>0.42849999999999999</v>
-      </c>
-      <c r="O8" s="81">
-        <v>25.71</v>
-      </c>
-      <c r="P8" s="76">
-        <v>589.5</v>
-      </c>
-      <c r="Q8" s="76">
-        <v>1</v>
-      </c>
-      <c r="R8" s="76">
-        <v>1000</v>
-      </c>
-      <c r="S8" s="78">
-        <v>0.98</v>
-      </c>
-      <c r="T8" s="76">
-        <v>20</v>
-      </c>
-      <c r="U8" s="80">
-        <v>0.02</v>
-      </c>
-      <c r="V8" s="76" t="s">
-        <v>42</v>
-      </c>
-      <c r="W8" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="X8" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y8" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z8" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA8" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB8" s="76" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="76">
-        <v>7</v>
-      </c>
-      <c r="B9" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="76" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="76" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="76">
-        <v>261874</v>
-      </c>
-      <c r="G9" s="76" t="s">
-        <v>167</v>
-      </c>
-      <c r="H9" s="76">
-        <v>2500</v>
-      </c>
-      <c r="I9" s="78">
-        <v>0.96</v>
-      </c>
-      <c r="J9" s="78">
-        <v>0.69899999999999995</v>
-      </c>
-      <c r="K9" s="76" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="78">
-        <v>1677.6</v>
-      </c>
-      <c r="M9" s="79">
-        <v>1747.5</v>
-      </c>
-      <c r="N9" s="80">
-        <v>0.4854</v>
-      </c>
-      <c r="O9" s="81">
-        <v>29.13</v>
-      </c>
-      <c r="P9" s="76">
-        <v>654.29999999999995</v>
-      </c>
-      <c r="Q9" s="76">
-        <v>1</v>
-      </c>
-      <c r="R9" s="76">
-        <v>1000</v>
-      </c>
-      <c r="S9" s="78">
-        <v>0.96</v>
-      </c>
-      <c r="T9" s="76">
-        <v>40</v>
-      </c>
-      <c r="U9" s="80">
-        <v>0.04</v>
-      </c>
-      <c r="V9" s="76" t="s">
-        <v>42</v>
-      </c>
-      <c r="W9" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="X9" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y9" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z9" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA9" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB9" s="76" t="s">
+      <c r="AB10" s="99" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="19">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="97">
         <v>28780</v>
       </c>
-      <c r="I10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="N10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="O10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="P10" s="19">
+      <c r="I11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="19">
         <v>8548.1</v>
       </c>
-      <c r="Q10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="S10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="T10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="U10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="V10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="W10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="X10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB10" s="19" t="s">
+      <c r="Q11" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="R11" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="S11" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="T11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="X11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB11" s="19" t="s">
         <v>27</v>
       </c>
     </row>
@@ -18638,7 +20874,7 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="97" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -20691,7 +22927,7 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" scale="92" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="78" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="G9" numberStoredAsText="1"/>
   </ignoredErrors>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA9561A-E41C-4A17-8696-C158CF83EA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251182B1-68B0-4AA0-A21E-556A7806C375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="14" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1922,23 +1922,6 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2028,6 +2011,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2281,88 +2281,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="102" t="s">
         <v>309</v>
       </c>
-      <c r="B1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="69" t="s">
+      <c r="B1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="102" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3185,88 +3185,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="102" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="69" t="s">
+      <c r="B1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="102" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4004,88 +4004,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="107" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="74" t="s">
+      <c r="B1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="107" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4910,88 +4910,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="104" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="71" t="s">
+      <c r="B1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="104" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6327,88 +6327,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="102" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="69" t="s">
+      <c r="B1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="102" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6877,88 +6877,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="107" t="s">
         <v>343</v>
       </c>
-      <c r="B1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="74" t="s">
+      <c r="B1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="107" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7952,88 +7952,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="102" t="s">
         <v>365</v>
       </c>
-      <c r="B1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="69" t="s">
+      <c r="B1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="102" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8687,88 +8687,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="104" t="s">
         <v>402</v>
       </c>
-      <c r="B1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="71" t="s">
+      <c r="B1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="104" t="s">
         <v>27</v>
       </c>
     </row>
@@ -9676,88 +9676,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="108" t="s">
         <v>431</v>
       </c>
-      <c r="B1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="75" t="s">
+      <c r="B1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="108" t="s">
         <v>27</v>
       </c>
     </row>
@@ -11443,88 +11443,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="107" t="s">
         <v>435</v>
       </c>
-      <c r="B1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="74" t="s">
+      <c r="B1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="107" t="s">
         <v>27</v>
       </c>
     </row>
@@ -11615,432 +11615,432 @@
       </c>
     </row>
     <row r="3" spans="1:28" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="90">
+      <c r="A3" s="83">
         <v>1</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="90" t="s">
+      <c r="C3" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="90" t="s">
+      <c r="D3" s="83" t="s">
         <v>444</v>
       </c>
-      <c r="E3" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="90">
+      <c r="E3" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="83">
         <v>262040</v>
       </c>
-      <c r="G3" s="90" t="s">
+      <c r="G3" s="83" t="s">
         <v>445</v>
       </c>
-      <c r="H3" s="90">
+      <c r="H3" s="83">
         <v>480</v>
       </c>
-      <c r="I3" s="91">
+      <c r="I3" s="84">
         <v>0.78500000000000003</v>
       </c>
-      <c r="J3" s="91">
+      <c r="J3" s="84">
         <v>1.8280000000000001</v>
       </c>
-      <c r="K3" s="90" t="s">
+      <c r="K3" s="83" t="s">
         <v>446</v>
       </c>
-      <c r="L3" s="91">
+      <c r="L3" s="84">
         <v>688.79</v>
       </c>
-      <c r="M3" s="92">
+      <c r="M3" s="85">
         <v>438.7</v>
       </c>
-      <c r="N3" s="93">
+      <c r="N3" s="86">
         <v>6.0900000000000003E-2</v>
       </c>
-      <c r="O3" s="94">
+      <c r="O3" s="87">
         <v>3.66</v>
       </c>
-      <c r="P3" s="90">
+      <c r="P3" s="83">
         <v>408.5</v>
       </c>
-      <c r="Q3" s="90">
+      <c r="Q3" s="83">
         <v>2</v>
       </c>
-      <c r="R3" s="90">
+      <c r="R3" s="83">
         <v>1600</v>
       </c>
-      <c r="S3" s="91">
+      <c r="S3" s="84">
         <v>1.57</v>
       </c>
-      <c r="T3" s="90">
+      <c r="T3" s="83">
         <v>30</v>
       </c>
-      <c r="U3" s="93">
+      <c r="U3" s="86">
         <v>1.8700000000000001E-2</v>
       </c>
-      <c r="V3" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="90" t="s">
+      <c r="V3" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="X3" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z3" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA3" s="90" t="s">
+      <c r="X3" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="AB3" s="90" t="s">
+      <c r="AB3" s="83" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="89" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="83">
+    <row r="4" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="76">
         <v>1</v>
       </c>
-      <c r="B4" s="84" t="s">
+      <c r="B4" s="77" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="83" t="s">
+      <c r="C4" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="83" t="s">
+      <c r="D4" s="76" t="s">
         <v>439</v>
       </c>
-      <c r="E4" s="83" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="83">
+      <c r="E4" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="76">
         <v>262039</v>
       </c>
-      <c r="G4" s="83" t="s">
+      <c r="G4" s="76" t="s">
         <v>440</v>
       </c>
-      <c r="H4" s="83">
+      <c r="H4" s="76">
         <v>140</v>
       </c>
-      <c r="I4" s="85">
+      <c r="I4" s="78">
         <v>1.49</v>
       </c>
-      <c r="J4" s="85">
+      <c r="J4" s="78">
         <v>2.61</v>
       </c>
-      <c r="K4" s="83" t="s">
+      <c r="K4" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="85">
+      <c r="L4" s="78">
         <v>540.79200000000003</v>
       </c>
-      <c r="M4" s="86">
+      <c r="M4" s="79">
         <v>365.4</v>
       </c>
-      <c r="N4" s="87">
+      <c r="N4" s="80">
         <v>0.10150000000000001</v>
       </c>
-      <c r="O4" s="88">
+      <c r="O4" s="81">
         <v>6.09</v>
       </c>
-      <c r="P4" s="83">
+      <c r="P4" s="76">
         <v>320.7</v>
       </c>
-      <c r="Q4" s="83">
+      <c r="Q4" s="76">
         <v>1</v>
       </c>
-      <c r="R4" s="83">
+      <c r="R4" s="76">
         <v>1500</v>
       </c>
-      <c r="S4" s="85">
+      <c r="S4" s="78">
         <v>1.48</v>
       </c>
-      <c r="T4" s="83">
+      <c r="T4" s="76">
         <v>20</v>
       </c>
-      <c r="U4" s="87">
+      <c r="U4" s="80">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="V4" s="83" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="83" t="s">
+      <c r="V4" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="X4" s="83" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="83" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z4" s="83" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA4" s="83" t="s">
+      <c r="X4" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z4" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA4" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="AB4" s="83" t="s">
+      <c r="AB4" s="76" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="76" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="77">
+    <row r="5" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="70">
         <v>2</v>
       </c>
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="71" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="77" t="s">
+      <c r="C5" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="70" t="s">
         <v>439</v>
       </c>
-      <c r="E5" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="77">
+      <c r="E5" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="70">
         <v>262037</v>
       </c>
-      <c r="G5" s="77" t="s">
+      <c r="G5" s="70" t="s">
         <v>440</v>
       </c>
-      <c r="H5" s="77">
+      <c r="H5" s="70">
         <v>800</v>
       </c>
-      <c r="I5" s="79">
+      <c r="I5" s="72">
         <v>0.64200000000000002</v>
       </c>
-      <c r="J5" s="79">
+      <c r="J5" s="72">
         <v>2.2000000000000002</v>
       </c>
-      <c r="K5" s="77" t="s">
+      <c r="K5" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="79">
+      <c r="L5" s="72">
         <v>1129.92</v>
       </c>
-      <c r="M5" s="80">
+      <c r="M5" s="73">
         <v>880</v>
       </c>
-      <c r="N5" s="81">
+      <c r="N5" s="74">
         <v>0.1222</v>
       </c>
-      <c r="O5" s="82">
+      <c r="O5" s="75">
         <v>7.33</v>
       </c>
-      <c r="P5" s="77">
+      <c r="P5" s="70">
         <v>670</v>
       </c>
-      <c r="Q5" s="77">
+      <c r="Q5" s="70">
         <v>2</v>
       </c>
-      <c r="R5" s="77">
+      <c r="R5" s="70">
         <v>1350</v>
       </c>
-      <c r="S5" s="79">
+      <c r="S5" s="72">
         <v>1.284</v>
       </c>
-      <c r="T5" s="77">
+      <c r="T5" s="70">
         <v>66</v>
       </c>
-      <c r="U5" s="81">
+      <c r="U5" s="74">
         <v>4.8899999999999999E-2</v>
       </c>
-      <c r="V5" s="77" t="s">
-        <v>28</v>
-      </c>
-      <c r="W5" s="77" t="s">
+      <c r="V5" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="X5" s="77" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="77" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z5" s="77" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA5" s="77" t="s">
+      <c r="X5" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z5" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA5" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="AB5" s="77" t="s">
+      <c r="AB5" s="70" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="76" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90">
+    <row r="6" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="83">
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="90" t="s">
+      <c r="C6" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="83" t="s">
         <v>444</v>
       </c>
-      <c r="E6" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="90">
+      <c r="E6" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="83">
         <v>262042</v>
       </c>
-      <c r="G6" s="90" t="s">
+      <c r="G6" s="83" t="s">
         <v>445</v>
       </c>
-      <c r="H6" s="90">
+      <c r="H6" s="83">
         <v>700</v>
       </c>
-      <c r="I6" s="91">
+      <c r="I6" s="84">
         <v>0.63700000000000001</v>
       </c>
-      <c r="J6" s="91">
+      <c r="J6" s="84">
         <v>1.7450000000000001</v>
       </c>
-      <c r="K6" s="90" t="s">
+      <c r="K6" s="83" t="s">
         <v>448</v>
       </c>
-      <c r="L6" s="91">
+      <c r="L6" s="84">
         <v>778.096</v>
       </c>
-      <c r="M6" s="92">
+      <c r="M6" s="85">
         <v>610.79999999999995</v>
       </c>
-      <c r="N6" s="93">
+      <c r="N6" s="86">
         <v>8.48E-2</v>
       </c>
-      <c r="O6" s="94">
+      <c r="O6" s="87">
         <v>5.09</v>
       </c>
-      <c r="P6" s="90">
+      <c r="P6" s="83">
         <v>461.4</v>
       </c>
-      <c r="Q6" s="90">
+      <c r="Q6" s="83">
         <v>2</v>
       </c>
-      <c r="R6" s="90">
+      <c r="R6" s="83">
         <v>1300</v>
       </c>
-      <c r="S6" s="91">
+      <c r="S6" s="84">
         <v>1.274</v>
       </c>
-      <c r="T6" s="90">
+      <c r="T6" s="83">
         <v>26</v>
       </c>
-      <c r="U6" s="93">
+      <c r="U6" s="86">
         <v>0.02</v>
       </c>
-      <c r="V6" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="W6" s="90" t="s">
+      <c r="V6" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="X6" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y6" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z6" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA6" s="90" t="s">
+      <c r="X6" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z6" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA6" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="AB6" s="90" t="s">
+      <c r="AB6" s="83" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="76" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="77">
+    <row r="7" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="70">
         <v>3</v>
       </c>
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="71" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="77" t="s">
+      <c r="C7" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="77" t="s">
+      <c r="D7" s="70" t="s">
         <v>439</v>
       </c>
-      <c r="E7" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="77">
+      <c r="E7" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="70">
         <v>262038</v>
       </c>
-      <c r="G7" s="77" t="s">
+      <c r="G7" s="70" t="s">
         <v>440</v>
       </c>
-      <c r="H7" s="77">
+      <c r="H7" s="70">
         <v>1100</v>
       </c>
-      <c r="I7" s="79">
+      <c r="I7" s="72">
         <v>0.59499999999999997</v>
       </c>
-      <c r="J7" s="79">
+      <c r="J7" s="72">
         <v>1.6579999999999999</v>
       </c>
-      <c r="K7" s="77" t="s">
+      <c r="K7" s="70" t="s">
         <v>442</v>
       </c>
-      <c r="L7" s="79">
+      <c r="L7" s="72">
         <v>1085.1610000000001</v>
       </c>
-      <c r="M7" s="80">
+      <c r="M7" s="73">
         <v>911.9</v>
       </c>
-      <c r="N7" s="81">
+      <c r="N7" s="74">
         <v>0.12670000000000001</v>
       </c>
-      <c r="O7" s="82">
+      <c r="O7" s="75">
         <v>7.6</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="70">
         <v>643.5</v>
       </c>
-      <c r="Q7" s="77">
+      <c r="Q7" s="70">
         <v>2</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="70">
         <v>1250</v>
       </c>
-      <c r="S7" s="79">
+      <c r="S7" s="72">
         <v>1.19</v>
       </c>
-      <c r="T7" s="77">
+      <c r="T7" s="70">
         <v>60</v>
       </c>
-      <c r="U7" s="81">
+      <c r="U7" s="74">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="V7" s="77" t="s">
-        <v>28</v>
-      </c>
-      <c r="W7" s="77" t="s">
+      <c r="V7" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="X7" s="77" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y7" s="77" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z7" s="77" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA7" s="77" t="s">
+      <c r="X7" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y7" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z7" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA7" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="AB7" s="77" t="s">
+      <c r="AB7" s="70" t="s">
         <v>443</v>
       </c>
     </row>
@@ -12131,174 +12131,174 @@
       </c>
     </row>
     <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="90">
+      <c r="A9" s="83">
         <v>3</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="90" t="s">
+      <c r="C9" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="90" t="s">
+      <c r="D9" s="83" t="s">
         <v>444</v>
       </c>
-      <c r="E9" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="90">
+      <c r="E9" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="83">
         <v>262043</v>
       </c>
-      <c r="G9" s="90" t="s">
+      <c r="G9" s="83" t="s">
         <v>445</v>
       </c>
-      <c r="H9" s="90">
+      <c r="H9" s="83">
         <v>1800</v>
       </c>
-      <c r="I9" s="91">
+      <c r="I9" s="84">
         <v>0.42699999999999999</v>
       </c>
-      <c r="J9" s="91">
+      <c r="J9" s="84">
         <v>1.214</v>
       </c>
-      <c r="K9" s="90" t="s">
+      <c r="K9" s="83" t="s">
         <v>450</v>
       </c>
-      <c r="L9" s="91">
+      <c r="L9" s="84">
         <v>933.08</v>
       </c>
-      <c r="M9" s="92">
+      <c r="M9" s="85">
         <v>1092.5999999999999</v>
       </c>
-      <c r="N9" s="93">
+      <c r="N9" s="86">
         <v>0.1517</v>
       </c>
-      <c r="O9" s="94">
+      <c r="O9" s="87">
         <v>9.1</v>
       </c>
-      <c r="P9" s="90">
+      <c r="P9" s="83">
         <v>321.89999999999998</v>
       </c>
-      <c r="Q9" s="90">
+      <c r="Q9" s="83">
         <v>2</v>
       </c>
-      <c r="R9" s="90">
+      <c r="R9" s="83">
         <v>900</v>
       </c>
-      <c r="S9" s="91">
+      <c r="S9" s="84">
         <v>0.85399999999999998</v>
       </c>
-      <c r="T9" s="90">
+      <c r="T9" s="83">
         <v>46</v>
       </c>
-      <c r="U9" s="93">
+      <c r="U9" s="86">
         <v>5.11E-2</v>
       </c>
-      <c r="V9" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="W9" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="X9" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y9" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z9" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA9" s="90" t="s">
+      <c r="V9" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="W9" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="X9" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y9" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="AB9" s="90" t="s">
+      <c r="AB9" s="83" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="90">
+      <c r="A10" s="83">
         <v>4</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="C10" s="90" t="s">
+      <c r="C10" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="90" t="s">
+      <c r="D10" s="83" t="s">
         <v>444</v>
       </c>
-      <c r="E10" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="90">
+      <c r="E10" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="83">
         <v>262041</v>
       </c>
-      <c r="G10" s="90" t="s">
+      <c r="G10" s="83" t="s">
         <v>445</v>
       </c>
-      <c r="H10" s="90">
+      <c r="H10" s="83">
         <v>3000</v>
       </c>
-      <c r="I10" s="91">
+      <c r="I10" s="84">
         <v>0.34</v>
       </c>
-      <c r="J10" s="91">
+      <c r="J10" s="84">
         <v>1.01</v>
       </c>
-      <c r="K10" s="90" t="s">
+      <c r="K10" s="83" t="s">
         <v>452</v>
       </c>
-      <c r="L10" s="91">
+      <c r="L10" s="84">
         <v>1030.2</v>
       </c>
-      <c r="M10" s="92">
+      <c r="M10" s="85">
         <v>1515</v>
       </c>
-      <c r="N10" s="93">
+      <c r="N10" s="86">
         <v>0.2104</v>
       </c>
-      <c r="O10" s="94">
+      <c r="O10" s="87">
         <v>12.63</v>
       </c>
-      <c r="P10" s="90">
+      <c r="P10" s="83">
         <v>355.4</v>
       </c>
-      <c r="Q10" s="90">
+      <c r="Q10" s="83">
         <v>2</v>
       </c>
-      <c r="R10" s="90">
+      <c r="R10" s="83">
         <v>700</v>
       </c>
-      <c r="S10" s="91">
+      <c r="S10" s="84">
         <v>0.68</v>
       </c>
-      <c r="T10" s="90">
+      <c r="T10" s="83">
         <v>20</v>
       </c>
-      <c r="U10" s="93">
+      <c r="U10" s="86">
         <v>2.86E-2</v>
       </c>
-      <c r="V10" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="W10" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="X10" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y10" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z10" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA10" s="90" t="s">
+      <c r="V10" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="AB10" s="90" t="s">
+      <c r="AB10" s="83" t="s">
         <v>453</v>
       </c>
     </row>
@@ -12432,88 +12432,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="108" t="s">
         <v>490</v>
       </c>
-      <c r="B1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="75" t="s">
+      <c r="B1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="108" t="s">
         <v>27</v>
       </c>
     </row>
@@ -14455,88 +14455,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="103" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="70" t="s">
+      <c r="B1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="103" t="s">
         <v>27</v>
       </c>
     </row>
@@ -15361,88 +15361,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="104" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="72" t="s">
+      <c r="B1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="105" t="s">
         <v>27</v>
       </c>
     </row>
@@ -17557,88 +17557,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="105" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="72" t="s">
+      <c r="B1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="105" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="105" t="s">
         <v>27</v>
       </c>
     </row>
@@ -18119,88 +18119,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="104" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="71" t="s">
+      <c r="B1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="104" t="s">
         <v>27</v>
       </c>
     </row>
@@ -19366,88 +19366,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="106" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="73" t="s">
+      <c r="B1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="106" t="s">
         <v>27</v>
       </c>
     </row>
@@ -19899,14 +19899,14 @@
   <dimension ref="A1:AB11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.21875" style="98" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" style="91" customWidth="1"/>
     <col min="2" max="2" width="9.44140625" style="1" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="98" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" style="98" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" style="98" customWidth="1"/>
+    <col min="6" max="6" width="13" style="91" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" style="91" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" style="91" customWidth="1"/>
     <col min="9" max="9" width="6.5546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="7.5546875" style="1" customWidth="1"/>
     <col min="11" max="11" width="13" style="1" customWidth="1"/>
@@ -19914,9 +19914,9 @@
     <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
     <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="8.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="4.33203125" style="98" customWidth="1"/>
-    <col min="18" max="18" width="5.77734375" style="98" customWidth="1"/>
-    <col min="19" max="19" width="6.44140625" style="98" customWidth="1"/>
+    <col min="17" max="17" width="4.33203125" style="91" customWidth="1"/>
+    <col min="18" max="18" width="5.77734375" style="91" customWidth="1"/>
+    <col min="19" max="19" width="6.44140625" style="91" customWidth="1"/>
     <col min="20" max="20" width="6.21875" style="1" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="7.33203125" style="1" customWidth="1"/>
@@ -19930,93 +19930,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="107" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="74" t="s">
+      <c r="B1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="107" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="88" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -20031,13 +20031,13 @@
       <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="95" t="s">
+      <c r="F2" s="88" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="95" t="s">
+      <c r="G2" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="95" t="s">
+      <c r="H2" s="88" t="s">
         <v>5</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -20064,13 +20064,13 @@
       <c r="P2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="95" t="s">
+      <c r="Q2" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="95" t="s">
+      <c r="S2" s="88" t="s">
         <v>16</v>
       </c>
       <c r="T2" s="2" t="s">
@@ -20101,83 +20101,83 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="108" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100">
+    <row r="3" spans="1:28" s="101" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="93">
         <v>1</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="100" t="s">
         <v>454</v>
       </c>
-      <c r="C3" s="107" t="s">
+      <c r="C3" s="100" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="107">
+      <c r="D3" s="100">
         <v>46238</v>
       </c>
-      <c r="E3" s="107"/>
-      <c r="F3" s="100">
+      <c r="E3" s="100"/>
+      <c r="F3" s="93">
         <v>262045</v>
       </c>
-      <c r="G3" s="100">
+      <c r="G3" s="93">
         <v>2054</v>
       </c>
-      <c r="H3" s="100">
+      <c r="H3" s="93">
         <v>1000</v>
       </c>
-      <c r="I3" s="107">
+      <c r="I3" s="100">
         <v>0.73</v>
       </c>
-      <c r="J3" s="107">
+      <c r="J3" s="100">
         <v>0.76500000000000001</v>
       </c>
-      <c r="K3" s="107" t="s">
+      <c r="K3" s="100" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="107">
+      <c r="L3" s="100">
         <v>558450</v>
       </c>
-      <c r="M3" s="107" t="s">
+      <c r="M3" s="100" t="s">
         <v>455</v>
       </c>
-      <c r="N3" s="107" t="s">
+      <c r="N3" s="100" t="s">
         <v>456</v>
       </c>
-      <c r="O3" s="107" t="s">
+      <c r="O3" s="100" t="s">
         <v>457</v>
       </c>
-      <c r="P3" s="107" t="s">
+      <c r="P3" s="100" t="s">
         <v>458</v>
       </c>
-      <c r="Q3" s="100">
+      <c r="Q3" s="93">
         <v>2</v>
       </c>
-      <c r="R3" s="100">
+      <c r="R3" s="93">
         <v>1500</v>
       </c>
-      <c r="S3" s="100">
+      <c r="S3" s="93">
         <v>1460</v>
       </c>
-      <c r="T3" s="107">
+      <c r="T3" s="100">
         <v>40</v>
       </c>
-      <c r="U3" s="107" t="s">
+      <c r="U3" s="100" t="s">
         <v>459</v>
       </c>
-      <c r="V3" s="107" t="s">
+      <c r="V3" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="W3" s="107" t="s">
-        <v>28</v>
-      </c>
-      <c r="X3" s="107" t="s">
+      <c r="W3" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="Y3" s="107"/>
-      <c r="Z3" s="107"/>
-      <c r="AA3" s="107">
+      <c r="Y3" s="100"/>
+      <c r="Z3" s="100"/>
+      <c r="AA3" s="100">
         <v>2</v>
       </c>
-      <c r="AB3" s="107" t="s">
+      <c r="AB3" s="100" t="s">
         <v>460</v>
       </c>
     </row>
@@ -20197,13 +20197,13 @@
       <c r="E4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="96">
+      <c r="F4" s="89">
         <v>261872</v>
       </c>
-      <c r="G4" s="96" t="s">
+      <c r="G4" s="89" t="s">
         <v>178</v>
       </c>
-      <c r="H4" s="96">
+      <c r="H4" s="89">
         <v>8920</v>
       </c>
       <c r="I4" s="7">
@@ -20230,13 +20230,13 @@
       <c r="P4" s="5">
         <v>4290.7</v>
       </c>
-      <c r="Q4" s="96">
+      <c r="Q4" s="89">
         <v>2</v>
       </c>
-      <c r="R4" s="96">
+      <c r="R4" s="89">
         <v>1300</v>
       </c>
-      <c r="S4" s="96">
+      <c r="S4" s="89">
         <v>1.244</v>
       </c>
       <c r="T4" s="5">
@@ -20283,13 +20283,13 @@
       <c r="E5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="96">
+      <c r="F5" s="89">
         <v>261871</v>
       </c>
-      <c r="G5" s="96" t="s">
+      <c r="G5" s="89" t="s">
         <v>176</v>
       </c>
-      <c r="H5" s="96">
+      <c r="H5" s="89">
         <v>4460</v>
       </c>
       <c r="I5" s="7">
@@ -20316,13 +20316,13 @@
       <c r="P5" s="5">
         <v>528.4</v>
       </c>
-      <c r="Q5" s="96">
+      <c r="Q5" s="89">
         <v>3</v>
       </c>
-      <c r="R5" s="96">
+      <c r="R5" s="89">
         <v>1000</v>
       </c>
-      <c r="S5" s="96">
+      <c r="S5" s="89">
         <v>0.96</v>
       </c>
       <c r="T5" s="5">
@@ -20353,438 +20353,438 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="106" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="100">
+    <row r="6" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="93">
         <v>4</v>
       </c>
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="99" t="s">
+      <c r="C6" s="92" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="99" t="s">
+      <c r="D6" s="92" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="101">
+      <c r="E6" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="94">
         <v>261877</v>
       </c>
-      <c r="G6" s="101" t="s">
+      <c r="G6" s="94" t="s">
         <v>175</v>
       </c>
-      <c r="H6" s="101">
+      <c r="H6" s="94">
         <v>3400</v>
       </c>
-      <c r="I6" s="102">
+      <c r="I6" s="95">
         <v>0.4</v>
       </c>
-      <c r="J6" s="102">
+      <c r="J6" s="95">
         <v>0.9</v>
       </c>
-      <c r="K6" s="99" t="s">
+      <c r="K6" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="102">
+      <c r="L6" s="95">
         <v>1224</v>
       </c>
-      <c r="M6" s="103">
+      <c r="M6" s="96">
         <v>1020</v>
       </c>
-      <c r="N6" s="104">
+      <c r="N6" s="97">
         <v>9.4399999999999998E-2</v>
       </c>
-      <c r="O6" s="105">
+      <c r="O6" s="98">
         <v>5.67</v>
       </c>
-      <c r="P6" s="99">
+      <c r="P6" s="92">
         <v>446.8</v>
       </c>
-      <c r="Q6" s="101">
+      <c r="Q6" s="94">
         <v>3</v>
       </c>
-      <c r="R6" s="101">
+      <c r="R6" s="94">
         <v>1250</v>
       </c>
-      <c r="S6" s="101">
+      <c r="S6" s="94">
         <v>1.2</v>
       </c>
-      <c r="T6" s="99">
+      <c r="T6" s="92">
         <v>50</v>
       </c>
-      <c r="U6" s="104">
+      <c r="U6" s="97">
         <v>0.04</v>
       </c>
-      <c r="V6" s="99" t="s">
+      <c r="V6" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="W6" s="99" t="s">
-        <v>28</v>
-      </c>
-      <c r="X6" s="99" t="s">
+      <c r="W6" s="92" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="Y6" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z6" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA6" s="99" t="s">
+      <c r="Y6" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="AB6" s="99" t="s">
+      <c r="AB6" s="92" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="106" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="100">
+    <row r="7" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="93">
         <v>5</v>
       </c>
-      <c r="B7" s="99" t="s">
+      <c r="B7" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="99" t="s">
+      <c r="C7" s="92" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="99" t="s">
+      <c r="D7" s="92" t="s">
         <v>131</v>
       </c>
-      <c r="E7" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="101">
+      <c r="E7" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="94">
         <v>261875</v>
       </c>
-      <c r="G7" s="101" t="s">
+      <c r="G7" s="94" t="s">
         <v>173</v>
       </c>
-      <c r="H7" s="101">
+      <c r="H7" s="94">
         <v>3500</v>
       </c>
-      <c r="I7" s="102">
+      <c r="I7" s="95">
         <v>1.1499999999999999</v>
       </c>
-      <c r="J7" s="102">
+      <c r="J7" s="95">
         <v>0.59899999999999998</v>
       </c>
-      <c r="K7" s="99" t="s">
+      <c r="K7" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="102">
+      <c r="L7" s="95">
         <v>2410.9749999999999</v>
       </c>
-      <c r="M7" s="103">
+      <c r="M7" s="96">
         <v>2096.5</v>
       </c>
-      <c r="N7" s="104">
+      <c r="N7" s="97">
         <v>0.58240000000000003</v>
       </c>
-      <c r="O7" s="105">
+      <c r="O7" s="98">
         <v>34.94</v>
       </c>
-      <c r="P7" s="99">
+      <c r="P7" s="92">
         <v>940.3</v>
       </c>
-      <c r="Q7" s="101">
+      <c r="Q7" s="94">
         <v>1</v>
       </c>
-      <c r="R7" s="101">
+      <c r="R7" s="94">
         <v>1200</v>
       </c>
-      <c r="S7" s="101">
+      <c r="S7" s="94">
         <v>1.1499999999999999</v>
       </c>
-      <c r="T7" s="99">
+      <c r="T7" s="92">
         <v>50</v>
       </c>
-      <c r="U7" s="104">
+      <c r="U7" s="97">
         <v>4.1700000000000001E-2</v>
       </c>
-      <c r="V7" s="99" t="s">
+      <c r="V7" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="W7" s="99" t="s">
-        <v>28</v>
-      </c>
-      <c r="X7" s="99" t="s">
+      <c r="W7" s="92" t="s">
+        <v>28</v>
+      </c>
+      <c r="X7" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="Y7" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z7" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA7" s="99" t="s">
+      <c r="Y7" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="AB7" s="99" t="s">
+      <c r="AB7" s="92" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="106" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="100">
+    <row r="8" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="93">
         <v>6</v>
       </c>
-      <c r="B8" s="99" t="s">
+      <c r="B8" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="99" t="s">
+      <c r="C8" s="92" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="99" t="s">
+      <c r="D8" s="92" t="s">
         <v>131</v>
       </c>
-      <c r="E8" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="101">
+      <c r="E8" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="94">
         <v>261876</v>
       </c>
-      <c r="G8" s="101" t="s">
+      <c r="G8" s="94" t="s">
         <v>171</v>
       </c>
-      <c r="H8" s="101">
+      <c r="H8" s="94">
         <v>3500</v>
       </c>
-      <c r="I8" s="102">
+      <c r="I8" s="95">
         <v>1.151</v>
       </c>
-      <c r="J8" s="102">
+      <c r="J8" s="95">
         <v>0.69899999999999995</v>
       </c>
-      <c r="K8" s="99" t="s">
+      <c r="K8" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="L8" s="102">
+      <c r="L8" s="95">
         <v>2815.9209999999998</v>
       </c>
-      <c r="M8" s="103">
+      <c r="M8" s="96">
         <v>2446.5</v>
       </c>
-      <c r="N8" s="104">
+      <c r="N8" s="97">
         <v>0.67959999999999998</v>
       </c>
-      <c r="O8" s="105">
+      <c r="O8" s="98">
         <v>40.770000000000003</v>
       </c>
-      <c r="P8" s="99">
+      <c r="P8" s="92">
         <v>1098.2</v>
       </c>
-      <c r="Q8" s="101">
+      <c r="Q8" s="94">
         <v>1</v>
       </c>
-      <c r="R8" s="101">
+      <c r="R8" s="94">
         <v>1200</v>
       </c>
-      <c r="S8" s="101">
+      <c r="S8" s="94">
         <v>1.151</v>
       </c>
-      <c r="T8" s="99">
+      <c r="T8" s="92">
         <v>49</v>
       </c>
-      <c r="U8" s="104">
+      <c r="U8" s="97">
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="V8" s="99" t="s">
+      <c r="V8" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="W8" s="99" t="s">
-        <v>28</v>
-      </c>
-      <c r="X8" s="99" t="s">
+      <c r="W8" s="92" t="s">
+        <v>28</v>
+      </c>
+      <c r="X8" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="Y8" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z8" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA8" s="99" t="s">
+      <c r="Y8" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="AB8" s="99" t="s">
+      <c r="AB8" s="92" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="106" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="100">
+    <row r="9" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="93">
         <v>7</v>
       </c>
-      <c r="B9" s="99" t="s">
+      <c r="B9" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="99" t="s">
+      <c r="C9" s="92" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="99" t="s">
+      <c r="D9" s="92" t="s">
         <v>131</v>
       </c>
-      <c r="E9" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="101">
+      <c r="E9" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="94">
         <v>261873</v>
       </c>
-      <c r="G9" s="101" t="s">
+      <c r="G9" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="H9" s="101">
+      <c r="H9" s="94">
         <v>2500</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="95">
         <v>0.98</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="95">
         <v>0.61699999999999999</v>
       </c>
-      <c r="K9" s="99" t="s">
+      <c r="K9" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="95">
         <v>1511.65</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="96">
         <v>1542.5</v>
       </c>
-      <c r="N9" s="104">
+      <c r="N9" s="97">
         <v>0.42849999999999999</v>
       </c>
-      <c r="O9" s="105">
+      <c r="O9" s="98">
         <v>25.71</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="92">
         <v>589.5</v>
       </c>
-      <c r="Q9" s="101">
+      <c r="Q9" s="94">
         <v>1</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="94">
         <v>1000</v>
       </c>
-      <c r="S9" s="101">
+      <c r="S9" s="94">
         <v>0.98</v>
       </c>
-      <c r="T9" s="99">
+      <c r="T9" s="92">
         <v>20</v>
       </c>
-      <c r="U9" s="104">
+      <c r="U9" s="97">
         <v>0.02</v>
       </c>
-      <c r="V9" s="99" t="s">
+      <c r="V9" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="W9" s="99" t="s">
-        <v>28</v>
-      </c>
-      <c r="X9" s="99" t="s">
+      <c r="W9" s="92" t="s">
+        <v>28</v>
+      </c>
+      <c r="X9" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="Y9" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z9" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA9" s="99" t="s">
+      <c r="Y9" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="AB9" s="99" t="s">
+      <c r="AB9" s="92" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="106" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="100">
+    <row r="10" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="93">
         <v>8</v>
       </c>
-      <c r="B10" s="99" t="s">
+      <c r="B10" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="99" t="s">
+      <c r="C10" s="92" t="s">
         <v>132</v>
       </c>
-      <c r="D10" s="99" t="s">
+      <c r="D10" s="92" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="101">
+      <c r="E10" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="94">
         <v>261874</v>
       </c>
-      <c r="G10" s="101" t="s">
+      <c r="G10" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="H10" s="101">
+      <c r="H10" s="94">
         <v>2500</v>
       </c>
-      <c r="I10" s="102">
+      <c r="I10" s="95">
         <v>0.96</v>
       </c>
-      <c r="J10" s="102">
+      <c r="J10" s="95">
         <v>0.69899999999999995</v>
       </c>
-      <c r="K10" s="99" t="s">
+      <c r="K10" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="L10" s="102">
+      <c r="L10" s="95">
         <v>1677.6</v>
       </c>
-      <c r="M10" s="103">
+      <c r="M10" s="96">
         <v>1747.5</v>
       </c>
-      <c r="N10" s="104">
+      <c r="N10" s="97">
         <v>0.4854</v>
       </c>
-      <c r="O10" s="105">
+      <c r="O10" s="98">
         <v>29.13</v>
       </c>
-      <c r="P10" s="99">
+      <c r="P10" s="92">
         <v>654.29999999999995</v>
       </c>
-      <c r="Q10" s="101">
+      <c r="Q10" s="94">
         <v>1</v>
       </c>
-      <c r="R10" s="101">
+      <c r="R10" s="94">
         <v>1000</v>
       </c>
-      <c r="S10" s="101">
+      <c r="S10" s="94">
         <v>0.96</v>
       </c>
-      <c r="T10" s="99">
+      <c r="T10" s="92">
         <v>40</v>
       </c>
-      <c r="U10" s="104">
+      <c r="U10" s="97">
         <v>0.04</v>
       </c>
-      <c r="V10" s="99" t="s">
+      <c r="V10" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="W10" s="99" t="s">
-        <v>28</v>
-      </c>
-      <c r="X10" s="99" t="s">
+      <c r="W10" s="92" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="Y10" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z10" s="99" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA10" s="99" t="s">
+      <c r="Y10" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="AB10" s="99" t="s">
+      <c r="AB10" s="92" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="97" t="s">
+      <c r="A11" s="90" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="19" t="s">
@@ -20799,13 +20799,13 @@
       <c r="E11" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="97">
+      <c r="F11" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="90">
         <v>28780</v>
       </c>
       <c r="I11" s="19" t="s">
@@ -20832,13 +20832,13 @@
       <c r="P11" s="19">
         <v>8548.1</v>
       </c>
-      <c r="Q11" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="R11" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="S11" s="97" t="s">
+      <c r="Q11" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="R11" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="S11" s="90" t="s">
         <v>27</v>
       </c>
       <c r="T11" s="19" t="s">
@@ -20917,88 +20917,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="104" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="71" t="s">
+      <c r="B1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="104" t="s">
         <v>27</v>
       </c>
     </row>
@@ -21734,88 +21734,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="103" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="70" t="s">
+      <c r="B1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="103" t="s">
         <v>27</v>
       </c>
     </row>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251182B1-68B0-4AA0-A21E-556A7806C375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5887289-CBFC-4F67-8DFA-43F8D13D6924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="14" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="17" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051" sheetId="60" r:id="rId1"/>
@@ -32,6 +32,8 @@
     <sheet name="HARMONY EMBALAGENS 1073" sheetId="58" r:id="rId17"/>
     <sheet name="ABAPEL 1074" sheetId="63" r:id="rId18"/>
     <sheet name="CARPEL 1078" sheetId="67" r:id="rId19"/>
+    <sheet name="ABAPEL 1079" sheetId="68" r:id="rId20"/>
+    <sheet name="HARMONY EMBALAGENS 1080" sheetId="69" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023'!$A$1:$AB$10</definedName>
@@ -57,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4162" uniqueCount="520">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1136,9 +1138,6 @@
     <t>1191x1620</t>
   </si>
   <si>
-    <t>0.,800</t>
-  </si>
-  <si>
     <t>1080x1380</t>
   </si>
   <si>
@@ -1530,6 +1529,96 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA - CARPEL  —  OF: 001078</t>
+  </si>
+  <si>
+    <t>1200x1974</t>
+  </si>
+  <si>
+    <t>8112</t>
+  </si>
+  <si>
+    <t>05/08/2026</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - ABAPEL  —  OF: 001079</t>
+  </si>
+  <si>
+    <t>1118x1578</t>
+  </si>
+  <si>
+    <t>35x154x104x154x102</t>
+  </si>
+  <si>
+    <t>04-08-26</t>
+  </si>
+  <si>
+    <t>1190x2142</t>
+  </si>
+  <si>
+    <t>117x156x117</t>
+  </si>
+  <si>
+    <t>949x1654</t>
+  </si>
+  <si>
+    <t>35x224x224x224x222</t>
+  </si>
+  <si>
+    <t>960x2158</t>
+  </si>
+  <si>
+    <t>111x248x111</t>
+  </si>
+  <si>
+    <t>1160x1259</t>
+  </si>
+  <si>
+    <t>101x178x101</t>
+  </si>
+  <si>
+    <t>P50C</t>
+  </si>
+  <si>
+    <t>889x2079</t>
+  </si>
+  <si>
+    <t>240x389x240</t>
+  </si>
+  <si>
+    <t>948x1219</t>
+  </si>
+  <si>
+    <t>115x234x115</t>
+  </si>
+  <si>
+    <t>1028x1339</t>
+  </si>
+  <si>
+    <t>125x254x125</t>
+  </si>
+  <si>
+    <t>1216x1711</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>213x770x213</t>
+  </si>
+  <si>
+    <t>644x1779</t>
+  </si>
+  <si>
+    <t>180x264x180</t>
+  </si>
+  <si>
+    <t>769x1919</t>
+  </si>
+  <si>
+    <t>200x349x200</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - HARMONY EMBALAGENS  —  OF: 001080</t>
   </si>
 </sst>
 </file>
@@ -1730,7 +1819,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2028,6 +2117,37 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5092,7 +5212,7 @@
         <v>45</v>
       </c>
       <c r="D3" s="58" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E3" s="58" t="s">
         <v>27</v>
@@ -5164,7 +5284,7 @@
         <v>39</v>
       </c>
       <c r="AB3" s="58" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="4" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5178,7 +5298,7 @@
         <v>45</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>27</v>
@@ -5250,7 +5370,7 @@
         <v>39</v>
       </c>
       <c r="AB4" s="58" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5706,8 +5826,8 @@
       <c r="H10" s="58">
         <v>1000</v>
       </c>
-      <c r="I10" s="60" t="s">
-        <v>359</v>
+      <c r="I10" s="60">
+        <v>0.8</v>
       </c>
       <c r="J10" s="60">
         <v>1.171</v>
@@ -6521,28 +6641,28 @@
         <v>200</v>
       </c>
       <c r="I3" s="56" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J3" s="42">
         <v>2500</v>
       </c>
       <c r="K3" s="56" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L3" s="42">
         <v>393000</v>
       </c>
       <c r="M3" s="56" t="s">
+        <v>375</v>
+      </c>
+      <c r="N3" s="56" t="s">
         <v>376</v>
-      </c>
-      <c r="N3" s="56" t="s">
-        <v>377</v>
       </c>
       <c r="O3" s="56" t="s">
         <v>252</v>
       </c>
       <c r="P3" s="56" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q3" s="56">
         <v>2</v>
@@ -6557,7 +6677,7 @@
         <v>28</v>
       </c>
       <c r="U3" s="56" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="V3" s="56" t="s">
         <v>29</v>
@@ -6578,7 +6698,7 @@
         <v>2</v>
       </c>
       <c r="AB3" s="56" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6604,28 +6724,28 @@
         <v>500</v>
       </c>
       <c r="I4" s="56" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J4" s="42">
         <v>2062</v>
       </c>
       <c r="K4" s="56" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="L4" s="42">
         <v>725824</v>
       </c>
       <c r="M4" s="56" t="s">
+        <v>367</v>
+      </c>
+      <c r="N4" s="56" t="s">
         <v>368</v>
       </c>
-      <c r="N4" s="56" t="s">
+      <c r="O4" s="56" t="s">
         <v>369</v>
       </c>
-      <c r="O4" s="56" t="s">
+      <c r="P4" s="56" t="s">
         <v>370</v>
-      </c>
-      <c r="P4" s="56" t="s">
-        <v>371</v>
       </c>
       <c r="Q4" s="56">
         <v>2</v>
@@ -6640,7 +6760,7 @@
         <v>42</v>
       </c>
       <c r="U4" s="56" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="V4" s="56" t="s">
         <v>28</v>
@@ -6655,7 +6775,7 @@
         <v>2</v>
       </c>
       <c r="AB4" s="56" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:28" s="17" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -7953,7 +8073,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="102" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B1" s="102" t="s">
         <v>27</v>
@@ -8128,7 +8248,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C3" s="38" t="s">
         <v>165</v>
@@ -8206,7 +8326,7 @@
         <v>30</v>
       </c>
       <c r="AB3" s="33" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -8214,7 +8334,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>165</v>
@@ -8292,7 +8412,7 @@
         <v>33</v>
       </c>
       <c r="AB4" s="33" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -8300,7 +8420,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>53</v>
@@ -8378,7 +8498,7 @@
         <v>39</v>
       </c>
       <c r="AB5" s="33" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -8386,7 +8506,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>53</v>
@@ -8472,7 +8592,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>165</v>
@@ -8550,7 +8670,7 @@
         <v>33</v>
       </c>
       <c r="AB7" s="33" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -8688,7 +8808,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="104" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B1" s="104" t="s">
         <v>27</v>
@@ -8866,10 +8986,10 @@
         <v>133</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>27</v>
@@ -8878,7 +8998,7 @@
         <v>262012</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H3" s="11">
         <v>300</v>
@@ -8890,7 +9010,7 @@
         <v>1.855</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L3" s="13">
         <v>424.053</v>
@@ -8923,13 +9043,13 @@
         <v>1.6799999999999999E-2</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="W3" s="11" t="s">
         <v>42</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Y3" s="11" t="s">
         <v>27</v>
@@ -8941,7 +9061,7 @@
         <v>39</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -8952,10 +9072,10 @@
         <v>133</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>27</v>
@@ -8964,7 +9084,7 @@
         <v>262014</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H4" s="11">
         <v>2000</v>
@@ -8976,7 +9096,7 @@
         <v>1.915</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L4" s="13">
         <v>2458.86</v>
@@ -9027,7 +9147,7 @@
         <v>52</v>
       </c>
       <c r="AB4" s="11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9038,10 +9158,10 @@
         <v>133</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>27</v>
@@ -9050,7 +9170,7 @@
         <v>262013</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H5" s="11">
         <v>2000</v>
@@ -9062,7 +9182,7 @@
         <v>1.915</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L5" s="13">
         <v>2535.46</v>
@@ -9113,7 +9233,7 @@
         <v>52</v>
       </c>
       <c r="AB5" s="11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9127,7 +9247,7 @@
         <v>132</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>27</v>
@@ -9136,7 +9256,7 @@
         <v>262008</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H6" s="11">
         <v>300</v>
@@ -9148,7 +9268,7 @@
         <v>1.7849999999999999</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L6" s="13">
         <v>534.42899999999997</v>
@@ -9199,7 +9319,7 @@
         <v>39</v>
       </c>
       <c r="AB6" s="11" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9213,7 +9333,7 @@
         <v>132</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>27</v>
@@ -9222,7 +9342,7 @@
         <v>262007</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H7" s="11">
         <v>1000</v>
@@ -9234,7 +9354,7 @@
         <v>0.94</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L7" s="13">
         <v>430.52</v>
@@ -9285,7 +9405,7 @@
         <v>39</v>
       </c>
       <c r="AB7" s="11" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9299,7 +9419,7 @@
         <v>132</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>27</v>
@@ -9308,7 +9428,7 @@
         <v>262009</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H8" s="11">
         <v>500</v>
@@ -9320,7 +9440,7 @@
         <v>0.875</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L8" s="13">
         <v>165.375</v>
@@ -9371,7 +9491,7 @@
         <v>39</v>
       </c>
       <c r="AB8" s="11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9385,7 +9505,7 @@
         <v>132</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>27</v>
@@ -9394,7 +9514,7 @@
         <v>262011</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H9" s="11">
         <v>400</v>
@@ -9406,7 +9526,7 @@
         <v>1.105</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L9" s="13">
         <v>151.16399999999999</v>
@@ -9457,7 +9577,7 @@
         <v>39</v>
       </c>
       <c r="AB9" s="11" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9471,7 +9591,7 @@
         <v>132</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>27</v>
@@ -9480,7 +9600,7 @@
         <v>262010</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H10" s="11">
         <v>1000</v>
@@ -9492,7 +9612,7 @@
         <v>0.83899999999999997</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L10" s="13">
         <v>271.83600000000001</v>
@@ -9543,7 +9663,7 @@
         <v>39</v>
       </c>
       <c r="AB10" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9677,7 +9797,7 @@
   <sheetData>
     <row r="1" spans="1:28" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="108" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B1" s="108" t="s">
         <v>27</v>
@@ -9852,13 +9972,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>27</v>
@@ -9867,7 +9987,7 @@
         <v>262017</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H3" s="5">
         <v>1250</v>
@@ -9930,7 +10050,7 @@
         <v>32</v>
       </c>
       <c r="AB3" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -9938,13 +10058,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>27</v>
@@ -9953,7 +10073,7 @@
         <v>262027</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H4" s="5">
         <v>200</v>
@@ -9965,7 +10085,7 @@
         <v>1.5389999999999999</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L4" s="7">
         <v>198.53100000000001</v>
@@ -10016,7 +10136,7 @@
         <v>33</v>
       </c>
       <c r="AB4" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -10024,13 +10144,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>181</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>27</v>
@@ -10039,7 +10159,7 @@
         <v>262031</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H5" s="5">
         <v>400</v>
@@ -10110,13 +10230,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>27</v>
@@ -10125,7 +10245,7 @@
         <v>262030</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H6" s="5">
         <v>100</v>
@@ -10196,13 +10316,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>27</v>
@@ -10211,7 +10331,7 @@
         <v>262029</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H7" s="5">
         <v>700</v>
@@ -10223,7 +10343,7 @@
         <v>1.7190000000000001</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L7" s="7">
         <v>666.62800000000004</v>
@@ -10274,7 +10394,7 @@
         <v>33</v>
       </c>
       <c r="AB7" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -10282,13 +10402,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>27</v>
@@ -10297,7 +10417,7 @@
         <v>262015</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H8" s="5">
         <v>660</v>
@@ -10309,7 +10429,7 @@
         <v>1.7030000000000001</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L8" s="7">
         <v>629.42899999999997</v>
@@ -10360,7 +10480,7 @@
         <v>33</v>
       </c>
       <c r="AB8" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -10368,13 +10488,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>27</v>
@@ -10383,7 +10503,7 @@
         <v>262028</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H9" s="5">
         <v>150</v>
@@ -10395,7 +10515,7 @@
         <v>1.5589999999999999</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L9" s="7">
         <v>256.06599999999997</v>
@@ -10446,7 +10566,7 @@
         <v>39</v>
       </c>
       <c r="AB9" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -10454,13 +10574,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>27</v>
@@ -10469,7 +10589,7 @@
         <v>262018</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H10" s="5">
         <v>2500</v>
@@ -10481,7 +10601,7 @@
         <v>1.4990000000000001</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L10" s="7">
         <v>1626.415</v>
@@ -10532,7 +10652,7 @@
         <v>80</v>
       </c>
       <c r="AB10" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -10540,13 +10660,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>189</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>27</v>
@@ -10555,7 +10675,7 @@
         <v>262022</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H11" s="5">
         <v>250</v>
@@ -10618,7 +10738,7 @@
         <v>39</v>
       </c>
       <c r="AB11" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -10626,13 +10746,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>189</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>27</v>
@@ -10641,7 +10761,7 @@
         <v>262021</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H12" s="5">
         <v>350</v>
@@ -10704,7 +10824,7 @@
         <v>39</v>
       </c>
       <c r="AB12" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -10712,13 +10832,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>27</v>
@@ -10727,7 +10847,7 @@
         <v>262026</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H13" s="5">
         <v>300</v>
@@ -10739,7 +10859,7 @@
         <v>1.649</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L13" s="7">
         <v>420</v>
@@ -10790,7 +10910,7 @@
         <v>39</v>
       </c>
       <c r="AB13" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -10798,13 +10918,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>27</v>
@@ -10813,7 +10933,7 @@
         <v>262019</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H14" s="5">
         <v>1100</v>
@@ -10825,7 +10945,7 @@
         <v>1.133</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L14" s="7">
         <v>501.01299999999998</v>
@@ -10876,7 +10996,7 @@
         <v>39</v>
       </c>
       <c r="AB14" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -10884,13 +11004,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>53</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>27</v>
@@ -10899,7 +11019,7 @@
         <v>262023</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H15" s="5">
         <v>2000</v>
@@ -10911,7 +11031,7 @@
         <v>1.649</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L15" s="7">
         <v>2618.6120000000001</v>
@@ -10962,7 +11082,7 @@
         <v>52</v>
       </c>
       <c r="AB15" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -10970,13 +11090,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>27</v>
@@ -10985,7 +11105,7 @@
         <v>262024</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H16" s="5">
         <v>1300</v>
@@ -10997,7 +11117,7 @@
         <v>1.7689999999999999</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L16" s="7">
         <v>1894.953</v>
@@ -11048,7 +11168,7 @@
         <v>32</v>
       </c>
       <c r="AB16" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -11056,13 +11176,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>53</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>27</v>
@@ -11071,7 +11191,7 @@
         <v>262020</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H17" s="5">
         <v>1200</v>
@@ -11134,7 +11254,7 @@
         <v>39</v>
       </c>
       <c r="AB17" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -11142,13 +11262,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>27</v>
@@ -11157,7 +11277,7 @@
         <v>262025</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H18" s="5">
         <v>1000</v>
@@ -11169,7 +11289,7 @@
         <v>0.79900000000000004</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L18" s="7">
         <v>287.64</v>
@@ -11220,7 +11340,7 @@
         <v>39</v>
       </c>
       <c r="AB18" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -11228,13 +11348,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>53</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>27</v>
@@ -11243,7 +11363,7 @@
         <v>262016</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H19" s="5">
         <v>1000</v>
@@ -11255,7 +11375,7 @@
         <v>0.84899999999999998</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L19" s="7">
         <v>249.60599999999999</v>
@@ -11306,7 +11426,7 @@
         <v>39</v>
       </c>
       <c r="AB19" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
@@ -11444,7 +11564,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="107" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B1" s="107" t="s">
         <v>27</v>
@@ -11625,7 +11745,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="83" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E3" s="83" t="s">
         <v>27</v>
@@ -11634,7 +11754,7 @@
         <v>262040</v>
       </c>
       <c r="G3" s="83" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H3" s="83">
         <v>480</v>
@@ -11646,7 +11766,7 @@
         <v>1.8280000000000001</v>
       </c>
       <c r="K3" s="83" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L3" s="84">
         <v>688.79</v>
@@ -11697,7 +11817,7 @@
         <v>30</v>
       </c>
       <c r="AB3" s="83" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="4" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11711,7 +11831,7 @@
         <v>26</v>
       </c>
       <c r="D4" s="76" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E4" s="76" t="s">
         <v>27</v>
@@ -11720,7 +11840,7 @@
         <v>262039</v>
       </c>
       <c r="G4" s="76" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H4" s="76">
         <v>140</v>
@@ -11783,7 +11903,7 @@
         <v>39</v>
       </c>
       <c r="AB4" s="76" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11797,7 +11917,7 @@
         <v>26</v>
       </c>
       <c r="D5" s="70" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E5" s="70" t="s">
         <v>27</v>
@@ -11806,7 +11926,7 @@
         <v>262037</v>
       </c>
       <c r="G5" s="70" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H5" s="70">
         <v>800</v>
@@ -11883,7 +12003,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="83" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E6" s="83" t="s">
         <v>27</v>
@@ -11892,7 +12012,7 @@
         <v>262042</v>
       </c>
       <c r="G6" s="83" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H6" s="83">
         <v>700</v>
@@ -11904,7 +12024,7 @@
         <v>1.7450000000000001</v>
       </c>
       <c r="K6" s="83" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L6" s="84">
         <v>778.096</v>
@@ -11955,7 +12075,7 @@
         <v>32</v>
       </c>
       <c r="AB6" s="83" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11969,7 +12089,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="70" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E7" s="70" t="s">
         <v>27</v>
@@ -11978,7 +12098,7 @@
         <v>262038</v>
       </c>
       <c r="G7" s="70" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H7" s="70">
         <v>1100</v>
@@ -11990,7 +12110,7 @@
         <v>1.6579999999999999</v>
       </c>
       <c r="K7" s="70" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L7" s="72">
         <v>1085.1610000000001</v>
@@ -12041,7 +12161,7 @@
         <v>41</v>
       </c>
       <c r="AB7" s="70" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12055,7 +12175,7 @@
         <v>26</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>27</v>
@@ -12064,7 +12184,7 @@
         <v>262033</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H8" s="5">
         <v>1000</v>
@@ -12076,7 +12196,7 @@
         <v>1.04</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L8" s="7">
         <v>600.08000000000004</v>
@@ -12127,7 +12247,7 @@
         <v>33</v>
       </c>
       <c r="AB8" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12141,7 +12261,7 @@
         <v>36</v>
       </c>
       <c r="D9" s="83" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E9" s="83" t="s">
         <v>27</v>
@@ -12150,7 +12270,7 @@
         <v>262043</v>
       </c>
       <c r="G9" s="83" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H9" s="83">
         <v>1800</v>
@@ -12162,7 +12282,7 @@
         <v>1.214</v>
       </c>
       <c r="K9" s="83" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L9" s="84">
         <v>933.08</v>
@@ -12213,7 +12333,7 @@
         <v>30</v>
       </c>
       <c r="AB9" s="83" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -12227,7 +12347,7 @@
         <v>36</v>
       </c>
       <c r="D10" s="83" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E10" s="83" t="s">
         <v>27</v>
@@ -12236,7 +12356,7 @@
         <v>262041</v>
       </c>
       <c r="G10" s="83" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H10" s="83">
         <v>3000</v>
@@ -12248,7 +12368,7 @@
         <v>1.01</v>
       </c>
       <c r="K10" s="83" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L10" s="84">
         <v>1030.2</v>
@@ -12299,7 +12419,7 @@
         <v>33</v>
       </c>
       <c r="AB10" s="83" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12433,7 +12553,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="108" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B1" s="108" t="s">
         <v>27</v>
@@ -12608,13 +12728,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>27</v>
@@ -12623,7 +12743,7 @@
         <v>262061</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H3" s="5">
         <v>500</v>
@@ -12635,7 +12755,7 @@
         <v>1.28</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L3" s="7">
         <v>453.76</v>
@@ -12686,7 +12806,7 @@
         <v>39</v>
       </c>
       <c r="AB3" s="5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
@@ -12694,13 +12814,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>27</v>
@@ -12709,7 +12829,7 @@
         <v>262062</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H4" s="5">
         <v>500</v>
@@ -12718,10 +12838,10 @@
         <v>0.70899999999999996</v>
       </c>
       <c r="J4" s="7">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L4" s="7">
         <v>354.5</v>
@@ -12772,7 +12892,7 @@
         <v>39</v>
       </c>
       <c r="AB4" s="5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
@@ -12780,13 +12900,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>27</v>
@@ -12795,7 +12915,7 @@
         <v>262049</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H5" s="5">
         <v>2000</v>
@@ -12858,7 +12978,7 @@
         <v>33</v>
       </c>
       <c r="AB5" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
@@ -12866,13 +12986,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>27</v>
@@ -12881,7 +13001,7 @@
         <v>262050</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H6" s="5">
         <v>2000</v>
@@ -12944,7 +13064,7 @@
         <v>39</v>
       </c>
       <c r="AB6" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
@@ -12952,13 +13072,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>27</v>
@@ -12967,7 +13087,7 @@
         <v>262065</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H7" s="5">
         <v>500</v>
@@ -12979,7 +13099,7 @@
         <v>0.59</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L7" s="7">
         <v>181.13</v>
@@ -13030,7 +13150,7 @@
         <v>39</v>
       </c>
       <c r="AB7" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
@@ -13038,13 +13158,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>27</v>
@@ -13053,7 +13173,7 @@
         <v>262046</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H8" s="5">
         <v>1000</v>
@@ -13116,7 +13236,7 @@
         <v>39</v>
       </c>
       <c r="AB8" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
@@ -13124,13 +13244,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>27</v>
@@ -13139,7 +13259,7 @@
         <v>262048</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H9" s="5">
         <v>10000</v>
@@ -13202,7 +13322,7 @@
         <v>52</v>
       </c>
       <c r="AB9" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
@@ -13210,13 +13330,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>27</v>
@@ -13225,7 +13345,7 @@
         <v>262063</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H10" s="5">
         <v>500</v>
@@ -13288,7 +13408,7 @@
         <v>39</v>
       </c>
       <c r="AB10" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
@@ -13296,13 +13416,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>27</v>
@@ -13311,7 +13431,7 @@
         <v>262064</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H11" s="5">
         <v>1000</v>
@@ -13374,7 +13494,7 @@
         <v>39</v>
       </c>
       <c r="AB11" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
@@ -13382,13 +13502,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>27</v>
@@ -13397,19 +13517,19 @@
         <v>262053</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H12" s="5">
         <v>4000</v>
       </c>
       <c r="I12" s="7">
-        <v>0.56999999999999995</v>
+        <v>0.56399999999999995</v>
       </c>
       <c r="J12" s="7">
         <v>2.16</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="L12" s="7">
         <v>4924.8</v>
@@ -13460,7 +13580,7 @@
         <v>52</v>
       </c>
       <c r="AB12" s="5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
@@ -13468,13 +13588,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>27</v>
@@ -13483,7 +13603,7 @@
         <v>262052</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H13" s="5">
         <v>1500</v>
@@ -13546,7 +13666,7 @@
         <v>39</v>
       </c>
       <c r="AB13" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
@@ -13554,13 +13674,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>27</v>
@@ -13569,7 +13689,7 @@
         <v>262051</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H14" s="5">
         <v>2000</v>
@@ -13581,7 +13701,7 @@
         <v>2.2040000000000002</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L14" s="7">
         <v>2442.0320000000002</v>
@@ -13632,7 +13752,7 @@
         <v>52</v>
       </c>
       <c r="AB14" s="5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
@@ -13640,13 +13760,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>27</v>
@@ -13655,7 +13775,7 @@
         <v>262059</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H15" s="5">
         <v>1500</v>
@@ -13667,7 +13787,7 @@
         <v>2.14</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L15" s="7">
         <v>1682.04</v>
@@ -13718,7 +13838,7 @@
         <v>33</v>
       </c>
       <c r="AB15" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
@@ -13726,13 +13846,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>27</v>
@@ -13741,7 +13861,7 @@
         <v>262056</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H16" s="5">
         <v>500</v>
@@ -13804,7 +13924,7 @@
         <v>39</v>
       </c>
       <c r="AB16" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
@@ -13812,13 +13932,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>27</v>
@@ -13827,7 +13947,7 @@
         <v>262058</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H17" s="5">
         <v>500</v>
@@ -13890,7 +14010,7 @@
         <v>39</v>
       </c>
       <c r="AB17" s="5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.3">
@@ -13898,13 +14018,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>27</v>
@@ -13913,7 +14033,7 @@
         <v>262057</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H18" s="5">
         <v>700</v>
@@ -13925,7 +14045,7 @@
         <v>1.56</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L18" s="7">
         <v>539.44799999999998</v>
@@ -13976,7 +14096,7 @@
         <v>39</v>
       </c>
       <c r="AB18" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.3">
@@ -13984,13 +14104,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>27</v>
@@ -13999,7 +14119,7 @@
         <v>262060</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H19" s="5">
         <v>1000</v>
@@ -14062,7 +14182,7 @@
         <v>30</v>
       </c>
       <c r="AB19" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
@@ -14070,13 +14190,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>27</v>
@@ -14085,7 +14205,7 @@
         <v>262055</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H20" s="5">
         <v>2000</v>
@@ -14097,7 +14217,7 @@
         <v>1.36</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L20" s="7">
         <v>1071.68</v>
@@ -14148,7 +14268,7 @@
         <v>30</v>
       </c>
       <c r="AB20" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
@@ -14156,13 +14276,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>27</v>
@@ -14171,7 +14291,7 @@
         <v>262047</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H21" s="5">
         <v>1000</v>
@@ -14234,7 +14354,7 @@
         <v>33</v>
       </c>
       <c r="AB21" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.3">
@@ -14242,13 +14362,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>27</v>
@@ -14257,7 +14377,7 @@
         <v>262054</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H22" s="5">
         <v>2000</v>
@@ -14269,7 +14389,7 @@
         <v>1.26</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="L22" s="7">
         <v>866.88</v>
@@ -14320,7 +14440,7 @@
         <v>33</v>
       </c>
       <c r="AB22" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.3">
@@ -15320,6 +15440,1726 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup scale="78" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6DECCF-0481-438A-8BDD-F0275CF2BE70}">
+  <dimension ref="A1:AB4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.21875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6" style="1" customWidth="1"/>
+    <col min="17" max="17" width="3.33203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="7.88671875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="7" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.88671875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="3.33203125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="10.44140625" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="119" t="s">
+        <v>493</v>
+      </c>
+      <c r="B1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="119" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="116">
+        <v>1</v>
+      </c>
+      <c r="B3" s="118" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="116" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="116" t="s">
+        <v>492</v>
+      </c>
+      <c r="E3" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="116">
+        <v>262067</v>
+      </c>
+      <c r="G3" s="116" t="s">
+        <v>491</v>
+      </c>
+      <c r="H3" s="116">
+        <v>340</v>
+      </c>
+      <c r="I3" s="117">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="J3" s="117">
+        <v>2.06</v>
+      </c>
+      <c r="K3" s="116" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="113">
+        <v>684.29100000000005</v>
+      </c>
+      <c r="M3" s="115">
+        <v>700.4</v>
+      </c>
+      <c r="N3" s="112">
+        <v>0.1946</v>
+      </c>
+      <c r="O3" s="114">
+        <v>11.67</v>
+      </c>
+      <c r="P3" s="111">
+        <v>405.8</v>
+      </c>
+      <c r="Q3" s="111">
+        <v>1</v>
+      </c>
+      <c r="R3" s="111">
+        <v>1000</v>
+      </c>
+      <c r="S3" s="113">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="T3" s="111">
+        <v>23</v>
+      </c>
+      <c r="U3" s="112">
+        <v>2.3E-2</v>
+      </c>
+      <c r="V3" s="111" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="111" t="s">
+        <v>29</v>
+      </c>
+      <c r="X3" s="111" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="111" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="111" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="111" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB3" s="111" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="110">
+        <v>340</v>
+      </c>
+      <c r="I4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="109">
+        <v>405.8</v>
+      </c>
+      <c r="Q4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="S4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="U4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="X4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB4" s="109" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{819F2E85-837E-49CE-91A8-B709D04980B6}">
+  <dimension ref="A1:AB15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="6" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.21875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="7.109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="3.33203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.44140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="7" style="1" customWidth="1"/>
+    <col min="23" max="23" width="7.109375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5546875" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7.44140625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.109375" style="1" customWidth="1"/>
+    <col min="27" max="27" width="3.5546875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="10.109375" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="108" t="s">
+        <v>519</v>
+      </c>
+      <c r="B1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="108" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="5">
+        <v>262068</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H3" s="5">
+        <v>500</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0.749</v>
+      </c>
+      <c r="J3" s="7">
+        <v>1.899</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="L3" s="7">
+        <v>711.17499999999995</v>
+      </c>
+      <c r="M3" s="9">
+        <v>474.8</v>
+      </c>
+      <c r="N3" s="6">
+        <v>6.59E-2</v>
+      </c>
+      <c r="O3" s="8">
+        <v>3.96</v>
+      </c>
+      <c r="P3" s="5">
+        <v>421.7</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>2</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1550</v>
+      </c>
+      <c r="S3" s="7">
+        <v>1.498</v>
+      </c>
+      <c r="T3" s="5">
+        <v>52</v>
+      </c>
+      <c r="U3" s="6">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="5">
+        <v>262075</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H4" s="5">
+        <v>300</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.624</v>
+      </c>
+      <c r="J4" s="7">
+        <v>1.7589999999999999</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="L4" s="7">
+        <v>329.28500000000003</v>
+      </c>
+      <c r="M4" s="9">
+        <v>263.8</v>
+      </c>
+      <c r="N4" s="6">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="O4" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P4" s="5">
+        <v>195.3</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>2</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1300</v>
+      </c>
+      <c r="S4" s="7">
+        <v>1.248</v>
+      </c>
+      <c r="T4" s="5">
+        <v>52</v>
+      </c>
+      <c r="U4" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="5">
+        <v>262078</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1600</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1.196</v>
+      </c>
+      <c r="J5" s="7">
+        <v>1.6910000000000001</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="L5" s="7">
+        <v>3235.8980000000001</v>
+      </c>
+      <c r="M5" s="9">
+        <v>2705.6</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0.75160000000000005</v>
+      </c>
+      <c r="O5" s="8">
+        <v>45.09</v>
+      </c>
+      <c r="P5" s="5">
+        <v>2025.7</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1250</v>
+      </c>
+      <c r="S5" s="7">
+        <v>1.196</v>
+      </c>
+      <c r="T5" s="5">
+        <v>54</v>
+      </c>
+      <c r="U5" s="6">
+        <v>4.3200000000000002E-2</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="5">
+        <v>262071</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H6" s="5">
+        <v>600</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0.504</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1.319</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="L6" s="7">
+        <v>398.86599999999999</v>
+      </c>
+      <c r="M6" s="9">
+        <v>395.7</v>
+      </c>
+      <c r="N6" s="6">
+        <v>5.5E-2</v>
+      </c>
+      <c r="O6" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="P6" s="5">
+        <v>236.5</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>2</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1050</v>
+      </c>
+      <c r="S6" s="7">
+        <v>1.008</v>
+      </c>
+      <c r="T6" s="5">
+        <v>42</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB6" s="5" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="5">
+        <v>262070</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H7" s="5">
+        <v>600</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0.46400000000000002</v>
+      </c>
+      <c r="J7" s="7">
+        <v>1.1990000000000001</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="L7" s="7">
+        <v>333.80200000000002</v>
+      </c>
+      <c r="M7" s="9">
+        <v>359.7</v>
+      </c>
+      <c r="N7" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="O7" s="8">
+        <v>3</v>
+      </c>
+      <c r="P7" s="5">
+        <v>197.9</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>2</v>
+      </c>
+      <c r="R7" s="5">
+        <v>950</v>
+      </c>
+      <c r="S7" s="7">
+        <v>0.92800000000000005</v>
+      </c>
+      <c r="T7" s="5">
+        <v>22</v>
+      </c>
+      <c r="U7" s="6">
+        <v>2.3199999999999998E-2</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="X7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB7" s="5" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="5">
+        <v>262069</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H8" s="5">
+        <v>500</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.86899999999999999</v>
+      </c>
+      <c r="J8" s="7">
+        <v>2.0590000000000002</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="L8" s="7">
+        <v>894.63499999999999</v>
+      </c>
+      <c r="M8" s="9">
+        <v>1029.5</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="O8" s="8">
+        <v>17.16</v>
+      </c>
+      <c r="P8" s="5">
+        <v>530.5</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5">
+        <v>900</v>
+      </c>
+      <c r="S8" s="7">
+        <v>0.86899999999999999</v>
+      </c>
+      <c r="T8" s="5">
+        <v>31</v>
+      </c>
+      <c r="U8" s="6">
+        <v>3.44E-2</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB8" s="5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>7</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="5">
+        <v>262077</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H9" s="5">
+        <v>4500</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0.38</v>
+      </c>
+      <c r="J9" s="7">
+        <v>1.2390000000000001</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="L9" s="7">
+        <v>2118.69</v>
+      </c>
+      <c r="M9" s="9">
+        <v>2787.8</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0.38719999999999999</v>
+      </c>
+      <c r="O9" s="8">
+        <v>23.23</v>
+      </c>
+      <c r="P9" s="5">
+        <v>822.1</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>2</v>
+      </c>
+      <c r="R9" s="5">
+        <v>800</v>
+      </c>
+      <c r="S9" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="T9" s="5">
+        <v>40</v>
+      </c>
+      <c r="U9" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB9" s="5" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="5">
+        <v>262074</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H10" s="5">
+        <v>550</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0.47</v>
+      </c>
+      <c r="J10" s="7">
+        <v>1.069</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="L10" s="7">
+        <v>276.33600000000001</v>
+      </c>
+      <c r="M10" s="9">
+        <v>294</v>
+      </c>
+      <c r="N10" s="6">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="O10" s="8">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="P10" s="5">
+        <v>95.3</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>2</v>
+      </c>
+      <c r="R10" s="5">
+        <v>1000</v>
+      </c>
+      <c r="S10" s="7">
+        <v>0.94</v>
+      </c>
+      <c r="T10" s="5">
+        <v>60</v>
+      </c>
+      <c r="U10" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB10" s="5" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="5">
+        <v>262075</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H11" s="5">
+        <v>300</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="J11" s="7">
+        <v>1.6339999999999999</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="L11" s="7">
+        <v>455.39600000000002</v>
+      </c>
+      <c r="M11" s="9">
+        <v>490.2</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0.13619999999999999</v>
+      </c>
+      <c r="O11" s="8">
+        <v>8.17</v>
+      </c>
+      <c r="P11" s="5">
+        <v>157.1</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>1</v>
+      </c>
+      <c r="R11" s="5">
+        <v>950</v>
+      </c>
+      <c r="S11" s="7">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="T11" s="5">
+        <v>21</v>
+      </c>
+      <c r="U11" s="6">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB11" s="5" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="5">
+        <v>262072</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1200</v>
+      </c>
+      <c r="I12" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0.63</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="7">
+        <v>627.48</v>
+      </c>
+      <c r="M12" s="9">
+        <v>756</v>
+      </c>
+      <c r="N12" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="O12" s="8">
+        <v>12.6</v>
+      </c>
+      <c r="P12" s="5">
+        <v>229</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>1</v>
+      </c>
+      <c r="R12" s="5">
+        <v>850</v>
+      </c>
+      <c r="S12" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="T12" s="5">
+        <v>20</v>
+      </c>
+      <c r="U12" s="6">
+        <v>2.35E-2</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="W12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB12" s="5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="5">
+        <v>262073</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I13" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="J13" s="7">
+        <v>1.0609999999999999</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="L13" s="7">
+        <v>413.79</v>
+      </c>
+      <c r="M13" s="9">
+        <v>530.5</v>
+      </c>
+      <c r="N13" s="6">
+        <v>7.3700000000000002E-2</v>
+      </c>
+      <c r="O13" s="8">
+        <v>4.42</v>
+      </c>
+      <c r="P13" s="5">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>2</v>
+      </c>
+      <c r="R13" s="5">
+        <v>800</v>
+      </c>
+      <c r="S13" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="T13" s="5">
+        <v>20</v>
+      </c>
+      <c r="U13" s="6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="V13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB13" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="5">
+        <v>262076</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H14" s="5">
+        <v>250</v>
+      </c>
+      <c r="I14" s="7">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="J14" s="7">
+        <v>1.5580000000000001</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="L14" s="7">
+        <v>213.83600000000001</v>
+      </c>
+      <c r="M14" s="9">
+        <v>389.5</v>
+      </c>
+      <c r="N14" s="6">
+        <v>0.1082</v>
+      </c>
+      <c r="O14" s="8">
+        <v>6.49</v>
+      </c>
+      <c r="P14" s="5">
+        <v>73.8</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>1</v>
+      </c>
+      <c r="R14" s="5">
+        <v>700</v>
+      </c>
+      <c r="S14" s="7">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="T14" s="5">
+        <v>151</v>
+      </c>
+      <c r="U14" s="6">
+        <v>0.2157</v>
+      </c>
+      <c r="V14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB14" s="5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="19">
+        <v>11900</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" s="19">
+        <v>5127.7</v>
+      </c>
+      <c r="Q15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="X15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB15" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
@@ -20106,7 +21946,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="100" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C3" s="100" t="s">
         <v>53</v>
@@ -20137,16 +21977,16 @@
         <v>558450</v>
       </c>
       <c r="M3" s="100" t="s">
+        <v>454</v>
+      </c>
+      <c r="N3" s="100" t="s">
         <v>455</v>
       </c>
-      <c r="N3" s="100" t="s">
+      <c r="O3" s="100" t="s">
         <v>456</v>
       </c>
-      <c r="O3" s="100" t="s">
+      <c r="P3" s="100" t="s">
         <v>457</v>
-      </c>
-      <c r="P3" s="100" t="s">
-        <v>458</v>
       </c>
       <c r="Q3" s="93">
         <v>2</v>
@@ -20161,7 +22001,7 @@
         <v>40</v>
       </c>
       <c r="U3" s="100" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V3" s="100" t="s">
         <v>29</v>
@@ -20178,7 +22018,7 @@
         <v>2</v>
       </c>
       <c r="AB3" s="100" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5887289-CBFC-4F67-8DFA-43F8D13D6924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489DF3A1-E2A8-4F88-AA9B-B0EA80CC18EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="17" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="19" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051" sheetId="60" r:id="rId1"/>
@@ -34,6 +34,8 @@
     <sheet name="CARPEL 1078" sheetId="67" r:id="rId19"/>
     <sheet name="ABAPEL 1079" sheetId="68" r:id="rId20"/>
     <sheet name="HARMONY EMBALAGENS 1080" sheetId="69" r:id="rId21"/>
+    <sheet name="FAVINCO 1081" sheetId="70" r:id="rId22"/>
+    <sheet name="PCBOX EMBALAGENS LTDA 1083" sheetId="71" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023'!$A$1:$AB$10</definedName>
@@ -59,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4162" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4378" uniqueCount="531">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1619,6 +1621,39 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA - HARMONY EMBALAGENS  —  OF: 001080</t>
+  </si>
+  <si>
+    <t>1190x1630</t>
+  </si>
+  <si>
+    <t>155x275x155</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - FAVINCO  —  OF: 001081</t>
+  </si>
+  <si>
+    <t>1056x1601</t>
+  </si>
+  <si>
+    <t>187x144x374x144x187</t>
+  </si>
+  <si>
+    <t>1.560</t>
+  </si>
+  <si>
+    <t>232x129x464x129x232</t>
+  </si>
+  <si>
+    <t>1267x1641</t>
+  </si>
+  <si>
+    <t>235x154x469x154x235</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - PCBOX EMBALAGENS LTDA  —  OF: 001083</t>
   </si>
 </sst>
 </file>
@@ -17163,6 +17198,951 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C91923-7AE7-4461-9C2E-05FE2CED0119}">
+  <dimension ref="A1:AB4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4.109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.21875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="3.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.21875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="7.44140625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.77734375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7.88671875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="8.88671875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="3.77734375" style="1" customWidth="1"/>
+    <col min="28" max="28" width="10.109375" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="119" t="s">
+        <v>523</v>
+      </c>
+      <c r="B1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="119" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="116">
+        <v>1</v>
+      </c>
+      <c r="B3" s="118" t="s">
+        <v>190</v>
+      </c>
+      <c r="C3" s="116" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="116" t="s">
+        <v>492</v>
+      </c>
+      <c r="E3" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="116">
+        <v>262079</v>
+      </c>
+      <c r="G3" s="116" t="s">
+        <v>522</v>
+      </c>
+      <c r="H3" s="116">
+        <v>530</v>
+      </c>
+      <c r="I3" s="117">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="J3" s="117">
+        <v>1.61</v>
+      </c>
+      <c r="K3" s="116" t="s">
+        <v>521</v>
+      </c>
+      <c r="L3" s="113">
+        <v>499.18</v>
+      </c>
+      <c r="M3" s="115">
+        <v>426.7</v>
+      </c>
+      <c r="N3" s="112">
+        <v>5.9299999999999999E-2</v>
+      </c>
+      <c r="O3" s="114">
+        <v>3.56</v>
+      </c>
+      <c r="P3" s="111">
+        <v>172.2</v>
+      </c>
+      <c r="Q3" s="111">
+        <v>2</v>
+      </c>
+      <c r="R3" s="111">
+        <v>1200</v>
+      </c>
+      <c r="S3" s="113">
+        <v>1.17</v>
+      </c>
+      <c r="T3" s="111">
+        <v>30</v>
+      </c>
+      <c r="U3" s="112">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="V3" s="111" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="111" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="111" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="111" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="111" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="111" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB3" s="111" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="110">
+        <v>530</v>
+      </c>
+      <c r="I4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="109">
+        <v>172.2</v>
+      </c>
+      <c r="Q4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="S4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="U4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="X4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB4" s="109" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03314351-54CF-4392-B40B-54F11BAD5EE2}">
+  <dimension ref="A1:AB6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="5.88671875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="4" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="6.44140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="23" width="8.44140625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="8" style="1" customWidth="1"/>
+    <col min="25" max="25" width="8.33203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="8" style="1" customWidth="1"/>
+    <col min="27" max="27" width="3.6640625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="10.88671875" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="108" t="s">
+        <v>530</v>
+      </c>
+      <c r="B1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="108" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="5">
+        <v>262082</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="H3" s="5">
+        <v>100</v>
+      </c>
+      <c r="I3" s="7">
+        <v>1.2470000000000001</v>
+      </c>
+      <c r="J3" s="7">
+        <v>1.621</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="L3" s="7">
+        <v>202.13900000000001</v>
+      </c>
+      <c r="M3" s="9">
+        <v>162.1</v>
+      </c>
+      <c r="N3" s="6">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="O3" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="P3" s="5">
+        <v>126.5</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>1</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1300</v>
+      </c>
+      <c r="S3" s="7">
+        <v>1.2470000000000001</v>
+      </c>
+      <c r="T3" s="5">
+        <v>53</v>
+      </c>
+      <c r="U3" s="6">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="5">
+        <v>262081</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="H4" s="5">
+        <v>100</v>
+      </c>
+      <c r="I4" s="7">
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="J4" s="7">
+        <v>1.246</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="L4" s="7">
+        <v>147.77600000000001</v>
+      </c>
+      <c r="M4" s="9">
+        <v>124.6</v>
+      </c>
+      <c r="N4" s="6">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="O4" s="8">
+        <v>2.08</v>
+      </c>
+      <c r="P4" s="5">
+        <v>92.5</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1250</v>
+      </c>
+      <c r="S4" s="7">
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="T4" s="5">
+        <v>64</v>
+      </c>
+      <c r="U4" s="6">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="5">
+        <v>262083</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="H5" s="5">
+        <v>100</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1.036</v>
+      </c>
+      <c r="J5" s="7">
+        <v>1.581</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="L5" s="7">
+        <v>163.792</v>
+      </c>
+      <c r="M5" s="9">
+        <v>158.1</v>
+      </c>
+      <c r="N5" s="6">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="O5" s="8">
+        <v>2.63</v>
+      </c>
+      <c r="P5" s="5">
+        <v>102.5</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1100</v>
+      </c>
+      <c r="S5" s="7">
+        <v>1.036</v>
+      </c>
+      <c r="T5" s="5">
+        <v>64</v>
+      </c>
+      <c r="U5" s="6">
+        <v>5.8200000000000002E-2</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="19">
+        <v>300</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" s="19">
+        <v>321.60000000000002</v>
+      </c>
+      <c r="Q6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="X6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB6" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8560783-F1AE-41B7-817A-6D1BAC7508D9}">
   <sheetPr>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489DF3A1-E2A8-4F88-AA9B-B0EA80CC18EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A599DEF-7C0A-46A7-A6E0-8AA695F60268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="19" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="22" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051" sheetId="60" r:id="rId1"/>
@@ -36,6 +36,7 @@
     <sheet name="HARMONY EMBALAGENS 1080" sheetId="69" r:id="rId21"/>
     <sheet name="FAVINCO 1081" sheetId="70" r:id="rId22"/>
     <sheet name="PCBOX EMBALAGENS LTDA 1083" sheetId="71" r:id="rId23"/>
+    <sheet name="PCBOX EMBALAGENS LTDA - IPE EMB" sheetId="73" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023'!$A$1:$AB$10</definedName>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4378" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4564" uniqueCount="541">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1654,6 +1655,36 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA - PCBOX EMBALAGENS LTDA  —  OF: 001083</t>
+  </si>
+  <si>
+    <t>770x1520</t>
+  </si>
+  <si>
+    <t>1.599</t>
+  </si>
+  <si>
+    <t>770x1980</t>
+  </si>
+  <si>
+    <t>1154x1803</t>
+  </si>
+  <si>
+    <t>171x225x171</t>
+  </si>
+  <si>
+    <t>1.597</t>
+  </si>
+  <si>
+    <t>898x1403</t>
+  </si>
+  <si>
+    <t>172x534x172</t>
+  </si>
+  <si>
+    <t>1.596</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - PCBOX EMBALAGENS LTDA - IPE EMBALAGENS LTDA  —  OF: 001085</t>
   </si>
 </sst>
 </file>
@@ -1665,7 +1696,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1854,7 +1885,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2135,23 +2166,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2182,7 +2196,45 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2404,7 +2456,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="23.44140625" style="3" customWidth="1"/>
@@ -2435,93 +2487,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="102" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="112" t="s">
         <v>309</v>
       </c>
-      <c r="B1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="102" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="112" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2607,7 +2659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1">
       <c r="A3" s="38">
         <v>1</v>
       </c>
@@ -2693,7 +2745,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1">
       <c r="A4" s="38">
         <v>2</v>
       </c>
@@ -2779,7 +2831,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1">
       <c r="A5" s="38">
         <v>3</v>
       </c>
@@ -2865,7 +2917,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1">
       <c r="A6" s="38">
         <v>4</v>
       </c>
@@ -2951,7 +3003,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1">
       <c r="A7" s="38">
         <v>5</v>
       </c>
@@ -3037,7 +3089,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1">
       <c r="A8" s="38">
         <v>6</v>
       </c>
@@ -3123,7 +3175,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1">
       <c r="A9" s="38">
         <v>7</v>
       </c>
@@ -3209,7 +3261,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" ht="22.05" customHeight="1">
       <c r="A10" s="32" t="s">
         <v>27</v>
       </c>
@@ -3307,7 +3359,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6468C93-3B43-46CB-8998-F687C6A9465C}">
   <dimension ref="A1:AB9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
@@ -3339,93 +3391,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="102" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="112" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="102" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="112" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="52.8" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -3511,7 +3563,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28">
       <c r="A3" s="38">
         <v>1</v>
       </c>
@@ -3597,7 +3649,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28">
       <c r="A4" s="38">
         <v>2</v>
       </c>
@@ -3683,7 +3735,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28">
       <c r="A5" s="38">
         <v>3</v>
       </c>
@@ -3769,7 +3821,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28">
       <c r="A6" s="38">
         <v>4</v>
       </c>
@@ -3855,7 +3907,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28">
       <c r="A7" s="38">
         <v>5</v>
       </c>
@@ -3941,7 +3993,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28">
       <c r="A8" s="38">
         <v>6</v>
       </c>
@@ -4027,7 +4079,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28">
       <c r="A9" s="32" t="s">
         <v>27</v>
       </c>
@@ -4127,7 +4179,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -4158,93 +4210,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="117" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="107" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="117" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="48" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -4330,7 +4382,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -4416,7 +4468,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -4502,7 +4554,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -4588,7 +4640,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -4674,7 +4726,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -4760,7 +4812,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -4846,7 +4898,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -4932,7 +4984,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" ht="22.05" customHeight="1">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -5033,7 +5085,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" style="3" hidden="1" customWidth="1"/>
@@ -5064,93 +5116,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="114" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="104" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="114" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="53.4" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -5236,7 +5288,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1">
       <c r="A3" s="58">
         <v>1</v>
       </c>
@@ -5322,7 +5374,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1">
       <c r="A4" s="58">
         <v>2</v>
       </c>
@@ -5408,7 +5460,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
       <c r="A5" s="58">
         <v>1</v>
       </c>
@@ -5494,7 +5546,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
       <c r="A6" s="58">
         <v>2</v>
       </c>
@@ -5580,7 +5632,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
       <c r="A7" s="58">
         <v>3</v>
       </c>
@@ -5666,7 +5718,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
       <c r="A8" s="58">
         <v>4</v>
       </c>
@@ -5752,7 +5804,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
       <c r="A9" s="58">
         <v>5</v>
       </c>
@@ -5838,7 +5890,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
       <c r="A10" s="58">
         <v>6</v>
       </c>
@@ -5918,7 +5970,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
       <c r="A11" s="58">
         <v>7</v>
       </c>
@@ -6004,7 +6056,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
       <c r="A12" s="58">
         <v>8</v>
       </c>
@@ -6090,7 +6142,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
       <c r="A13" s="58">
         <v>9</v>
       </c>
@@ -6176,7 +6228,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
       <c r="A14" s="58">
         <v>10</v>
       </c>
@@ -6262,7 +6314,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
       <c r="A15" s="58">
         <v>11</v>
       </c>
@@ -6348,7 +6400,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
       <c r="A16" s="68" t="s">
         <v>27</v>
       </c>
@@ -6449,7 +6501,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="3" customWidth="1"/>
     <col min="2" max="2" width="11" style="3" customWidth="1"/>
@@ -6481,93 +6533,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="102" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="112" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="102" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="112" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -6653,7 +6705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1">
       <c r="A3" s="56">
         <v>1</v>
       </c>
@@ -6736,7 +6788,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1">
       <c r="A4" s="56">
         <v>2</v>
       </c>
@@ -6813,7 +6865,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="17" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" s="17" customFormat="1" ht="25.05" customHeight="1">
       <c r="A5" s="56">
         <v>3</v>
       </c>
@@ -6899,7 +6951,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28">
       <c r="A6" s="32" t="s">
         <v>27</v>
       </c>
@@ -7000,7 +7052,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="1.109375" style="1" hidden="1" customWidth="1"/>
@@ -7031,93 +7083,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="117" t="s">
         <v>343</v>
       </c>
-      <c r="B1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="107" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="117" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -7203,7 +7255,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="47" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" s="47" customFormat="1" ht="25.05" customHeight="1">
       <c r="A3" s="47">
         <v>1</v>
       </c>
@@ -7286,7 +7338,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1">
       <c r="A4" s="50">
         <v>2</v>
       </c>
@@ -7372,7 +7424,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1">
       <c r="A5" s="50">
         <v>3</v>
       </c>
@@ -7458,7 +7510,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1">
       <c r="A6" s="50">
         <v>4</v>
       </c>
@@ -7544,7 +7596,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1">
       <c r="A7" s="50">
         <v>5</v>
       </c>
@@ -7630,7 +7682,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1">
       <c r="A8" s="50">
         <v>6</v>
       </c>
@@ -7716,7 +7768,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1">
       <c r="A9" s="50">
         <v>7</v>
       </c>
@@ -7802,7 +7854,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" ht="25.05" customHeight="1">
       <c r="A10" s="50">
         <v>8</v>
       </c>
@@ -7888,7 +7940,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1">
       <c r="A11" s="50">
         <v>9</v>
       </c>
@@ -7974,7 +8026,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" ht="25.05" customHeight="1">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -8075,7 +8127,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4.109375" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
@@ -8106,93 +8158,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="102" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="112" t="s">
         <v>364</v>
       </c>
-      <c r="B1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="102" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="112" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="44.4" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -8278,7 +8330,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1">
       <c r="A3" s="38">
         <v>1</v>
       </c>
@@ -8364,7 +8416,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1">
       <c r="A4" s="38">
         <v>2</v>
       </c>
@@ -8450,7 +8502,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1">
       <c r="A5" s="38">
         <v>3</v>
       </c>
@@ -8536,7 +8588,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1">
       <c r="A6" s="38">
         <v>4</v>
       </c>
@@ -8622,7 +8674,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1">
       <c r="A7" s="38">
         <v>5</v>
       </c>
@@ -8708,7 +8760,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1">
       <c r="A8" s="32" t="s">
         <v>27</v>
       </c>
@@ -8809,7 +8861,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" style="3" hidden="1" customWidth="1"/>
@@ -8841,93 +8893,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="114" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="104" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="114" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="62.4" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -9013,7 +9065,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -9099,7 +9151,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -9185,7 +9237,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -9271,7 +9323,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -9357,7 +9409,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -9443,7 +9495,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -9529,7 +9581,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -9615,7 +9667,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" ht="25.05" customHeight="1">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -9701,7 +9753,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1">
       <c r="A11" s="18" t="s">
         <v>27</v>
       </c>
@@ -9799,7 +9851,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{823A5C13-D88D-428D-8A9C-6D7FD6C65A08}">
   <dimension ref="A1:AB20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -9830,93 +9882,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="108" t="s">
+    <row r="1" spans="1:28" s="21" customFormat="1" ht="18" customHeight="1">
+      <c r="A1" s="118" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="108" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" s="21" customFormat="1" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="118" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" s="21" customFormat="1" ht="60.6" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -10002,7 +10054,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" s="21" customFormat="1">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -10088,7 +10140,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" s="21" customFormat="1">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -10174,7 +10226,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" s="21" customFormat="1">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -10260,7 +10312,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" s="21" customFormat="1">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -10346,7 +10398,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" s="21" customFormat="1">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -10432,7 +10484,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" s="21" customFormat="1">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -10518,7 +10570,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" s="21" customFormat="1">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -10604,7 +10656,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" s="21" customFormat="1">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -10690,7 +10742,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" s="21" customFormat="1">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -10776,7 +10828,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" s="21" customFormat="1">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -10862,7 +10914,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" s="21" customFormat="1">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -10948,7 +11000,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" s="21" customFormat="1">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -11034,7 +11086,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" s="21" customFormat="1">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -11120,7 +11172,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" s="21" customFormat="1">
       <c r="A16" s="5">
         <v>14</v>
       </c>
@@ -11206,7 +11258,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="17" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" s="21" customFormat="1">
       <c r="A17" s="5">
         <v>15</v>
       </c>
@@ -11292,7 +11344,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="18" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" s="21" customFormat="1">
       <c r="A18" s="5">
         <v>16</v>
       </c>
@@ -11378,7 +11430,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="19" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" s="21" customFormat="1">
       <c r="A19" s="5">
         <v>17</v>
       </c>
@@ -11464,7 +11516,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="20" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" s="21" customFormat="1">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -11564,7 +11616,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -11597,93 +11649,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="117" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="107" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="117" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="60" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -11769,7 +11821,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" customFormat="1" ht="21.6" customHeight="1">
       <c r="A3" s="83">
         <v>1</v>
       </c>
@@ -11855,7 +11907,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1">
       <c r="A4" s="76">
         <v>1</v>
       </c>
@@ -11941,7 +11993,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1">
       <c r="A5" s="70">
         <v>2</v>
       </c>
@@ -12027,7 +12079,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1">
       <c r="A6" s="83">
         <v>2</v>
       </c>
@@ -12113,7 +12165,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1">
       <c r="A7" s="70">
         <v>3</v>
       </c>
@@ -12199,7 +12251,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1">
       <c r="A8" s="5">
         <v>1</v>
       </c>
@@ -12285,7 +12337,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1">
       <c r="A9" s="83">
         <v>3</v>
       </c>
@@ -12371,7 +12423,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" ht="22.8" customHeight="1">
       <c r="A10" s="83">
         <v>4</v>
       </c>
@@ -12457,7 +12509,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -12555,7 +12607,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1FA60D2-9EE8-4466-8FFC-C8F46CF7934D}">
   <dimension ref="A1:AB23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -12586,93 +12638,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="108" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="118" t="s">
         <v>489</v>
       </c>
-      <c r="B1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="108" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="118" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -12758,7 +12810,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -12844,7 +12896,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -12930,7 +12982,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -13016,7 +13068,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -13102,7 +13154,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -13188,7 +13240,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -13274,7 +13326,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -13360,7 +13412,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -13446,7 +13498,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -13532,7 +13584,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -13618,7 +13670,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -13704,7 +13756,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -13790,7 +13842,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -13876,7 +13928,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28">
       <c r="A16" s="5">
         <v>14</v>
       </c>
@@ -13962,7 +14014,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28">
       <c r="A17" s="5">
         <v>15</v>
       </c>
@@ -14048,7 +14100,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28">
       <c r="A18" s="5">
         <v>16</v>
       </c>
@@ -14134,7 +14186,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28">
       <c r="A19" s="5">
         <v>17</v>
       </c>
@@ -14220,7 +14272,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28">
       <c r="A20" s="5">
         <v>18</v>
       </c>
@@ -14306,7 +14358,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28">
       <c r="A21" s="5">
         <v>19</v>
       </c>
@@ -14392,7 +14444,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28">
       <c r="A22" s="5">
         <v>20</v>
       </c>
@@ -14478,7 +14530,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28">
       <c r="A23" s="19" t="s">
         <v>27</v>
       </c>
@@ -14578,7 +14630,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
@@ -14609,93 +14661,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="103" t="s">
+    <row r="1" spans="1:28" ht="18.600000000000001" customHeight="1">
+      <c r="A1" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="103" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="113" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -14781,7 +14833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -14867,7 +14919,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -14953,7 +15005,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -15039,7 +15091,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -15125,7 +15177,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -15211,7 +15263,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -15297,7 +15349,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -15383,7 +15435,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -15481,7 +15533,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6DECCF-0481-438A-8BDD-F0275CF2BE70}">
   <dimension ref="A1:AB4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -15513,7 +15565,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
       <c r="A1" s="119" t="s">
         <v>493</v>
       </c>
@@ -15599,7 +15651,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" ht="52.8" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -15685,175 +15737,175 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="116">
+    <row r="3" spans="1:28" ht="19.8" customHeight="1">
+      <c r="A3" s="109">
         <v>1</v>
       </c>
-      <c r="B3" s="118" t="s">
+      <c r="B3" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="116" t="s">
+      <c r="C3" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="109" t="s">
         <v>492</v>
       </c>
-      <c r="E3" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="116">
+      <c r="E3" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="109">
         <v>262067</v>
       </c>
-      <c r="G3" s="116" t="s">
+      <c r="G3" s="109" t="s">
         <v>491</v>
       </c>
-      <c r="H3" s="116">
+      <c r="H3" s="109">
         <v>340</v>
       </c>
-      <c r="I3" s="117">
+      <c r="I3" s="110">
         <v>0.97699999999999998</v>
       </c>
-      <c r="J3" s="117">
+      <c r="J3" s="110">
         <v>2.06</v>
       </c>
-      <c r="K3" s="116" t="s">
+      <c r="K3" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="113">
+      <c r="L3" s="106">
         <v>684.29100000000005</v>
       </c>
-      <c r="M3" s="115">
+      <c r="M3" s="108">
         <v>700.4</v>
       </c>
-      <c r="N3" s="112">
+      <c r="N3" s="105">
         <v>0.1946</v>
       </c>
-      <c r="O3" s="114">
+      <c r="O3" s="107">
         <v>11.67</v>
       </c>
-      <c r="P3" s="111">
+      <c r="P3" s="104">
         <v>405.8</v>
       </c>
-      <c r="Q3" s="111">
+      <c r="Q3" s="104">
         <v>1</v>
       </c>
-      <c r="R3" s="111">
+      <c r="R3" s="104">
         <v>1000</v>
       </c>
-      <c r="S3" s="113">
+      <c r="S3" s="106">
         <v>0.97699999999999998</v>
       </c>
-      <c r="T3" s="111">
+      <c r="T3" s="104">
         <v>23</v>
       </c>
-      <c r="U3" s="112">
+      <c r="U3" s="105">
         <v>2.3E-2</v>
       </c>
-      <c r="V3" s="111" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="111" t="s">
+      <c r="V3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="X3" s="111" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="111" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z3" s="111" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA3" s="111" t="s">
+      <c r="X3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="AB3" s="111" t="s">
+      <c r="AB3" s="104" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="110">
+    <row r="4" spans="1:28">
+      <c r="A4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="103">
         <v>340</v>
       </c>
-      <c r="I4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="109">
+      <c r="I4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="102">
         <v>405.8</v>
       </c>
-      <c r="Q4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="R4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="S4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="T4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="U4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="V4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="W4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="X4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB4" s="109" t="s">
+      <c r="Q4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="S4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="U4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="X4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB4" s="102" t="s">
         <v>27</v>
       </c>
     </row>
@@ -15868,7 +15920,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{819F2E85-837E-49CE-91A8-B709D04980B6}">
   <dimension ref="A1:AB15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -15900,93 +15952,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="108" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="118" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="108" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="118" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="55.2" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -16072,7 +16124,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -16158,7 +16210,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -16244,7 +16296,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -16330,7 +16382,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -16416,7 +16468,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -16502,7 +16554,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -16588,7 +16640,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -16674,7 +16726,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -16760,7 +16812,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -16846,7 +16898,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -16932,7 +16984,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -17018,7 +17070,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -17104,7 +17156,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -17201,7 +17253,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C91923-7AE7-4461-9C2E-05FE2CED0119}">
   <dimension ref="A1:AB4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -17233,7 +17285,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
       <c r="A1" s="119" t="s">
         <v>523</v>
       </c>
@@ -17319,7 +17371,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" ht="50.4" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -17405,175 +17457,175 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" s="116">
+    <row r="3" spans="1:28">
+      <c r="A3" s="109">
         <v>1</v>
       </c>
-      <c r="B3" s="118" t="s">
+      <c r="B3" s="111" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="116" t="s">
+      <c r="C3" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="109" t="s">
         <v>492</v>
       </c>
-      <c r="E3" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="116">
+      <c r="E3" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="109">
         <v>262079</v>
       </c>
-      <c r="G3" s="116" t="s">
+      <c r="G3" s="109" t="s">
         <v>522</v>
       </c>
-      <c r="H3" s="116">
+      <c r="H3" s="109">
         <v>530</v>
       </c>
-      <c r="I3" s="117">
+      <c r="I3" s="110">
         <v>0.58499999999999996</v>
       </c>
-      <c r="J3" s="117">
+      <c r="J3" s="110">
         <v>1.61</v>
       </c>
-      <c r="K3" s="116" t="s">
+      <c r="K3" s="109" t="s">
         <v>521</v>
       </c>
-      <c r="L3" s="113">
+      <c r="L3" s="106">
         <v>499.18</v>
       </c>
-      <c r="M3" s="115">
+      <c r="M3" s="108">
         <v>426.7</v>
       </c>
-      <c r="N3" s="112">
+      <c r="N3" s="105">
         <v>5.9299999999999999E-2</v>
       </c>
-      <c r="O3" s="114">
+      <c r="O3" s="107">
         <v>3.56</v>
       </c>
-      <c r="P3" s="111">
+      <c r="P3" s="104">
         <v>172.2</v>
       </c>
-      <c r="Q3" s="111">
+      <c r="Q3" s="104">
         <v>2</v>
       </c>
-      <c r="R3" s="111">
+      <c r="R3" s="104">
         <v>1200</v>
       </c>
-      <c r="S3" s="113">
+      <c r="S3" s="106">
         <v>1.17</v>
       </c>
-      <c r="T3" s="111">
+      <c r="T3" s="104">
         <v>30</v>
       </c>
-      <c r="U3" s="112">
+      <c r="U3" s="105">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="V3" s="111" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="111" t="s">
-        <v>28</v>
-      </c>
-      <c r="X3" s="111" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="111" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z3" s="111" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA3" s="111" t="s">
+      <c r="V3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="AB3" s="111" t="s">
+      <c r="AB3" s="104" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="110">
+    <row r="4" spans="1:28">
+      <c r="A4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="103">
         <v>530</v>
       </c>
-      <c r="I4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="109">
+      <c r="I4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="102">
         <v>172.2</v>
       </c>
-      <c r="Q4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="R4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="S4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="T4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="U4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="V4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="W4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="X4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB4" s="109" t="s">
+      <c r="Q4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="S4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="U4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="X4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB4" s="102" t="s">
         <v>27</v>
       </c>
     </row>
@@ -17588,7 +17640,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03314351-54CF-4392-B40B-54F11BAD5EE2}">
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -17619,93 +17671,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="108" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="118" t="s">
         <v>530</v>
       </c>
-      <c r="B1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="108" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="118" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="63" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -17791,7 +17843,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -17877,7 +17929,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -17963,7 +18015,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -18049,7 +18101,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28">
       <c r="A6" s="19" t="s">
         <v>27</v>
       </c>
@@ -18140,6 +18192,999 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCFE926-707C-4947-AB95-1A017E0FBDCA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AB11"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="8.77734375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="3.21875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.33203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="8.109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="8.44140625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.109375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7.33203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.88671875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="3.77734375" style="1" customWidth="1"/>
+    <col min="28" max="28" width="11" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="113" t="s">
+        <v>540</v>
+      </c>
+      <c r="B1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="113" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="39.6" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="25.05" customHeight="1">
+      <c r="A3" s="120">
+        <v>1</v>
+      </c>
+      <c r="B3" s="121" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="120" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="120" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="120">
+        <v>262089</v>
+      </c>
+      <c r="G3" s="120" t="s">
+        <v>526</v>
+      </c>
+      <c r="H3" s="120">
+        <v>100</v>
+      </c>
+      <c r="I3" s="122">
+        <v>1.2470000000000001</v>
+      </c>
+      <c r="J3" s="122">
+        <v>1.621</v>
+      </c>
+      <c r="K3" s="120" t="s">
+        <v>529</v>
+      </c>
+      <c r="L3" s="122">
+        <v>202.13900000000001</v>
+      </c>
+      <c r="M3" s="123">
+        <v>162.1</v>
+      </c>
+      <c r="N3" s="124">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="O3" s="125">
+        <v>2.7</v>
+      </c>
+      <c r="P3" s="120">
+        <v>122.5</v>
+      </c>
+      <c r="Q3" s="120">
+        <v>1</v>
+      </c>
+      <c r="R3" s="120">
+        <v>1300</v>
+      </c>
+      <c r="S3" s="122">
+        <v>1.2470000000000001</v>
+      </c>
+      <c r="T3" s="120">
+        <v>53</v>
+      </c>
+      <c r="U3" s="124">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="V3" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="W3" s="120" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z3" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA3" s="120" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB3" s="120" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+      <c r="A4" s="120">
+        <v>2</v>
+      </c>
+      <c r="B4" s="121" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="120" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="120" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="120">
+        <v>262088</v>
+      </c>
+      <c r="G4" s="120" t="s">
+        <v>526</v>
+      </c>
+      <c r="H4" s="120">
+        <v>100</v>
+      </c>
+      <c r="I4" s="122">
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="J4" s="122">
+        <v>1.246</v>
+      </c>
+      <c r="K4" s="120" t="s">
+        <v>527</v>
+      </c>
+      <c r="L4" s="122">
+        <v>147.77600000000001</v>
+      </c>
+      <c r="M4" s="123">
+        <v>124.6</v>
+      </c>
+      <c r="N4" s="124">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="O4" s="125">
+        <v>2.08</v>
+      </c>
+      <c r="P4" s="120">
+        <v>89.6</v>
+      </c>
+      <c r="Q4" s="120">
+        <v>1</v>
+      </c>
+      <c r="R4" s="120">
+        <v>1250</v>
+      </c>
+      <c r="S4" s="122">
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="T4" s="120">
+        <v>64</v>
+      </c>
+      <c r="U4" s="124">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="V4" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="W4" s="120" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y4" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z4" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA4" s="120" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB4" s="120" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+      <c r="A5" s="120">
+        <v>3</v>
+      </c>
+      <c r="B5" s="121" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="120" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="120" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="120">
+        <v>262090</v>
+      </c>
+      <c r="G5" s="120" t="s">
+        <v>526</v>
+      </c>
+      <c r="H5" s="120">
+        <v>100</v>
+      </c>
+      <c r="I5" s="122">
+        <v>1.036</v>
+      </c>
+      <c r="J5" s="122">
+        <v>1.581</v>
+      </c>
+      <c r="K5" s="120" t="s">
+        <v>525</v>
+      </c>
+      <c r="L5" s="122">
+        <v>163.792</v>
+      </c>
+      <c r="M5" s="123">
+        <v>158.1</v>
+      </c>
+      <c r="N5" s="124">
+        <v>4.3900000000000002E-2</v>
+      </c>
+      <c r="O5" s="125">
+        <v>2.63</v>
+      </c>
+      <c r="P5" s="120">
+        <v>99.3</v>
+      </c>
+      <c r="Q5" s="120">
+        <v>1</v>
+      </c>
+      <c r="R5" s="120">
+        <v>1100</v>
+      </c>
+      <c r="S5" s="122">
+        <v>1.036</v>
+      </c>
+      <c r="T5" s="120">
+        <v>64</v>
+      </c>
+      <c r="U5" s="124">
+        <v>5.8200000000000002E-2</v>
+      </c>
+      <c r="V5" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="W5" s="120" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y5" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z5" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA5" s="120" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5" s="120" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+      <c r="A6" s="120">
+        <v>4</v>
+      </c>
+      <c r="B6" s="121" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="120" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="120" t="s">
+        <v>492</v>
+      </c>
+      <c r="E6" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="120">
+        <v>262094</v>
+      </c>
+      <c r="G6" s="120" t="s">
+        <v>539</v>
+      </c>
+      <c r="H6" s="120">
+        <v>1500</v>
+      </c>
+      <c r="I6" s="122">
+        <v>0.878</v>
+      </c>
+      <c r="J6" s="122">
+        <v>1.383</v>
+      </c>
+      <c r="K6" s="120" t="s">
+        <v>538</v>
+      </c>
+      <c r="L6" s="122">
+        <v>1821.4110000000001</v>
+      </c>
+      <c r="M6" s="123">
+        <v>2074.5</v>
+      </c>
+      <c r="N6" s="124">
+        <v>0.57630000000000003</v>
+      </c>
+      <c r="O6" s="125">
+        <v>34.58</v>
+      </c>
+      <c r="P6" s="120">
+        <v>1103.8</v>
+      </c>
+      <c r="Q6" s="120">
+        <v>1</v>
+      </c>
+      <c r="R6" s="120">
+        <v>900</v>
+      </c>
+      <c r="S6" s="122">
+        <v>0.878</v>
+      </c>
+      <c r="T6" s="120">
+        <v>22</v>
+      </c>
+      <c r="U6" s="124">
+        <v>2.4400000000000002E-2</v>
+      </c>
+      <c r="V6" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="W6" s="120" t="s">
+        <v>40</v>
+      </c>
+      <c r="X6" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y6" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z6" s="120" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA6" s="120" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB6" s="120" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="25.05" customHeight="1">
+      <c r="A7" s="120">
+        <v>5</v>
+      </c>
+      <c r="B7" s="121" t="s">
+        <v>279</v>
+      </c>
+      <c r="C7" s="120" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="120" t="s">
+        <v>492</v>
+      </c>
+      <c r="E7" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="120">
+        <v>262091</v>
+      </c>
+      <c r="G7" s="120" t="s">
+        <v>532</v>
+      </c>
+      <c r="H7" s="120">
+        <v>750</v>
+      </c>
+      <c r="I7" s="122">
+        <v>0.75</v>
+      </c>
+      <c r="J7" s="122">
+        <v>0.49</v>
+      </c>
+      <c r="K7" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="122">
+        <v>275.625</v>
+      </c>
+      <c r="M7" s="123">
+        <v>183.8</v>
+      </c>
+      <c r="N7" s="124">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="O7" s="125">
+        <v>1.53</v>
+      </c>
+      <c r="P7" s="120">
+        <v>117.8</v>
+      </c>
+      <c r="Q7" s="120">
+        <v>2</v>
+      </c>
+      <c r="R7" s="120">
+        <v>1550</v>
+      </c>
+      <c r="S7" s="122">
+        <v>1.5</v>
+      </c>
+      <c r="T7" s="120">
+        <v>50</v>
+      </c>
+      <c r="U7" s="124">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="V7" s="120" t="s">
+        <v>42</v>
+      </c>
+      <c r="W7" s="120" t="s">
+        <v>42</v>
+      </c>
+      <c r="X7" s="120" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y7" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="120" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB7" s="120" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+      <c r="A8" s="120">
+        <v>6</v>
+      </c>
+      <c r="B8" s="121" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="120" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="120" t="s">
+        <v>492</v>
+      </c>
+      <c r="E8" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="120">
+        <v>262092</v>
+      </c>
+      <c r="G8" s="120" t="s">
+        <v>532</v>
+      </c>
+      <c r="H8" s="120">
+        <v>1250</v>
+      </c>
+      <c r="I8" s="122">
+        <v>0.75</v>
+      </c>
+      <c r="J8" s="122">
+        <v>0.75</v>
+      </c>
+      <c r="K8" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="122">
+        <v>703.125</v>
+      </c>
+      <c r="M8" s="123">
+        <v>468.8</v>
+      </c>
+      <c r="N8" s="124">
+        <v>6.5100000000000005E-2</v>
+      </c>
+      <c r="O8" s="125">
+        <v>3.91</v>
+      </c>
+      <c r="P8" s="120">
+        <v>300.60000000000002</v>
+      </c>
+      <c r="Q8" s="120">
+        <v>2</v>
+      </c>
+      <c r="R8" s="120">
+        <v>1550</v>
+      </c>
+      <c r="S8" s="122">
+        <v>1.5</v>
+      </c>
+      <c r="T8" s="120">
+        <v>50</v>
+      </c>
+      <c r="U8" s="124">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="V8" s="120" t="s">
+        <v>42</v>
+      </c>
+      <c r="W8" s="120" t="s">
+        <v>42</v>
+      </c>
+      <c r="X8" s="120" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y8" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="120" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB8" s="120" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" ht="25.05" customHeight="1">
+      <c r="A9" s="120">
+        <v>7</v>
+      </c>
+      <c r="B9" s="121" t="s">
+        <v>279</v>
+      </c>
+      <c r="C9" s="120" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="120" t="s">
+        <v>492</v>
+      </c>
+      <c r="E9" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="120">
+        <v>262093</v>
+      </c>
+      <c r="G9" s="120" t="s">
+        <v>532</v>
+      </c>
+      <c r="H9" s="120">
+        <v>1250</v>
+      </c>
+      <c r="I9" s="122">
+        <v>0.75</v>
+      </c>
+      <c r="J9" s="122">
+        <v>0.75</v>
+      </c>
+      <c r="K9" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="122">
+        <v>703.125</v>
+      </c>
+      <c r="M9" s="123">
+        <v>468.8</v>
+      </c>
+      <c r="N9" s="124">
+        <v>6.5100000000000005E-2</v>
+      </c>
+      <c r="O9" s="125">
+        <v>3.91</v>
+      </c>
+      <c r="P9" s="120">
+        <v>300.60000000000002</v>
+      </c>
+      <c r="Q9" s="120">
+        <v>2</v>
+      </c>
+      <c r="R9" s="120">
+        <v>1550</v>
+      </c>
+      <c r="S9" s="122">
+        <v>1.5</v>
+      </c>
+      <c r="T9" s="120">
+        <v>50</v>
+      </c>
+      <c r="U9" s="124">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="V9" s="120" t="s">
+        <v>42</v>
+      </c>
+      <c r="W9" s="120" t="s">
+        <v>42</v>
+      </c>
+      <c r="X9" s="120" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y9" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="120" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB9" s="120" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" ht="25.05" customHeight="1">
+      <c r="A10" s="120">
+        <v>8</v>
+      </c>
+      <c r="B10" s="121" t="s">
+        <v>279</v>
+      </c>
+      <c r="C10" s="120" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="120" t="s">
+        <v>492</v>
+      </c>
+      <c r="E10" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="120">
+        <v>262095</v>
+      </c>
+      <c r="G10" s="120" t="s">
+        <v>536</v>
+      </c>
+      <c r="H10" s="120">
+        <v>1200</v>
+      </c>
+      <c r="I10" s="122">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="J10" s="122">
+        <v>1.7829999999999999</v>
+      </c>
+      <c r="K10" s="120" t="s">
+        <v>535</v>
+      </c>
+      <c r="L10" s="122">
+        <v>1213.153</v>
+      </c>
+      <c r="M10" s="123">
+        <v>1069.8</v>
+      </c>
+      <c r="N10" s="124">
+        <v>0.14860000000000001</v>
+      </c>
+      <c r="O10" s="125">
+        <v>8.91</v>
+      </c>
+      <c r="P10" s="120">
+        <v>418.5</v>
+      </c>
+      <c r="Q10" s="120">
+        <v>2</v>
+      </c>
+      <c r="R10" s="120">
+        <v>1200</v>
+      </c>
+      <c r="S10" s="122">
+        <v>1.1339999999999999</v>
+      </c>
+      <c r="T10" s="120">
+        <v>66</v>
+      </c>
+      <c r="U10" s="124">
+        <v>5.5E-2</v>
+      </c>
+      <c r="V10" s="120" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="120" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="120" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="120" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB10" s="120" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+      <c r="A11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="126">
+        <v>6250</v>
+      </c>
+      <c r="I11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="126">
+        <v>2552.6</v>
+      </c>
+      <c r="Q11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="R11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="S11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="T11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="U11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="V11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="W11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="X11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA11" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB11" s="126" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.5" top="1.33" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup scale="82" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18149,7 +19194,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4.21875" style="3" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="3" customWidth="1"/>
@@ -18180,93 +19225,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="114" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="105" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="115" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="41.4" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -18352,7 +19397,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="12">
         <v>1</v>
       </c>
@@ -18438,7 +19483,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A4" s="12">
         <v>2</v>
       </c>
@@ -18524,7 +19569,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A5" s="12">
         <v>3</v>
       </c>
@@ -18610,7 +19655,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A6" s="12">
         <v>4</v>
       </c>
@@ -18696,7 +19741,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A7" s="12">
         <v>5</v>
       </c>
@@ -18782,7 +19827,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A8" s="12">
         <v>6</v>
       </c>
@@ -18868,7 +19913,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A9" s="12">
         <v>7</v>
       </c>
@@ -18954,7 +19999,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A10" s="12">
         <v>8</v>
       </c>
@@ -19040,7 +20085,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A11" s="12">
         <v>9</v>
       </c>
@@ -19126,7 +20171,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A12" s="12">
         <v>10</v>
       </c>
@@ -19212,7 +20257,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A13" s="12">
         <v>11</v>
       </c>
@@ -19298,7 +20343,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A14" s="12">
         <v>12</v>
       </c>
@@ -19384,7 +20429,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A15" s="12">
         <v>13</v>
       </c>
@@ -19470,7 +20515,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A16" s="12">
         <v>14</v>
       </c>
@@ -19556,7 +20601,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A17" s="12">
         <v>15</v>
       </c>
@@ -19642,7 +20687,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A18" s="12">
         <v>16</v>
       </c>
@@ -19728,7 +20773,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A19" s="12">
         <v>17</v>
       </c>
@@ -19814,7 +20859,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A20" s="12">
         <v>18</v>
       </c>
@@ -19900,7 +20945,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A21" s="12">
         <v>19</v>
       </c>
@@ -19986,7 +21031,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A22" s="12">
         <v>20</v>
       </c>
@@ -20072,7 +21117,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A23" s="12">
         <v>21</v>
       </c>
@@ -20158,7 +21203,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A24" s="12">
         <v>22</v>
       </c>
@@ -20244,7 +21289,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
       <c r="A25" s="18" t="s">
         <v>27</v>
       </c>
@@ -20345,7 +21390,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.88671875" style="3" customWidth="1"/>
@@ -20376,93 +21421,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="105" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="115" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="105" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="115" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -20548,7 +21593,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -20634,7 +21679,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -20720,7 +21765,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -20806,7 +21851,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1">
       <c r="A6" s="18" t="s">
         <v>27</v>
       </c>
@@ -20907,7 +21952,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="11.77734375" style="3" hidden="1" customWidth="1"/>
@@ -20938,93 +21983,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="114" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="104" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="114" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="39.6" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -21110,7 +22155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -21196,7 +22241,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -21282,7 +22327,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -21368,7 +22413,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -21454,7 +22499,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -21540,7 +22585,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -21626,7 +22671,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -21712,7 +22757,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" ht="22.05" customHeight="1">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -21798,7 +22843,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" ht="22.05" customHeight="1">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -21884,7 +22929,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" ht="22.05" customHeight="1">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -21970,7 +23015,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" ht="22.05" customHeight="1">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -22056,7 +23101,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" ht="22.05" customHeight="1">
       <c r="A14" s="18" t="s">
         <v>27</v>
       </c>
@@ -22154,7 +23199,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BE450D-ABF8-4C4B-88DF-0F4B0CF61565}">
   <dimension ref="A1:AB9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
@@ -22185,93 +23230,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="116" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="106" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="106" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="116" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="46.8" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -22357,7 +23402,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28">
       <c r="A3" s="23">
         <v>1</v>
       </c>
@@ -22443,7 +23488,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28">
       <c r="A4" s="23">
         <v>2</v>
       </c>
@@ -22527,7 +23572,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28">
       <c r="A5" s="23">
         <v>3</v>
       </c>
@@ -22613,7 +23658,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28">
       <c r="A6" s="22" t="s">
         <v>27</v>
       </c>
@@ -22699,7 +23744,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28">
       <c r="G9" s="46"/>
     </row>
   </sheetData>
@@ -22717,7 +23762,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="91" customWidth="1"/>
     <col min="2" max="2" width="9.44140625" style="1" hidden="1" customWidth="1"/>
@@ -22749,93 +23794,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="117" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="107" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="107" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="117" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="117" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="52.2" customHeight="1">
       <c r="A2" s="88" t="s">
         <v>0</v>
       </c>
@@ -22921,7 +23966,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="101" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" s="101" customFormat="1" ht="19.8" customHeight="1">
       <c r="A3" s="93">
         <v>1</v>
       </c>
@@ -23001,7 +24046,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1">
       <c r="A4" s="47">
         <v>2</v>
       </c>
@@ -23087,7 +24132,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1">
       <c r="A5" s="47">
         <v>3</v>
       </c>
@@ -23173,7 +24218,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
       <c r="A6" s="93">
         <v>4</v>
       </c>
@@ -23259,7 +24304,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
       <c r="A7" s="93">
         <v>5</v>
       </c>
@@ -23345,7 +24390,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
       <c r="A8" s="93">
         <v>6</v>
       </c>
@@ -23431,7 +24476,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
       <c r="A9" s="93">
         <v>7</v>
       </c>
@@ -23517,7 +24562,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
       <c r="A10" s="93">
         <v>8</v>
       </c>
@@ -23603,7 +24648,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1">
       <c r="A11" s="90" t="s">
         <v>27</v>
       </c>
@@ -23704,7 +24749,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="10.77734375" style="3" hidden="1" customWidth="1"/>
@@ -23736,93 +24781,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="114" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="104" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="114" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="114" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="52.8" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -23908,7 +24953,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" customFormat="1" ht="22.05" customHeight="1">
       <c r="A3" s="29">
         <v>1</v>
       </c>
@@ -23992,7 +25037,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:28" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" customFormat="1" ht="22.05" customHeight="1">
       <c r="A4" s="29">
         <v>2</v>
       </c>
@@ -24076,7 +25121,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1">
       <c r="A5" s="29">
         <v>3</v>
       </c>
@@ -24162,7 +25207,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1">
       <c r="A6" s="29">
         <v>4</v>
       </c>
@@ -24248,7 +25293,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1">
       <c r="A7" s="29">
         <v>5</v>
       </c>
@@ -24334,7 +25379,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1">
       <c r="A8" s="29">
         <v>6</v>
       </c>
@@ -24420,7 +25465,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1">
       <c r="A9" s="18" t="s">
         <v>27</v>
       </c>
@@ -24506,7 +25551,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:28" ht="22.05" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AB1"/>
@@ -24522,7 +25567,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.77734375" style="1" customWidth="1"/>
@@ -24553,93 +25598,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="103" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="113" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="103" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="113" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="54" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -24725,7 +25770,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="47" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" s="47" customFormat="1" ht="22.2" customHeight="1">
       <c r="A3" s="47">
         <v>1</v>
       </c>
@@ -24802,7 +25847,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
       <c r="A4" s="47">
         <v>2</v>
       </c>
@@ -24888,7 +25933,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
       <c r="A5" s="47">
         <v>3</v>
       </c>
@@ -24974,7 +26019,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
       <c r="A6" s="47">
         <v>4</v>
       </c>
@@ -25060,7 +26105,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
       <c r="A7" s="47">
         <v>5</v>
       </c>
@@ -25146,7 +26191,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
       <c r="A8" s="47">
         <v>6</v>
       </c>
@@ -25232,7 +26277,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
       <c r="A9" s="47">
         <v>7</v>
       </c>
@@ -25318,7 +26363,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
       <c r="A10" s="47">
         <v>8</v>
       </c>
@@ -25404,7 +26449,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
       <c r="A11" s="47">
         <v>9</v>
       </c>
@@ -25490,7 +26535,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
       <c r="A12" s="47">
         <v>10</v>
       </c>
@@ -25576,7 +26621,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
       <c r="A13" s="47">
         <v>11</v>
       </c>
@@ -25656,7 +26701,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
       <c r="A14" s="19" t="s">
         <v>27</v>
       </c>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A599DEF-7C0A-46A7-A6E0-8AA695F60268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919D25F4-F08A-40A8-8DFB-2E62B810478F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="22" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="22" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051" sheetId="60" r:id="rId1"/>
@@ -35,8 +35,7 @@
     <sheet name="ABAPEL 1079" sheetId="68" r:id="rId20"/>
     <sheet name="HARMONY EMBALAGENS 1080" sheetId="69" r:id="rId21"/>
     <sheet name="FAVINCO 1081" sheetId="70" r:id="rId22"/>
-    <sheet name="PCBOX EMBALAGENS LTDA 1083" sheetId="71" r:id="rId23"/>
-    <sheet name="PCBOX EMBALAGENS LTDA - IPE EMB" sheetId="73" r:id="rId24"/>
+    <sheet name="PCBOX EMBALAGENS LTDA - IPE EMB" sheetId="73" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023'!$A$1:$AB$10</definedName>
@@ -62,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4564" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4443" uniqueCount="540">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1652,9 +1651,6 @@
   </si>
   <si>
     <t>235x154x469x154x235</t>
-  </si>
-  <si>
-    <t>PROGRAMAÇÃO ONDULADEIRA - PCBOX EMBALAGENS LTDA  —  OF: 001083</t>
   </si>
   <si>
     <t>770x1520</t>
@@ -17638,564 +17634,6 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03314351-54CF-4392-B40B-54F11BAD5EE2}">
-  <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="4.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.77734375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="5.88671875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="4" style="1" customWidth="1"/>
-    <col min="18" max="18" width="6.109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="6.44140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="22" max="23" width="8.44140625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="8" style="1" customWidth="1"/>
-    <col min="25" max="25" width="8.33203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="8" style="1" customWidth="1"/>
-    <col min="27" max="27" width="3.6640625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="10.88671875" style="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="118" t="s">
-        <v>530</v>
-      </c>
-      <c r="B1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="118" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="63" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="5">
-        <v>262082</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="H3" s="5">
-        <v>100</v>
-      </c>
-      <c r="I3" s="7">
-        <v>1.2470000000000001</v>
-      </c>
-      <c r="J3" s="7">
-        <v>1.621</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="L3" s="7">
-        <v>202.13900000000001</v>
-      </c>
-      <c r="M3" s="9">
-        <v>162.1</v>
-      </c>
-      <c r="N3" s="6">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="O3" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="P3" s="5">
-        <v>126.5</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>1</v>
-      </c>
-      <c r="R3" s="5">
-        <v>1300</v>
-      </c>
-      <c r="S3" s="7">
-        <v>1.2470000000000001</v>
-      </c>
-      <c r="T3" s="5">
-        <v>53</v>
-      </c>
-      <c r="U3" s="6">
-        <v>4.0800000000000003E-2</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB3" s="5" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28">
-      <c r="A4" s="5">
-        <v>2</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="5">
-        <v>262081</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="H4" s="5">
-        <v>100</v>
-      </c>
-      <c r="I4" s="7">
-        <v>1.1859999999999999</v>
-      </c>
-      <c r="J4" s="7">
-        <v>1.246</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="L4" s="7">
-        <v>147.77600000000001</v>
-      </c>
-      <c r="M4" s="9">
-        <v>124.6</v>
-      </c>
-      <c r="N4" s="6">
-        <v>3.4599999999999999E-2</v>
-      </c>
-      <c r="O4" s="8">
-        <v>2.08</v>
-      </c>
-      <c r="P4" s="5">
-        <v>92.5</v>
-      </c>
-      <c r="Q4" s="5">
-        <v>1</v>
-      </c>
-      <c r="R4" s="5">
-        <v>1250</v>
-      </c>
-      <c r="S4" s="7">
-        <v>1.1859999999999999</v>
-      </c>
-      <c r="T4" s="5">
-        <v>64</v>
-      </c>
-      <c r="U4" s="6">
-        <v>5.1200000000000002E-2</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB4" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28">
-      <c r="A5" s="5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="5">
-        <v>262083</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="H5" s="5">
-        <v>100</v>
-      </c>
-      <c r="I5" s="7">
-        <v>1.036</v>
-      </c>
-      <c r="J5" s="7">
-        <v>1.581</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="L5" s="7">
-        <v>163.792</v>
-      </c>
-      <c r="M5" s="9">
-        <v>158.1</v>
-      </c>
-      <c r="N5" s="6">
-        <v>4.3900000000000002E-2</v>
-      </c>
-      <c r="O5" s="8">
-        <v>2.63</v>
-      </c>
-      <c r="P5" s="5">
-        <v>102.5</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5">
-        <v>1100</v>
-      </c>
-      <c r="S5" s="7">
-        <v>1.036</v>
-      </c>
-      <c r="T5" s="5">
-        <v>64</v>
-      </c>
-      <c r="U5" s="6">
-        <v>5.8200000000000002E-2</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="W5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB5" s="5" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28">
-      <c r="A6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="19">
-        <v>300</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="P6" s="19">
-        <v>321.60000000000002</v>
-      </c>
-      <c r="Q6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="S6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="T6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="U6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="V6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="W6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="X6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB6" s="19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AB1"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCFE926-707C-4947-AB95-1A017E0FBDCA}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -18235,7 +17673,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
       <c r="A1" s="113" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B1" s="113" t="s">
         <v>27</v>
@@ -18574,7 +18012,7 @@
         <v>33</v>
       </c>
       <c r="AB4" s="120" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="25.05" customHeight="1">
@@ -18683,7 +18121,7 @@
         <v>262094</v>
       </c>
       <c r="G6" s="120" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H6" s="120">
         <v>1500</v>
@@ -18695,7 +18133,7 @@
         <v>1.383</v>
       </c>
       <c r="K6" s="120" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L6" s="122">
         <v>1821.4110000000001</v>
@@ -18746,7 +18184,7 @@
         <v>62</v>
       </c>
       <c r="AB6" s="120" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="25.05" customHeight="1">
@@ -18769,7 +18207,7 @@
         <v>262091</v>
       </c>
       <c r="G7" s="120" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H7" s="120">
         <v>750</v>
@@ -18832,7 +18270,7 @@
         <v>39</v>
       </c>
       <c r="AB7" s="120" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="25.05" customHeight="1">
@@ -18855,7 +18293,7 @@
         <v>262092</v>
       </c>
       <c r="G8" s="120" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H8" s="120">
         <v>1250</v>
@@ -18918,7 +18356,7 @@
         <v>33</v>
       </c>
       <c r="AB8" s="120" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="25.05" customHeight="1">
@@ -18941,7 +18379,7 @@
         <v>262093</v>
       </c>
       <c r="G9" s="120" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H9" s="120">
         <v>1250</v>
@@ -19004,7 +18442,7 @@
         <v>33</v>
       </c>
       <c r="AB9" s="120" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="25.05" customHeight="1">
@@ -19027,7 +18465,7 @@
         <v>262095</v>
       </c>
       <c r="G10" s="120" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H10" s="120">
         <v>1200</v>
@@ -19039,7 +18477,7 @@
         <v>1.7829999999999999</v>
       </c>
       <c r="K10" s="120" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L10" s="122">
         <v>1213.153</v>
@@ -19090,7 +18528,7 @@
         <v>33</v>
       </c>
       <c r="AB10" s="120" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="25.05" customHeight="1">

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919D25F4-F08A-40A8-8DFB-2E62B810478F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434491C5-E1E4-4121-8DA5-02892F595F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="22" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="20" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051" sheetId="60" r:id="rId1"/>
@@ -35,7 +35,8 @@
     <sheet name="ABAPEL 1079" sheetId="68" r:id="rId20"/>
     <sheet name="HARMONY EMBALAGENS 1080" sheetId="69" r:id="rId21"/>
     <sheet name="FAVINCO 1081" sheetId="70" r:id="rId22"/>
-    <sheet name="PCBOX EMBALAGENS LTDA - IPE EMB" sheetId="73" r:id="rId23"/>
+    <sheet name="PCBOX - IPE EMB 1085" sheetId="73" r:id="rId23"/>
+    <sheet name="RM EMBALAGENS  1087" sheetId="74" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023'!$A$1:$AB$10</definedName>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4443" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4577" uniqueCount="553">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1681,6 +1682,45 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA - PCBOX EMBALAGENS LTDA - IPE EMBALAGENS LTDA  —  OF: 001085</t>
+  </si>
+  <si>
+    <t>1145x1300</t>
+  </si>
+  <si>
+    <t>126x123x126</t>
+  </si>
+  <si>
+    <t>8.118</t>
+  </si>
+  <si>
+    <t>1196x1300</t>
+  </si>
+  <si>
+    <t>126x140x126</t>
+  </si>
+  <si>
+    <t>820x1344</t>
+  </si>
+  <si>
+    <t>496</t>
+  </si>
+  <si>
+    <t>RM EMBALAGENS DE PAPELÃO LTDA</t>
+  </si>
+  <si>
+    <t>1028x2250</t>
+  </si>
+  <si>
+    <t>825x1480</t>
+  </si>
+  <si>
+    <t>65x80x660</t>
+  </si>
+  <si>
+    <t>1484x3010</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - RM EMBALAGENS DE PAPELÃO LTDA  —  OF: 001087</t>
   </si>
 </sst>
 </file>
@@ -1881,7 +1921,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2231,6 +2271,32 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15528,7 +15594,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6DECCF-0481-438A-8BDD-F0275CF2BE70}">
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
@@ -15538,7 +15604,7 @@
     <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="7.21875" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="3.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.6640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="5.44140625" style="1" customWidth="1"/>
     <col min="10" max="10" width="5.5546875" style="1" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" style="1" customWidth="1"/>
@@ -15819,90 +15885,184 @@
         <v>490</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
-      <c r="A4" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="103">
-        <v>340</v>
-      </c>
-      <c r="I4" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="102">
-        <v>405.8</v>
-      </c>
-      <c r="Q4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="R4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="S4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="T4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="U4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="V4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="W4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="X4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB4" s="102" t="s">
-        <v>27</v>
+    <row r="4" spans="1:28" s="69" customFormat="1">
+      <c r="A4" s="132">
+        <v>1</v>
+      </c>
+      <c r="B4" s="134" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="132" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="132" t="s">
+        <v>492</v>
+      </c>
+      <c r="E4" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="132">
+        <v>262097</v>
+      </c>
+      <c r="G4" s="132" t="s">
+        <v>542</v>
+      </c>
+      <c r="H4" s="132">
+        <v>2000</v>
+      </c>
+      <c r="I4" s="133">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="J4" s="133">
+        <v>1.28</v>
+      </c>
+      <c r="K4" s="132" t="s">
+        <v>544</v>
+      </c>
+      <c r="L4" s="129">
+        <v>1003.52</v>
+      </c>
+      <c r="M4" s="131">
+        <v>1280</v>
+      </c>
+      <c r="N4" s="128">
+        <v>0.17780000000000001</v>
+      </c>
+      <c r="O4" s="130">
+        <v>10.67</v>
+      </c>
+      <c r="P4" s="127">
+        <v>346.2</v>
+      </c>
+      <c r="Q4" s="127">
+        <v>2</v>
+      </c>
+      <c r="R4" s="127">
+        <v>850</v>
+      </c>
+      <c r="S4" s="129">
+        <v>0.78400000000000003</v>
+      </c>
+      <c r="T4" s="127">
+        <v>66</v>
+      </c>
+      <c r="U4" s="128">
+        <v>7.7600000000000002E-2</v>
+      </c>
+      <c r="V4" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="127" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB4" s="127" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" s="69" customFormat="1">
+      <c r="A5" s="132">
+        <v>2</v>
+      </c>
+      <c r="B5" s="134" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="132" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="132" t="s">
+        <v>492</v>
+      </c>
+      <c r="E5" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="132">
+        <v>262096</v>
+      </c>
+      <c r="G5" s="132" t="s">
+        <v>542</v>
+      </c>
+      <c r="H5" s="132">
+        <v>2000</v>
+      </c>
+      <c r="I5" s="133">
+        <v>0.375</v>
+      </c>
+      <c r="J5" s="133">
+        <v>1.28</v>
+      </c>
+      <c r="K5" s="132" t="s">
+        <v>541</v>
+      </c>
+      <c r="L5" s="129">
+        <v>960</v>
+      </c>
+      <c r="M5" s="131">
+        <v>1280</v>
+      </c>
+      <c r="N5" s="128">
+        <v>0.17780000000000001</v>
+      </c>
+      <c r="O5" s="130">
+        <v>10.67</v>
+      </c>
+      <c r="P5" s="127">
+        <v>331.2</v>
+      </c>
+      <c r="Q5" s="127">
+        <v>2</v>
+      </c>
+      <c r="R5" s="127">
+        <v>800</v>
+      </c>
+      <c r="S5" s="129">
+        <v>0.75</v>
+      </c>
+      <c r="T5" s="127">
+        <v>50</v>
+      </c>
+      <c r="U5" s="128">
+        <v>6.25E-2</v>
+      </c>
+      <c r="V5" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="127" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB5" s="127" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" s="135" customFormat="1">
+      <c r="H6" s="135">
+        <v>4340</v>
+      </c>
+      <c r="P6" s="135">
+        <v>1083</v>
       </c>
     </row>
   </sheetData>
@@ -15910,6 +16070,7 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18626,6 +18787,650 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47514BAB-BD75-470F-9A41-8686D45C5BAB}">
+  <dimension ref="A1:AB7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="2.21875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="4.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="5.44140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.88671875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="6.21875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="3.44140625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="6.109375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="5.88671875" style="3" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="22" max="23" width="7.88671875" style="3" customWidth="1"/>
+    <col min="24" max="24" width="8.33203125" style="3" customWidth="1"/>
+    <col min="25" max="25" width="7.33203125" style="3" customWidth="1"/>
+    <col min="26" max="26" width="8" style="3" customWidth="1"/>
+    <col min="27" max="27" width="3.5546875" style="3" customWidth="1"/>
+    <col min="28" max="28" width="10.88671875" style="3" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="136" t="s">
+        <v>552</v>
+      </c>
+      <c r="B1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="136" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="52.8" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
+      <c r="A3" s="38">
+        <v>1</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>547</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>492</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="38">
+        <v>262099</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>546</v>
+      </c>
+      <c r="H3" s="38">
+        <v>170</v>
+      </c>
+      <c r="I3" s="39">
+        <v>1.464</v>
+      </c>
+      <c r="J3" s="39">
+        <v>2.99</v>
+      </c>
+      <c r="K3" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="35">
+        <v>744.15099999999995</v>
+      </c>
+      <c r="M3" s="37">
+        <v>508.3</v>
+      </c>
+      <c r="N3" s="34">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="O3" s="36">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="P3" s="33">
+        <v>441.3</v>
+      </c>
+      <c r="Q3" s="33">
+        <v>1</v>
+      </c>
+      <c r="R3" s="33">
+        <v>1500</v>
+      </c>
+      <c r="S3" s="35">
+        <v>1.464</v>
+      </c>
+      <c r="T3" s="33">
+        <v>36</v>
+      </c>
+      <c r="U3" s="34">
+        <v>2.4E-2</v>
+      </c>
+      <c r="V3" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="X3" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB3" s="33" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
+      <c r="A4" s="38">
+        <v>2</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>547</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>492</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="38">
+        <v>262101</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>546</v>
+      </c>
+      <c r="H4" s="38">
+        <v>3500</v>
+      </c>
+      <c r="I4" s="39">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="J4" s="39">
+        <v>1.46</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>550</v>
+      </c>
+      <c r="L4" s="35">
+        <v>4113.55</v>
+      </c>
+      <c r="M4" s="37">
+        <v>5110</v>
+      </c>
+      <c r="N4" s="34">
+        <v>1.4194</v>
+      </c>
+      <c r="O4" s="36">
+        <v>85.17</v>
+      </c>
+      <c r="P4" s="33">
+        <v>1419.2</v>
+      </c>
+      <c r="Q4" s="33">
+        <v>1</v>
+      </c>
+      <c r="R4" s="33">
+        <v>850</v>
+      </c>
+      <c r="S4" s="35">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="T4" s="33">
+        <v>45</v>
+      </c>
+      <c r="U4" s="34">
+        <v>5.2900000000000003E-2</v>
+      </c>
+      <c r="V4" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="33" t="s">
+        <v>513</v>
+      </c>
+      <c r="AB4" s="33" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
+      <c r="A5" s="38">
+        <v>3</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>547</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>492</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="38">
+        <v>262098</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>546</v>
+      </c>
+      <c r="H5" s="38">
+        <v>1300</v>
+      </c>
+      <c r="I5" s="39">
+        <v>1.008</v>
+      </c>
+      <c r="J5" s="39">
+        <v>2.23</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="35">
+        <v>2922.192</v>
+      </c>
+      <c r="M5" s="37">
+        <v>1449.5</v>
+      </c>
+      <c r="N5" s="34">
+        <v>0.20130000000000001</v>
+      </c>
+      <c r="O5" s="36">
+        <v>12.08</v>
+      </c>
+      <c r="P5" s="33">
+        <v>1008.2</v>
+      </c>
+      <c r="Q5" s="33">
+        <v>2</v>
+      </c>
+      <c r="R5" s="33">
+        <v>850</v>
+      </c>
+      <c r="S5" s="35">
+        <v>2.016</v>
+      </c>
+      <c r="T5" s="33">
+        <v>-1166</v>
+      </c>
+      <c r="U5" s="34">
+        <v>-1.3717999999999999</v>
+      </c>
+      <c r="V5" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB5" s="33" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
+      <c r="A6" s="38">
+        <v>4</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>547</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>492</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="38">
+        <v>262100</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>546</v>
+      </c>
+      <c r="H6" s="38">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="39">
+        <v>0.8</v>
+      </c>
+      <c r="J6" s="39">
+        <v>1.3240000000000001</v>
+      </c>
+      <c r="K6" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="35">
+        <v>1059.2</v>
+      </c>
+      <c r="M6" s="37">
+        <v>1324</v>
+      </c>
+      <c r="N6" s="34">
+        <v>0.36780000000000002</v>
+      </c>
+      <c r="O6" s="36">
+        <v>22.07</v>
+      </c>
+      <c r="P6" s="33">
+        <v>365.4</v>
+      </c>
+      <c r="Q6" s="33">
+        <v>1</v>
+      </c>
+      <c r="R6" s="33">
+        <v>850</v>
+      </c>
+      <c r="S6" s="35">
+        <v>0.8</v>
+      </c>
+      <c r="T6" s="33">
+        <v>50</v>
+      </c>
+      <c r="U6" s="34">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="V6" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB6" s="33" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
+      <c r="A7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="32">
+        <v>5970</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="31">
+        <v>3234</v>
+      </c>
+      <c r="Q7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="T7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="X7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB7" s="31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8560783-F1AE-41B7-817A-6D1BAC7508D9}">
   <sheetPr>
@@ -23227,7 +24032,7 @@
     <col min="24" max="24" width="7" style="1" customWidth="1"/>
     <col min="25" max="25" width="7.44140625" style="1" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="7.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="5.109375" style="1" customWidth="1"/>
+    <col min="27" max="27" width="7.77734375" style="1" customWidth="1"/>
     <col min="28" max="28" width="11.77734375" style="1" customWidth="1"/>
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434491C5-E1E4-4121-8DA5-02892F595F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5639FEA7-EB4E-46EC-8A7F-1F380BA17B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="20" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051" sheetId="60" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="FAVINCO 1081" sheetId="70" r:id="rId22"/>
     <sheet name="PCBOX - IPE EMB 1085" sheetId="73" r:id="rId23"/>
     <sheet name="RM EMBALAGENS  1087" sheetId="74" r:id="rId24"/>
+    <sheet name="ABAPEL 1046" sheetId="75" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023'!$A$1:$AB$10</definedName>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4577" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4750" uniqueCount="572">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1721,6 +1722,63 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA - RM EMBALAGENS DE PAPELÃO LTDA  —  OF: 001087</t>
+  </si>
+  <si>
+    <t>824x2100</t>
+  </si>
+  <si>
+    <t>101x200x101</t>
+  </si>
+  <si>
+    <t>8.035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABAPEL </t>
+  </si>
+  <si>
+    <t>940x1920</t>
+  </si>
+  <si>
+    <t>8.058</t>
+  </si>
+  <si>
+    <t>845x1688</t>
+  </si>
+  <si>
+    <t>205x415x205</t>
+  </si>
+  <si>
+    <t>8.046</t>
+  </si>
+  <si>
+    <t>887x1760</t>
+  </si>
+  <si>
+    <t>176x515x176</t>
+  </si>
+  <si>
+    <t>1120x1800</t>
+  </si>
+  <si>
+    <t>8.038</t>
+  </si>
+  <si>
+    <t>1092x1940</t>
+  </si>
+  <si>
+    <t>236x600x236</t>
+  </si>
+  <si>
+    <t>1210x2610</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>260x670x260</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA  —  ABAPEL OF: 001046</t>
   </si>
 </sst>
 </file>
@@ -1921,7 +1979,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2232,24 +2290,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2296,7 +2336,30 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2550,88 +2613,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="128" t="s">
         <v>309</v>
       </c>
-      <c r="B1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="112" t="s">
+      <c r="B1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="128" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3454,88 +3517,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="128" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="112" t="s">
+      <c r="B1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="128" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4273,88 +4336,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="133" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="117" t="s">
+      <c r="B1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="133" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5179,88 +5242,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="130" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="114" t="s">
+      <c r="B1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="130" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6596,88 +6659,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="128" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="112" t="s">
+      <c r="B1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="128" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7146,88 +7209,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="133" t="s">
         <v>343</v>
       </c>
-      <c r="B1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="117" t="s">
+      <c r="B1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="133" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8221,88 +8284,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="128" t="s">
         <v>364</v>
       </c>
-      <c r="B1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="112" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="112" t="s">
+      <c r="B1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="128" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8956,88 +9019,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="130" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="114" t="s">
+      <c r="B1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="130" t="s">
         <v>27</v>
       </c>
     </row>
@@ -9945,88 +10008,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="21" customFormat="1" ht="18" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="134" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="118" t="s">
+      <c r="B1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="134" t="s">
         <v>27</v>
       </c>
     </row>
@@ -11712,88 +11775,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="133" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="117" t="s">
+      <c r="B1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="133" t="s">
         <v>27</v>
       </c>
     </row>
@@ -12701,88 +12764,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="134" t="s">
         <v>489</v>
       </c>
-      <c r="B1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="118" t="s">
+      <c r="B1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="134" t="s">
         <v>27</v>
       </c>
     </row>
@@ -14724,88 +14787,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18.600000000000001" customHeight="1">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="129" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="113" t="s">
+      <c r="B1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="129" t="s">
         <v>27</v>
       </c>
     </row>
@@ -15628,88 +15691,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="135" t="s">
         <v>493</v>
       </c>
-      <c r="B1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="119" t="s">
+      <c r="B1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="135" t="s">
         <v>27</v>
       </c>
     </row>
@@ -15886,182 +15949,182 @@
       </c>
     </row>
     <row r="4" spans="1:28" s="69" customFormat="1">
-      <c r="A4" s="132">
+      <c r="A4" s="124">
         <v>1</v>
       </c>
-      <c r="B4" s="134" t="s">
+      <c r="B4" s="126" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="132" t="s">
+      <c r="C4" s="124" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="132" t="s">
+      <c r="D4" s="124" t="s">
         <v>492</v>
       </c>
-      <c r="E4" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="132">
+      <c r="E4" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="124">
         <v>262097</v>
       </c>
-      <c r="G4" s="132" t="s">
+      <c r="G4" s="124" t="s">
         <v>542</v>
       </c>
-      <c r="H4" s="132">
+      <c r="H4" s="124">
         <v>2000</v>
       </c>
-      <c r="I4" s="133">
+      <c r="I4" s="125">
         <v>0.39200000000000002</v>
       </c>
-      <c r="J4" s="133">
+      <c r="J4" s="125">
         <v>1.28</v>
       </c>
-      <c r="K4" s="132" t="s">
+      <c r="K4" s="124" t="s">
         <v>544</v>
       </c>
-      <c r="L4" s="129">
+      <c r="L4" s="121">
         <v>1003.52</v>
       </c>
-      <c r="M4" s="131">
+      <c r="M4" s="123">
         <v>1280</v>
       </c>
-      <c r="N4" s="128">
+      <c r="N4" s="120">
         <v>0.17780000000000001</v>
       </c>
-      <c r="O4" s="130">
+      <c r="O4" s="122">
         <v>10.67</v>
       </c>
-      <c r="P4" s="127">
+      <c r="P4" s="119">
         <v>346.2</v>
       </c>
-      <c r="Q4" s="127">
+      <c r="Q4" s="119">
         <v>2</v>
       </c>
-      <c r="R4" s="127">
+      <c r="R4" s="119">
         <v>850</v>
       </c>
-      <c r="S4" s="129">
+      <c r="S4" s="121">
         <v>0.78400000000000003</v>
       </c>
-      <c r="T4" s="127">
+      <c r="T4" s="119">
         <v>66</v>
       </c>
-      <c r="U4" s="128">
+      <c r="U4" s="120">
         <v>7.7600000000000002E-2</v>
       </c>
-      <c r="V4" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="X4" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="127" t="s">
+      <c r="V4" s="119" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="119" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="119" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="AB4" s="127" t="s">
+      <c r="AB4" s="119" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="5" spans="1:28" s="69" customFormat="1">
-      <c r="A5" s="132">
+      <c r="A5" s="124">
         <v>2</v>
       </c>
-      <c r="B5" s="134" t="s">
+      <c r="B5" s="126" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="132" t="s">
+      <c r="C5" s="124" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="132" t="s">
+      <c r="D5" s="124" t="s">
         <v>492</v>
       </c>
-      <c r="E5" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="132">
+      <c r="E5" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="124">
         <v>262096</v>
       </c>
-      <c r="G5" s="132" t="s">
+      <c r="G5" s="124" t="s">
         <v>542</v>
       </c>
-      <c r="H5" s="132">
+      <c r="H5" s="124">
         <v>2000</v>
       </c>
-      <c r="I5" s="133">
+      <c r="I5" s="125">
         <v>0.375</v>
       </c>
-      <c r="J5" s="133">
+      <c r="J5" s="125">
         <v>1.28</v>
       </c>
-      <c r="K5" s="132" t="s">
+      <c r="K5" s="124" t="s">
         <v>541</v>
       </c>
-      <c r="L5" s="129">
+      <c r="L5" s="121">
         <v>960</v>
       </c>
-      <c r="M5" s="131">
+      <c r="M5" s="123">
         <v>1280</v>
       </c>
-      <c r="N5" s="128">
+      <c r="N5" s="120">
         <v>0.17780000000000001</v>
       </c>
-      <c r="O5" s="130">
+      <c r="O5" s="122">
         <v>10.67</v>
       </c>
-      <c r="P5" s="127">
+      <c r="P5" s="119">
         <v>331.2</v>
       </c>
-      <c r="Q5" s="127">
+      <c r="Q5" s="119">
         <v>2</v>
       </c>
-      <c r="R5" s="127">
+      <c r="R5" s="119">
         <v>800</v>
       </c>
-      <c r="S5" s="129">
+      <c r="S5" s="121">
         <v>0.75</v>
       </c>
-      <c r="T5" s="127">
+      <c r="T5" s="119">
         <v>50</v>
       </c>
-      <c r="U5" s="128">
+      <c r="U5" s="120">
         <v>6.25E-2</v>
       </c>
-      <c r="V5" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="W5" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="X5" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z5" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA5" s="127" t="s">
+      <c r="V5" s="119" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="119" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="119" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="119" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="AB5" s="127" t="s">
+      <c r="AB5" s="119" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="135" customFormat="1">
-      <c r="H6" s="135">
+    <row r="6" spans="1:28" s="127" customFormat="1">
+      <c r="H6" s="127">
         <v>4340</v>
       </c>
-      <c r="P6" s="135">
+      <c r="P6" s="127">
         <v>1083</v>
       </c>
     </row>
@@ -16110,88 +16173,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="134" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="118" t="s">
+      <c r="B1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="134" t="s">
         <v>27</v>
       </c>
     </row>
@@ -17443,88 +17506,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="135" t="s">
         <v>523</v>
       </c>
-      <c r="B1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="119" t="s">
+      <c r="B1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="135" t="s">
         <v>27</v>
       </c>
     </row>
@@ -17833,88 +17896,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="129" t="s">
         <v>539</v>
       </c>
-      <c r="B1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="113" t="s">
+      <c r="B1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="129" t="s">
         <v>27</v>
       </c>
     </row>
@@ -18005,776 +18068,776 @@
       </c>
     </row>
     <row r="3" spans="1:28" ht="25.05" customHeight="1">
-      <c r="A3" s="120">
+      <c r="A3" s="112">
         <v>1</v>
       </c>
-      <c r="B3" s="121" t="s">
+      <c r="B3" s="113" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="120" t="s">
+      <c r="C3" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="120" t="s">
+      <c r="D3" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E3" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="120">
+      <c r="E3" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="112">
         <v>262089</v>
       </c>
-      <c r="G3" s="120" t="s">
+      <c r="G3" s="112" t="s">
         <v>526</v>
       </c>
-      <c r="H3" s="120">
+      <c r="H3" s="112">
         <v>100</v>
       </c>
-      <c r="I3" s="122">
+      <c r="I3" s="114">
         <v>1.2470000000000001</v>
       </c>
-      <c r="J3" s="122">
+      <c r="J3" s="114">
         <v>1.621</v>
       </c>
-      <c r="K3" s="120" t="s">
+      <c r="K3" s="112" t="s">
         <v>529</v>
       </c>
-      <c r="L3" s="122">
+      <c r="L3" s="114">
         <v>202.13900000000001</v>
       </c>
-      <c r="M3" s="123">
+      <c r="M3" s="115">
         <v>162.1</v>
       </c>
-      <c r="N3" s="124">
+      <c r="N3" s="116">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="O3" s="125">
+      <c r="O3" s="117">
         <v>2.7</v>
       </c>
-      <c r="P3" s="120">
+      <c r="P3" s="112">
         <v>122.5</v>
       </c>
-      <c r="Q3" s="120">
+      <c r="Q3" s="112">
         <v>1</v>
       </c>
-      <c r="R3" s="120">
+      <c r="R3" s="112">
         <v>1300</v>
       </c>
-      <c r="S3" s="122">
+      <c r="S3" s="114">
         <v>1.2470000000000001</v>
       </c>
-      <c r="T3" s="120">
+      <c r="T3" s="112">
         <v>53</v>
       </c>
-      <c r="U3" s="124">
+      <c r="U3" s="116">
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="V3" s="120" t="s">
+      <c r="V3" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="W3" s="120" t="s">
+      <c r="W3" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="120" t="s">
+      <c r="X3" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="Y3" s="120" t="s">
+      <c r="Y3" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="Z3" s="120" t="s">
+      <c r="Z3" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="AA3" s="120" t="s">
+      <c r="AA3" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="AB3" s="120" t="s">
+      <c r="AB3" s="112" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="25.05" customHeight="1">
-      <c r="A4" s="120">
+      <c r="A4" s="112">
         <v>2</v>
       </c>
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="113" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E4" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="120">
+      <c r="E4" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="112">
         <v>262088</v>
       </c>
-      <c r="G4" s="120" t="s">
+      <c r="G4" s="112" t="s">
         <v>526</v>
       </c>
-      <c r="H4" s="120">
+      <c r="H4" s="112">
         <v>100</v>
       </c>
-      <c r="I4" s="122">
+      <c r="I4" s="114">
         <v>1.1859999999999999</v>
       </c>
-      <c r="J4" s="122">
+      <c r="J4" s="114">
         <v>1.246</v>
       </c>
-      <c r="K4" s="120" t="s">
+      <c r="K4" s="112" t="s">
         <v>527</v>
       </c>
-      <c r="L4" s="122">
+      <c r="L4" s="114">
         <v>147.77600000000001</v>
       </c>
-      <c r="M4" s="123">
+      <c r="M4" s="115">
         <v>124.6</v>
       </c>
-      <c r="N4" s="124">
+      <c r="N4" s="116">
         <v>3.4599999999999999E-2</v>
       </c>
-      <c r="O4" s="125">
+      <c r="O4" s="117">
         <v>2.08</v>
       </c>
-      <c r="P4" s="120">
+      <c r="P4" s="112">
         <v>89.6</v>
       </c>
-      <c r="Q4" s="120">
+      <c r="Q4" s="112">
         <v>1</v>
       </c>
-      <c r="R4" s="120">
+      <c r="R4" s="112">
         <v>1250</v>
       </c>
-      <c r="S4" s="122">
+      <c r="S4" s="114">
         <v>1.1859999999999999</v>
       </c>
-      <c r="T4" s="120">
+      <c r="T4" s="112">
         <v>64</v>
       </c>
-      <c r="U4" s="124">
+      <c r="U4" s="116">
         <v>5.1200000000000002E-2</v>
       </c>
-      <c r="V4" s="120" t="s">
+      <c r="V4" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="W4" s="120" t="s">
+      <c r="W4" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="X4" s="120" t="s">
+      <c r="X4" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="Y4" s="120" t="s">
+      <c r="Y4" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="Z4" s="120" t="s">
+      <c r="Z4" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="AA4" s="120" t="s">
+      <c r="AA4" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="AB4" s="120" t="s">
+      <c r="AB4" s="112" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="25.05" customHeight="1">
-      <c r="A5" s="120">
+      <c r="A5" s="112">
         <v>3</v>
       </c>
-      <c r="B5" s="121" t="s">
+      <c r="B5" s="113" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="120" t="s">
+      <c r="C5" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="120" t="s">
+      <c r="D5" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E5" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="120">
+      <c r="E5" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="112">
         <v>262090</v>
       </c>
-      <c r="G5" s="120" t="s">
+      <c r="G5" s="112" t="s">
         <v>526</v>
       </c>
-      <c r="H5" s="120">
+      <c r="H5" s="112">
         <v>100</v>
       </c>
-      <c r="I5" s="122">
+      <c r="I5" s="114">
         <v>1.036</v>
       </c>
-      <c r="J5" s="122">
+      <c r="J5" s="114">
         <v>1.581</v>
       </c>
-      <c r="K5" s="120" t="s">
+      <c r="K5" s="112" t="s">
         <v>525</v>
       </c>
-      <c r="L5" s="122">
+      <c r="L5" s="114">
         <v>163.792</v>
       </c>
-      <c r="M5" s="123">
+      <c r="M5" s="115">
         <v>158.1</v>
       </c>
-      <c r="N5" s="124">
+      <c r="N5" s="116">
         <v>4.3900000000000002E-2</v>
       </c>
-      <c r="O5" s="125">
+      <c r="O5" s="117">
         <v>2.63</v>
       </c>
-      <c r="P5" s="120">
+      <c r="P5" s="112">
         <v>99.3</v>
       </c>
-      <c r="Q5" s="120">
+      <c r="Q5" s="112">
         <v>1</v>
       </c>
-      <c r="R5" s="120">
+      <c r="R5" s="112">
         <v>1100</v>
       </c>
-      <c r="S5" s="122">
+      <c r="S5" s="114">
         <v>1.036</v>
       </c>
-      <c r="T5" s="120">
+      <c r="T5" s="112">
         <v>64</v>
       </c>
-      <c r="U5" s="124">
+      <c r="U5" s="116">
         <v>5.8200000000000002E-2</v>
       </c>
-      <c r="V5" s="120" t="s">
+      <c r="V5" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="W5" s="120" t="s">
+      <c r="W5" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="X5" s="120" t="s">
+      <c r="X5" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="Y5" s="120" t="s">
+      <c r="Y5" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="Z5" s="120" t="s">
+      <c r="Z5" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="AA5" s="120" t="s">
+      <c r="AA5" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="AB5" s="120" t="s">
+      <c r="AB5" s="112" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="25.05" customHeight="1">
-      <c r="A6" s="120">
+      <c r="A6" s="112">
         <v>4</v>
       </c>
-      <c r="B6" s="121" t="s">
+      <c r="B6" s="113" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="120" t="s">
+      <c r="C6" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="120" t="s">
+      <c r="D6" s="112" t="s">
         <v>492</v>
       </c>
-      <c r="E6" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="120">
+      <c r="E6" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="112">
         <v>262094</v>
       </c>
-      <c r="G6" s="120" t="s">
+      <c r="G6" s="112" t="s">
         <v>538</v>
       </c>
-      <c r="H6" s="120">
+      <c r="H6" s="112">
         <v>1500</v>
       </c>
-      <c r="I6" s="122">
+      <c r="I6" s="114">
         <v>0.878</v>
       </c>
-      <c r="J6" s="122">
+      <c r="J6" s="114">
         <v>1.383</v>
       </c>
-      <c r="K6" s="120" t="s">
+      <c r="K6" s="112" t="s">
         <v>537</v>
       </c>
-      <c r="L6" s="122">
+      <c r="L6" s="114">
         <v>1821.4110000000001</v>
       </c>
-      <c r="M6" s="123">
+      <c r="M6" s="115">
         <v>2074.5</v>
       </c>
-      <c r="N6" s="124">
+      <c r="N6" s="116">
         <v>0.57630000000000003</v>
       </c>
-      <c r="O6" s="125">
+      <c r="O6" s="117">
         <v>34.58</v>
       </c>
-      <c r="P6" s="120">
+      <c r="P6" s="112">
         <v>1103.8</v>
       </c>
-      <c r="Q6" s="120">
+      <c r="Q6" s="112">
         <v>1</v>
       </c>
-      <c r="R6" s="120">
+      <c r="R6" s="112">
         <v>900</v>
       </c>
-      <c r="S6" s="122">
+      <c r="S6" s="114">
         <v>0.878</v>
       </c>
-      <c r="T6" s="120">
+      <c r="T6" s="112">
         <v>22</v>
       </c>
-      <c r="U6" s="124">
+      <c r="U6" s="116">
         <v>2.4400000000000002E-2</v>
       </c>
-      <c r="V6" s="120" t="s">
+      <c r="V6" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="W6" s="120" t="s">
+      <c r="W6" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="X6" s="120" t="s">
+      <c r="X6" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="Y6" s="120" t="s">
+      <c r="Y6" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="Z6" s="120" t="s">
+      <c r="Z6" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="AA6" s="120" t="s">
+      <c r="AA6" s="112" t="s">
         <v>62</v>
       </c>
-      <c r="AB6" s="120" t="s">
+      <c r="AB6" s="112" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="25.05" customHeight="1">
-      <c r="A7" s="120">
+      <c r="A7" s="112">
         <v>5</v>
       </c>
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="113" t="s">
         <v>279</v>
       </c>
-      <c r="C7" s="120" t="s">
+      <c r="C7" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="120" t="s">
+      <c r="D7" s="112" t="s">
         <v>492</v>
       </c>
-      <c r="E7" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="120">
+      <c r="E7" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="112">
         <v>262091</v>
       </c>
-      <c r="G7" s="120" t="s">
+      <c r="G7" s="112" t="s">
         <v>531</v>
       </c>
-      <c r="H7" s="120">
+      <c r="H7" s="112">
         <v>750</v>
       </c>
-      <c r="I7" s="122">
+      <c r="I7" s="114">
         <v>0.75</v>
       </c>
-      <c r="J7" s="122">
+      <c r="J7" s="114">
         <v>0.49</v>
       </c>
-      <c r="K7" s="120" t="s">
+      <c r="K7" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="122">
+      <c r="L7" s="114">
         <v>275.625</v>
       </c>
-      <c r="M7" s="123">
+      <c r="M7" s="115">
         <v>183.8</v>
       </c>
-      <c r="N7" s="124">
+      <c r="N7" s="116">
         <v>2.5499999999999998E-2</v>
       </c>
-      <c r="O7" s="125">
+      <c r="O7" s="117">
         <v>1.53</v>
       </c>
-      <c r="P7" s="120">
+      <c r="P7" s="112">
         <v>117.8</v>
       </c>
-      <c r="Q7" s="120">
+      <c r="Q7" s="112">
         <v>2</v>
       </c>
-      <c r="R7" s="120">
+      <c r="R7" s="112">
         <v>1550</v>
       </c>
-      <c r="S7" s="122">
+      <c r="S7" s="114">
         <v>1.5</v>
       </c>
-      <c r="T7" s="120">
+      <c r="T7" s="112">
         <v>50</v>
       </c>
-      <c r="U7" s="124">
+      <c r="U7" s="116">
         <v>3.2300000000000002E-2</v>
       </c>
-      <c r="V7" s="120" t="s">
+      <c r="V7" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="W7" s="120" t="s">
+      <c r="W7" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="X7" s="120" t="s">
+      <c r="X7" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="Y7" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z7" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA7" s="120" t="s">
+      <c r="Y7" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="AB7" s="120" t="s">
+      <c r="AB7" s="112" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="25.05" customHeight="1">
-      <c r="A8" s="120">
+      <c r="A8" s="112">
         <v>6</v>
       </c>
-      <c r="B8" s="121" t="s">
+      <c r="B8" s="113" t="s">
         <v>279</v>
       </c>
-      <c r="C8" s="120" t="s">
+      <c r="C8" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="120" t="s">
+      <c r="D8" s="112" t="s">
         <v>492</v>
       </c>
-      <c r="E8" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="120">
+      <c r="E8" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="112">
         <v>262092</v>
       </c>
-      <c r="G8" s="120" t="s">
+      <c r="G8" s="112" t="s">
         <v>531</v>
       </c>
-      <c r="H8" s="120">
+      <c r="H8" s="112">
         <v>1250</v>
       </c>
-      <c r="I8" s="122">
+      <c r="I8" s="114">
         <v>0.75</v>
       </c>
-      <c r="J8" s="122">
+      <c r="J8" s="114">
         <v>0.75</v>
       </c>
-      <c r="K8" s="120" t="s">
+      <c r="K8" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="L8" s="122">
+      <c r="L8" s="114">
         <v>703.125</v>
       </c>
-      <c r="M8" s="123">
+      <c r="M8" s="115">
         <v>468.8</v>
       </c>
-      <c r="N8" s="124">
+      <c r="N8" s="116">
         <v>6.5100000000000005E-2</v>
       </c>
-      <c r="O8" s="125">
+      <c r="O8" s="117">
         <v>3.91</v>
       </c>
-      <c r="P8" s="120">
+      <c r="P8" s="112">
         <v>300.60000000000002</v>
       </c>
-      <c r="Q8" s="120">
+      <c r="Q8" s="112">
         <v>2</v>
       </c>
-      <c r="R8" s="120">
+      <c r="R8" s="112">
         <v>1550</v>
       </c>
-      <c r="S8" s="122">
+      <c r="S8" s="114">
         <v>1.5</v>
       </c>
-      <c r="T8" s="120">
+      <c r="T8" s="112">
         <v>50</v>
       </c>
-      <c r="U8" s="124">
+      <c r="U8" s="116">
         <v>3.2300000000000002E-2</v>
       </c>
-      <c r="V8" s="120" t="s">
+      <c r="V8" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="W8" s="120" t="s">
+      <c r="W8" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="X8" s="120" t="s">
+      <c r="X8" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="Y8" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z8" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA8" s="120" t="s">
+      <c r="Y8" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="AB8" s="120" t="s">
+      <c r="AB8" s="112" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="25.05" customHeight="1">
-      <c r="A9" s="120">
+      <c r="A9" s="112">
         <v>7</v>
       </c>
-      <c r="B9" s="121" t="s">
+      <c r="B9" s="113" t="s">
         <v>279</v>
       </c>
-      <c r="C9" s="120" t="s">
+      <c r="C9" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="120" t="s">
+      <c r="D9" s="112" t="s">
         <v>492</v>
       </c>
-      <c r="E9" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="120">
+      <c r="E9" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="112">
         <v>262093</v>
       </c>
-      <c r="G9" s="120" t="s">
+      <c r="G9" s="112" t="s">
         <v>531</v>
       </c>
-      <c r="H9" s="120">
+      <c r="H9" s="112">
         <v>1250</v>
       </c>
-      <c r="I9" s="122">
+      <c r="I9" s="114">
         <v>0.75</v>
       </c>
-      <c r="J9" s="122">
+      <c r="J9" s="114">
         <v>0.75</v>
       </c>
-      <c r="K9" s="120" t="s">
+      <c r="K9" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="122">
+      <c r="L9" s="114">
         <v>703.125</v>
       </c>
-      <c r="M9" s="123">
+      <c r="M9" s="115">
         <v>468.8</v>
       </c>
-      <c r="N9" s="124">
+      <c r="N9" s="116">
         <v>6.5100000000000005E-2</v>
       </c>
-      <c r="O9" s="125">
+      <c r="O9" s="117">
         <v>3.91</v>
       </c>
-      <c r="P9" s="120">
+      <c r="P9" s="112">
         <v>300.60000000000002</v>
       </c>
-      <c r="Q9" s="120">
+      <c r="Q9" s="112">
         <v>2</v>
       </c>
-      <c r="R9" s="120">
+      <c r="R9" s="112">
         <v>1550</v>
       </c>
-      <c r="S9" s="122">
+      <c r="S9" s="114">
         <v>1.5</v>
       </c>
-      <c r="T9" s="120">
+      <c r="T9" s="112">
         <v>50</v>
       </c>
-      <c r="U9" s="124">
+      <c r="U9" s="116">
         <v>3.2300000000000002E-2</v>
       </c>
-      <c r="V9" s="120" t="s">
+      <c r="V9" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="W9" s="120" t="s">
+      <c r="W9" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="X9" s="120" t="s">
+      <c r="X9" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="Y9" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z9" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA9" s="120" t="s">
+      <c r="Y9" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="AB9" s="120" t="s">
+      <c r="AB9" s="112" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="25.05" customHeight="1">
-      <c r="A10" s="120">
+      <c r="A10" s="112">
         <v>8</v>
       </c>
-      <c r="B10" s="121" t="s">
+      <c r="B10" s="113" t="s">
         <v>279</v>
       </c>
-      <c r="C10" s="120" t="s">
+      <c r="C10" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="120" t="s">
+      <c r="D10" s="112" t="s">
         <v>492</v>
       </c>
-      <c r="E10" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="120">
+      <c r="E10" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="112">
         <v>262095</v>
       </c>
-      <c r="G10" s="120" t="s">
+      <c r="G10" s="112" t="s">
         <v>535</v>
       </c>
-      <c r="H10" s="120">
+      <c r="H10" s="112">
         <v>1200</v>
       </c>
-      <c r="I10" s="122">
+      <c r="I10" s="114">
         <v>0.56699999999999995</v>
       </c>
-      <c r="J10" s="122">
+      <c r="J10" s="114">
         <v>1.7829999999999999</v>
       </c>
-      <c r="K10" s="120" t="s">
+      <c r="K10" s="112" t="s">
         <v>534</v>
       </c>
-      <c r="L10" s="122">
+      <c r="L10" s="114">
         <v>1213.153</v>
       </c>
-      <c r="M10" s="123">
+      <c r="M10" s="115">
         <v>1069.8</v>
       </c>
-      <c r="N10" s="124">
+      <c r="N10" s="116">
         <v>0.14860000000000001</v>
       </c>
-      <c r="O10" s="125">
+      <c r="O10" s="117">
         <v>8.91</v>
       </c>
-      <c r="P10" s="120">
+      <c r="P10" s="112">
         <v>418.5</v>
       </c>
-      <c r="Q10" s="120">
+      <c r="Q10" s="112">
         <v>2</v>
       </c>
-      <c r="R10" s="120">
+      <c r="R10" s="112">
         <v>1200</v>
       </c>
-      <c r="S10" s="122">
+      <c r="S10" s="114">
         <v>1.1339999999999999</v>
       </c>
-      <c r="T10" s="120">
+      <c r="T10" s="112">
         <v>66</v>
       </c>
-      <c r="U10" s="124">
+      <c r="U10" s="116">
         <v>5.5E-2</v>
       </c>
-      <c r="V10" s="120" t="s">
-        <v>28</v>
-      </c>
-      <c r="W10" s="120" t="s">
-        <v>28</v>
-      </c>
-      <c r="X10" s="120" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y10" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z10" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA10" s="120" t="s">
+      <c r="V10" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="AB10" s="120" t="s">
+      <c r="AB10" s="112" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="25.05" customHeight="1">
-      <c r="A11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="126">
+      <c r="A11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="118">
         <v>6250</v>
       </c>
-      <c r="I11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="N11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="O11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="P11" s="126">
+      <c r="I11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="118">
         <v>2552.6</v>
       </c>
-      <c r="Q11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="R11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="S11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="T11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="U11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="V11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="W11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="X11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA11" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB11" s="126" t="s">
+      <c r="Q11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="R11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="S11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="T11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="U11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="V11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="W11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="X11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA11" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB11" s="118" t="s">
         <v>27</v>
       </c>
     </row>
@@ -18822,88 +18885,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="131" t="s">
         <v>552</v>
       </c>
-      <c r="B1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="136" t="s">
+      <c r="B1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="131" t="s">
         <v>27</v>
       </c>
     </row>
@@ -18994,432 +19057,432 @@
       </c>
     </row>
     <row r="3" spans="1:28">
-      <c r="A3" s="38">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="12" t="s">
         <v>547</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="E3" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="38">
+      <c r="E3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="11">
         <v>262099</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="H3" s="38">
+      <c r="H3" s="11">
         <v>170</v>
       </c>
-      <c r="I3" s="39">
+      <c r="I3" s="13">
         <v>1.464</v>
       </c>
-      <c r="J3" s="39">
+      <c r="J3" s="13">
         <v>2.99</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="35">
+      <c r="L3" s="13">
         <v>744.15099999999995</v>
       </c>
-      <c r="M3" s="37">
+      <c r="M3" s="14">
         <v>508.3</v>
       </c>
-      <c r="N3" s="34">
+      <c r="N3" s="15">
         <v>0.14119999999999999</v>
       </c>
-      <c r="O3" s="36">
+      <c r="O3" s="16">
         <v>8.4700000000000006</v>
       </c>
-      <c r="P3" s="33">
+      <c r="P3" s="11">
         <v>441.3</v>
       </c>
-      <c r="Q3" s="33">
+      <c r="Q3" s="11">
         <v>1</v>
       </c>
-      <c r="R3" s="33">
+      <c r="R3" s="11">
         <v>1500</v>
       </c>
-      <c r="S3" s="35">
+      <c r="S3" s="13">
         <v>1.464</v>
       </c>
-      <c r="T3" s="33">
+      <c r="T3" s="11">
         <v>36</v>
       </c>
-      <c r="U3" s="34">
+      <c r="U3" s="15">
         <v>2.4E-2</v>
       </c>
-      <c r="V3" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="33" t="s">
+      <c r="V3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="X3" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z3" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA3" s="33" t="s">
+      <c r="X3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AB3" s="33" t="s">
+      <c r="AB3" s="11" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:28">
-      <c r="A4" s="38">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="12" t="s">
         <v>547</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="E4" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="38">
+      <c r="E4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="11">
         <v>262101</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="H4" s="38">
+      <c r="H4" s="11">
         <v>3500</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="13">
         <v>0.80500000000000005</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="13">
         <v>1.46</v>
       </c>
-      <c r="K4" s="38" t="s">
+      <c r="K4" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="13">
         <v>4113.55</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="14">
         <v>5110</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="15">
         <v>1.4194</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="16">
         <v>85.17</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="11">
         <v>1419.2</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="11">
         <v>1</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="11">
         <v>850</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="13">
         <v>0.80500000000000005</v>
       </c>
-      <c r="T4" s="33">
+      <c r="T4" s="11">
         <v>45</v>
       </c>
-      <c r="U4" s="34">
+      <c r="U4" s="15">
         <v>5.2900000000000003E-2</v>
       </c>
-      <c r="V4" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="X4" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="33" t="s">
+      <c r="V4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="11" t="s">
         <v>513</v>
       </c>
-      <c r="AB4" s="33" t="s">
+      <c r="AB4" s="11" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="5" spans="1:28">
-      <c r="A5" s="38">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="12" t="s">
         <v>547</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="E5" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="38">
+      <c r="E5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="11">
         <v>262098</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="H5" s="38">
+      <c r="H5" s="11">
         <v>1300</v>
       </c>
-      <c r="I5" s="39">
+      <c r="I5" s="13">
         <v>1.008</v>
       </c>
-      <c r="J5" s="39">
+      <c r="J5" s="13">
         <v>2.23</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="K5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="35">
+      <c r="L5" s="13">
         <v>2922.192</v>
       </c>
-      <c r="M5" s="37">
+      <c r="M5" s="14">
         <v>1449.5</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="15">
         <v>0.20130000000000001</v>
       </c>
-      <c r="O5" s="36">
+      <c r="O5" s="16">
         <v>12.08</v>
       </c>
-      <c r="P5" s="33">
+      <c r="P5" s="11">
         <v>1008.2</v>
       </c>
-      <c r="Q5" s="33">
+      <c r="Q5" s="11">
         <v>2</v>
       </c>
-      <c r="R5" s="33">
+      <c r="R5" s="11">
         <v>850</v>
       </c>
-      <c r="S5" s="35">
+      <c r="S5" s="13">
         <v>2.016</v>
       </c>
-      <c r="T5" s="33">
+      <c r="T5" s="11">
         <v>-1166</v>
       </c>
-      <c r="U5" s="34">
+      <c r="U5" s="15">
         <v>-1.3717999999999999</v>
       </c>
-      <c r="V5" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="W5" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="X5" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z5" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA5" s="33" t="s">
+      <c r="V5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AB5" s="33" t="s">
+      <c r="AB5" s="11" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="6" spans="1:28">
-      <c r="A6" s="38">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="12" t="s">
         <v>547</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="E6" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="38">
+      <c r="E6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="11">
         <v>262100</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="11">
         <v>1000</v>
       </c>
-      <c r="I6" s="39">
+      <c r="I6" s="13">
         <v>0.8</v>
       </c>
-      <c r="J6" s="39">
+      <c r="J6" s="13">
         <v>1.3240000000000001</v>
       </c>
-      <c r="K6" s="38" t="s">
+      <c r="K6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="35">
+      <c r="L6" s="13">
         <v>1059.2</v>
       </c>
-      <c r="M6" s="37">
+      <c r="M6" s="14">
         <v>1324</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="15">
         <v>0.36780000000000002</v>
       </c>
-      <c r="O6" s="36">
+      <c r="O6" s="16">
         <v>22.07</v>
       </c>
-      <c r="P6" s="33">
+      <c r="P6" s="11">
         <v>365.4</v>
       </c>
-      <c r="Q6" s="33">
+      <c r="Q6" s="11">
         <v>1</v>
       </c>
-      <c r="R6" s="33">
+      <c r="R6" s="11">
         <v>850</v>
       </c>
-      <c r="S6" s="35">
+      <c r="S6" s="13">
         <v>0.8</v>
       </c>
-      <c r="T6" s="33">
+      <c r="T6" s="11">
         <v>50</v>
       </c>
-      <c r="U6" s="34">
+      <c r="U6" s="15">
         <v>5.8799999999999998E-2</v>
       </c>
-      <c r="V6" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="W6" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="X6" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y6" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z6" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA6" s="33" t="s">
+      <c r="V6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="AB6" s="33" t="s">
+      <c r="AB6" s="11" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="7" spans="1:28">
-      <c r="A7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="32">
+      <c r="A7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="18">
         <v>5970</v>
       </c>
-      <c r="I7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" s="31">
+      <c r="I7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="18">
         <v>3234</v>
       </c>
-      <c r="Q7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="R7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="S7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="T7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="U7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="V7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="W7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB7" s="31" t="s">
+      <c r="Q7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="T7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="X7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB7" s="18" t="s">
         <v>27</v>
       </c>
     </row>
@@ -19428,6 +19491,912 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B94081E-63F3-4EB2-9912-4027E5C3741C}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AB10"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.21875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" style="1" customWidth="1"/>
+    <col min="9" max="10" width="5.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.21875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="7.21875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="2.88671875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6" style="1" customWidth="1"/>
+    <col min="19" max="19" width="6.44140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="7.77734375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.6640625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7.44140625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.88671875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="4" style="1" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="137" t="s">
+        <v>571</v>
+      </c>
+      <c r="B1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="137" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="59.4" customHeight="1">
+      <c r="A2" s="136" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="136" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="136" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="136" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="136" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="136" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="136" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="136" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="136" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="136" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="136" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="136" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="136" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="136" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="136" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="136" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="136" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="136" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="136" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="136" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="136" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="136" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="136" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="136" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="136" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="136" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="136" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="136" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="22.05" customHeight="1">
+      <c r="A3" s="112">
+        <v>1</v>
+      </c>
+      <c r="B3" s="113" t="s">
+        <v>556</v>
+      </c>
+      <c r="C3" s="112" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="112" t="s">
+        <v>180</v>
+      </c>
+      <c r="E3" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="112">
+        <v>261904</v>
+      </c>
+      <c r="G3" s="112" t="s">
+        <v>558</v>
+      </c>
+      <c r="H3" s="112">
+        <v>2970</v>
+      </c>
+      <c r="I3" s="114">
+        <v>1.19</v>
+      </c>
+      <c r="J3" s="114">
+        <v>2.59</v>
+      </c>
+      <c r="K3" s="112" t="s">
+        <v>570</v>
+      </c>
+      <c r="L3" s="114">
+        <v>9153.8369999999995</v>
+      </c>
+      <c r="M3" s="115">
+        <v>7692.3</v>
+      </c>
+      <c r="N3" s="116">
+        <v>2.1366999999999998</v>
+      </c>
+      <c r="O3" s="117">
+        <v>128.19999999999999</v>
+      </c>
+      <c r="P3" s="112">
+        <v>5547.2</v>
+      </c>
+      <c r="Q3" s="112">
+        <v>1</v>
+      </c>
+      <c r="R3" s="112">
+        <v>1250</v>
+      </c>
+      <c r="S3" s="114">
+        <v>1.19</v>
+      </c>
+      <c r="T3" s="112">
+        <v>60</v>
+      </c>
+      <c r="U3" s="116">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="V3" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="112" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z3" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="112" t="s">
+        <v>569</v>
+      </c>
+      <c r="AB3" s="112" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="22.05" customHeight="1">
+      <c r="A4" s="112">
+        <v>2</v>
+      </c>
+      <c r="B4" s="113" t="s">
+        <v>556</v>
+      </c>
+      <c r="C4" s="112" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="112" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="112">
+        <v>261902</v>
+      </c>
+      <c r="G4" s="112" t="s">
+        <v>558</v>
+      </c>
+      <c r="H4" s="112">
+        <v>550</v>
+      </c>
+      <c r="I4" s="114">
+        <v>1.0720000000000001</v>
+      </c>
+      <c r="J4" s="114">
+        <v>1.92</v>
+      </c>
+      <c r="K4" s="112" t="s">
+        <v>567</v>
+      </c>
+      <c r="L4" s="114">
+        <v>1132.0319999999999</v>
+      </c>
+      <c r="M4" s="115">
+        <v>1056</v>
+      </c>
+      <c r="N4" s="116">
+        <v>0.29330000000000001</v>
+      </c>
+      <c r="O4" s="117">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="P4" s="112">
+        <v>686</v>
+      </c>
+      <c r="Q4" s="112">
+        <v>1</v>
+      </c>
+      <c r="R4" s="112">
+        <v>1100</v>
+      </c>
+      <c r="S4" s="114">
+        <v>1.0720000000000001</v>
+      </c>
+      <c r="T4" s="112">
+        <v>28</v>
+      </c>
+      <c r="U4" s="116">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="V4" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="112" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z4" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA4" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB4" s="112" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+      <c r="A5" s="112">
+        <v>3</v>
+      </c>
+      <c r="B5" s="113" t="s">
+        <v>556</v>
+      </c>
+      <c r="C5" s="112" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="112" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="112">
+        <v>261899</v>
+      </c>
+      <c r="G5" s="112" t="s">
+        <v>565</v>
+      </c>
+      <c r="H5" s="112">
+        <v>6600</v>
+      </c>
+      <c r="I5" s="114">
+        <v>0.89</v>
+      </c>
+      <c r="J5" s="114">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K5" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="114">
+        <v>6461.4</v>
+      </c>
+      <c r="M5" s="115">
+        <v>7260</v>
+      </c>
+      <c r="N5" s="116">
+        <v>2.0167000000000002</v>
+      </c>
+      <c r="O5" s="117">
+        <v>121</v>
+      </c>
+      <c r="P5" s="112">
+        <v>3915.6</v>
+      </c>
+      <c r="Q5" s="112">
+        <v>1</v>
+      </c>
+      <c r="R5" s="112">
+        <v>950</v>
+      </c>
+      <c r="S5" s="114">
+        <v>0.89</v>
+      </c>
+      <c r="T5" s="112">
+        <v>60</v>
+      </c>
+      <c r="U5" s="116">
+        <v>6.3200000000000006E-2</v>
+      </c>
+      <c r="V5" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="112" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z5" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA5" s="112" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB5" s="112" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+      <c r="A6" s="112">
+        <v>4</v>
+      </c>
+      <c r="B6" s="113" t="s">
+        <v>556</v>
+      </c>
+      <c r="C6" s="112" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="112" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="112">
+        <v>261900</v>
+      </c>
+      <c r="G6" s="112" t="s">
+        <v>561</v>
+      </c>
+      <c r="H6" s="112">
+        <v>355</v>
+      </c>
+      <c r="I6" s="114">
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="J6" s="114">
+        <v>1.74</v>
+      </c>
+      <c r="K6" s="112" t="s">
+        <v>563</v>
+      </c>
+      <c r="L6" s="114">
+        <v>535.54600000000005</v>
+      </c>
+      <c r="M6" s="115">
+        <v>617.70000000000005</v>
+      </c>
+      <c r="N6" s="116">
+        <v>0.1716</v>
+      </c>
+      <c r="O6" s="117">
+        <v>10.29</v>
+      </c>
+      <c r="P6" s="112">
+        <v>324.5</v>
+      </c>
+      <c r="Q6" s="112">
+        <v>1</v>
+      </c>
+      <c r="R6" s="112">
+        <v>900</v>
+      </c>
+      <c r="S6" s="114">
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="T6" s="112">
+        <v>33</v>
+      </c>
+      <c r="U6" s="116">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="V6" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="112" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z6" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA6" s="112" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB6" s="112" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="22.05" customHeight="1">
+      <c r="A7" s="112">
+        <v>5</v>
+      </c>
+      <c r="B7" s="113" t="s">
+        <v>556</v>
+      </c>
+      <c r="C7" s="112" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="112" t="s">
+        <v>180</v>
+      </c>
+      <c r="E7" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="112">
+        <v>261901</v>
+      </c>
+      <c r="G7" s="112" t="s">
+        <v>561</v>
+      </c>
+      <c r="H7" s="112">
+        <v>385</v>
+      </c>
+      <c r="I7" s="114">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="J7" s="114">
+        <v>1.6679999999999999</v>
+      </c>
+      <c r="K7" s="112" t="s">
+        <v>560</v>
+      </c>
+      <c r="L7" s="114">
+        <v>529.798</v>
+      </c>
+      <c r="M7" s="115">
+        <v>642.20000000000005</v>
+      </c>
+      <c r="N7" s="116">
+        <v>0.1784</v>
+      </c>
+      <c r="O7" s="117">
+        <v>10.7</v>
+      </c>
+      <c r="P7" s="112">
+        <v>321.10000000000002</v>
+      </c>
+      <c r="Q7" s="112">
+        <v>1</v>
+      </c>
+      <c r="R7" s="112">
+        <v>850</v>
+      </c>
+      <c r="S7" s="114">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="T7" s="112">
+        <v>25</v>
+      </c>
+      <c r="U7" s="116">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="V7" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="X7" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y7" s="112" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z7" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA7" s="112" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB7" s="112" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="22.05" customHeight="1">
+      <c r="A8" s="112">
+        <v>6</v>
+      </c>
+      <c r="B8" s="113" t="s">
+        <v>556</v>
+      </c>
+      <c r="C8" s="112" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="112" t="s">
+        <v>180</v>
+      </c>
+      <c r="E8" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="112">
+        <v>261903</v>
+      </c>
+      <c r="G8" s="112" t="s">
+        <v>558</v>
+      </c>
+      <c r="H8" s="112">
+        <v>3300</v>
+      </c>
+      <c r="I8" s="114">
+        <v>0.46</v>
+      </c>
+      <c r="J8" s="114">
+        <v>0.95</v>
+      </c>
+      <c r="K8" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="114">
+        <v>1442.1</v>
+      </c>
+      <c r="M8" s="115">
+        <v>1045</v>
+      </c>
+      <c r="N8" s="116">
+        <v>9.6799999999999997E-2</v>
+      </c>
+      <c r="O8" s="117">
+        <v>5.81</v>
+      </c>
+      <c r="P8" s="112">
+        <v>497.5</v>
+      </c>
+      <c r="Q8" s="112">
+        <v>3</v>
+      </c>
+      <c r="R8" s="112">
+        <v>1400</v>
+      </c>
+      <c r="S8" s="114">
+        <v>1.38</v>
+      </c>
+      <c r="T8" s="112">
+        <v>20</v>
+      </c>
+      <c r="U8" s="116">
+        <v>1.43E-2</v>
+      </c>
+      <c r="V8" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="W8" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="X8" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y8" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB8" s="112" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" ht="22.05" customHeight="1">
+      <c r="A9" s="112">
+        <v>7</v>
+      </c>
+      <c r="B9" s="113" t="s">
+        <v>556</v>
+      </c>
+      <c r="C9" s="112" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="112" t="s">
+        <v>180</v>
+      </c>
+      <c r="E9" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="112">
+        <v>261898</v>
+      </c>
+      <c r="G9" s="112" t="s">
+        <v>555</v>
+      </c>
+      <c r="H9" s="112">
+        <v>2200</v>
+      </c>
+      <c r="I9" s="114">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="J9" s="114">
+        <v>1.04</v>
+      </c>
+      <c r="K9" s="112" t="s">
+        <v>554</v>
+      </c>
+      <c r="L9" s="114">
+        <v>919.77599999999995</v>
+      </c>
+      <c r="M9" s="115">
+        <v>1144</v>
+      </c>
+      <c r="N9" s="116">
+        <v>0.15890000000000001</v>
+      </c>
+      <c r="O9" s="117">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="P9" s="112">
+        <v>317.3</v>
+      </c>
+      <c r="Q9" s="112">
+        <v>2</v>
+      </c>
+      <c r="R9" s="112">
+        <v>850</v>
+      </c>
+      <c r="S9" s="114">
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="T9" s="112">
+        <v>46</v>
+      </c>
+      <c r="U9" s="116">
+        <v>5.4100000000000002E-2</v>
+      </c>
+      <c r="V9" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="W9" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="X9" s="112" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y9" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="112" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB9" s="112" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" ht="22.05" customHeight="1">
+      <c r="A10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="118">
+        <v>16360</v>
+      </c>
+      <c r="I10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" s="118">
+        <v>11609.3</v>
+      </c>
+      <c r="Q10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="R10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="S10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="T10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="U10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="V10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="W10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="X10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB10" s="118" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" scale="99" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19469,88 +20438,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="130" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="115" t="s">
+      <c r="B1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="131" t="s">
         <v>27</v>
       </c>
     </row>
@@ -21665,88 +22634,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="131" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="115" t="s">
+      <c r="B1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="131" t="s">
         <v>27</v>
       </c>
     </row>
@@ -22227,88 +23196,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="130" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="114" t="s">
+      <c r="B1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="130" t="s">
         <v>27</v>
       </c>
     </row>
@@ -23474,88 +24443,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="132" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="116" t="s">
+      <c r="B1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="132" t="s">
         <v>27</v>
       </c>
     </row>
@@ -24038,88 +25007,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="133" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="117" t="s">
+      <c r="B1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="133" t="s">
         <v>27</v>
       </c>
     </row>
@@ -25025,88 +25994,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="130" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="114" t="s">
+      <c r="B1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="130" t="s">
         <v>27</v>
       </c>
     </row>
@@ -25842,88 +26811,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="129" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="113" t="s">
+      <c r="B1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="129" t="s">
         <v>27</v>
       </c>
     </row>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,41 +8,41 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5639FEA7-EB4E-46EC-8A7F-1F380BA17B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0FABA7-42E7-4A1D-A5D8-A45EF9E14AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="21" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DR  VÔ CHICO S MIGUEL - 1051" sheetId="60" r:id="rId1"/>
-    <sheet name="ABAPEL 8023" sheetId="22" r:id="rId2"/>
-    <sheet name="HARMONY 1031" sheetId="30" r:id="rId3"/>
-    <sheet name="DR Embalagem - UPAPER 1032" sheetId="31" r:id="rId4"/>
-    <sheet name="Renovapel 1034" sheetId="34" r:id="rId5"/>
+    <sheet name="DR  VÔ CHICO S MIGUEL - 1051 M" sheetId="60" r:id="rId1"/>
+    <sheet name="ABAPEL 8023 M" sheetId="22" r:id="rId2"/>
+    <sheet name="HARMONY 1031 M" sheetId="30" r:id="rId3"/>
+    <sheet name="DR Embalagem - UPAPER 1032 M" sheetId="31" r:id="rId4"/>
+    <sheet name="Renovapel 1034 M" sheetId="34" r:id="rId5"/>
     <sheet name="DANPACK 1036" sheetId="35" r:id="rId6"/>
-    <sheet name="UPAPER 1039" sheetId="38" r:id="rId7"/>
-    <sheet name="FAVINCO 1049" sheetId="44" r:id="rId8"/>
-    <sheet name="FAVINCO 1054" sheetId="47" r:id="rId9"/>
-    <sheet name="PCBOX  - IPE EMB 1060" sheetId="49" r:id="rId10"/>
-    <sheet name="IPE  - PCBOX 1063" sheetId="51" r:id="rId11"/>
-    <sheet name="PCBOX IPE 1065" sheetId="52" r:id="rId12"/>
-    <sheet name="FAVINCO 1066" sheetId="53" r:id="rId13"/>
-    <sheet name="ABAPEL 1067" sheetId="54" r:id="rId14"/>
-    <sheet name="Tolecaixas 1070" sheetId="56" r:id="rId15"/>
-    <sheet name="Renovapel 1072 " sheetId="57" r:id="rId16"/>
+    <sheet name="UPAPER 1039 M" sheetId="38" r:id="rId7"/>
+    <sheet name="FAVINCO 1049 M" sheetId="44" r:id="rId8"/>
+    <sheet name="FAVINCO 1054 M" sheetId="47" r:id="rId9"/>
+    <sheet name="PCBOX  - IPE EMB 1060 M" sheetId="49" r:id="rId10"/>
+    <sheet name="IPE  - PCBOX 1063 M" sheetId="51" r:id="rId11"/>
+    <sheet name="PCBOX IPE 1065 M" sheetId="52" r:id="rId12"/>
+    <sheet name="FAVINCO 1066 M" sheetId="53" r:id="rId13"/>
+    <sheet name="ABAPEL 1067 M" sheetId="54" r:id="rId14"/>
+    <sheet name="Tolecaixas 1070 M" sheetId="56" r:id="rId15"/>
+    <sheet name="Renovapel 1072  M" sheetId="57" r:id="rId16"/>
     <sheet name="HARMONY EMBALAGENS 1073" sheetId="58" r:id="rId17"/>
-    <sheet name="ABAPEL 1074" sheetId="63" r:id="rId18"/>
+    <sheet name="ABAPEL 1074 M" sheetId="63" r:id="rId18"/>
     <sheet name="CARPEL 1078" sheetId="67" r:id="rId19"/>
     <sheet name="ABAPEL 1079" sheetId="68" r:id="rId20"/>
     <sheet name="HARMONY EMBALAGENS 1080" sheetId="69" r:id="rId21"/>
     <sheet name="FAVINCO 1081" sheetId="70" r:id="rId22"/>
-    <sheet name="PCBOX - IPE EMB 1085" sheetId="73" r:id="rId23"/>
+    <sheet name="PCBOX - IPE EMB 1085 M" sheetId="73" r:id="rId23"/>
     <sheet name="RM EMBALAGENS  1087" sheetId="74" r:id="rId24"/>
     <sheet name="ABAPEL 1046" sheetId="75" r:id="rId25"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023'!$A$1:$AB$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'DR Embalagem - UPAPER 1032'!$A$1:$AB$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'HARMONY 1031'!$A$1:$AB$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023 M'!$A$1:$AB$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'DR Embalagem - UPAPER 1032 M'!$A$1:$AB$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'HARMONY 1031 M'!$A$1:$AB$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1790,7 +1790,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2336,6 +2336,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -2354,9 +2357,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2581,7 +2581,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="23.44140625" style="3" customWidth="1"/>
@@ -2612,93 +2612,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="129" t="s">
         <v>309</v>
       </c>
-      <c r="B1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="128" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="30" customHeight="1">
+      <c r="B1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="129" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="38">
         <v>1</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="38">
         <v>2</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>3</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>4</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>5</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>6</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>7</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1">
+    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>27</v>
       </c>
@@ -3484,7 +3484,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6468C93-3B43-46CB-8998-F687C6A9465C}">
   <dimension ref="A1:AB9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
@@ -3516,93 +3516,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="129" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="128" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="52.8" customHeight="1">
+      <c r="B1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="129" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="38">
         <v>1</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="38">
         <v>2</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>3</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>4</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>5</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>6</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
         <v>27</v>
       </c>
@@ -4304,7 +4304,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -4335,93 +4335,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="133" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="134" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="133" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="48" customHeight="1">
+      <c r="B1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="134" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -4937,7 +4937,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1">
+    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -5210,7 +5210,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB16"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" style="3" hidden="1" customWidth="1"/>
@@ -5241,93 +5241,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="130" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="131" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="130" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="53.4" customHeight="1">
+      <c r="B1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="131" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58">
         <v>1</v>
       </c>
@@ -5499,7 +5499,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="58">
         <v>2</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58">
         <v>1</v>
       </c>
@@ -5671,7 +5671,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="58">
         <v>2</v>
       </c>
@@ -5757,7 +5757,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58">
         <v>3</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="58">
         <v>4</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58">
         <v>5</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="58">
         <v>6</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58">
         <v>7</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="12" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="58">
         <v>8</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="13" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58">
         <v>9</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="14" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="58">
         <v>10</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="15" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58">
         <v>11</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="16" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="68" t="s">
         <v>27</v>
       </c>
@@ -6626,7 +6626,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="3" customWidth="1"/>
     <col min="2" max="2" width="11" style="3" customWidth="1"/>
@@ -6658,93 +6658,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="129" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="128" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1">
+      <c r="B1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="129" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="56">
         <v>1</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="56">
         <v>2</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="17" customFormat="1" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" s="17" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="56">
         <v>3</v>
       </c>
@@ -7076,7 +7076,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="32" t="s">
         <v>27</v>
       </c>
@@ -7177,7 +7177,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="1.109375" style="1" hidden="1" customWidth="1"/>
@@ -7208,93 +7208,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="133" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="134" t="s">
         <v>343</v>
       </c>
-      <c r="B1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="133" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1">
+      <c r="B1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="134" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -7380,7 +7380,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="47" customFormat="1" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" s="47" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="47">
         <v>1</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="50">
         <v>2</v>
       </c>
@@ -7549,7 +7549,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="50">
         <v>3</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="50">
         <v>4</v>
       </c>
@@ -7721,7 +7721,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50">
         <v>5</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50">
         <v>6</v>
       </c>
@@ -7893,7 +7893,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="50">
         <v>7</v>
       </c>
@@ -7979,7 +7979,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50">
         <v>8</v>
       </c>
@@ -8065,7 +8065,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="50">
         <v>9</v>
       </c>
@@ -8151,7 +8151,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="25.05" customHeight="1">
+    <row r="12" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -8252,7 +8252,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.109375" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
@@ -8283,93 +8283,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="128" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="129" t="s">
         <v>364</v>
       </c>
-      <c r="B1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="128" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="44.4" customHeight="1">
+      <c r="B1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="129" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -8455,7 +8455,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="38">
         <v>1</v>
       </c>
@@ -8541,7 +8541,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="38">
         <v>2</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>3</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>4</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>5</v>
       </c>
@@ -8885,7 +8885,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
         <v>27</v>
       </c>
@@ -8986,7 +8986,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" style="3" hidden="1" customWidth="1"/>
@@ -9018,93 +9018,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="130" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="131" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="130" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="62.4" customHeight="1">
+      <c r="B1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="131" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -9190,7 +9190,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -9362,7 +9362,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -9620,7 +9620,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -9706,7 +9706,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -9878,7 +9878,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>27</v>
       </c>
@@ -9976,7 +9976,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{823A5C13-D88D-428D-8A9C-6D7FD6C65A08}">
   <dimension ref="A1:AB20"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -10007,93 +10007,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="21" customFormat="1" ht="18" customHeight="1">
-      <c r="A1" s="134" t="s">
+    <row r="1" spans="1:28" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="135" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="134" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" s="21" customFormat="1" ht="60.6" customHeight="1">
+      <c r="B1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="135" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" s="21" customFormat="1" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -10179,7 +10179,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="21" customFormat="1">
+    <row r="3" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -10265,7 +10265,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1">
+    <row r="4" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -10351,7 +10351,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="21" customFormat="1">
+    <row r="5" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -10437,7 +10437,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="21" customFormat="1">
+    <row r="6" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -10523,7 +10523,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="21" customFormat="1">
+    <row r="7" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -10609,7 +10609,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="21" customFormat="1">
+    <row r="8" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="21" customFormat="1">
+    <row r="9" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -10781,7 +10781,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="21" customFormat="1">
+    <row r="10" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -10867,7 +10867,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="21" customFormat="1">
+    <row r="11" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="21" customFormat="1">
+    <row r="12" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -11039,7 +11039,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="21" customFormat="1">
+    <row r="13" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -11125,7 +11125,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="21" customFormat="1">
+    <row r="14" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -11211,7 +11211,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="21" customFormat="1">
+    <row r="15" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -11297,7 +11297,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="21" customFormat="1">
+    <row r="16" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>14</v>
       </c>
@@ -11383,7 +11383,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="17" spans="1:28" s="21" customFormat="1">
+    <row r="17" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>15</v>
       </c>
@@ -11469,7 +11469,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="18" spans="1:28" s="21" customFormat="1">
+    <row r="18" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>16</v>
       </c>
@@ -11555,7 +11555,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="19" spans="1:28" s="21" customFormat="1">
+    <row r="19" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>17</v>
       </c>
@@ -11641,7 +11641,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="20" spans="1:28" s="21" customFormat="1">
+    <row r="20" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -11741,7 +11741,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -11774,93 +11774,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="133" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="134" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="133" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="60" customHeight="1">
+      <c r="B1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="134" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -11946,7 +11946,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" customFormat="1" ht="21.6" customHeight="1">
+    <row r="3" spans="1:28" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="83">
         <v>1</v>
       </c>
@@ -12032,7 +12032,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="76">
         <v>1</v>
       </c>
@@ -12118,7 +12118,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="70">
         <v>2</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="83">
         <v>2</v>
       </c>
@@ -12290,7 +12290,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="70">
         <v>3</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>1</v>
       </c>
@@ -12462,7 +12462,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="83">
         <v>3</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.8" customHeight="1">
+    <row r="10" spans="1:28" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="83">
         <v>4</v>
       </c>
@@ -12634,7 +12634,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -12732,7 +12732,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1FA60D2-9EE8-4466-8FFC-C8F46CF7934D}">
   <dimension ref="A1:AB23"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -12763,93 +12763,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="134" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="135" t="s">
         <v>489</v>
       </c>
-      <c r="B1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="134" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="30" customHeight="1">
+      <c r="B1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="135" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -12935,7 +12935,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -13021,7 +13021,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -13193,7 +13193,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -13279,7 +13279,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -13365,7 +13365,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -13537,7 +13537,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -13623,7 +13623,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -13709,7 +13709,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -13795,7 +13795,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -13881,7 +13881,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -13967,7 +13967,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -14053,7 +14053,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>14</v>
       </c>
@@ -14139,7 +14139,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="17" spans="1:28">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>15</v>
       </c>
@@ -14225,7 +14225,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="18" spans="1:28">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>16</v>
       </c>
@@ -14311,7 +14311,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="19" spans="1:28">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>17</v>
       </c>
@@ -14397,7 +14397,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="20" spans="1:28">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>18</v>
       </c>
@@ -14483,7 +14483,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="21" spans="1:28">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>19</v>
       </c>
@@ -14569,7 +14569,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="22" spans="1:28">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>20</v>
       </c>
@@ -14655,7 +14655,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="23" spans="1:28">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>27</v>
       </c>
@@ -14755,7 +14755,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
@@ -14786,93 +14786,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18.600000000000001" customHeight="1">
-      <c r="A1" s="129" t="s">
+    <row r="1" spans="1:28" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="130" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="129" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1">
+      <c r="B1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="130" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -14958,7 +14958,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="3" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -15044,7 +15044,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -15130,7 +15130,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -15216,7 +15216,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -15302,7 +15302,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -15388,7 +15388,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="8" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -15474,7 +15474,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="9" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -15560,7 +15560,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="10" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -15658,7 +15658,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6DECCF-0481-438A-8BDD-F0275CF2BE70}">
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -15690,93 +15690,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="135" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="136" t="s">
         <v>493</v>
       </c>
-      <c r="B1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="135" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="52.8" customHeight="1">
+      <c r="B1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="136" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -15862,7 +15862,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="19.8" customHeight="1">
+    <row r="3" spans="1:28" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="109">
         <v>1</v>
       </c>
@@ -15948,7 +15948,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="69" customFormat="1">
+    <row r="4" spans="1:28" s="69" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="124">
         <v>1</v>
       </c>
@@ -16034,7 +16034,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="69" customFormat="1">
+    <row r="5" spans="1:28" s="69" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="124">
         <v>2</v>
       </c>
@@ -16120,7 +16120,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="127" customFormat="1">
+    <row r="6" spans="1:28" s="127" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H6" s="127">
         <v>4340</v>
       </c>
@@ -16140,7 +16140,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{819F2E85-837E-49CE-91A8-B709D04980B6}">
   <dimension ref="A1:AB15"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -16172,93 +16172,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="134" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="135" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="134" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="55.2" customHeight="1">
+      <c r="B1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="135" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -16344,7 +16344,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -16430,7 +16430,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -16516,7 +16516,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -16602,7 +16602,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -16688,7 +16688,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -16774,7 +16774,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -16860,7 +16860,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -16946,7 +16946,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -17032,7 +17032,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -17118,7 +17118,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -17204,7 +17204,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -17290,7 +17290,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -17376,7 +17376,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -17473,7 +17473,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C91923-7AE7-4461-9C2E-05FE2CED0119}">
   <dimension ref="A1:AB4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -17505,93 +17505,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="135" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="136" t="s">
         <v>523</v>
       </c>
-      <c r="B1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="135" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="50.4" customHeight="1">
+      <c r="B1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="136" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -17677,7 +17677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="109">
         <v>1</v>
       </c>
@@ -17763,7 +17763,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="103" t="s">
         <v>27</v>
       </c>
@@ -17863,7 +17863,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -17895,93 +17895,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="129" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="130" t="s">
         <v>539</v>
       </c>
-      <c r="B1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="129" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="39.6" customHeight="1">
+      <c r="B1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="130" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -18067,7 +18067,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="112">
         <v>1</v>
       </c>
@@ -18153,7 +18153,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="112">
         <v>2</v>
       </c>
@@ -18239,7 +18239,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="112">
         <v>3</v>
       </c>
@@ -18325,7 +18325,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="112">
         <v>4</v>
       </c>
@@ -18411,7 +18411,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="112">
         <v>5</v>
       </c>
@@ -18440,7 +18440,7 @@
         <v>0.75</v>
       </c>
       <c r="J7" s="114">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="K7" s="112" t="s">
         <v>34</v>
@@ -18497,7 +18497,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="112">
         <v>6</v>
       </c>
@@ -18583,7 +18583,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="112">
         <v>7</v>
       </c>
@@ -18669,7 +18669,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="112">
         <v>8</v>
       </c>
@@ -18755,7 +18755,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="118" t="s">
         <v>27</v>
       </c>
@@ -18853,7 +18853,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47514BAB-BD75-470F-9A41-8686D45C5BAB}">
   <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.21875" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
@@ -18884,93 +18884,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="131" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="132" t="s">
         <v>552</v>
       </c>
-      <c r="B1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="52.8" customHeight="1">
+      <c r="B1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="132" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -19056,7 +19056,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -19142,7 +19142,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -19228,7 +19228,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -19314,7 +19314,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -19400,7 +19400,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>27</v>
       </c>
@@ -19500,7 +19500,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -19531,7 +19531,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="137" t="s">
         <v>571</v>
       </c>
@@ -19617,93 +19617,93 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="59.4" customHeight="1">
-      <c r="A2" s="136" t="s">
+    <row r="2" spans="1:28" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="136" t="s">
+      <c r="B2" s="128" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="136" t="s">
+      <c r="C2" s="128" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="136" t="s">
+      <c r="D2" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="136" t="s">
+      <c r="E2" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="136" t="s">
+      <c r="F2" s="128" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="136" t="s">
+      <c r="G2" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="136" t="s">
+      <c r="H2" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="136" t="s">
+      <c r="I2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="136" t="s">
+      <c r="J2" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="136" t="s">
+      <c r="K2" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="136" t="s">
+      <c r="L2" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="136" t="s">
+      <c r="M2" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="136" t="s">
+      <c r="N2" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="136" t="s">
+      <c r="O2" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="136" t="s">
+      <c r="P2" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="136" t="s">
+      <c r="Q2" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="136" t="s">
+      <c r="R2" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="136" t="s">
+      <c r="S2" s="128" t="s">
         <v>16</v>
       </c>
-      <c r="T2" s="136" t="s">
+      <c r="T2" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="U2" s="136" t="s">
+      <c r="U2" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="V2" s="136" t="s">
+      <c r="V2" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="W2" s="136" t="s">
+      <c r="W2" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="X2" s="136" t="s">
+      <c r="X2" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" s="136" t="s">
+      <c r="Y2" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="Z2" s="136" t="s">
+      <c r="Z2" s="128" t="s">
         <v>23</v>
       </c>
-      <c r="AA2" s="136" t="s">
+      <c r="AA2" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="AB2" s="136" t="s">
+      <c r="AB2" s="128" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="112">
         <v>1</v>
       </c>
@@ -19789,7 +19789,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="112">
         <v>2</v>
       </c>
@@ -19875,7 +19875,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="112">
         <v>3</v>
       </c>
@@ -19961,7 +19961,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="112">
         <v>4</v>
       </c>
@@ -20047,7 +20047,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="112">
         <v>5</v>
       </c>
@@ -20133,7 +20133,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="112">
         <v>6</v>
       </c>
@@ -20219,7 +20219,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="112">
         <v>7</v>
       </c>
@@ -20305,7 +20305,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1">
+    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="118" t="s">
         <v>27</v>
       </c>
@@ -20406,7 +20406,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB25"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.21875" style="3" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="3" customWidth="1"/>
@@ -20437,93 +20437,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="130" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="131" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="41.4" customHeight="1">
+      <c r="B1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="132" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="132" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -20609,7 +20609,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="3" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>1</v>
       </c>
@@ -20695,7 +20695,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="4" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>2</v>
       </c>
@@ -20781,7 +20781,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="5" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>3</v>
       </c>
@@ -20867,7 +20867,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="6" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>4</v>
       </c>
@@ -20953,7 +20953,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="7" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>5</v>
       </c>
@@ -21039,7 +21039,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="8" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>6</v>
       </c>
@@ -21125,7 +21125,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="9" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>7</v>
       </c>
@@ -21211,7 +21211,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="10" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>8</v>
       </c>
@@ -21297,7 +21297,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="11" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12">
         <v>9</v>
       </c>
@@ -21383,7 +21383,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="12" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12">
         <v>10</v>
       </c>
@@ -21469,7 +21469,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="13" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12">
         <v>11</v>
       </c>
@@ -21555,7 +21555,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="14" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12">
         <v>12</v>
       </c>
@@ -21641,7 +21641,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="15" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12">
         <v>13</v>
       </c>
@@ -21727,7 +21727,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="16" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12">
         <v>14</v>
       </c>
@@ -21813,7 +21813,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="17" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12">
         <v>15</v>
       </c>
@@ -21899,7 +21899,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="18" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12">
         <v>16</v>
       </c>
@@ -21985,7 +21985,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="19" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12">
         <v>17</v>
       </c>
@@ -22071,7 +22071,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="20" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12">
         <v>18</v>
       </c>
@@ -22157,7 +22157,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="21" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12">
         <v>19</v>
       </c>
@@ -22243,7 +22243,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="22" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12">
         <v>20</v>
       </c>
@@ -22329,7 +22329,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="23" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12">
         <v>21</v>
       </c>
@@ -22415,7 +22415,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="24" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12">
         <v>22</v>
       </c>
@@ -22501,7 +22501,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="25" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>27</v>
       </c>
@@ -22602,7 +22602,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.88671875" style="3" customWidth="1"/>
@@ -22633,7 +22633,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="131" t="s">
         <v>126</v>
       </c>
@@ -22719,7 +22719,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="30" customHeight="1">
+    <row r="2" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -22805,7 +22805,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -22891,7 +22891,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -22977,7 +22977,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -23063,7 +23063,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>27</v>
       </c>
@@ -23164,7 +23164,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="11.77734375" style="3" hidden="1" customWidth="1"/>
@@ -23195,93 +23195,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="130" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="131" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="130" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="39.6" customHeight="1">
+      <c r="B1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="131" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -23367,7 +23367,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -23453,7 +23453,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -23539,7 +23539,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -23625,7 +23625,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -23711,7 +23711,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -23797,7 +23797,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -23883,7 +23883,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -23969,7 +23969,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1">
+    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -24055,7 +24055,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="22.05" customHeight="1">
+    <row r="11" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -24141,7 +24141,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="22.05" customHeight="1">
+    <row r="12" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -24227,7 +24227,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="22.05" customHeight="1">
+    <row r="13" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -24313,7 +24313,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="22.05" customHeight="1">
+    <row r="14" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>27</v>
       </c>
@@ -24411,7 +24411,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BE450D-ABF8-4C4B-88DF-0F4B0CF61565}">
   <dimension ref="A1:AB9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
@@ -24442,93 +24442,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="132" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="133" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="132" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="46.8" customHeight="1">
+      <c r="B1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="133" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -24614,7 +24614,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="23">
         <v>1</v>
       </c>
@@ -24700,7 +24700,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="23">
         <v>2</v>
       </c>
@@ -24784,7 +24784,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="23">
         <v>3</v>
       </c>
@@ -24870,7 +24870,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>27</v>
       </c>
@@ -24956,7 +24956,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="G9" s="46"/>
     </row>
   </sheetData>
@@ -24974,7 +24974,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="91" customWidth="1"/>
     <col min="2" max="2" width="9.44140625" style="1" hidden="1" customWidth="1"/>
@@ -25006,93 +25006,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="133" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="134" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="133" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="52.2" customHeight="1">
+      <c r="B1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="134" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="134" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="88" t="s">
         <v>0</v>
       </c>
@@ -25178,7 +25178,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="101" customFormat="1" ht="19.8" customHeight="1">
+    <row r="3" spans="1:28" s="101" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="93">
         <v>1</v>
       </c>
@@ -25258,7 +25258,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="47">
         <v>2</v>
       </c>
@@ -25344,7 +25344,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="47">
         <v>3</v>
       </c>
@@ -25430,7 +25430,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="93">
         <v>4</v>
       </c>
@@ -25516,7 +25516,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="93">
         <v>5</v>
       </c>
@@ -25602,7 +25602,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="93">
         <v>6</v>
       </c>
@@ -25688,7 +25688,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="93">
         <v>7</v>
       </c>
@@ -25774,7 +25774,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="93">
         <v>8</v>
       </c>
@@ -25860,7 +25860,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="90" t="s">
         <v>27</v>
       </c>
@@ -25961,7 +25961,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="10.77734375" style="3" hidden="1" customWidth="1"/>
@@ -25993,93 +25993,93 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="130" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="131" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="130" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="52.8" customHeight="1">
+      <c r="B1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="131" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -26165,7 +26165,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" customFormat="1" ht="22.05" customHeight="1">
+    <row r="3" spans="1:28" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29">
         <v>1</v>
       </c>
@@ -26249,7 +26249,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:28" customFormat="1" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="29">
         <v>2</v>
       </c>
@@ -26333,7 +26333,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="29">
         <v>3</v>
       </c>
@@ -26419,7 +26419,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
         <v>4</v>
       </c>
@@ -26505,7 +26505,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="29">
         <v>5</v>
       </c>
@@ -26591,7 +26591,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="29">
         <v>6</v>
       </c>
@@ -26677,7 +26677,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>27</v>
       </c>
@@ -26763,7 +26763,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1"/>
+    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AB1"/>
@@ -26779,7 +26779,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.77734375" style="1" customWidth="1"/>
@@ -26810,93 +26810,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="129" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="130" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="129" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="54" customHeight="1">
+      <c r="B1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="130" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -26982,7 +26982,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="47" customFormat="1" ht="22.2" customHeight="1">
+    <row r="3" spans="1:28" s="47" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="47">
         <v>1</v>
       </c>
@@ -27059,7 +27059,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="47">
         <v>2</v>
       </c>
@@ -27145,7 +27145,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="47">
         <v>3</v>
       </c>
@@ -27231,7 +27231,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="47">
         <v>4</v>
       </c>
@@ -27317,7 +27317,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>5</v>
       </c>
@@ -27403,7 +27403,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="8" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>6</v>
       </c>
@@ -27489,7 +27489,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="9" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="47">
         <v>7</v>
       </c>
@@ -27575,7 +27575,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="10" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="47">
         <v>8</v>
       </c>
@@ -27661,7 +27661,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="11" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>9</v>
       </c>
@@ -27747,7 +27747,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="12" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47">
         <v>10</v>
       </c>
@@ -27833,7 +27833,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="13" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47">
         <v>11</v>
       </c>
@@ -27913,7 +27913,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="14" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>27</v>
       </c>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0FABA7-42E7-4A1D-A5D8-A45EF9E14AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F168F1BC-1F1B-441A-B46E-8EAEC76264FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="21" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="23" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051 M" sheetId="60" r:id="rId1"/>
@@ -38,6 +38,7 @@
     <sheet name="PCBOX - IPE EMB 1085 M" sheetId="73" r:id="rId23"/>
     <sheet name="RM EMBALAGENS  1087" sheetId="74" r:id="rId24"/>
     <sheet name="ABAPEL 1046" sheetId="75" r:id="rId25"/>
+    <sheet name="CARTOMIL EMBALAGENS LTDA 1089" sheetId="76" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023 M'!$A$1:$AB$10</definedName>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4750" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4884" uniqueCount="579">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1779,6 +1780,27 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA  —  ABAPEL OF: 001046</t>
+  </si>
+  <si>
+    <t>1130x1751</t>
+  </si>
+  <si>
+    <t>58x461x58</t>
+  </si>
+  <si>
+    <t>0508</t>
+  </si>
+  <si>
+    <t>CARTOMIL EMBALAGENS LTDA</t>
+  </si>
+  <si>
+    <t>1174x1720</t>
+  </si>
+  <si>
+    <t>870x2180</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - CARTOMIL EMBALAGENS LTDA  —  OF: 001089</t>
   </si>
 </sst>
 </file>
@@ -1979,7 +2001,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2360,6 +2382,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -20400,6 +20423,650 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7588871-7EF6-4AC9-81DD-CFF44DED789D}">
+  <dimension ref="A1:AB7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.77734375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.21875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="5.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="6.44140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="6" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="8.77734375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="3.77734375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="5.33203125" style="3" customWidth="1"/>
+    <col min="19" max="19" width="6.44140625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="3" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="7.44140625" style="3" customWidth="1"/>
+    <col min="23" max="23" width="8" style="3" customWidth="1"/>
+    <col min="24" max="24" width="7" style="3" customWidth="1"/>
+    <col min="25" max="26" width="11.77734375" style="3" customWidth="1"/>
+    <col min="27" max="27" width="3.6640625" style="3" customWidth="1"/>
+    <col min="28" max="28" width="10.33203125" style="3" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="138" t="s">
+        <v>578</v>
+      </c>
+      <c r="B1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="138" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="38">
+        <v>1</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>492</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="38">
+        <v>262103</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>574</v>
+      </c>
+      <c r="H3" s="38">
+        <v>3500</v>
+      </c>
+      <c r="I3" s="39">
+        <v>0.45</v>
+      </c>
+      <c r="J3" s="39">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="K3" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="35">
+        <v>1031.625</v>
+      </c>
+      <c r="M3" s="37">
+        <v>1146.3</v>
+      </c>
+      <c r="N3" s="34">
+        <v>0.15920000000000001</v>
+      </c>
+      <c r="O3" s="36">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="P3" s="33">
+        <v>355.9</v>
+      </c>
+      <c r="Q3" s="33">
+        <v>2</v>
+      </c>
+      <c r="R3" s="33">
+        <v>1500</v>
+      </c>
+      <c r="S3" s="35">
+        <v>0.9</v>
+      </c>
+      <c r="T3" s="33">
+        <v>600</v>
+      </c>
+      <c r="U3" s="34">
+        <v>0.4</v>
+      </c>
+      <c r="V3" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB3" s="33" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="38">
+        <v>2</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>492</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="38">
+        <v>262104</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>574</v>
+      </c>
+      <c r="H4" s="38">
+        <v>2000</v>
+      </c>
+      <c r="I4" s="39">
+        <v>0.72</v>
+      </c>
+      <c r="J4" s="39">
+        <v>0.85</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="35">
+        <v>1224</v>
+      </c>
+      <c r="M4" s="37">
+        <v>850</v>
+      </c>
+      <c r="N4" s="34">
+        <v>0.1181</v>
+      </c>
+      <c r="O4" s="36">
+        <v>7.08</v>
+      </c>
+      <c r="P4" s="33">
+        <v>422.3</v>
+      </c>
+      <c r="Q4" s="33">
+        <v>2</v>
+      </c>
+      <c r="R4" s="33">
+        <v>1500</v>
+      </c>
+      <c r="S4" s="35">
+        <v>1.44</v>
+      </c>
+      <c r="T4" s="33">
+        <v>60</v>
+      </c>
+      <c r="U4" s="34">
+        <v>0.04</v>
+      </c>
+      <c r="V4" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB4" s="33" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" s="38">
+        <v>3</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>492</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="38">
+        <v>262105</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>574</v>
+      </c>
+      <c r="H5" s="38">
+        <v>3000</v>
+      </c>
+      <c r="I5" s="39">
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="J5" s="39">
+        <v>0.85</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>573</v>
+      </c>
+      <c r="L5" s="35">
+        <v>1471.35</v>
+      </c>
+      <c r="M5" s="37">
+        <v>1275</v>
+      </c>
+      <c r="N5" s="34">
+        <v>0.17710000000000001</v>
+      </c>
+      <c r="O5" s="36">
+        <v>10.63</v>
+      </c>
+      <c r="P5" s="33">
+        <v>541.5</v>
+      </c>
+      <c r="Q5" s="33">
+        <v>2</v>
+      </c>
+      <c r="R5" s="33">
+        <v>1200</v>
+      </c>
+      <c r="S5" s="35">
+        <v>1.1539999999999999</v>
+      </c>
+      <c r="T5" s="33">
+        <v>46</v>
+      </c>
+      <c r="U5" s="34">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="V5" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="W5" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="X5" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB5" s="33" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" s="38">
+        <v>4</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>492</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="38">
+        <v>262106</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>574</v>
+      </c>
+      <c r="H6" s="38">
+        <v>2100</v>
+      </c>
+      <c r="I6" s="39">
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="J6" s="39">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="K6" s="38" t="s">
+        <v>573</v>
+      </c>
+      <c r="L6" s="35">
+        <v>1344.9870000000001</v>
+      </c>
+      <c r="M6" s="37">
+        <v>1165.5</v>
+      </c>
+      <c r="N6" s="34">
+        <v>0.16189999999999999</v>
+      </c>
+      <c r="O6" s="36">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="P6" s="33">
+        <v>495</v>
+      </c>
+      <c r="Q6" s="33">
+        <v>2</v>
+      </c>
+      <c r="R6" s="33">
+        <v>1200</v>
+      </c>
+      <c r="S6" s="35">
+        <v>1.1539999999999999</v>
+      </c>
+      <c r="T6" s="33">
+        <v>46</v>
+      </c>
+      <c r="U6" s="34">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="V6" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="W6" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="X6" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB6" s="33" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="32">
+        <v>10600</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="31">
+        <v>1814.6</v>
+      </c>
+      <c r="Q7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="T7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="X7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB7" s="31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8560783-F1AE-41B7-817A-6D1BAC7508D9}">
   <sheetPr>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F168F1BC-1F1B-441A-B46E-8EAEC76264FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB7D65A-7AFC-4479-A0F0-6198204999FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="23" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="24" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051 M" sheetId="60" r:id="rId1"/>
@@ -29,16 +29,17 @@
     <sheet name="ABAPEL 1067 M" sheetId="54" r:id="rId14"/>
     <sheet name="Tolecaixas 1070 M" sheetId="56" r:id="rId15"/>
     <sheet name="Renovapel 1072  M" sheetId="57" r:id="rId16"/>
-    <sheet name="HARMONY EMBALAGENS 1073" sheetId="58" r:id="rId17"/>
+    <sheet name="HARMONY EMBALAGENS 1073 P" sheetId="58" r:id="rId17"/>
     <sheet name="ABAPEL 1074 M" sheetId="63" r:id="rId18"/>
     <sheet name="CARPEL 1078" sheetId="67" r:id="rId19"/>
-    <sheet name="ABAPEL 1079" sheetId="68" r:id="rId20"/>
-    <sheet name="HARMONY EMBALAGENS 1080" sheetId="69" r:id="rId21"/>
+    <sheet name="ABAPEL 1079 M" sheetId="68" r:id="rId20"/>
+    <sheet name="HARMONY EMBALAGENS 1080 P" sheetId="69" r:id="rId21"/>
     <sheet name="FAVINCO 1081" sheetId="70" r:id="rId22"/>
     <sheet name="PCBOX - IPE EMB 1085 M" sheetId="73" r:id="rId23"/>
-    <sheet name="RM EMBALAGENS  1087" sheetId="74" r:id="rId24"/>
-    <sheet name="ABAPEL 1046" sheetId="75" r:id="rId25"/>
-    <sheet name="CARTOMIL EMBALAGENS LTDA 1089" sheetId="76" r:id="rId26"/>
+    <sheet name="RM EMBALAGENS 1087 P" sheetId="74" r:id="rId24"/>
+    <sheet name="ABAPEL 1046 P" sheetId="75" r:id="rId25"/>
+    <sheet name="CARTOMIL EMBALAGENS LTDA 1089 P" sheetId="76" r:id="rId26"/>
+    <sheet name="UPAPER 1090" sheetId="77" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023 M'!$A$1:$AB$10</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4884" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4992" uniqueCount="582">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1801,6 +1802,15 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA - CARTOMIL EMBALAGENS LTDA  —  OF: 001089</t>
+  </si>
+  <si>
+    <t>2046</t>
+  </si>
+  <si>
+    <t>35789</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - Z4A EMBALAGENS  —  OF: 001090</t>
   </si>
 </sst>
 </file>
@@ -1812,11 +1822,18 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1998,125 +2015,125 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2125,26 +2142,115 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="14" fontId="14" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2157,232 +2263,168 @@
     <xf numFmtId="2" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="14" fontId="13" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="19" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2636,88 +2678,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="120" t="s">
         <v>309</v>
       </c>
-      <c r="B1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="129" t="s">
+      <c r="B1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="120" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3540,88 +3582,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="120" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="129" t="s">
+      <c r="B1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="120" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4359,88 +4401,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="125" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="134" t="s">
+      <c r="B1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="125" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5265,88 +5307,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="122" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="131" t="s">
+      <c r="B1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="122" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6682,88 +6724,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="120" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="129" t="s">
+      <c r="B1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="120" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7232,88 +7274,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="125" t="s">
         <v>343</v>
       </c>
-      <c r="B1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="134" t="s">
+      <c r="B1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="125" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8307,88 +8349,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="120" t="s">
         <v>364</v>
       </c>
-      <c r="B1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="129" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="129" t="s">
+      <c r="B1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="120" t="s">
         <v>27</v>
       </c>
     </row>
@@ -9042,88 +9084,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="122" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="131" t="s">
+      <c r="B1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="122" t="s">
         <v>27</v>
       </c>
     </row>
@@ -9998,6 +10040,9 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{823A5C13-D88D-428D-8A9C-6D7FD6C65A08}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AB20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10031,88 +10076,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="125" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="135" t="s">
+      <c r="B1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="125" t="s">
         <v>27</v>
       </c>
     </row>
@@ -10202,7 +10247,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -10288,7 +10333,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -10374,7 +10419,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -10460,7 +10505,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -10546,7 +10591,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -10632,7 +10677,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -10718,7 +10763,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -10804,7 +10849,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -10890,7 +10935,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -10976,7 +11021,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -11062,7 +11107,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -11148,7 +11193,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -11234,7 +11279,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -11320,7 +11365,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>14</v>
       </c>
@@ -11406,7 +11451,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="17" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>15</v>
       </c>
@@ -11492,7 +11537,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="18" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>16</v>
       </c>
@@ -11578,7 +11623,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="19" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>17</v>
       </c>
@@ -11664,7 +11709,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="20" spans="1:28" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -11755,6 +11800,7 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" scale="87" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11798,88 +11844,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="125" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="134" t="s">
+      <c r="B1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="125" t="s">
         <v>27</v>
       </c>
     </row>
@@ -12787,88 +12833,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="126" t="s">
         <v>489</v>
       </c>
-      <c r="B1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="135" t="s">
+      <c r="B1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="126" t="s">
         <v>27</v>
       </c>
     </row>
@@ -14810,88 +14856,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="121" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="130" t="s">
+      <c r="B1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="121" t="s">
         <v>27</v>
       </c>
     </row>
@@ -15680,6 +15726,9 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6DECCF-0481-438A-8BDD-F0275CF2BE70}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AB6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15714,88 +15763,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="121" t="s">
         <v>493</v>
       </c>
-      <c r="B1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="136" t="s">
+      <c r="B1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="121" t="s">
         <v>27</v>
       </c>
     </row>
@@ -15885,269 +15934,269 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="109">
+    <row r="3" spans="1:28" s="136" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="128">
         <v>1</v>
       </c>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="109" t="s">
+      <c r="C3" s="128" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="109" t="s">
+      <c r="D3" s="128" t="s">
         <v>492</v>
       </c>
-      <c r="E3" s="109" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="109">
+      <c r="E3" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="128">
         <v>262067</v>
       </c>
-      <c r="G3" s="109" t="s">
+      <c r="G3" s="128" t="s">
         <v>491</v>
       </c>
-      <c r="H3" s="109">
+      <c r="H3" s="128">
         <v>340</v>
       </c>
-      <c r="I3" s="110">
+      <c r="I3" s="130">
         <v>0.97699999999999998</v>
       </c>
-      <c r="J3" s="110">
+      <c r="J3" s="130">
         <v>2.06</v>
       </c>
-      <c r="K3" s="109" t="s">
+      <c r="K3" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="106">
+      <c r="L3" s="131">
         <v>684.29100000000005</v>
       </c>
-      <c r="M3" s="108">
+      <c r="M3" s="132">
         <v>700.4</v>
       </c>
-      <c r="N3" s="105">
+      <c r="N3" s="133">
         <v>0.1946</v>
       </c>
-      <c r="O3" s="107">
+      <c r="O3" s="134">
         <v>11.67</v>
       </c>
-      <c r="P3" s="104">
+      <c r="P3" s="135">
         <v>405.8</v>
       </c>
-      <c r="Q3" s="104">
+      <c r="Q3" s="135">
         <v>1</v>
       </c>
-      <c r="R3" s="104">
+      <c r="R3" s="135">
         <v>1000</v>
       </c>
-      <c r="S3" s="106">
+      <c r="S3" s="131">
         <v>0.97699999999999998</v>
       </c>
-      <c r="T3" s="104">
+      <c r="T3" s="135">
         <v>23</v>
       </c>
-      <c r="U3" s="105">
+      <c r="U3" s="133">
         <v>2.3E-2</v>
       </c>
-      <c r="V3" s="104" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="104" t="s">
+      <c r="V3" s="135" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="X3" s="104" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="104" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z3" s="104" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA3" s="104" t="s">
+      <c r="X3" s="135" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="135" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="135" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="135" t="s">
         <v>39</v>
       </c>
-      <c r="AB3" s="104" t="s">
+      <c r="AB3" s="135" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="69" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="124">
+    <row r="4" spans="1:28" s="145" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="137">
         <v>1</v>
       </c>
-      <c r="B4" s="126" t="s">
+      <c r="B4" s="138" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="124" t="s">
+      <c r="C4" s="137" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="124" t="s">
+      <c r="D4" s="137" t="s">
         <v>492</v>
       </c>
-      <c r="E4" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="124">
+      <c r="E4" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="137">
         <v>262097</v>
       </c>
-      <c r="G4" s="124" t="s">
+      <c r="G4" s="137" t="s">
         <v>542</v>
       </c>
-      <c r="H4" s="124">
+      <c r="H4" s="137">
         <v>2000</v>
       </c>
-      <c r="I4" s="125">
+      <c r="I4" s="139">
         <v>0.39200000000000002</v>
       </c>
-      <c r="J4" s="125">
+      <c r="J4" s="139">
         <v>1.28</v>
       </c>
-      <c r="K4" s="124" t="s">
+      <c r="K4" s="137" t="s">
         <v>544</v>
       </c>
-      <c r="L4" s="121">
+      <c r="L4" s="140">
         <v>1003.52</v>
       </c>
-      <c r="M4" s="123">
+      <c r="M4" s="141">
         <v>1280</v>
       </c>
-      <c r="N4" s="120">
+      <c r="N4" s="142">
         <v>0.17780000000000001</v>
       </c>
-      <c r="O4" s="122">
+      <c r="O4" s="143">
         <v>10.67</v>
       </c>
-      <c r="P4" s="119">
+      <c r="P4" s="144">
         <v>346.2</v>
       </c>
-      <c r="Q4" s="119">
+      <c r="Q4" s="144">
         <v>2</v>
       </c>
-      <c r="R4" s="119">
+      <c r="R4" s="144">
         <v>850</v>
       </c>
-      <c r="S4" s="121">
+      <c r="S4" s="140">
         <v>0.78400000000000003</v>
       </c>
-      <c r="T4" s="119">
+      <c r="T4" s="144">
         <v>66</v>
       </c>
-      <c r="U4" s="120">
+      <c r="U4" s="142">
         <v>7.7600000000000002E-2</v>
       </c>
-      <c r="V4" s="119" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="119" t="s">
-        <v>28</v>
-      </c>
-      <c r="X4" s="119" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="119" t="s">
+      <c r="V4" s="144" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="144" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="144" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="144" t="s">
         <v>33</v>
       </c>
-      <c r="AB4" s="119" t="s">
+      <c r="AB4" s="144" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="69" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="124">
+    <row r="5" spans="1:28" s="145" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="137">
         <v>2</v>
       </c>
-      <c r="B5" s="126" t="s">
+      <c r="B5" s="138" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="124" t="s">
+      <c r="C5" s="137" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="124" t="s">
+      <c r="D5" s="137" t="s">
         <v>492</v>
       </c>
-      <c r="E5" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="124">
+      <c r="E5" s="137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="137">
         <v>262096</v>
       </c>
-      <c r="G5" s="124" t="s">
+      <c r="G5" s="137" t="s">
         <v>542</v>
       </c>
-      <c r="H5" s="124">
+      <c r="H5" s="137">
         <v>2000</v>
       </c>
-      <c r="I5" s="125">
+      <c r="I5" s="139">
         <v>0.375</v>
       </c>
-      <c r="J5" s="125">
+      <c r="J5" s="139">
         <v>1.28</v>
       </c>
-      <c r="K5" s="124" t="s">
+      <c r="K5" s="137" t="s">
         <v>541</v>
       </c>
-      <c r="L5" s="121">
+      <c r="L5" s="140">
         <v>960</v>
       </c>
-      <c r="M5" s="123">
+      <c r="M5" s="141">
         <v>1280</v>
       </c>
-      <c r="N5" s="120">
+      <c r="N5" s="142">
         <v>0.17780000000000001</v>
       </c>
-      <c r="O5" s="122">
+      <c r="O5" s="143">
         <v>10.67</v>
       </c>
-      <c r="P5" s="119">
+      <c r="P5" s="144">
         <v>331.2</v>
       </c>
-      <c r="Q5" s="119">
+      <c r="Q5" s="144">
         <v>2</v>
       </c>
-      <c r="R5" s="119">
+      <c r="R5" s="144">
         <v>800</v>
       </c>
-      <c r="S5" s="121">
+      <c r="S5" s="140">
         <v>0.75</v>
       </c>
-      <c r="T5" s="119">
+      <c r="T5" s="144">
         <v>50</v>
       </c>
-      <c r="U5" s="120">
+      <c r="U5" s="142">
         <v>6.25E-2</v>
       </c>
-      <c r="V5" s="119" t="s">
-        <v>28</v>
-      </c>
-      <c r="W5" s="119" t="s">
-        <v>28</v>
-      </c>
-      <c r="X5" s="119" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z5" s="119" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA5" s="119" t="s">
+      <c r="V5" s="144" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="144" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="144" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="144" t="s">
         <v>33</v>
       </c>
-      <c r="AB5" s="119" t="s">
+      <c r="AB5" s="144" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="127" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="H6" s="127">
+    <row r="6" spans="1:28" s="146" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H6" s="146">
         <v>4340</v>
       </c>
-      <c r="P6" s="127">
+      <c r="P6" s="146">
         <v>1083</v>
       </c>
     </row>
@@ -16156,12 +16205,15 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{819F2E85-837E-49CE-91A8-B709D04980B6}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AB15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16196,88 +16248,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="125" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="135" t="s">
+      <c r="B1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="125" t="s">
         <v>27</v>
       </c>
     </row>
@@ -16367,7 +16419,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -16453,7 +16505,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -16539,7 +16591,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -16625,7 +16677,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -16711,7 +16763,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -16797,7 +16849,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -16883,7 +16935,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -16969,7 +17021,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -17055,7 +17107,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -17141,7 +17193,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -17227,7 +17279,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -17313,7 +17365,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -17399,7 +17451,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -17490,6 +17542,7 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" scale="93" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -17529,88 +17582,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="127" t="s">
         <v>523</v>
       </c>
-      <c r="B1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="136" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="136" t="s">
+      <c r="B1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="127" t="s">
         <v>27</v>
       </c>
     </row>
@@ -17919,88 +17972,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="121" t="s">
         <v>539</v>
       </c>
-      <c r="B1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="130" t="s">
+      <c r="B1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="121" t="s">
         <v>27</v>
       </c>
     </row>
@@ -18875,6 +18928,9 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47514BAB-BD75-470F-9A41-8686D45C5BAB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -18908,88 +18964,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="122" t="s">
         <v>552</v>
       </c>
-      <c r="B1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="132" t="s">
+      <c r="B1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="122" t="s">
         <v>27</v>
       </c>
     </row>
@@ -19079,7 +19135,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -19165,7 +19221,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -19251,7 +19307,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -19337,7 +19393,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -19423,7 +19479,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>27</v>
       </c>
@@ -19514,6 +19570,7 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup scale="95" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19555,174 +19612,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="147" t="s">
         <v>571</v>
       </c>
-      <c r="B1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="137" t="s">
+      <c r="B1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="147" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="147" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="128" t="s">
+      <c r="A2" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="128" t="s">
+      <c r="B2" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="128" t="s">
+      <c r="C2" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="128" t="s">
+      <c r="D2" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="128" t="s">
+      <c r="E2" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="128" t="s">
+      <c r="F2" s="119" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="128" t="s">
+      <c r="G2" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="128" t="s">
+      <c r="H2" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="128" t="s">
+      <c r="I2" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="128" t="s">
+      <c r="J2" s="119" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="128" t="s">
+      <c r="K2" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="128" t="s">
+      <c r="L2" s="119" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="128" t="s">
+      <c r="M2" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="128" t="s">
+      <c r="N2" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="128" t="s">
+      <c r="O2" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="128" t="s">
+      <c r="P2" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="128" t="s">
+      <c r="Q2" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="128" t="s">
+      <c r="R2" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="128" t="s">
+      <c r="S2" s="119" t="s">
         <v>16</v>
       </c>
-      <c r="T2" s="128" t="s">
+      <c r="T2" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="U2" s="128" t="s">
+      <c r="U2" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="V2" s="128" t="s">
+      <c r="V2" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="W2" s="128" t="s">
+      <c r="W2" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="X2" s="128" t="s">
+      <c r="X2" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" s="128" t="s">
+      <c r="Y2" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="Z2" s="128" t="s">
+      <c r="Z2" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="AA2" s="128" t="s">
+      <c r="AA2" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="AB2" s="128" t="s">
+      <c r="AB2" s="119" t="s">
         <v>25</v>
       </c>
     </row>
@@ -20425,6 +20482,9 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7588871-7EF6-4AC9-81DD-CFF44DED789D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -20457,89 +20517,89 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="138" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="122" t="s">
         <v>578</v>
       </c>
-      <c r="B1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="138" t="s">
+      <c r="B1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="122" t="s">
         <v>27</v>
       </c>
     </row>
@@ -20629,433 +20689,907 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="11">
+        <v>262103</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="H3" s="11">
+        <v>3500</v>
+      </c>
+      <c r="I3" s="13">
+        <v>0.45</v>
+      </c>
+      <c r="J3" s="13">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="13">
+        <v>1031.625</v>
+      </c>
+      <c r="M3" s="14">
+        <v>1146.3</v>
+      </c>
+      <c r="N3" s="15">
+        <v>0.15920000000000001</v>
+      </c>
+      <c r="O3" s="16">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="P3" s="11">
+        <v>355.9</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>2</v>
+      </c>
+      <c r="R3" s="11">
+        <v>1500</v>
+      </c>
+      <c r="S3" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="T3" s="11">
+        <v>600</v>
+      </c>
+      <c r="U3" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB3" s="11" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="11">
+        <v>262104</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="H4" s="11">
+        <v>2000</v>
+      </c>
+      <c r="I4" s="13">
+        <v>0.72</v>
+      </c>
+      <c r="J4" s="13">
+        <v>0.85</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="13">
+        <v>1224</v>
+      </c>
+      <c r="M4" s="14">
+        <v>850</v>
+      </c>
+      <c r="N4" s="15">
+        <v>0.1181</v>
+      </c>
+      <c r="O4" s="16">
+        <v>7.08</v>
+      </c>
+      <c r="P4" s="11">
+        <v>422.3</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>2</v>
+      </c>
+      <c r="R4" s="11">
+        <v>1500</v>
+      </c>
+      <c r="S4" s="13">
+        <v>1.44</v>
+      </c>
+      <c r="T4" s="11">
+        <v>60</v>
+      </c>
+      <c r="U4" s="15">
+        <v>0.04</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB4" s="11" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="11">
+        <v>262105</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="H5" s="11">
+        <v>3000</v>
+      </c>
+      <c r="I5" s="13">
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="J5" s="13">
+        <v>0.85</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>573</v>
+      </c>
+      <c r="L5" s="13">
+        <v>1471.35</v>
+      </c>
+      <c r="M5" s="14">
+        <v>1275</v>
+      </c>
+      <c r="N5" s="15">
+        <v>0.17710000000000001</v>
+      </c>
+      <c r="O5" s="16">
+        <v>10.63</v>
+      </c>
+      <c r="P5" s="11">
+        <v>541.5</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>2</v>
+      </c>
+      <c r="R5" s="11">
+        <v>1200</v>
+      </c>
+      <c r="S5" s="13">
+        <v>1.1539999999999999</v>
+      </c>
+      <c r="T5" s="11">
+        <v>46</v>
+      </c>
+      <c r="U5" s="15">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
+        <v>4</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="11">
+        <v>262106</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="H6" s="11">
+        <v>2100</v>
+      </c>
+      <c r="I6" s="13">
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="J6" s="13">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>573</v>
+      </c>
+      <c r="L6" s="13">
+        <v>1344.9870000000001</v>
+      </c>
+      <c r="M6" s="14">
+        <v>1165.5</v>
+      </c>
+      <c r="N6" s="15">
+        <v>0.16189999999999999</v>
+      </c>
+      <c r="O6" s="16">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="P6" s="11">
+        <v>495</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>2</v>
+      </c>
+      <c r="R6" s="11">
+        <v>1200</v>
+      </c>
+      <c r="S6" s="13">
+        <v>1.1539999999999999</v>
+      </c>
+      <c r="T6" s="11">
+        <v>46</v>
+      </c>
+      <c r="U6" s="15">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB6" s="11" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="18">
+        <v>10600</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="18">
+        <v>1814.6</v>
+      </c>
+      <c r="Q7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="T7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="X7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB7" s="18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" scale="93" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDEB15C-42FB-4253-81FF-1E9A43ACCCA8}">
+  <dimension ref="A1:AB5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="7.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="3.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="4.77734375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="7.21875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="7.88671875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.21875" style="1" customWidth="1"/>
+    <col min="25" max="25" width="9.77734375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="3.44140625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="9.33203125" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="127" t="s">
+        <v>581</v>
+      </c>
+      <c r="B1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="127" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" s="38">
+      <c r="A3" s="109">
         <v>1</v>
       </c>
-      <c r="B3" s="40" t="s">
-        <v>575</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="38" t="s">
-        <v>492</v>
-      </c>
-      <c r="E3" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="38">
-        <v>262103</v>
-      </c>
-      <c r="G3" s="38" t="s">
-        <v>574</v>
-      </c>
-      <c r="H3" s="38">
-        <v>3500</v>
-      </c>
-      <c r="I3" s="39">
-        <v>0.45</v>
-      </c>
-      <c r="J3" s="39">
-        <v>0.65500000000000003</v>
-      </c>
-      <c r="K3" s="38" t="s">
+      <c r="B3" s="111" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="109" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="109" t="s">
+        <v>383</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="109">
+        <v>262108</v>
+      </c>
+      <c r="G3" s="109" t="s">
+        <v>580</v>
+      </c>
+      <c r="H3" s="109">
+        <v>8920</v>
+      </c>
+      <c r="I3" s="110">
+        <v>0.622</v>
+      </c>
+      <c r="J3" s="110">
+        <v>1.8089999999999999</v>
+      </c>
+      <c r="K3" s="109" t="s">
+        <v>177</v>
+      </c>
+      <c r="L3" s="106">
+        <v>10036.766</v>
+      </c>
+      <c r="M3" s="108">
+        <v>8068.1</v>
+      </c>
+      <c r="N3" s="105">
+        <v>1.1206</v>
+      </c>
+      <c r="O3" s="107">
+        <v>67.23</v>
+      </c>
+      <c r="P3" s="104">
+        <v>4290.7</v>
+      </c>
+      <c r="Q3" s="104">
+        <v>2</v>
+      </c>
+      <c r="R3" s="104">
+        <v>1300</v>
+      </c>
+      <c r="S3" s="106">
+        <v>1.244</v>
+      </c>
+      <c r="T3" s="104">
+        <v>56</v>
+      </c>
+      <c r="U3" s="105">
+        <v>4.3099999999999999E-2</v>
+      </c>
+      <c r="V3" s="104" t="s">
+        <v>42</v>
+      </c>
+      <c r="W3" s="104" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" s="104" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y3" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="104" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB3" s="104" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="109">
+        <v>2</v>
+      </c>
+      <c r="B4" s="111" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>383</v>
+      </c>
+      <c r="E4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="109">
+        <v>262108</v>
+      </c>
+      <c r="G4" s="109" t="s">
+        <v>579</v>
+      </c>
+      <c r="H4" s="109">
+        <v>4460</v>
+      </c>
+      <c r="I4" s="110">
+        <v>0.32</v>
+      </c>
+      <c r="J4" s="110">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="K4" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="35">
-        <v>1031.625</v>
-      </c>
-      <c r="M3" s="37">
-        <v>1146.3</v>
-      </c>
-      <c r="N3" s="34">
-        <v>0.15920000000000001</v>
-      </c>
-      <c r="O3" s="36">
-        <v>9.5500000000000007</v>
-      </c>
-      <c r="P3" s="33">
-        <v>355.9</v>
-      </c>
-      <c r="Q3" s="33">
-        <v>2</v>
-      </c>
-      <c r="R3" s="33">
-        <v>1500</v>
-      </c>
-      <c r="S3" s="35">
-        <v>0.9</v>
-      </c>
-      <c r="T3" s="33">
-        <v>600</v>
-      </c>
-      <c r="U3" s="34">
-        <v>0.4</v>
-      </c>
-      <c r="V3" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="X3" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z3" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA3" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB3" s="33" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="38">
-        <v>2</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>575</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="38" t="s">
-        <v>492</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="38">
-        <v>262104</v>
-      </c>
-      <c r="G4" s="38" t="s">
-        <v>574</v>
-      </c>
-      <c r="H4" s="38">
-        <v>2000</v>
-      </c>
-      <c r="I4" s="39">
-        <v>0.72</v>
-      </c>
-      <c r="J4" s="39">
-        <v>0.85</v>
-      </c>
-      <c r="K4" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="35">
-        <v>1224</v>
-      </c>
-      <c r="M4" s="37">
-        <v>850</v>
-      </c>
-      <c r="N4" s="34">
-        <v>0.1181</v>
-      </c>
-      <c r="O4" s="36">
-        <v>7.08</v>
-      </c>
-      <c r="P4" s="33">
-        <v>422.3</v>
-      </c>
-      <c r="Q4" s="33">
-        <v>2</v>
-      </c>
-      <c r="R4" s="33">
-        <v>1500</v>
-      </c>
-      <c r="S4" s="35">
-        <v>1.44</v>
-      </c>
-      <c r="T4" s="33">
-        <v>60</v>
-      </c>
-      <c r="U4" s="34">
+      <c r="L4" s="106">
+        <v>1235.9549999999999</v>
+      </c>
+      <c r="M4" s="108">
+        <v>1287.5</v>
+      </c>
+      <c r="N4" s="105">
+        <v>0.1192</v>
+      </c>
+      <c r="O4" s="107">
+        <v>7.15</v>
+      </c>
+      <c r="P4" s="104">
+        <v>528.4</v>
+      </c>
+      <c r="Q4" s="104">
+        <v>3</v>
+      </c>
+      <c r="R4" s="104">
+        <v>1000</v>
+      </c>
+      <c r="S4" s="106">
+        <v>0.96</v>
+      </c>
+      <c r="T4" s="104">
+        <v>40</v>
+      </c>
+      <c r="U4" s="105">
         <v>0.04</v>
       </c>
-      <c r="V4" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="X4" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB4" s="33" t="s">
-        <v>577</v>
+      <c r="V4" s="104" t="s">
+        <v>42</v>
+      </c>
+      <c r="W4" s="104" t="s">
+        <v>42</v>
+      </c>
+      <c r="X4" s="104" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y4" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="104" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB4" s="104" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" s="38">
-        <v>3</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>575</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>492</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="38">
-        <v>262105</v>
-      </c>
-      <c r="G5" s="38" t="s">
-        <v>574</v>
-      </c>
-      <c r="H5" s="38">
-        <v>3000</v>
-      </c>
-      <c r="I5" s="39">
-        <v>0.57699999999999996</v>
-      </c>
-      <c r="J5" s="39">
-        <v>0.85</v>
-      </c>
-      <c r="K5" s="38" t="s">
-        <v>573</v>
-      </c>
-      <c r="L5" s="35">
-        <v>1471.35</v>
-      </c>
-      <c r="M5" s="37">
-        <v>1275</v>
-      </c>
-      <c r="N5" s="34">
-        <v>0.17710000000000001</v>
-      </c>
-      <c r="O5" s="36">
-        <v>10.63</v>
-      </c>
-      <c r="P5" s="33">
-        <v>541.5</v>
-      </c>
-      <c r="Q5" s="33">
-        <v>2</v>
-      </c>
-      <c r="R5" s="33">
-        <v>1200</v>
-      </c>
-      <c r="S5" s="35">
-        <v>1.1539999999999999</v>
-      </c>
-      <c r="T5" s="33">
-        <v>46</v>
-      </c>
-      <c r="U5" s="34">
-        <v>3.8300000000000001E-2</v>
-      </c>
-      <c r="V5" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="W5" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="X5" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z5" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA5" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB5" s="33" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="38">
-        <v>4</v>
-      </c>
-      <c r="B6" s="40" t="s">
-        <v>575</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>492</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="38">
-        <v>262106</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>574</v>
-      </c>
-      <c r="H6" s="38">
-        <v>2100</v>
-      </c>
-      <c r="I6" s="39">
-        <v>0.57699999999999996</v>
-      </c>
-      <c r="J6" s="39">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="K6" s="38" t="s">
-        <v>573</v>
-      </c>
-      <c r="L6" s="35">
-        <v>1344.9870000000001</v>
-      </c>
-      <c r="M6" s="37">
-        <v>1165.5</v>
-      </c>
-      <c r="N6" s="34">
-        <v>0.16189999999999999</v>
-      </c>
-      <c r="O6" s="36">
-        <v>9.7100000000000009</v>
-      </c>
-      <c r="P6" s="33">
-        <v>495</v>
-      </c>
-      <c r="Q6" s="33">
-        <v>2</v>
-      </c>
-      <c r="R6" s="33">
-        <v>1200</v>
-      </c>
-      <c r="S6" s="35">
-        <v>1.1539999999999999</v>
-      </c>
-      <c r="T6" s="33">
-        <v>46</v>
-      </c>
-      <c r="U6" s="34">
-        <v>3.8300000000000001E-2</v>
-      </c>
-      <c r="V6" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="W6" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="X6" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y6" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z6" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA6" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB6" s="33" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="32">
-        <v>10600</v>
-      </c>
-      <c r="I7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" s="31">
-        <v>1814.6</v>
-      </c>
-      <c r="Q7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="R7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="S7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="T7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="U7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="V7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="W7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA7" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB7" s="31" t="s">
+      <c r="A5" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="103">
+        <v>13380</v>
+      </c>
+      <c r="I5" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" s="102">
+        <v>4819.1000000000004</v>
+      </c>
+      <c r="Q5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="S5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="U5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="V5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="X5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB5" s="102" t="s">
         <v>27</v>
       </c>
     </row>
@@ -21105,88 +21639,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="122" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="132" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="132" t="s">
+      <c r="B1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="123" t="s">
         <v>27</v>
       </c>
     </row>
@@ -23301,88 +23835,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="122" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="131" t="s">
+      <c r="B1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="122" t="s">
         <v>27</v>
       </c>
     </row>
@@ -23863,88 +24397,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="122" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="131" t="s">
+      <c r="B1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="122" t="s">
         <v>27</v>
       </c>
     </row>
@@ -25110,88 +25644,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="124" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="133" t="s">
+      <c r="B1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="124" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="124" t="s">
         <v>27</v>
       </c>
     </row>
@@ -25674,88 +26208,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="125" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="134" t="s">
+      <c r="B1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="125" t="s">
         <v>27</v>
       </c>
     </row>
@@ -26661,88 +27195,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="122" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="131" t="s">
+      <c r="B1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="122" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="122" t="s">
         <v>27</v>
       </c>
     </row>
@@ -27478,88 +28012,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="121" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="130" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="130" t="s">
+      <c r="B1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="121" t="s">
         <v>27</v>
       </c>
     </row>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB7D65A-7AFC-4479-A0F0-6198204999FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DF9EBC-16BB-49B1-B2D6-E196FB5328F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="24" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="25" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051 M" sheetId="60" r:id="rId1"/>
@@ -40,6 +40,7 @@
     <sheet name="ABAPEL 1046 P" sheetId="75" r:id="rId25"/>
     <sheet name="CARTOMIL EMBALAGENS LTDA 1089 P" sheetId="76" r:id="rId26"/>
     <sheet name="UPAPER 1090" sheetId="77" r:id="rId27"/>
+    <sheet name="HARMONY EMBALAGENS 1091 P" sheetId="78" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023 M'!$A$1:$AB$10</definedName>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4992" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5126" uniqueCount="592">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1811,6 +1812,36 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA - Z4A EMBALAGENS  —  OF: 001090</t>
+  </si>
+  <si>
+    <t>06-08-26</t>
+  </si>
+  <si>
+    <t>06/08/2026</t>
+  </si>
+  <si>
+    <t>1055x1878</t>
+  </si>
+  <si>
+    <t>86x173x86</t>
+  </si>
+  <si>
+    <t>830x2018</t>
+  </si>
+  <si>
+    <t>106x193x106</t>
+  </si>
+  <si>
+    <t>922x1875</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>329x244x329</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - HARMONY EMBALAGENS  —  OF: 001091</t>
   </si>
 </sst>
 </file>
@@ -1822,7 +1853,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1948,6 +1979,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2018,7 +2056,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2353,24 +2391,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2422,9 +2442,46 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2678,88 +2735,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="139" t="s">
         <v>309</v>
       </c>
-      <c r="B1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="120" t="s">
+      <c r="B1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="139" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3582,88 +3639,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="139" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="120" t="s">
+      <c r="B1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="139" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4401,88 +4458,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="144" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="125" t="s">
+      <c r="B1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="144" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5307,88 +5364,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="141" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="122" t="s">
+      <c r="B1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="141" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6724,88 +6781,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="139" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="120" t="s">
+      <c r="B1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="139" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7274,88 +7331,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="144" t="s">
         <v>343</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="125" t="s">
+      <c r="B1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="144" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8349,88 +8406,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="139" t="s">
         <v>364</v>
       </c>
-      <c r="B1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="120" t="s">
+      <c r="B1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="139" t="s">
         <v>27</v>
       </c>
     </row>
@@ -9084,88 +9141,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="141" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="122" t="s">
+      <c r="B1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="141" t="s">
         <v>27</v>
       </c>
     </row>
@@ -10076,88 +10133,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="144" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="125" t="s">
+      <c r="B1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="144" t="s">
         <v>27</v>
       </c>
     </row>
@@ -11844,88 +11901,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="144" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="125" t="s">
+      <c r="B1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="144" t="s">
         <v>27</v>
       </c>
     </row>
@@ -12833,88 +12890,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="145" t="s">
         <v>489</v>
       </c>
-      <c r="B1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="126" t="s">
+      <c r="B1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="145" t="s">
         <v>27</v>
       </c>
     </row>
@@ -14856,88 +14913,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="121" t="s">
+      <c r="B1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="140" t="s">
         <v>27</v>
       </c>
     </row>
@@ -15763,88 +15820,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="140" t="s">
         <v>493</v>
       </c>
-      <c r="B1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="121" t="s">
+      <c r="B1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="140" t="s">
         <v>27</v>
       </c>
     </row>
@@ -15934,269 +15991,269 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="136" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="128">
+    <row r="3" spans="1:28" s="128" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="120">
         <v>1</v>
       </c>
-      <c r="B3" s="129" t="s">
+      <c r="B3" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="128" t="s">
+      <c r="C3" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="128" t="s">
+      <c r="D3" s="120" t="s">
         <v>492</v>
       </c>
-      <c r="E3" s="128" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="128">
+      <c r="E3" s="120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="120">
         <v>262067</v>
       </c>
-      <c r="G3" s="128" t="s">
+      <c r="G3" s="120" t="s">
         <v>491</v>
       </c>
-      <c r="H3" s="128">
+      <c r="H3" s="120">
         <v>340</v>
       </c>
-      <c r="I3" s="130">
+      <c r="I3" s="122">
         <v>0.97699999999999998</v>
       </c>
-      <c r="J3" s="130">
+      <c r="J3" s="122">
         <v>2.06</v>
       </c>
-      <c r="K3" s="128" t="s">
+      <c r="K3" s="120" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="131">
+      <c r="L3" s="123">
         <v>684.29100000000005</v>
       </c>
-      <c r="M3" s="132">
+      <c r="M3" s="124">
         <v>700.4</v>
       </c>
-      <c r="N3" s="133">
+      <c r="N3" s="125">
         <v>0.1946</v>
       </c>
-      <c r="O3" s="134">
+      <c r="O3" s="126">
         <v>11.67</v>
       </c>
-      <c r="P3" s="135">
+      <c r="P3" s="127">
         <v>405.8</v>
       </c>
-      <c r="Q3" s="135">
+      <c r="Q3" s="127">
         <v>1</v>
       </c>
-      <c r="R3" s="135">
+      <c r="R3" s="127">
         <v>1000</v>
       </c>
-      <c r="S3" s="131">
+      <c r="S3" s="123">
         <v>0.97699999999999998</v>
       </c>
-      <c r="T3" s="135">
+      <c r="T3" s="127">
         <v>23</v>
       </c>
-      <c r="U3" s="133">
+      <c r="U3" s="125">
         <v>2.3E-2</v>
       </c>
-      <c r="V3" s="135" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="135" t="s">
+      <c r="V3" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="X3" s="135" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="135" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z3" s="135" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA3" s="135" t="s">
+      <c r="X3" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="AB3" s="135" t="s">
+      <c r="AB3" s="127" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="145" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="137">
+    <row r="4" spans="1:28" s="137" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="129">
         <v>1</v>
       </c>
-      <c r="B4" s="138" t="s">
+      <c r="B4" s="130" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="137" t="s">
+      <c r="C4" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="129" t="s">
         <v>492</v>
       </c>
-      <c r="E4" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="137">
+      <c r="E4" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="129">
         <v>262097</v>
       </c>
-      <c r="G4" s="137" t="s">
+      <c r="G4" s="129" t="s">
         <v>542</v>
       </c>
-      <c r="H4" s="137">
+      <c r="H4" s="129">
         <v>2000</v>
       </c>
-      <c r="I4" s="139">
+      <c r="I4" s="131">
         <v>0.39200000000000002</v>
       </c>
-      <c r="J4" s="139">
+      <c r="J4" s="131">
         <v>1.28</v>
       </c>
-      <c r="K4" s="137" t="s">
+      <c r="K4" s="129" t="s">
         <v>544</v>
       </c>
-      <c r="L4" s="140">
+      <c r="L4" s="132">
         <v>1003.52</v>
       </c>
-      <c r="M4" s="141">
+      <c r="M4" s="133">
         <v>1280</v>
       </c>
-      <c r="N4" s="142">
+      <c r="N4" s="134">
         <v>0.17780000000000001</v>
       </c>
-      <c r="O4" s="143">
+      <c r="O4" s="135">
         <v>10.67</v>
       </c>
-      <c r="P4" s="144">
+      <c r="P4" s="136">
         <v>346.2</v>
       </c>
-      <c r="Q4" s="144">
+      <c r="Q4" s="136">
         <v>2</v>
       </c>
-      <c r="R4" s="144">
+      <c r="R4" s="136">
         <v>850</v>
       </c>
-      <c r="S4" s="140">
+      <c r="S4" s="132">
         <v>0.78400000000000003</v>
       </c>
-      <c r="T4" s="144">
+      <c r="T4" s="136">
         <v>66</v>
       </c>
-      <c r="U4" s="142">
+      <c r="U4" s="134">
         <v>7.7600000000000002E-2</v>
       </c>
-      <c r="V4" s="144" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="144" t="s">
-        <v>28</v>
-      </c>
-      <c r="X4" s="144" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="144" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="144" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="144" t="s">
+      <c r="V4" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="136" t="s">
         <v>33</v>
       </c>
-      <c r="AB4" s="144" t="s">
+      <c r="AB4" s="136" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="145" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="137">
+    <row r="5" spans="1:28" s="137" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="129">
         <v>2</v>
       </c>
-      <c r="B5" s="138" t="s">
+      <c r="B5" s="130" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="137" t="s">
+      <c r="C5" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="137" t="s">
+      <c r="D5" s="129" t="s">
         <v>492</v>
       </c>
-      <c r="E5" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="137">
+      <c r="E5" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="129">
         <v>262096</v>
       </c>
-      <c r="G5" s="137" t="s">
+      <c r="G5" s="129" t="s">
         <v>542</v>
       </c>
-      <c r="H5" s="137">
+      <c r="H5" s="129">
         <v>2000</v>
       </c>
-      <c r="I5" s="139">
+      <c r="I5" s="131">
         <v>0.375</v>
       </c>
-      <c r="J5" s="139">
+      <c r="J5" s="131">
         <v>1.28</v>
       </c>
-      <c r="K5" s="137" t="s">
+      <c r="K5" s="129" t="s">
         <v>541</v>
       </c>
-      <c r="L5" s="140">
+      <c r="L5" s="132">
         <v>960</v>
       </c>
-      <c r="M5" s="141">
+      <c r="M5" s="133">
         <v>1280</v>
       </c>
-      <c r="N5" s="142">
+      <c r="N5" s="134">
         <v>0.17780000000000001</v>
       </c>
-      <c r="O5" s="143">
+      <c r="O5" s="135">
         <v>10.67</v>
       </c>
-      <c r="P5" s="144">
+      <c r="P5" s="136">
         <v>331.2</v>
       </c>
-      <c r="Q5" s="144">
+      <c r="Q5" s="136">
         <v>2</v>
       </c>
-      <c r="R5" s="144">
+      <c r="R5" s="136">
         <v>800</v>
       </c>
-      <c r="S5" s="140">
+      <c r="S5" s="132">
         <v>0.75</v>
       </c>
-      <c r="T5" s="144">
+      <c r="T5" s="136">
         <v>50</v>
       </c>
-      <c r="U5" s="142">
+      <c r="U5" s="134">
         <v>6.25E-2</v>
       </c>
-      <c r="V5" s="144" t="s">
-        <v>28</v>
-      </c>
-      <c r="W5" s="144" t="s">
-        <v>28</v>
-      </c>
-      <c r="X5" s="144" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="144" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z5" s="144" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA5" s="144" t="s">
+      <c r="V5" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="136" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="136" t="s">
         <v>33</v>
       </c>
-      <c r="AB5" s="144" t="s">
+      <c r="AB5" s="136" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="146" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H6" s="146">
+    <row r="6" spans="1:28" s="138" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H6" s="138">
         <v>4340</v>
       </c>
-      <c r="P6" s="146">
+      <c r="P6" s="138">
         <v>1083</v>
       </c>
     </row>
@@ -16248,88 +16305,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="144" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="125" t="s">
+      <c r="B1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="144" t="s">
         <v>27</v>
       </c>
     </row>
@@ -17582,88 +17639,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="146" t="s">
         <v>523</v>
       </c>
-      <c r="B1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="127" t="s">
+      <c r="B1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="146" t="s">
         <v>27</v>
       </c>
     </row>
@@ -17972,88 +18029,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="140" t="s">
         <v>539</v>
       </c>
-      <c r="B1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="121" t="s">
+      <c r="B1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="140" t="s">
         <v>27</v>
       </c>
     </row>
@@ -18964,88 +19021,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="141" t="s">
         <v>552</v>
       </c>
-      <c r="B1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="122" t="s">
+      <c r="B1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="141" t="s">
         <v>27</v>
       </c>
     </row>
@@ -20518,88 +20575,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="141" t="s">
         <v>578</v>
       </c>
-      <c r="B1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="122" t="s">
+      <c r="B1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="141" t="s">
         <v>27</v>
       </c>
     </row>
@@ -21164,88 +21221,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="146" t="s">
         <v>581</v>
       </c>
-      <c r="B1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="127" t="s">
+      <c r="B1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="146" t="s">
         <v>27</v>
       </c>
     </row>
@@ -21598,6 +21655,652 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE16CF0-4795-4B1D-AE0A-7B6EE187B0C8}">
+  <dimension ref="A1:AB7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="7" style="1" customWidth="1"/>
+    <col min="17" max="17" width="3" style="1" customWidth="1"/>
+    <col min="18" max="18" width="4.6640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="6.44140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="7.88671875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="8.109375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5546875" style="1" customWidth="1"/>
+    <col min="25" max="25" width="6.88671875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="3.5546875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="11.21875" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="144" t="s">
+        <v>591</v>
+      </c>
+      <c r="B1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="144" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" s="154" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="148">
+        <v>1</v>
+      </c>
+      <c r="B3" s="149" t="s">
+        <v>405</v>
+      </c>
+      <c r="C3" s="148" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="148" t="s">
+        <v>583</v>
+      </c>
+      <c r="E3" s="148" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="148">
+        <v>262110</v>
+      </c>
+      <c r="G3" s="148" t="s">
+        <v>582</v>
+      </c>
+      <c r="H3" s="148">
+        <v>2000</v>
+      </c>
+      <c r="I3" s="150">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="J3" s="150">
+        <v>1.855</v>
+      </c>
+      <c r="K3" s="148" t="s">
+        <v>590</v>
+      </c>
+      <c r="L3" s="150">
+        <v>3346.42</v>
+      </c>
+      <c r="M3" s="151">
+        <v>3710</v>
+      </c>
+      <c r="N3" s="152">
+        <v>1.0306</v>
+      </c>
+      <c r="O3" s="153">
+        <v>61.83</v>
+      </c>
+      <c r="P3" s="148">
+        <v>2027.9</v>
+      </c>
+      <c r="Q3" s="148">
+        <v>1</v>
+      </c>
+      <c r="R3" s="148">
+        <v>950</v>
+      </c>
+      <c r="S3" s="150">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="T3" s="148">
+        <v>48</v>
+      </c>
+      <c r="U3" s="152">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="V3" s="148" t="s">
+        <v>35</v>
+      </c>
+      <c r="W3" s="148" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="148" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" s="148" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z3" s="148" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA3" s="148" t="s">
+        <v>589</v>
+      </c>
+      <c r="AB3" s="148" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="5">
+        <v>262111</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1500</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0.999</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="L4" s="7">
+        <v>606.89300000000003</v>
+      </c>
+      <c r="M4" s="9">
+        <v>749.3</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0.1041</v>
+      </c>
+      <c r="O4" s="8">
+        <v>6.24</v>
+      </c>
+      <c r="P4" s="5">
+        <v>209.4</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>2</v>
+      </c>
+      <c r="R4" s="5">
+        <v>850</v>
+      </c>
+      <c r="S4" s="7">
+        <v>0.81</v>
+      </c>
+      <c r="T4" s="5">
+        <v>40</v>
+      </c>
+      <c r="U4" s="6">
+        <v>4.7100000000000003E-2</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="5">
+        <v>262112</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="H5" s="5">
+        <v>500</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="L5" s="7">
+        <v>160.25200000000001</v>
+      </c>
+      <c r="M5" s="9">
+        <v>232.3</v>
+      </c>
+      <c r="N5" s="6">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="O5" s="8">
+        <v>1.94</v>
+      </c>
+      <c r="P5" s="5">
+        <v>55.3</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>2</v>
+      </c>
+      <c r="R5" s="5">
+        <v>750</v>
+      </c>
+      <c r="S5" s="7">
+        <v>0.69</v>
+      </c>
+      <c r="T5" s="5">
+        <v>60</v>
+      </c>
+      <c r="U5" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="5">
+        <v>262113</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="H6" s="5">
+        <v>5000</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1.369</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" s="7">
+        <v>1943.98</v>
+      </c>
+      <c r="M6" s="9">
+        <v>3422.5</v>
+      </c>
+      <c r="N6" s="6">
+        <v>0.4753</v>
+      </c>
+      <c r="O6" s="8">
+        <v>28.52</v>
+      </c>
+      <c r="P6" s="5">
+        <v>670.7</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>2</v>
+      </c>
+      <c r="R6" s="5">
+        <v>600</v>
+      </c>
+      <c r="S6" s="7">
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="T6" s="5">
+        <v>32</v>
+      </c>
+      <c r="U6" s="6">
+        <v>5.33E-2</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB6" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="19">
+        <v>9000</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="19">
+        <v>2963.3</v>
+      </c>
+      <c r="Q7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="X7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB7" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -21639,88 +22342,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="123" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="123" t="s">
+      <c r="B1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="142" t="s">
         <v>27</v>
       </c>
     </row>
@@ -23835,88 +24538,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="141" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="122" t="s">
+      <c r="B1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="141" t="s">
         <v>27</v>
       </c>
     </row>
@@ -24397,88 +25100,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="141" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="122" t="s">
+      <c r="B1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="141" t="s">
         <v>27</v>
       </c>
     </row>
@@ -25644,88 +26347,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="143" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="124" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="124" t="s">
+      <c r="B1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="143" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="143" t="s">
         <v>27</v>
       </c>
     </row>
@@ -26208,88 +26911,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="144" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="125" t="s">
+      <c r="B1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="144" t="s">
         <v>27</v>
       </c>
     </row>
@@ -27195,88 +27898,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="141" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="122" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="122" t="s">
+      <c r="B1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="141" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="141" t="s">
         <v>27</v>
       </c>
     </row>
@@ -28012,88 +28715,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="140" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="121" t="s">
+      <c r="B1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="140" t="s">
         <v>27</v>
       </c>
     </row>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DF9EBC-16BB-49B1-B2D6-E196FB5328F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEFF1C9-AADA-4201-B45E-422CDEA9164E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="25" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="26" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051 M" sheetId="60" r:id="rId1"/>
@@ -41,6 +41,7 @@
     <sheet name="CARTOMIL EMBALAGENS LTDA 1089 P" sheetId="76" r:id="rId26"/>
     <sheet name="UPAPER 1090" sheetId="77" r:id="rId27"/>
     <sheet name="HARMONY EMBALAGENS 1091 P" sheetId="78" r:id="rId28"/>
+    <sheet name="IPE - PCBOX EMBALAGENS 1094" sheetId="79" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023 M'!$A$1:$AB$10</definedName>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5126" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5286" uniqueCount="610">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1842,6 +1843,60 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA - HARMONY EMBALAGENS  —  OF: 001091</t>
+  </si>
+  <si>
+    <t>1143x1700</t>
+  </si>
+  <si>
+    <t>108x204x108</t>
+  </si>
+  <si>
+    <t>1.603</t>
+  </si>
+  <si>
+    <t>944x1583</t>
+  </si>
+  <si>
+    <t>156x150x156</t>
+  </si>
+  <si>
+    <t>932x1581</t>
+  </si>
+  <si>
+    <t>154x148x154</t>
+  </si>
+  <si>
+    <t>1.602</t>
+  </si>
+  <si>
+    <t>998x1367</t>
+  </si>
+  <si>
+    <t>92x794x92</t>
+  </si>
+  <si>
+    <t>1.601</t>
+  </si>
+  <si>
+    <t>953x1825</t>
+  </si>
+  <si>
+    <t>1.588</t>
+  </si>
+  <si>
+    <t>810x2163</t>
+  </si>
+  <si>
+    <t>263x264x263</t>
+  </si>
+  <si>
+    <t>1.533</t>
+  </si>
+  <si>
+    <t>13/07/2026</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - IPE EMBALAGENS LTDA - PCBOX EMBALAGENS LTDA  —  OF: 001094</t>
   </si>
 </sst>
 </file>
@@ -1853,7 +1908,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1979,13 +2034,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2056,7 +2104,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2463,25 +2511,22 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -21660,6 +21705,9 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE16CF0-4795-4B1D-AE0A-7B6EE187B0C8}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -21865,11 +21913,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="154" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" s="153" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="148">
         <v>1</v>
       </c>
-      <c r="B3" s="149" t="s">
+      <c r="B3" s="92" t="s">
         <v>405</v>
       </c>
       <c r="C3" s="148" t="s">
@@ -21890,25 +21938,25 @@
       <c r="H3" s="148">
         <v>2000</v>
       </c>
-      <c r="I3" s="150">
+      <c r="I3" s="149">
         <v>0.90200000000000002</v>
       </c>
-      <c r="J3" s="150">
+      <c r="J3" s="149">
         <v>1.855</v>
       </c>
       <c r="K3" s="148" t="s">
         <v>590</v>
       </c>
-      <c r="L3" s="150">
+      <c r="L3" s="149">
         <v>3346.42</v>
       </c>
-      <c r="M3" s="151">
+      <c r="M3" s="150">
         <v>3710</v>
       </c>
-      <c r="N3" s="152">
+      <c r="N3" s="151">
         <v>1.0306</v>
       </c>
-      <c r="O3" s="153">
+      <c r="O3" s="152">
         <v>61.83</v>
       </c>
       <c r="P3" s="148">
@@ -21920,13 +21968,13 @@
       <c r="R3" s="148">
         <v>950</v>
       </c>
-      <c r="S3" s="150">
+      <c r="S3" s="149">
         <v>0.90200000000000002</v>
       </c>
       <c r="T3" s="148">
         <v>48</v>
       </c>
-      <c r="U3" s="152">
+      <c r="U3" s="151">
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="V3" s="148" t="s">
@@ -21951,7 +21999,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -22037,7 +22085,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -22123,7 +22171,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -22209,7 +22257,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>27</v>
       </c>
@@ -22292,6 +22340,823 @@
         <v>27</v>
       </c>
       <c r="AB7" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="1.73" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" scale="97" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9920A0AA-9240-4CDC-B26B-9F885FC523AF}">
+  <dimension ref="A1:AB9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="6.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.77734375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.6640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="3.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="6.88671875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="8.6640625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="8.109375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="8.6640625" style="1" customWidth="1"/>
+    <col min="25" max="26" width="11.77734375" style="1" customWidth="1"/>
+    <col min="27" max="27" width="3.21875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="146" t="s">
+        <v>609</v>
+      </c>
+      <c r="B1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="146" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="109">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111" t="s">
+        <v>279</v>
+      </c>
+      <c r="C3" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="109" t="s">
+        <v>608</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="109">
+        <v>262117</v>
+      </c>
+      <c r="G3" s="109" t="s">
+        <v>607</v>
+      </c>
+      <c r="H3" s="109">
+        <v>200</v>
+      </c>
+      <c r="I3" s="110">
+        <v>0.79</v>
+      </c>
+      <c r="J3" s="110">
+        <v>2.1429999999999998</v>
+      </c>
+      <c r="K3" s="109" t="s">
+        <v>606</v>
+      </c>
+      <c r="L3" s="106">
+        <v>338.59399999999999</v>
+      </c>
+      <c r="M3" s="108">
+        <v>214.3</v>
+      </c>
+      <c r="N3" s="105">
+        <v>2.98E-2</v>
+      </c>
+      <c r="O3" s="107">
+        <v>1.79</v>
+      </c>
+      <c r="P3" s="104">
+        <v>116.8</v>
+      </c>
+      <c r="Q3" s="104">
+        <v>2</v>
+      </c>
+      <c r="R3" s="104">
+        <v>1600</v>
+      </c>
+      <c r="S3" s="106">
+        <v>1.58</v>
+      </c>
+      <c r="T3" s="104">
+        <v>20</v>
+      </c>
+      <c r="U3" s="105">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="V3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB3" s="104" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="109">
+        <v>2</v>
+      </c>
+      <c r="B4" s="111" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>383</v>
+      </c>
+      <c r="E4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="109">
+        <v>262118</v>
+      </c>
+      <c r="G4" s="109" t="s">
+        <v>604</v>
+      </c>
+      <c r="H4" s="109">
+        <v>300</v>
+      </c>
+      <c r="I4" s="110">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="J4" s="110">
+        <v>1.8049999999999999</v>
+      </c>
+      <c r="K4" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="106">
+        <v>505.22</v>
+      </c>
+      <c r="M4" s="108">
+        <v>541.5</v>
+      </c>
+      <c r="N4" s="105">
+        <v>0.15040000000000001</v>
+      </c>
+      <c r="O4" s="107">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="P4" s="104">
+        <v>174.3</v>
+      </c>
+      <c r="Q4" s="104">
+        <v>1</v>
+      </c>
+      <c r="R4" s="104">
+        <v>1000</v>
+      </c>
+      <c r="S4" s="106">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="T4" s="104">
+        <v>67</v>
+      </c>
+      <c r="U4" s="105">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="V4" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB4" s="104" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" s="109">
+        <v>3</v>
+      </c>
+      <c r="B5" s="111" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>583</v>
+      </c>
+      <c r="E5" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="109">
+        <v>262119</v>
+      </c>
+      <c r="G5" s="109" t="s">
+        <v>602</v>
+      </c>
+      <c r="H5" s="109">
+        <v>300</v>
+      </c>
+      <c r="I5" s="110">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="J5" s="110">
+        <v>1.347</v>
+      </c>
+      <c r="K5" s="109" t="s">
+        <v>601</v>
+      </c>
+      <c r="L5" s="106">
+        <v>395.21</v>
+      </c>
+      <c r="M5" s="108">
+        <v>404.1</v>
+      </c>
+      <c r="N5" s="105">
+        <v>0.11219999999999999</v>
+      </c>
+      <c r="O5" s="107">
+        <v>6.73</v>
+      </c>
+      <c r="P5" s="104">
+        <v>136.30000000000001</v>
+      </c>
+      <c r="Q5" s="104">
+        <v>1</v>
+      </c>
+      <c r="R5" s="104">
+        <v>1000</v>
+      </c>
+      <c r="S5" s="106">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="T5" s="104">
+        <v>22</v>
+      </c>
+      <c r="U5" s="105">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="V5" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5" s="104" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" s="109">
+        <v>4</v>
+      </c>
+      <c r="B6" s="111" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="109" t="s">
+        <v>583</v>
+      </c>
+      <c r="E6" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="109">
+        <v>262120</v>
+      </c>
+      <c r="G6" s="109" t="s">
+        <v>599</v>
+      </c>
+      <c r="H6" s="109">
+        <v>3000</v>
+      </c>
+      <c r="I6" s="110">
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="J6" s="110">
+        <v>1.5609999999999999</v>
+      </c>
+      <c r="K6" s="109" t="s">
+        <v>598</v>
+      </c>
+      <c r="L6" s="106">
+        <v>2135.4479999999999</v>
+      </c>
+      <c r="M6" s="108">
+        <v>2341.5</v>
+      </c>
+      <c r="N6" s="105">
+        <v>0.32519999999999999</v>
+      </c>
+      <c r="O6" s="107">
+        <v>19.510000000000002</v>
+      </c>
+      <c r="P6" s="104">
+        <v>736.7</v>
+      </c>
+      <c r="Q6" s="104">
+        <v>2</v>
+      </c>
+      <c r="R6" s="104">
+        <v>950</v>
+      </c>
+      <c r="S6" s="106">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="T6" s="104">
+        <v>38</v>
+      </c>
+      <c r="U6" s="105">
+        <v>0.04</v>
+      </c>
+      <c r="V6" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="104" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB6" s="104" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="109">
+        <v>5</v>
+      </c>
+      <c r="B7" s="111" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="109" t="s">
+        <v>583</v>
+      </c>
+      <c r="E7" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="109">
+        <v>262122</v>
+      </c>
+      <c r="G7" s="109" t="s">
+        <v>594</v>
+      </c>
+      <c r="H7" s="109">
+        <v>2500</v>
+      </c>
+      <c r="I7" s="110">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="J7" s="110">
+        <v>1.5629999999999999</v>
+      </c>
+      <c r="K7" s="109" t="s">
+        <v>596</v>
+      </c>
+      <c r="L7" s="106">
+        <v>1805.2650000000001</v>
+      </c>
+      <c r="M7" s="108">
+        <v>1953.8</v>
+      </c>
+      <c r="N7" s="105">
+        <v>0.27139999999999997</v>
+      </c>
+      <c r="O7" s="107">
+        <v>16.28</v>
+      </c>
+      <c r="P7" s="104">
+        <v>622.79999999999995</v>
+      </c>
+      <c r="Q7" s="104">
+        <v>2</v>
+      </c>
+      <c r="R7" s="104">
+        <v>950</v>
+      </c>
+      <c r="S7" s="106">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="T7" s="104">
+        <v>26</v>
+      </c>
+      <c r="U7" s="105">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="V7" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X7" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y7" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="104" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB7" s="104" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" s="109">
+        <v>6</v>
+      </c>
+      <c r="B8" s="111" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="109" t="s">
+        <v>583</v>
+      </c>
+      <c r="E8" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="109">
+        <v>262121</v>
+      </c>
+      <c r="G8" s="109" t="s">
+        <v>594</v>
+      </c>
+      <c r="H8" s="109">
+        <v>2500</v>
+      </c>
+      <c r="I8" s="110">
+        <v>0.42</v>
+      </c>
+      <c r="J8" s="110">
+        <v>1.123</v>
+      </c>
+      <c r="K8" s="109" t="s">
+        <v>593</v>
+      </c>
+      <c r="L8" s="106">
+        <v>1179.1500000000001</v>
+      </c>
+      <c r="M8" s="108">
+        <v>1403.8</v>
+      </c>
+      <c r="N8" s="105">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="O8" s="107">
+        <v>11.7</v>
+      </c>
+      <c r="P8" s="104">
+        <v>406.8</v>
+      </c>
+      <c r="Q8" s="104">
+        <v>2</v>
+      </c>
+      <c r="R8" s="104">
+        <v>900</v>
+      </c>
+      <c r="S8" s="106">
+        <v>0.84</v>
+      </c>
+      <c r="T8" s="104">
+        <v>60</v>
+      </c>
+      <c r="U8" s="105">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="V8" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="W8" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X8" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y8" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="104" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB8" s="104" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="103">
+        <v>8800</v>
+      </c>
+      <c r="I9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" s="102">
+        <v>2193.8000000000002</v>
+      </c>
+      <c r="Q9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="S9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="T9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="U9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="V9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="W9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="X9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB9" s="102" t="s">
         <v>27</v>
       </c>
     </row>
@@ -22300,7 +23165,6 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EB2833-7B93-414B-AD4B-F0C7BDBEF127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE971FC9-7CE9-4C0D-BFE2-564A22735E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="22" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="28" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051 M" sheetId="60" r:id="rId1"/>
@@ -43,6 +43,8 @@
     <sheet name="HARMONY EMBALAGENS 1091 P" sheetId="78" r:id="rId28"/>
     <sheet name="IPE - PCBOX EMBALAGENS 1094" sheetId="79" r:id="rId29"/>
     <sheet name="ABAPEL 1095" sheetId="80" r:id="rId30"/>
+    <sheet name="FAVINCO 1096" sheetId="81" r:id="rId31"/>
+    <sheet name="São Miguel 1097" sheetId="82" r:id="rId32"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023 M'!$A$1:$AB$10</definedName>
@@ -68,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5537" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5857" uniqueCount="655">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1967,6 +1969,72 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA - ABAPEL COMERCIO DE EMBALAGENS LTDA  —  OF: 001095</t>
+  </si>
+  <si>
+    <t>1132x1720</t>
+  </si>
+  <si>
+    <t>50x128x100</t>
+  </si>
+  <si>
+    <t>PRIME 046</t>
+  </si>
+  <si>
+    <t>941x1780</t>
+  </si>
+  <si>
+    <t>84x139x84</t>
+  </si>
+  <si>
+    <t>820x2070</t>
+  </si>
+  <si>
+    <t>200x400x200</t>
+  </si>
+  <si>
+    <t>PRIME 047</t>
+  </si>
+  <si>
+    <t>1070x2120</t>
+  </si>
+  <si>
+    <t>125x275x125</t>
+  </si>
+  <si>
+    <t>P60B</t>
+  </si>
+  <si>
+    <t>1180x2020</t>
+  </si>
+  <si>
+    <t>PRIME 048</t>
+  </si>
+  <si>
+    <t>1020x1910</t>
+  </si>
+  <si>
+    <t>1020x2090</t>
+  </si>
+  <si>
+    <t>1020x2020</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - ANSELMO E FILHOS LTDA  —  OF: 001096</t>
+  </si>
+  <si>
+    <t>1100x2090</t>
+  </si>
+  <si>
+    <t>10/08/2026</t>
+  </si>
+  <si>
+    <t>São Miguel</t>
+  </si>
+  <si>
+    <t>1040x1990</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - São Miguel  —  OF: 001097</t>
   </si>
 </sst>
 </file>
@@ -26854,6 +26922,1638 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEE2B25-3AB7-403C-A289-9D2E4B6CDB55}">
+  <dimension ref="A1:AB11"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.21875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.77734375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.77734375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="7.77734375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="4.21875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.44140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="7.5546875" style="1" customWidth="1"/>
+    <col min="23" max="24" width="7.88671875" style="1" customWidth="1"/>
+    <col min="25" max="26" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="4.21875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="151" t="s">
+        <v>649</v>
+      </c>
+      <c r="B1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="151" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="41.4" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="5">
+        <v>262140</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1250</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="7">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="7">
+        <v>625</v>
+      </c>
+      <c r="M3" s="9">
+        <v>416.7</v>
+      </c>
+      <c r="N3" s="6">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="O3" s="8">
+        <v>2.31</v>
+      </c>
+      <c r="P3" s="5">
+        <v>215.6</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>3</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1550</v>
+      </c>
+      <c r="S3" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="T3" s="5">
+        <v>50</v>
+      </c>
+      <c r="U3" s="6">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="5">
+        <v>262142</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="H4" s="5">
+        <v>600</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.69</v>
+      </c>
+      <c r="J4" s="7">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="7">
+        <v>414</v>
+      </c>
+      <c r="M4" s="9">
+        <v>300</v>
+      </c>
+      <c r="N4" s="6">
+        <v>4.1700000000000001E-2</v>
+      </c>
+      <c r="O4" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="P4" s="5">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>2</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1400</v>
+      </c>
+      <c r="S4" s="7">
+        <v>1.38</v>
+      </c>
+      <c r="T4" s="5">
+        <v>20</v>
+      </c>
+      <c r="U4" s="6">
+        <v>1.43E-2</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="5">
+        <v>262143</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0.63</v>
+      </c>
+      <c r="J5" s="7">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="7">
+        <v>630</v>
+      </c>
+      <c r="M5" s="9">
+        <v>500</v>
+      </c>
+      <c r="N5" s="6">
+        <v>6.9400000000000003E-2</v>
+      </c>
+      <c r="O5" s="8">
+        <v>4.17</v>
+      </c>
+      <c r="P5" s="5">
+        <v>217.3</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>2</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1300</v>
+      </c>
+      <c r="S5" s="7">
+        <v>1.26</v>
+      </c>
+      <c r="T5" s="5">
+        <v>40</v>
+      </c>
+      <c r="U5" s="6">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="5">
+        <v>262141</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1250</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="7">
+        <v>725</v>
+      </c>
+      <c r="M6" s="9">
+        <v>625</v>
+      </c>
+      <c r="N6" s="6">
+        <v>8.6800000000000002E-2</v>
+      </c>
+      <c r="O6" s="8">
+        <v>5.21</v>
+      </c>
+      <c r="P6" s="5">
+        <v>250.1</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>2</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1200</v>
+      </c>
+      <c r="S6" s="7">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="T6" s="5">
+        <v>40</v>
+      </c>
+      <c r="U6" s="6">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB6" s="5" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="5">
+        <v>262136</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1100</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="J7" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="L7" s="7">
+        <v>606.375</v>
+      </c>
+      <c r="M7" s="9">
+        <v>577.5</v>
+      </c>
+      <c r="N7" s="6">
+        <v>8.0199999999999994E-2</v>
+      </c>
+      <c r="O7" s="8">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="P7" s="5">
+        <v>259.2</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>2</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1100</v>
+      </c>
+      <c r="S7" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="T7" s="5">
+        <v>50</v>
+      </c>
+      <c r="U7" s="6">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="X7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB7" s="5" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="5">
+        <v>262139</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="H8" s="5">
+        <v>300</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="J8" s="7">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="L8" s="7">
+        <v>492</v>
+      </c>
+      <c r="M8" s="9">
+        <v>615</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0.17080000000000001</v>
+      </c>
+      <c r="O8" s="8">
+        <v>10.25</v>
+      </c>
+      <c r="P8" s="5">
+        <v>190.9</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5">
+        <v>850</v>
+      </c>
+      <c r="S8" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="T8" s="5">
+        <v>50</v>
+      </c>
+      <c r="U8" s="6">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB8" s="5" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A9" s="5">
+        <v>7</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="5">
+        <v>262137</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0.307</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="L9" s="7">
+        <v>270.16000000000003</v>
+      </c>
+      <c r="M9" s="9">
+        <v>440</v>
+      </c>
+      <c r="N9" s="6">
+        <v>6.1100000000000002E-2</v>
+      </c>
+      <c r="O9" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="P9" s="5">
+        <v>93.2</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>2</v>
+      </c>
+      <c r="R9" s="5">
+        <v>650</v>
+      </c>
+      <c r="S9" s="7">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="T9" s="5">
+        <v>36</v>
+      </c>
+      <c r="U9" s="6">
+        <v>5.5399999999999998E-2</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB9" s="5" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A10" s="5">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="5">
+        <v>262138</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="H10" s="5">
+        <v>4000</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="L10" s="7">
+        <v>945.2</v>
+      </c>
+      <c r="M10" s="9">
+        <v>1700</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0.2361</v>
+      </c>
+      <c r="O10" s="8">
+        <v>14.17</v>
+      </c>
+      <c r="P10" s="5">
+        <v>326.10000000000002</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>2</v>
+      </c>
+      <c r="R10" s="5">
+        <v>600</v>
+      </c>
+      <c r="S10" s="7">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="T10" s="5">
+        <v>44</v>
+      </c>
+      <c r="U10" s="6">
+        <v>7.3300000000000004E-2</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB10" s="5" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="19">
+        <v>10500</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="19">
+        <v>1695.4</v>
+      </c>
+      <c r="Q11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="X11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB11" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E82F41-0460-47C8-967A-88BDF0BCF1B5}">
+  <dimension ref="A1:AB7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="4.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.21875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="8.77734375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="4.21875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="6.33203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="6.5546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="8.21875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="8.88671875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="8.21875" style="1" customWidth="1"/>
+    <col min="25" max="25" width="9.5546875" style="1" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="7.5546875" style="1" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="4.109375" style="1" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1">
+      <c r="A1" s="151" t="s">
+        <v>654</v>
+      </c>
+      <c r="B1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="151" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="62.4" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="5">
+        <v>262151</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="H3" s="5">
+        <v>4000</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0.51</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="7">
+        <v>2009.4</v>
+      </c>
+      <c r="M3" s="9">
+        <v>1313.3</v>
+      </c>
+      <c r="N3" s="6">
+        <v>0.1216</v>
+      </c>
+      <c r="O3" s="8">
+        <v>7.3</v>
+      </c>
+      <c r="P3" s="5">
+        <v>693.2</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>3</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1550</v>
+      </c>
+      <c r="S3" s="7">
+        <v>1.53</v>
+      </c>
+      <c r="T3" s="5">
+        <v>20</v>
+      </c>
+      <c r="U3" s="6">
+        <v>1.29E-2</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="5">
+        <v>262150</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4000</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.46</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0.89</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="7">
+        <v>1637.6</v>
+      </c>
+      <c r="M4" s="9">
+        <v>1186.7</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0.1099</v>
+      </c>
+      <c r="O4" s="8">
+        <v>6.59</v>
+      </c>
+      <c r="P4" s="5">
+        <v>565</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>3</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1400</v>
+      </c>
+      <c r="S4" s="7">
+        <v>1.38</v>
+      </c>
+      <c r="T4" s="5">
+        <v>20</v>
+      </c>
+      <c r="U4" s="6">
+        <v>1.43E-2</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="5">
+        <v>262148</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="H5" s="5">
+        <v>4000</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0.36</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.69</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="7">
+        <v>993.6</v>
+      </c>
+      <c r="M5" s="9">
+        <v>920</v>
+      </c>
+      <c r="N5" s="6">
+        <v>8.5199999999999998E-2</v>
+      </c>
+      <c r="O5" s="8">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="P5" s="5">
+        <v>342.8</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>3</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1100</v>
+      </c>
+      <c r="S5" s="7">
+        <v>1.08</v>
+      </c>
+      <c r="T5" s="5">
+        <v>20</v>
+      </c>
+      <c r="U5" s="6">
+        <v>1.8200000000000001E-2</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="5">
+        <v>262149</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="H6" s="5">
+        <v>4000</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0.36</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0.69</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="7">
+        <v>993.6</v>
+      </c>
+      <c r="M6" s="9">
+        <v>920</v>
+      </c>
+      <c r="N6" s="6">
+        <v>8.5199999999999998E-2</v>
+      </c>
+      <c r="O6" s="8">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="P6" s="5">
+        <v>375.6</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>3</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1100</v>
+      </c>
+      <c r="S6" s="7">
+        <v>1.08</v>
+      </c>
+      <c r="T6" s="5">
+        <v>20</v>
+      </c>
+      <c r="U6" s="6">
+        <v>1.8200000000000001E-2</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB6" s="5" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="19">
+        <v>16000</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="19">
+        <v>1976.6</v>
+      </c>
+      <c r="Q7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="X7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB7" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DED98A-7C54-481B-B12E-5DA15CD22C80}">
   <sheetPr>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE971FC9-7CE9-4C0D-BFE2-564A22735E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73743943-860C-41B4-BF0D-1317E6BFD6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="28" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="29" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051 M" sheetId="60" r:id="rId1"/>
@@ -42,9 +42,11 @@
     <sheet name="UPAPER 1090" sheetId="77" r:id="rId27"/>
     <sheet name="HARMONY EMBALAGENS 1091 P" sheetId="78" r:id="rId28"/>
     <sheet name="IPE - PCBOX EMBALAGENS 1094" sheetId="79" r:id="rId29"/>
-    <sheet name="ABAPEL 1095" sheetId="80" r:id="rId30"/>
+    <sheet name="ABAPEL 1095 P" sheetId="80" r:id="rId30"/>
     <sheet name="FAVINCO 1096" sheetId="81" r:id="rId31"/>
     <sheet name="São Miguel 1097" sheetId="82" r:id="rId32"/>
+    <sheet name="Tolecaixas 1099" sheetId="83" r:id="rId33"/>
+    <sheet name="DR Embalagens 1100" sheetId="84" r:id="rId34"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023 M'!$A$1:$AB$10</definedName>
@@ -70,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5857" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6158" uniqueCount="662">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -2035,6 +2037,27 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA - São Miguel  —  OF: 001097</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - Tolecaixas Indústria e Comércio Ltda  —  OF: 001099</t>
+  </si>
+  <si>
+    <t>DR Embalagens</t>
+  </si>
+  <si>
+    <t>840x1660</t>
+  </si>
+  <si>
+    <t>970x2030</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - LOSSO &amp; RUNDBUCHNER EMBALAGENS LTDA  —  OF: 001100</t>
+  </si>
+  <si>
+    <t>PRIME 049</t>
+  </si>
+  <si>
+    <t>713x2120</t>
   </si>
 </sst>
 </file>
@@ -2046,7 +2069,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2242,7 +2265,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2662,6 +2685,30 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2883,7 +2930,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="23.44140625" style="3" customWidth="1"/>
@@ -2914,7 +2961,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="145" t="s">
         <v>309</v>
       </c>
@@ -3000,7 +3047,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="30" customHeight="1">
+    <row r="2" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -3086,7 +3133,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="38">
         <v>1</v>
       </c>
@@ -3172,7 +3219,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="38">
         <v>2</v>
       </c>
@@ -3258,7 +3305,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>3</v>
       </c>
@@ -3344,7 +3391,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>4</v>
       </c>
@@ -3430,7 +3477,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>5</v>
       </c>
@@ -3516,7 +3563,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>6</v>
       </c>
@@ -3602,7 +3649,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>7</v>
       </c>
@@ -3688,7 +3735,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1">
+    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>27</v>
       </c>
@@ -3786,7 +3833,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6468C93-3B43-46CB-8998-F687C6A9465C}">
   <dimension ref="A1:AB9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
@@ -3818,7 +3865,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="145" t="s">
         <v>285</v>
       </c>
@@ -3904,7 +3951,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="52.8" customHeight="1">
+    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -3990,7 +4037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="38">
         <v>1</v>
       </c>
@@ -4076,7 +4123,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="38">
         <v>2</v>
       </c>
@@ -4162,7 +4209,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>3</v>
       </c>
@@ -4248,7 +4295,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>4</v>
       </c>
@@ -4334,7 +4381,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>5</v>
       </c>
@@ -4420,7 +4467,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>6</v>
       </c>
@@ -4506,7 +4553,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
         <v>27</v>
       </c>
@@ -4606,7 +4653,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -4637,7 +4684,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="150" t="s">
         <v>308</v>
       </c>
@@ -4723,7 +4770,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="48" customHeight="1">
+    <row r="2" spans="1:28" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -4809,7 +4856,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -4895,7 +4942,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -4981,7 +5028,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -5067,7 +5114,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -5153,7 +5200,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -5239,7 +5286,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -5325,7 +5372,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -5411,7 +5458,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1">
+    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -5512,7 +5559,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB16"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" style="3" hidden="1" customWidth="1"/>
@@ -5543,7 +5590,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="147" t="s">
         <v>326</v>
       </c>
@@ -5629,7 +5676,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="53.4" customHeight="1">
+    <row r="2" spans="1:28" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -5715,7 +5762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="58">
         <v>1</v>
       </c>
@@ -5801,7 +5848,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" s="64" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="58">
         <v>2</v>
       </c>
@@ -5887,7 +5934,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58">
         <v>1</v>
       </c>
@@ -5973,7 +6020,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="58">
         <v>2</v>
       </c>
@@ -6059,7 +6106,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="58">
         <v>3</v>
       </c>
@@ -6145,7 +6192,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="58">
         <v>4</v>
       </c>
@@ -6231,7 +6278,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58">
         <v>5</v>
       </c>
@@ -6317,7 +6364,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="58">
         <v>6</v>
       </c>
@@ -6397,7 +6444,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="58">
         <v>7</v>
       </c>
@@ -6483,7 +6530,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="12" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="58">
         <v>8</v>
       </c>
@@ -6569,7 +6616,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="13" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="58">
         <v>9</v>
       </c>
@@ -6655,7 +6702,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="14" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="58">
         <v>10</v>
       </c>
@@ -6741,7 +6788,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="15" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="58">
         <v>11</v>
       </c>
@@ -6827,7 +6874,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1">
+    <row r="16" spans="1:28" s="65" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="68" t="s">
         <v>27</v>
       </c>
@@ -6928,7 +6975,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="3" customWidth="1"/>
     <col min="2" max="2" width="11" style="3" customWidth="1"/>
@@ -6960,7 +7007,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="145" t="s">
         <v>330</v>
       </c>
@@ -7046,7 +7093,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1">
+    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -7132,7 +7179,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="56">
         <v>1</v>
       </c>
@@ -7215,7 +7262,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" s="56" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="56">
         <v>2</v>
       </c>
@@ -7292,7 +7339,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="17" customFormat="1" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" s="17" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="56">
         <v>3</v>
       </c>
@@ -7378,7 +7425,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="32" t="s">
         <v>27</v>
       </c>
@@ -7479,7 +7526,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="1.109375" style="1" hidden="1" customWidth="1"/>
@@ -7510,7 +7557,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="150" t="s">
         <v>343</v>
       </c>
@@ -7596,7 +7643,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1">
+    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -7682,7 +7729,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="47" customFormat="1" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" s="47" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="47">
         <v>1</v>
       </c>
@@ -7765,7 +7812,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="50">
         <v>2</v>
       </c>
@@ -7851,7 +7898,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="50">
         <v>3</v>
       </c>
@@ -7937,7 +7984,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="50">
         <v>4</v>
       </c>
@@ -8023,7 +8070,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50">
         <v>5</v>
       </c>
@@ -8109,7 +8156,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50">
         <v>6</v>
       </c>
@@ -8195,7 +8242,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="50">
         <v>7</v>
       </c>
@@ -8281,7 +8328,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50">
         <v>8</v>
       </c>
@@ -8367,7 +8414,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="50">
         <v>9</v>
       </c>
@@ -8453,7 +8500,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="25.05" customHeight="1">
+    <row r="12" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -8554,7 +8601,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.109375" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
@@ -8585,7 +8632,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="145" t="s">
         <v>364</v>
       </c>
@@ -8671,7 +8718,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="44.4" customHeight="1">
+    <row r="2" spans="1:28" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -8757,7 +8804,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="38">
         <v>1</v>
       </c>
@@ -8843,7 +8890,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="38">
         <v>2</v>
       </c>
@@ -8929,7 +8976,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>3</v>
       </c>
@@ -9015,7 +9062,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>4</v>
       </c>
@@ -9101,7 +9148,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>5</v>
       </c>
@@ -9187,7 +9234,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
         <v>27</v>
       </c>
@@ -9288,7 +9335,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" style="3" hidden="1" customWidth="1"/>
@@ -9320,7 +9367,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="147" t="s">
         <v>401</v>
       </c>
@@ -9406,7 +9453,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="62.4" customHeight="1">
+    <row r="2" spans="1:28" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -9492,7 +9539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -9578,7 +9625,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -9664,7 +9711,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -9750,7 +9797,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -9836,7 +9883,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -9922,7 +9969,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -10008,7 +10055,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -10094,7 +10141,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -10180,7 +10227,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>27</v>
       </c>
@@ -10281,7 +10328,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB20"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -10312,7 +10359,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="21" customFormat="1" ht="18" customHeight="1">
+    <row r="1" spans="1:28" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="150" t="s">
         <v>430</v>
       </c>
@@ -10398,7 +10445,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="21" customFormat="1" ht="60.6" customHeight="1">
+    <row r="2" spans="1:28" s="21" customFormat="1" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -10484,7 +10531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="3" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -10570,7 +10617,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -10656,7 +10703,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -10742,7 +10789,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -10828,7 +10875,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -10914,7 +10961,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="8" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -11000,7 +11047,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="9" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -11086,7 +11133,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="10" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -11172,7 +11219,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="11" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -11258,7 +11305,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="12" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -11344,7 +11391,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="13" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -11430,7 +11477,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="14" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -11516,7 +11563,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="15" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -11602,7 +11649,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="16" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>14</v>
       </c>
@@ -11688,7 +11735,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="17" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="17" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>15</v>
       </c>
@@ -11774,7 +11821,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="18" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="18" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>16</v>
       </c>
@@ -11860,7 +11907,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="19" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="19" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>17</v>
       </c>
@@ -11946,7 +11993,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="20" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1">
+    <row r="20" spans="1:28" s="21" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -12047,7 +12094,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -12080,7 +12127,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="150" t="s">
         <v>434</v>
       </c>
@@ -12166,7 +12213,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="60" customHeight="1">
+    <row r="2" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -12252,7 +12299,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" customFormat="1" ht="21.6" customHeight="1">
+    <row r="3" spans="1:28" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="83">
         <v>1</v>
       </c>
@@ -12338,7 +12385,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" s="82" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="76">
         <v>1</v>
       </c>
@@ -12424,7 +12471,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="70">
         <v>2</v>
       </c>
@@ -12510,7 +12557,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="83">
         <v>2</v>
       </c>
@@ -12596,7 +12643,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" s="69" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="70">
         <v>3</v>
       </c>
@@ -12682,7 +12729,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>1</v>
       </c>
@@ -12768,7 +12815,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="83">
         <v>3</v>
       </c>
@@ -12854,7 +12901,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.8" customHeight="1">
+    <row r="10" spans="1:28" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="83">
         <v>4</v>
       </c>
@@ -12940,7 +12987,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -13041,7 +13088,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB23"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -13072,7 +13119,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="150" t="s">
         <v>489</v>
       </c>
@@ -13158,7 +13205,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="30" customHeight="1">
+    <row r="2" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -13244,7 +13291,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -13330,7 +13377,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -13416,7 +13463,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -13502,7 +13549,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -13588,7 +13635,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -13674,7 +13721,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -13760,7 +13807,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -13846,7 +13893,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -13932,7 +13979,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -14018,7 +14065,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="25.05" customHeight="1">
+    <row r="12" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -14104,7 +14151,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="25.05" customHeight="1">
+    <row r="13" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -14190,7 +14237,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="25.05" customHeight="1">
+    <row r="14" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -14276,7 +14323,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="25.05" customHeight="1">
+    <row r="15" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -14362,7 +14409,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="25.05" customHeight="1">
+    <row r="16" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>14</v>
       </c>
@@ -14448,7 +14495,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="25.05" customHeight="1">
+    <row r="17" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>15</v>
       </c>
@@ -14534,7 +14581,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="25.05" customHeight="1">
+    <row r="18" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>16</v>
       </c>
@@ -14620,7 +14667,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="25.05" customHeight="1">
+    <row r="19" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>17</v>
       </c>
@@ -14706,7 +14753,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="25.05" customHeight="1">
+    <row r="20" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>18</v>
       </c>
@@ -14792,7 +14839,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="25.05" customHeight="1">
+    <row r="21" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>19</v>
       </c>
@@ -14878,7 +14925,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="25.05" customHeight="1">
+    <row r="22" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>20</v>
       </c>
@@ -14964,7 +15011,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="25.05" customHeight="1">
+    <row r="23" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>27</v>
       </c>
@@ -15065,7 +15112,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
@@ -15096,7 +15143,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18.600000000000001" customHeight="1">
+    <row r="1" spans="1:28" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="146" t="s">
         <v>127</v>
       </c>
@@ -15182,7 +15229,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1">
+    <row r="2" spans="1:28" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -15268,7 +15315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="3" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -15354,7 +15401,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -15440,7 +15487,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -15526,7 +15573,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -15612,7 +15659,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -15698,7 +15745,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="8" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -15784,7 +15831,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="9" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -15870,7 +15917,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1">
+    <row r="10" spans="1:28" s="21" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -15971,7 +16018,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -16003,7 +16050,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="146" t="s">
         <v>493</v>
       </c>
@@ -16089,7 +16136,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="52.8" customHeight="1">
+    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -16175,7 +16222,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="128" customFormat="1" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" s="128" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="120">
         <v>1</v>
       </c>
@@ -16261,7 +16308,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="137" customFormat="1" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" s="137" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="129">
         <v>1</v>
       </c>
@@ -16347,7 +16394,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="137" customFormat="1" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" s="137" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="129">
         <v>2</v>
       </c>
@@ -16433,7 +16480,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="138" customFormat="1" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" s="138" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H6" s="138">
         <v>4340</v>
       </c>
@@ -16456,7 +16503,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB15"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -16488,7 +16535,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="150" t="s">
         <v>519</v>
       </c>
@@ -16574,7 +16621,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="55.2" customHeight="1">
+    <row r="2" spans="1:28" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -16660,7 +16707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -16746,7 +16793,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -16832,7 +16879,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -16918,7 +16965,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -17004,7 +17051,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -17090,7 +17137,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -17176,7 +17223,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -17262,7 +17309,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -17348,7 +17395,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -17434,7 +17481,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="25.05" customHeight="1">
+    <row r="12" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -17520,7 +17567,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="25.05" customHeight="1">
+    <row r="13" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -17606,7 +17653,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="25.05" customHeight="1">
+    <row r="14" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -17692,7 +17739,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="25.05" customHeight="1">
+    <row r="15" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -17790,7 +17837,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C91923-7AE7-4461-9C2E-05FE2CED0119}">
   <dimension ref="A1:AB4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -17822,7 +17869,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="151" t="s">
         <v>523</v>
       </c>
@@ -17908,7 +17955,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="50.4" customHeight="1">
+    <row r="2" spans="1:28" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -17994,7 +18041,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="109">
         <v>1</v>
       </c>
@@ -18080,7 +18127,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="103" t="s">
         <v>27</v>
       </c>
@@ -18180,7 +18227,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -18212,7 +18259,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="146" t="s">
         <v>539</v>
       </c>
@@ -18298,7 +18345,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="39.6" customHeight="1">
+    <row r="2" spans="1:28" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -18384,7 +18431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="112">
         <v>1</v>
       </c>
@@ -18470,7 +18517,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="112">
         <v>2</v>
       </c>
@@ -18556,7 +18603,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="112">
         <v>3</v>
       </c>
@@ -18642,7 +18689,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="112">
         <v>4</v>
       </c>
@@ -18728,7 +18775,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="112">
         <v>5</v>
       </c>
@@ -18814,7 +18861,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="112">
         <v>6</v>
       </c>
@@ -18900,7 +18947,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="112">
         <v>7</v>
       </c>
@@ -18986,7 +19033,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="112">
         <v>8</v>
       </c>
@@ -19072,7 +19119,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="118" t="s">
         <v>27</v>
       </c>
@@ -19173,7 +19220,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.21875" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
@@ -19204,7 +19251,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="147" t="s">
         <v>552</v>
       </c>
@@ -19290,7 +19337,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="52.8" customHeight="1">
+    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -19376,7 +19423,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -19462,7 +19509,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -19548,7 +19595,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -19634,7 +19681,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -19720,7 +19767,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>27</v>
       </c>
@@ -19821,7 +19868,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -19852,7 +19899,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="152" t="s">
         <v>571</v>
       </c>
@@ -19938,7 +19985,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="59.4" customHeight="1">
+    <row r="2" spans="1:28" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="119" t="s">
         <v>0</v>
       </c>
@@ -20024,7 +20071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="112">
         <v>1</v>
       </c>
@@ -20110,7 +20157,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="112">
         <v>2</v>
       </c>
@@ -20196,7 +20243,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="112">
         <v>3</v>
       </c>
@@ -20282,7 +20329,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="112">
         <v>4</v>
       </c>
@@ -20368,7 +20415,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="112">
         <v>5</v>
       </c>
@@ -20454,7 +20501,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="112">
         <v>6</v>
       </c>
@@ -20540,7 +20587,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="112">
         <v>7</v>
       </c>
@@ -20626,7 +20673,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1">
+    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="118" t="s">
         <v>27</v>
       </c>
@@ -20727,7 +20774,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
@@ -20758,7 +20805,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="147" t="s">
         <v>578</v>
       </c>
@@ -20844,7 +20891,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="55.8" customHeight="1">
+    <row r="2" spans="1:28" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -20930,7 +20977,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="25.5" customHeight="1">
+    <row r="3" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -21016,7 +21063,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.5" customHeight="1">
+    <row r="4" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -21102,7 +21149,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.5" customHeight="1">
+    <row r="5" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -21188,7 +21235,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.5" customHeight="1">
+    <row r="6" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -21274,7 +21321,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25.5" customHeight="1">
+    <row r="7" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>27</v>
       </c>
@@ -21372,7 +21419,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDEB15C-42FB-4253-81FF-1E9A43ACCCA8}">
   <dimension ref="A1:AB5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.21875" style="1" hidden="1" customWidth="1"/>
@@ -21404,7 +21451,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="151" t="s">
         <v>581</v>
       </c>
@@ -21490,7 +21537,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="54.6" customHeight="1">
+    <row r="2" spans="1:28" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -21576,7 +21623,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="109">
         <v>1</v>
       </c>
@@ -21662,7 +21709,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="109">
         <v>2</v>
       </c>
@@ -21748,7 +21795,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="103" t="s">
         <v>27</v>
       </c>
@@ -21848,7 +21895,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -21880,7 +21927,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="150" t="s">
         <v>591</v>
       </c>
@@ -21966,7 +22013,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="52.8" customHeight="1">
+    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -22052,7 +22099,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="144" customFormat="1" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" s="144" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="139">
         <v>1</v>
       </c>
@@ -22138,7 +22185,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -22224,7 +22271,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -22310,7 +22357,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -22396,7 +22443,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.2" customHeight="1">
+    <row r="7" spans="1:28" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>27</v>
       </c>
@@ -22494,7 +22541,7 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9920A0AA-9240-4CDC-B26B-9F885FC523AF}">
   <dimension ref="A1:AB9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -22525,7 +22572,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="151" t="s">
         <v>609</v>
       </c>
@@ -22611,7 +22658,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="49.8" customHeight="1">
+    <row r="2" spans="1:28" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -22697,605 +22744,605 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="128" customFormat="1">
-      <c r="A3" s="120">
+    <row r="3" spans="1:28" s="159" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="153">
         <v>1</v>
       </c>
-      <c r="B3" s="121" t="s">
+      <c r="B3" s="154" t="s">
         <v>279</v>
       </c>
-      <c r="C3" s="120" t="s">
+      <c r="C3" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="120" t="s">
+      <c r="D3" s="153" t="s">
         <v>608</v>
       </c>
-      <c r="E3" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="120">
+      <c r="E3" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="153">
         <v>262117</v>
       </c>
-      <c r="G3" s="120" t="s">
+      <c r="G3" s="153" t="s">
         <v>607</v>
       </c>
-      <c r="H3" s="120">
+      <c r="H3" s="153">
         <v>200</v>
       </c>
-      <c r="I3" s="122">
+      <c r="I3" s="155">
         <v>0.79</v>
       </c>
-      <c r="J3" s="122">
+      <c r="J3" s="155">
         <v>2.1429999999999998</v>
       </c>
-      <c r="K3" s="120" t="s">
+      <c r="K3" s="153" t="s">
         <v>606</v>
       </c>
-      <c r="L3" s="123">
+      <c r="L3" s="155">
         <v>338.59399999999999</v>
       </c>
-      <c r="M3" s="124">
+      <c r="M3" s="156">
         <v>214.3</v>
       </c>
-      <c r="N3" s="125">
+      <c r="N3" s="157">
         <v>2.98E-2</v>
       </c>
-      <c r="O3" s="126">
+      <c r="O3" s="158">
         <v>1.79</v>
       </c>
-      <c r="P3" s="127">
+      <c r="P3" s="153">
         <v>116.8</v>
       </c>
-      <c r="Q3" s="127">
+      <c r="Q3" s="153">
         <v>2</v>
       </c>
-      <c r="R3" s="127">
+      <c r="R3" s="153">
         <v>1600</v>
       </c>
-      <c r="S3" s="123">
+      <c r="S3" s="155">
         <v>1.58</v>
       </c>
-      <c r="T3" s="127">
+      <c r="T3" s="153">
         <v>20</v>
       </c>
-      <c r="U3" s="125">
+      <c r="U3" s="157">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="V3" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="X3" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z3" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA3" s="127" t="s">
+      <c r="V3" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="AB3" s="127" t="s">
+      <c r="AB3" s="153" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="128" customFormat="1">
-      <c r="A4" s="120">
+    <row r="4" spans="1:28" s="159" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="153">
         <v>2</v>
       </c>
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="154" t="s">
         <v>279</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="153" t="s">
         <v>383</v>
       </c>
-      <c r="E4" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="120">
+      <c r="E4" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="153">
         <v>262118</v>
       </c>
-      <c r="G4" s="120" t="s">
+      <c r="G4" s="153" t="s">
         <v>604</v>
       </c>
-      <c r="H4" s="120">
+      <c r="H4" s="153">
         <v>300</v>
       </c>
-      <c r="I4" s="122">
+      <c r="I4" s="155">
         <v>0.93300000000000005</v>
       </c>
-      <c r="J4" s="122">
+      <c r="J4" s="155">
         <v>1.8049999999999999</v>
       </c>
-      <c r="K4" s="120" t="s">
+      <c r="K4" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="123">
+      <c r="L4" s="155">
         <v>505.22</v>
       </c>
-      <c r="M4" s="124">
+      <c r="M4" s="156">
         <v>541.5</v>
       </c>
-      <c r="N4" s="125">
+      <c r="N4" s="157">
         <v>0.15040000000000001</v>
       </c>
-      <c r="O4" s="126">
+      <c r="O4" s="158">
         <v>9.0299999999999994</v>
       </c>
-      <c r="P4" s="127">
+      <c r="P4" s="153">
         <v>174.3</v>
       </c>
-      <c r="Q4" s="127">
+      <c r="Q4" s="153">
         <v>1</v>
       </c>
-      <c r="R4" s="127">
+      <c r="R4" s="153">
         <v>1000</v>
       </c>
-      <c r="S4" s="123">
+      <c r="S4" s="155">
         <v>0.93300000000000005</v>
       </c>
-      <c r="T4" s="127">
+      <c r="T4" s="153">
         <v>67</v>
       </c>
-      <c r="U4" s="125">
+      <c r="U4" s="157">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="V4" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="X4" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="127" t="s">
+      <c r="V4" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="AB4" s="127" t="s">
+      <c r="AB4" s="153" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="128" customFormat="1">
-      <c r="A5" s="120">
+    <row r="5" spans="1:28" s="159" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="153">
         <v>3</v>
       </c>
-      <c r="B5" s="121" t="s">
+      <c r="B5" s="154" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="120" t="s">
+      <c r="C5" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="120" t="s">
+      <c r="D5" s="153" t="s">
         <v>583</v>
       </c>
-      <c r="E5" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="120">
+      <c r="E5" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="153">
         <v>262119</v>
       </c>
-      <c r="G5" s="120" t="s">
+      <c r="G5" s="153" t="s">
         <v>602</v>
       </c>
-      <c r="H5" s="120">
+      <c r="H5" s="153">
         <v>300</v>
       </c>
-      <c r="I5" s="122">
+      <c r="I5" s="155">
         <v>0.97799999999999998</v>
       </c>
-      <c r="J5" s="122">
+      <c r="J5" s="155">
         <v>1.347</v>
       </c>
-      <c r="K5" s="120" t="s">
+      <c r="K5" s="153" t="s">
         <v>601</v>
       </c>
-      <c r="L5" s="123">
+      <c r="L5" s="155">
         <v>395.21</v>
       </c>
-      <c r="M5" s="124">
+      <c r="M5" s="156">
         <v>404.1</v>
       </c>
-      <c r="N5" s="125">
+      <c r="N5" s="157">
         <v>0.11219999999999999</v>
       </c>
-      <c r="O5" s="126">
+      <c r="O5" s="158">
         <v>6.73</v>
       </c>
-      <c r="P5" s="127">
+      <c r="P5" s="153">
         <v>136.30000000000001</v>
       </c>
-      <c r="Q5" s="127">
+      <c r="Q5" s="153">
         <v>1</v>
       </c>
-      <c r="R5" s="127">
+      <c r="R5" s="153">
         <v>1000</v>
       </c>
-      <c r="S5" s="123">
+      <c r="S5" s="155">
         <v>0.97799999999999998</v>
       </c>
-      <c r="T5" s="127">
+      <c r="T5" s="153">
         <v>22</v>
       </c>
-      <c r="U5" s="125">
+      <c r="U5" s="157">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="V5" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="W5" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="X5" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z5" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA5" s="127" t="s">
+      <c r="V5" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="AB5" s="127" t="s">
+      <c r="AB5" s="153" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="128" customFormat="1">
-      <c r="A6" s="120">
+    <row r="6" spans="1:28" s="159" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="153">
         <v>4</v>
       </c>
-      <c r="B6" s="121" t="s">
+      <c r="B6" s="154" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="120" t="s">
+      <c r="C6" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="120" t="s">
+      <c r="D6" s="153" t="s">
         <v>583</v>
       </c>
-      <c r="E6" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="120">
+      <c r="E6" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="153">
         <v>262120</v>
       </c>
-      <c r="G6" s="120" t="s">
+      <c r="G6" s="153" t="s">
         <v>599</v>
       </c>
-      <c r="H6" s="120">
+      <c r="H6" s="153">
         <v>3000</v>
       </c>
-      <c r="I6" s="122">
+      <c r="I6" s="155">
         <v>0.45600000000000002</v>
       </c>
-      <c r="J6" s="122">
+      <c r="J6" s="155">
         <v>1.5609999999999999</v>
       </c>
-      <c r="K6" s="120" t="s">
+      <c r="K6" s="153" t="s">
         <v>598</v>
       </c>
-      <c r="L6" s="123">
+      <c r="L6" s="155">
         <v>2135.4479999999999</v>
       </c>
-      <c r="M6" s="124">
+      <c r="M6" s="156">
         <v>2341.5</v>
       </c>
-      <c r="N6" s="125">
+      <c r="N6" s="157">
         <v>0.32519999999999999</v>
       </c>
-      <c r="O6" s="126">
+      <c r="O6" s="158">
         <v>19.510000000000002</v>
       </c>
-      <c r="P6" s="127">
+      <c r="P6" s="153">
         <v>736.7</v>
       </c>
-      <c r="Q6" s="127">
+      <c r="Q6" s="153">
         <v>2</v>
       </c>
-      <c r="R6" s="127">
+      <c r="R6" s="153">
         <v>950</v>
       </c>
-      <c r="S6" s="123">
+      <c r="S6" s="155">
         <v>0.91200000000000003</v>
       </c>
-      <c r="T6" s="127">
+      <c r="T6" s="153">
         <v>38</v>
       </c>
-      <c r="U6" s="125">
+      <c r="U6" s="157">
         <v>0.04</v>
       </c>
-      <c r="V6" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="W6" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="X6" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y6" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z6" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA6" s="127" t="s">
+      <c r="V6" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="AB6" s="127" t="s">
+      <c r="AB6" s="153" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="128" customFormat="1">
-      <c r="A7" s="120">
+    <row r="7" spans="1:28" s="159" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="153">
         <v>5</v>
       </c>
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="154" t="s">
         <v>156</v>
       </c>
-      <c r="C7" s="120" t="s">
+      <c r="C7" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="120" t="s">
+      <c r="D7" s="153" t="s">
         <v>583</v>
       </c>
-      <c r="E7" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="120">
+      <c r="E7" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="153">
         <v>262122</v>
       </c>
-      <c r="G7" s="120" t="s">
+      <c r="G7" s="153" t="s">
         <v>594</v>
       </c>
-      <c r="H7" s="120">
+      <c r="H7" s="153">
         <v>2500</v>
       </c>
-      <c r="I7" s="122">
+      <c r="I7" s="155">
         <v>0.46200000000000002</v>
       </c>
-      <c r="J7" s="122">
+      <c r="J7" s="155">
         <v>1.5629999999999999</v>
       </c>
-      <c r="K7" s="120" t="s">
+      <c r="K7" s="153" t="s">
         <v>596</v>
       </c>
-      <c r="L7" s="123">
+      <c r="L7" s="155">
         <v>1805.2650000000001</v>
       </c>
-      <c r="M7" s="124">
+      <c r="M7" s="156">
         <v>1953.8</v>
       </c>
-      <c r="N7" s="125">
+      <c r="N7" s="157">
         <v>0.27139999999999997</v>
       </c>
-      <c r="O7" s="126">
+      <c r="O7" s="158">
         <v>16.28</v>
       </c>
-      <c r="P7" s="127">
+      <c r="P7" s="153">
         <v>622.79999999999995</v>
       </c>
-      <c r="Q7" s="127">
+      <c r="Q7" s="153">
         <v>2</v>
       </c>
-      <c r="R7" s="127">
+      <c r="R7" s="153">
         <v>950</v>
       </c>
-      <c r="S7" s="123">
+      <c r="S7" s="155">
         <v>0.92400000000000004</v>
       </c>
-      <c r="T7" s="127">
+      <c r="T7" s="153">
         <v>26</v>
       </c>
-      <c r="U7" s="125">
+      <c r="U7" s="157">
         <v>2.7400000000000001E-2</v>
       </c>
-      <c r="V7" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="W7" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="X7" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y7" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z7" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA7" s="127" t="s">
+      <c r="V7" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="X7" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y7" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="AB7" s="127" t="s">
+      <c r="AB7" s="153" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="128" customFormat="1">
-      <c r="A8" s="120">
+    <row r="8" spans="1:28" s="159" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="153">
         <v>6</v>
       </c>
-      <c r="B8" s="121" t="s">
+      <c r="B8" s="154" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="120" t="s">
+      <c r="C8" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="120" t="s">
+      <c r="D8" s="153" t="s">
         <v>583</v>
       </c>
-      <c r="E8" s="120" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="120">
+      <c r="E8" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="153">
         <v>262121</v>
       </c>
-      <c r="G8" s="120" t="s">
+      <c r="G8" s="153" t="s">
         <v>594</v>
       </c>
-      <c r="H8" s="120">
+      <c r="H8" s="153">
         <v>2500</v>
       </c>
-      <c r="I8" s="122">
+      <c r="I8" s="155">
         <v>0.42</v>
       </c>
-      <c r="J8" s="122">
+      <c r="J8" s="155">
         <v>1.123</v>
       </c>
-      <c r="K8" s="120" t="s">
+      <c r="K8" s="153" t="s">
         <v>593</v>
       </c>
-      <c r="L8" s="123">
+      <c r="L8" s="155">
         <v>1179.1500000000001</v>
       </c>
-      <c r="M8" s="124">
+      <c r="M8" s="156">
         <v>1403.8</v>
       </c>
-      <c r="N8" s="125">
+      <c r="N8" s="157">
         <v>0.19500000000000001</v>
       </c>
-      <c r="O8" s="126">
+      <c r="O8" s="158">
         <v>11.7</v>
       </c>
-      <c r="P8" s="127">
+      <c r="P8" s="153">
         <v>406.8</v>
       </c>
-      <c r="Q8" s="127">
+      <c r="Q8" s="153">
         <v>2</v>
       </c>
-      <c r="R8" s="127">
+      <c r="R8" s="153">
         <v>900</v>
       </c>
-      <c r="S8" s="123">
+      <c r="S8" s="155">
         <v>0.84</v>
       </c>
-      <c r="T8" s="127">
+      <c r="T8" s="153">
         <v>60</v>
       </c>
-      <c r="U8" s="125">
+      <c r="U8" s="157">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="V8" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="W8" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="X8" s="127" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y8" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z8" s="127" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA8" s="127" t="s">
+      <c r="V8" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="W8" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="X8" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y8" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="153" t="s">
         <v>33</v>
       </c>
-      <c r="AB8" s="127" t="s">
+      <c r="AB8" s="153" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
-      <c r="A9" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="103">
+    <row r="9" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="19">
         <v>8800</v>
       </c>
-      <c r="I9" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="P9" s="102">
+      <c r="I9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" s="19">
         <v>2193.8000000000002</v>
       </c>
-      <c r="Q9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="R9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="S9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="T9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="U9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="V9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="W9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="X9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA9" s="102" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB9" s="102" t="s">
+      <c r="Q9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="X9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB9" s="19" t="s">
         <v>27</v>
       </c>
     </row>
@@ -23313,7 +23360,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB25"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.21875" style="3" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="3" customWidth="1"/>
@@ -23344,7 +23391,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="147" t="s">
         <v>117</v>
       </c>
@@ -23430,7 +23477,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="41.4" customHeight="1">
+    <row r="2" spans="1:28" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -23516,7 +23563,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="3" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>1</v>
       </c>
@@ -23602,7 +23649,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="4" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>2</v>
       </c>
@@ -23688,7 +23735,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="5" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>3</v>
       </c>
@@ -23774,7 +23821,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="6" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>4</v>
       </c>
@@ -23860,7 +23907,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="7" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>5</v>
       </c>
@@ -23946,7 +23993,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="8" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>6</v>
       </c>
@@ -24032,7 +24079,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="9" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>7</v>
       </c>
@@ -24118,7 +24165,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="10" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>8</v>
       </c>
@@ -24204,7 +24251,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="11" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12">
         <v>9</v>
       </c>
@@ -24290,7 +24337,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="12" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12">
         <v>10</v>
       </c>
@@ -24376,7 +24423,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="13" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12">
         <v>11</v>
       </c>
@@ -24462,7 +24509,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="14" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12">
         <v>12</v>
       </c>
@@ -24548,7 +24595,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="15" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12">
         <v>13</v>
       </c>
@@ -24634,7 +24681,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="16" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12">
         <v>14</v>
       </c>
@@ -24720,7 +24767,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="17" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12">
         <v>15</v>
       </c>
@@ -24806,7 +24853,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="18" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12">
         <v>16</v>
       </c>
@@ -24892,7 +24939,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="19" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12">
         <v>17</v>
       </c>
@@ -24978,7 +25025,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="20" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12">
         <v>18</v>
       </c>
@@ -25064,7 +25111,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="21" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12">
         <v>19</v>
       </c>
@@ -25150,7 +25197,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="22" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12">
         <v>20</v>
       </c>
@@ -25236,7 +25283,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="23" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12">
         <v>21</v>
       </c>
@@ -25322,7 +25369,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="24" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12">
         <v>22</v>
       </c>
@@ -25408,7 +25455,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1">
+    <row r="25" spans="1:28" s="55" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>27</v>
       </c>
@@ -25505,8 +25552,11 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D101D3E4-8064-44B1-A384-F653E66C41A9}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AB16"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -25538,93 +25588,93 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
-      <c r="A1" s="151" t="s">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="146" t="s">
         <v>632</v>
       </c>
-      <c r="B1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="151" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="60.6" customHeight="1">
+      <c r="B1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="146" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="146" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -25710,7 +25760,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -25796,7 +25846,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -25882,7 +25932,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -25968,7 +26018,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -26054,7 +26104,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -26140,7 +26190,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -26226,7 +26276,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -26312,7 +26362,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -26398,7 +26448,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -26484,7 +26534,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="12" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -26570,7 +26620,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="13" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -26656,7 +26706,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="14" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -26742,7 +26792,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="15" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -26828,7 +26878,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="16" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -26918,17 +26968,18 @@
   <mergeCells count="1">
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="94" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEE2B25-3AB7-403C-A289-9D2E4B6CDB55}">
-  <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:AB12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="5.77734375" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
@@ -26955,7 +27006,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="151" t="s">
         <v>649</v>
       </c>
@@ -27041,7 +27092,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="41.4" customHeight="1">
+    <row r="2" spans="1:28" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -27127,7 +27178,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -27213,93 +27264,93 @@
         <v>648</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" s="160" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="5">
-        <v>262142</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>645</v>
-      </c>
-      <c r="H4" s="5">
-        <v>600</v>
-      </c>
-      <c r="I4" s="7">
-        <v>0.69</v>
-      </c>
-      <c r="J4" s="7">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5" t="s">
+      <c r="D4" s="70" t="s">
+        <v>651</v>
+      </c>
+      <c r="E4" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="70">
+        <v>262164</v>
+      </c>
+      <c r="G4" s="70" t="s">
+        <v>660</v>
+      </c>
+      <c r="H4" s="70">
+        <v>500</v>
+      </c>
+      <c r="I4" s="72">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="J4" s="72">
+        <v>0.7</v>
+      </c>
+      <c r="K4" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="7">
-        <v>414</v>
-      </c>
-      <c r="M4" s="9">
-        <v>300</v>
-      </c>
-      <c r="N4" s="6">
-        <v>4.1700000000000001E-2</v>
-      </c>
-      <c r="O4" s="8">
-        <v>2.5</v>
-      </c>
-      <c r="P4" s="5">
-        <v>142.80000000000001</v>
-      </c>
-      <c r="Q4" s="5">
+      <c r="L4" s="72">
+        <v>242.55</v>
+      </c>
+      <c r="M4" s="73">
+        <v>175</v>
+      </c>
+      <c r="N4" s="74">
+        <v>2.4299999999999999E-2</v>
+      </c>
+      <c r="O4" s="75">
+        <v>1.46</v>
+      </c>
+      <c r="P4" s="70">
+        <v>83.7</v>
+      </c>
+      <c r="Q4" s="70">
         <v>2</v>
       </c>
-      <c r="R4" s="5">
-        <v>1400</v>
-      </c>
-      <c r="S4" s="7">
-        <v>1.38</v>
-      </c>
-      <c r="T4" s="5">
-        <v>20</v>
-      </c>
-      <c r="U4" s="6">
-        <v>1.43E-2</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="5" t="s">
+      <c r="R4" s="70">
+        <v>1450</v>
+      </c>
+      <c r="S4" s="72">
+        <v>1.3859999999999999</v>
+      </c>
+      <c r="T4" s="70">
+        <v>64</v>
+      </c>
+      <c r="U4" s="74">
+        <v>4.41E-2</v>
+      </c>
+      <c r="V4" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="AB4" s="5" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+      <c r="AB4" s="70" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -27316,16 +27367,16 @@
         <v>27</v>
       </c>
       <c r="F5" s="5">
-        <v>262143</v>
+        <v>262142</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>645</v>
       </c>
       <c r="H5" s="5">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I5" s="7">
-        <v>0.63</v>
+        <v>0.69</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
@@ -27334,34 +27385,34 @@
         <v>34</v>
       </c>
       <c r="L5" s="7">
-        <v>630</v>
+        <v>414</v>
       </c>
       <c r="M5" s="9">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N5" s="6">
-        <v>6.9400000000000003E-2</v>
+        <v>4.1700000000000001E-2</v>
       </c>
       <c r="O5" s="8">
-        <v>4.17</v>
+        <v>2.5</v>
       </c>
       <c r="P5" s="5">
-        <v>217.3</v>
+        <v>142.80000000000001</v>
       </c>
       <c r="Q5" s="5">
         <v>2</v>
       </c>
       <c r="R5" s="5">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="S5" s="7">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="T5" s="5">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="U5" s="6">
-        <v>3.0800000000000001E-2</v>
+        <v>1.43E-2</v>
       </c>
       <c r="V5" s="5" t="s">
         <v>28</v>
@@ -27382,10 +27433,10 @@
         <v>39</v>
       </c>
       <c r="AB5" s="5" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -27402,16 +27453,16 @@
         <v>27</v>
       </c>
       <c r="F6" s="5">
-        <v>262141</v>
+        <v>262143</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>645</v>
       </c>
       <c r="H6" s="5">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="I6" s="7">
-        <v>0.57999999999999996</v>
+        <v>0.63</v>
       </c>
       <c r="J6" s="7">
         <v>1</v>
@@ -27420,34 +27471,34 @@
         <v>34</v>
       </c>
       <c r="L6" s="7">
-        <v>725</v>
+        <v>630</v>
       </c>
       <c r="M6" s="9">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="N6" s="6">
-        <v>8.6800000000000002E-2</v>
+        <v>6.9400000000000003E-2</v>
       </c>
       <c r="O6" s="8">
-        <v>5.21</v>
+        <v>4.17</v>
       </c>
       <c r="P6" s="5">
-        <v>250.1</v>
+        <v>217.3</v>
       </c>
       <c r="Q6" s="5">
         <v>2</v>
       </c>
       <c r="R6" s="5">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="S6" s="7">
-        <v>1.1599999999999999</v>
+        <v>1.26</v>
       </c>
       <c r="T6" s="5">
         <v>40</v>
       </c>
       <c r="U6" s="6">
-        <v>3.3300000000000003E-2</v>
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="V6" s="5" t="s">
         <v>28</v>
@@ -27468,10 +27519,10 @@
         <v>39</v>
       </c>
       <c r="AB6" s="5" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -27479,7 +27530,7 @@
         <v>190</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>643</v>
+        <v>36</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>613</v>
@@ -27488,61 +27539,61 @@
         <v>27</v>
       </c>
       <c r="F7" s="5">
-        <v>262136</v>
+        <v>262141</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="H7" s="5">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="I7" s="7">
-        <v>0.52500000000000002</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="J7" s="7">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>642</v>
+        <v>34</v>
       </c>
       <c r="L7" s="7">
-        <v>606.375</v>
+        <v>725</v>
       </c>
       <c r="M7" s="9">
-        <v>577.5</v>
+        <v>625</v>
       </c>
       <c r="N7" s="6">
-        <v>8.0199999999999994E-2</v>
+        <v>8.6800000000000002E-2</v>
       </c>
       <c r="O7" s="8">
-        <v>4.8099999999999996</v>
+        <v>5.21</v>
       </c>
       <c r="P7" s="5">
-        <v>259.2</v>
+        <v>250.1</v>
       </c>
       <c r="Q7" s="5">
         <v>2</v>
       </c>
       <c r="R7" s="5">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="S7" s="7">
-        <v>1.05</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="T7" s="5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="U7" s="6">
-        <v>4.5499999999999999E-2</v>
+        <v>3.3300000000000003E-2</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>27</v>
@@ -27554,10 +27605,10 @@
         <v>39</v>
       </c>
       <c r="AB7" s="5" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -27565,7 +27616,7 @@
         <v>190</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>189</v>
+        <v>643</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>613</v>
@@ -27574,61 +27625,61 @@
         <v>27</v>
       </c>
       <c r="F8" s="5">
-        <v>262139</v>
+        <v>262136</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="H8" s="5">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="I8" s="7">
-        <v>0.8</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="J8" s="7">
-        <v>2.0499999999999998</v>
+        <v>1.05</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="L8" s="7">
-        <v>492</v>
+        <v>606.375</v>
       </c>
       <c r="M8" s="9">
-        <v>615</v>
+        <v>577.5</v>
       </c>
       <c r="N8" s="6">
-        <v>0.17080000000000001</v>
+        <v>8.0199999999999994E-2</v>
       </c>
       <c r="O8" s="8">
-        <v>10.25</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="P8" s="5">
-        <v>190.9</v>
+        <v>259.2</v>
       </c>
       <c r="Q8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" s="5">
-        <v>850</v>
+        <v>1100</v>
       </c>
       <c r="S8" s="7">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="T8" s="5">
         <v>50</v>
       </c>
       <c r="U8" s="6">
-        <v>5.8799999999999998E-2</v>
+        <v>4.5499999999999999E-2</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>27</v>
@@ -27640,10 +27691,10 @@
         <v>39</v>
       </c>
       <c r="AB8" s="5" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -27651,7 +27702,7 @@
         <v>190</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>613</v>
@@ -27660,61 +27711,61 @@
         <v>27</v>
       </c>
       <c r="F9" s="5">
-        <v>262137</v>
+        <v>262139</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="H9" s="5">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="I9" s="7">
-        <v>0.307</v>
+        <v>0.8</v>
       </c>
       <c r="J9" s="7">
-        <v>0.88</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L9" s="7">
-        <v>270.16000000000003</v>
+        <v>492</v>
       </c>
       <c r="M9" s="9">
-        <v>440</v>
+        <v>615</v>
       </c>
       <c r="N9" s="6">
-        <v>6.1100000000000002E-2</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="O9" s="8">
-        <v>3.67</v>
+        <v>10.25</v>
       </c>
       <c r="P9" s="5">
-        <v>93.2</v>
+        <v>190.9</v>
       </c>
       <c r="Q9" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9" s="5">
-        <v>650</v>
+        <v>850</v>
       </c>
       <c r="S9" s="7">
-        <v>0.61399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="T9" s="5">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="U9" s="6">
-        <v>5.5399999999999998E-2</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y9" s="5" t="s">
         <v>27</v>
@@ -27726,10 +27777,10 @@
         <v>39</v>
       </c>
       <c r="AB9" s="5" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -27746,158 +27797,244 @@
         <v>27</v>
       </c>
       <c r="F10" s="5">
-        <v>262138</v>
+        <v>262137</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>635</v>
       </c>
       <c r="H10" s="5">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="I10" s="7">
-        <v>0.27800000000000002</v>
+        <v>0.307</v>
       </c>
       <c r="J10" s="7">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="L10" s="7">
-        <v>945.2</v>
+        <v>270.16000000000003</v>
       </c>
       <c r="M10" s="9">
-        <v>1700</v>
+        <v>440</v>
       </c>
       <c r="N10" s="6">
-        <v>0.2361</v>
+        <v>6.1100000000000002E-2</v>
       </c>
       <c r="O10" s="8">
-        <v>14.17</v>
+        <v>3.67</v>
       </c>
       <c r="P10" s="5">
-        <v>326.10000000000002</v>
+        <v>93.2</v>
       </c>
       <c r="Q10" s="5">
         <v>2</v>
       </c>
       <c r="R10" s="5">
+        <v>650</v>
+      </c>
+      <c r="S10" s="7">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="T10" s="5">
+        <v>36</v>
+      </c>
+      <c r="U10" s="6">
+        <v>5.5399999999999998E-2</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB10" s="5" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="5">
+        <v>262138</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="H11" s="5">
+        <v>4000</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="L11" s="7">
+        <v>945.2</v>
+      </c>
+      <c r="M11" s="9">
+        <v>1700</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0.2361</v>
+      </c>
+      <c r="O11" s="8">
+        <v>14.17</v>
+      </c>
+      <c r="P11" s="5">
+        <v>326.10000000000002</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>2</v>
+      </c>
+      <c r="R11" s="5">
         <v>600</v>
       </c>
-      <c r="S10" s="7">
+      <c r="S11" s="7">
         <v>0.55600000000000005</v>
       </c>
-      <c r="T10" s="5">
+      <c r="T11" s="5">
         <v>44</v>
       </c>
-      <c r="U10" s="6">
+      <c r="U11" s="6">
         <v>7.3300000000000004E-2</v>
       </c>
-      <c r="V10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="X10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA10" s="5" t="s">
+      <c r="V11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AB10" s="5" t="s">
+      <c r="AB11" s="5" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
-      <c r="A11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="19">
+    <row r="12" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="19">
         <v>10500</v>
       </c>
-      <c r="I11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="N11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="O11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="P11" s="19">
+      <c r="I12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" s="19">
         <v>1695.4</v>
       </c>
-      <c r="Q11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="S11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="T11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="U11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="V11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="W11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="X11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA11" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB11" s="19" t="s">
+      <c r="Q12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB12" s="19" t="s">
         <v>27</v>
       </c>
     </row>
@@ -27912,7 +28049,7 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E82F41-0460-47C8-967A-88BDF0BCF1B5}">
   <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
@@ -27944,7 +28081,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="151" t="s">
         <v>654</v>
       </c>
@@ -28030,7 +28167,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="62.4" customHeight="1">
+    <row r="2" spans="1:28" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -28116,7 +28253,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="3" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -28202,7 +28339,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -28288,7 +28425,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -28374,7 +28511,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -28460,7 +28597,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>27</v>
       </c>
@@ -28543,6 +28680,1466 @@
         <v>27</v>
       </c>
       <c r="AB7" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A25EA79B-0C15-4C6A-B661-EE70694C63BE}">
+  <dimension ref="A1:AB7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="7" style="1" customWidth="1"/>
+    <col min="17" max="17" width="3.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="7.109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="6.5546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="8" style="1" customWidth="1"/>
+    <col min="23" max="23" width="7.88671875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10" style="1" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="4.21875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="10.5546875" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="151" t="s">
+        <v>655</v>
+      </c>
+      <c r="B1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="151" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="109">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111" t="s">
+        <v>360</v>
+      </c>
+      <c r="C3" s="109" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" s="109" t="s">
+        <v>651</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="109">
+        <v>262154</v>
+      </c>
+      <c r="G3" s="109" t="s">
+        <v>207</v>
+      </c>
+      <c r="H3" s="109">
+        <v>1370</v>
+      </c>
+      <c r="I3" s="110">
+        <v>0.48</v>
+      </c>
+      <c r="J3" s="110">
+        <v>1.25</v>
+      </c>
+      <c r="K3" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="106">
+        <v>822</v>
+      </c>
+      <c r="M3" s="108">
+        <v>570.79999999999995</v>
+      </c>
+      <c r="N3" s="105">
+        <v>5.2900000000000003E-2</v>
+      </c>
+      <c r="O3" s="107">
+        <v>3.17</v>
+      </c>
+      <c r="P3" s="104">
+        <v>310.7</v>
+      </c>
+      <c r="Q3" s="104">
+        <v>3</v>
+      </c>
+      <c r="R3" s="104">
+        <v>1500</v>
+      </c>
+      <c r="S3" s="106">
+        <v>1.44</v>
+      </c>
+      <c r="T3" s="104">
+        <v>60</v>
+      </c>
+      <c r="U3" s="105">
+        <v>0.04</v>
+      </c>
+      <c r="V3" s="104" t="s">
+        <v>38</v>
+      </c>
+      <c r="W3" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="X3" s="104" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="104" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB3" s="104" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="109">
+        <v>2</v>
+      </c>
+      <c r="B4" s="111" t="s">
+        <v>360</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>651</v>
+      </c>
+      <c r="E4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="109">
+        <v>262155</v>
+      </c>
+      <c r="G4" s="109" t="s">
+        <v>207</v>
+      </c>
+      <c r="H4" s="109">
+        <v>1378</v>
+      </c>
+      <c r="I4" s="110">
+        <v>0.67</v>
+      </c>
+      <c r="J4" s="110">
+        <v>0.89</v>
+      </c>
+      <c r="K4" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="106">
+        <v>821.70100000000002</v>
+      </c>
+      <c r="M4" s="108">
+        <v>408.8</v>
+      </c>
+      <c r="N4" s="105">
+        <v>3.7900000000000003E-2</v>
+      </c>
+      <c r="O4" s="107">
+        <v>2.27</v>
+      </c>
+      <c r="P4" s="104">
+        <v>310.60000000000002</v>
+      </c>
+      <c r="Q4" s="104">
+        <v>3</v>
+      </c>
+      <c r="R4" s="104">
+        <v>1200</v>
+      </c>
+      <c r="S4" s="106">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="T4" s="104">
+        <v>-810</v>
+      </c>
+      <c r="U4" s="105">
+        <v>-0.67500000000000004</v>
+      </c>
+      <c r="V4" s="104" t="s">
+        <v>38</v>
+      </c>
+      <c r="W4" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="X4" s="104" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y4" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="104" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB4" s="104" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" s="109">
+        <v>3</v>
+      </c>
+      <c r="B5" s="111" t="s">
+        <v>360</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>651</v>
+      </c>
+      <c r="E5" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="109">
+        <v>262156</v>
+      </c>
+      <c r="G5" s="109" t="s">
+        <v>207</v>
+      </c>
+      <c r="H5" s="109">
+        <v>6104</v>
+      </c>
+      <c r="I5" s="110">
+        <v>0.39</v>
+      </c>
+      <c r="J5" s="110">
+        <v>0.71</v>
+      </c>
+      <c r="K5" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="106">
+        <v>1690.1980000000001</v>
+      </c>
+      <c r="M5" s="108">
+        <v>1444.6</v>
+      </c>
+      <c r="N5" s="105">
+        <v>0.1338</v>
+      </c>
+      <c r="O5" s="107">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="P5" s="104">
+        <v>616.9</v>
+      </c>
+      <c r="Q5" s="104">
+        <v>3</v>
+      </c>
+      <c r="R5" s="104">
+        <v>1200</v>
+      </c>
+      <c r="S5" s="106">
+        <v>1.17</v>
+      </c>
+      <c r="T5" s="104">
+        <v>30</v>
+      </c>
+      <c r="U5" s="105">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="V5" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="W5" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y5" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="104" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB5" s="104" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" s="109">
+        <v>4</v>
+      </c>
+      <c r="B6" s="111" t="s">
+        <v>360</v>
+      </c>
+      <c r="C6" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="109" t="s">
+        <v>651</v>
+      </c>
+      <c r="E6" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="109">
+        <v>262157</v>
+      </c>
+      <c r="G6" s="109" t="s">
+        <v>207</v>
+      </c>
+      <c r="H6" s="109">
+        <v>1658</v>
+      </c>
+      <c r="I6" s="110">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J6" s="110">
+        <v>0.91</v>
+      </c>
+      <c r="K6" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="106">
+        <v>844.91700000000003</v>
+      </c>
+      <c r="M6" s="108">
+        <v>754.4</v>
+      </c>
+      <c r="N6" s="105">
+        <v>0.1048</v>
+      </c>
+      <c r="O6" s="107">
+        <v>6.29</v>
+      </c>
+      <c r="P6" s="104">
+        <v>308.39999999999998</v>
+      </c>
+      <c r="Q6" s="104">
+        <v>2</v>
+      </c>
+      <c r="R6" s="104">
+        <v>1150</v>
+      </c>
+      <c r="S6" s="106">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="T6" s="104">
+        <v>30</v>
+      </c>
+      <c r="U6" s="105">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="V6" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="W6" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y6" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="104" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB6" s="104" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="103">
+        <v>10510</v>
+      </c>
+      <c r="I7" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="102">
+        <v>1546.6</v>
+      </c>
+      <c r="Q7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="T7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="X7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB7" s="102" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{196BA5F5-2581-4325-9A1B-E511B816C01C}">
+  <dimension ref="A1:AB9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" style="1" customWidth="1"/>
+    <col min="8" max="9" width="6.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.44140625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="4" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="6.44140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="8.44140625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="7.5546875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6.88671875" style="1" customWidth="1"/>
+    <col min="25" max="26" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="3.6640625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="151" t="s">
+        <v>659</v>
+      </c>
+      <c r="B1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="151" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="109">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111" t="s">
+        <v>656</v>
+      </c>
+      <c r="C3" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="109" t="s">
+        <v>651</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="109">
+        <v>262158</v>
+      </c>
+      <c r="G3" s="109">
+        <v>1008</v>
+      </c>
+      <c r="H3" s="109">
+        <v>2500</v>
+      </c>
+      <c r="I3" s="110">
+        <v>0.67</v>
+      </c>
+      <c r="J3" s="110">
+        <v>0.95</v>
+      </c>
+      <c r="K3" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="106">
+        <v>1591.25</v>
+      </c>
+      <c r="M3" s="108">
+        <v>1187.5</v>
+      </c>
+      <c r="N3" s="105">
+        <v>0.16489999999999999</v>
+      </c>
+      <c r="O3" s="107">
+        <v>9.9</v>
+      </c>
+      <c r="P3" s="104">
+        <v>549</v>
+      </c>
+      <c r="Q3" s="104">
+        <v>2</v>
+      </c>
+      <c r="R3" s="104">
+        <v>1400</v>
+      </c>
+      <c r="S3" s="106">
+        <v>1.34</v>
+      </c>
+      <c r="T3" s="104">
+        <v>60</v>
+      </c>
+      <c r="U3" s="105">
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="V3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="104" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB3" s="104" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="109">
+        <v>2</v>
+      </c>
+      <c r="B4" s="111" t="s">
+        <v>656</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>651</v>
+      </c>
+      <c r="E4" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="109">
+        <v>262161</v>
+      </c>
+      <c r="G4" s="109">
+        <v>1008</v>
+      </c>
+      <c r="H4" s="109">
+        <v>3000</v>
+      </c>
+      <c r="I4" s="110">
+        <v>0.46</v>
+      </c>
+      <c r="J4" s="110">
+        <v>0.92</v>
+      </c>
+      <c r="K4" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="106">
+        <v>1269.5999999999999</v>
+      </c>
+      <c r="M4" s="108">
+        <v>920</v>
+      </c>
+      <c r="N4" s="105">
+        <v>8.5199999999999998E-2</v>
+      </c>
+      <c r="O4" s="107">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="P4" s="104">
+        <v>479.9</v>
+      </c>
+      <c r="Q4" s="104">
+        <v>3</v>
+      </c>
+      <c r="R4" s="104">
+        <v>1400</v>
+      </c>
+      <c r="S4" s="106">
+        <v>1.38</v>
+      </c>
+      <c r="T4" s="104">
+        <v>20</v>
+      </c>
+      <c r="U4" s="105">
+        <v>1.43E-2</v>
+      </c>
+      <c r="V4" s="104" t="s">
+        <v>38</v>
+      </c>
+      <c r="W4" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="X4" s="104" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y4" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="104" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB4" s="104" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" s="109">
+        <v>3</v>
+      </c>
+      <c r="B5" s="111" t="s">
+        <v>656</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>651</v>
+      </c>
+      <c r="E5" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="109">
+        <v>262160</v>
+      </c>
+      <c r="G5" s="109">
+        <v>1008</v>
+      </c>
+      <c r="H5" s="109">
+        <v>1500</v>
+      </c>
+      <c r="I5" s="110">
+        <v>0.41</v>
+      </c>
+      <c r="J5" s="110">
+        <v>0.82</v>
+      </c>
+      <c r="K5" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="106">
+        <v>504.3</v>
+      </c>
+      <c r="M5" s="108">
+        <v>410</v>
+      </c>
+      <c r="N5" s="105">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="O5" s="107">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="P5" s="104">
+        <v>174</v>
+      </c>
+      <c r="Q5" s="104">
+        <v>3</v>
+      </c>
+      <c r="R5" s="104">
+        <v>1250</v>
+      </c>
+      <c r="S5" s="106">
+        <v>1.23</v>
+      </c>
+      <c r="T5" s="104">
+        <v>20</v>
+      </c>
+      <c r="U5" s="105">
+        <v>1.6E-2</v>
+      </c>
+      <c r="V5" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5" s="104" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" s="109">
+        <v>4</v>
+      </c>
+      <c r="B6" s="111" t="s">
+        <v>656</v>
+      </c>
+      <c r="C6" s="109" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="109" t="s">
+        <v>651</v>
+      </c>
+      <c r="E6" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="109">
+        <v>262162</v>
+      </c>
+      <c r="G6" s="109">
+        <v>1008</v>
+      </c>
+      <c r="H6" s="109">
+        <v>1500</v>
+      </c>
+      <c r="I6" s="110">
+        <v>0.41</v>
+      </c>
+      <c r="J6" s="110">
+        <v>0.82</v>
+      </c>
+      <c r="K6" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="106">
+        <v>504.3</v>
+      </c>
+      <c r="M6" s="108">
+        <v>410</v>
+      </c>
+      <c r="N6" s="105">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="O6" s="107">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="P6" s="104">
+        <v>190.6</v>
+      </c>
+      <c r="Q6" s="104">
+        <v>3</v>
+      </c>
+      <c r="R6" s="104">
+        <v>1250</v>
+      </c>
+      <c r="S6" s="106">
+        <v>1.23</v>
+      </c>
+      <c r="T6" s="104">
+        <v>20</v>
+      </c>
+      <c r="U6" s="105">
+        <v>1.6E-2</v>
+      </c>
+      <c r="V6" s="104" t="s">
+        <v>38</v>
+      </c>
+      <c r="W6" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="X6" s="104" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y6" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB6" s="104" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="109">
+        <v>5</v>
+      </c>
+      <c r="B7" s="111" t="s">
+        <v>656</v>
+      </c>
+      <c r="C7" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="109" t="s">
+        <v>651</v>
+      </c>
+      <c r="E7" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="109">
+        <v>262159</v>
+      </c>
+      <c r="G7" s="109">
+        <v>1008</v>
+      </c>
+      <c r="H7" s="109">
+        <v>1000</v>
+      </c>
+      <c r="I7" s="110">
+        <v>0.36</v>
+      </c>
+      <c r="J7" s="110">
+        <v>0.72</v>
+      </c>
+      <c r="K7" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="106">
+        <v>259.2</v>
+      </c>
+      <c r="M7" s="108">
+        <v>240</v>
+      </c>
+      <c r="N7" s="105">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="O7" s="107">
+        <v>1.33</v>
+      </c>
+      <c r="P7" s="104">
+        <v>89.4</v>
+      </c>
+      <c r="Q7" s="104">
+        <v>3</v>
+      </c>
+      <c r="R7" s="104">
+        <v>1100</v>
+      </c>
+      <c r="S7" s="106">
+        <v>1.08</v>
+      </c>
+      <c r="T7" s="104">
+        <v>20</v>
+      </c>
+      <c r="U7" s="105">
+        <v>1.8200000000000001E-2</v>
+      </c>
+      <c r="V7" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X7" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y7" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB7" s="104" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" s="109">
+        <v>6</v>
+      </c>
+      <c r="B8" s="111" t="s">
+        <v>656</v>
+      </c>
+      <c r="C8" s="109" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="109" t="s">
+        <v>651</v>
+      </c>
+      <c r="E8" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="109">
+        <v>262163</v>
+      </c>
+      <c r="G8" s="109">
+        <v>1008</v>
+      </c>
+      <c r="H8" s="109">
+        <v>1500</v>
+      </c>
+      <c r="I8" s="110">
+        <v>0.36</v>
+      </c>
+      <c r="J8" s="110">
+        <v>0.72</v>
+      </c>
+      <c r="K8" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="106">
+        <v>388.8</v>
+      </c>
+      <c r="M8" s="108">
+        <v>360</v>
+      </c>
+      <c r="N8" s="105">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="O8" s="107">
+        <v>2</v>
+      </c>
+      <c r="P8" s="104">
+        <v>147</v>
+      </c>
+      <c r="Q8" s="104">
+        <v>3</v>
+      </c>
+      <c r="R8" s="104">
+        <v>1100</v>
+      </c>
+      <c r="S8" s="106">
+        <v>1.08</v>
+      </c>
+      <c r="T8" s="104">
+        <v>20</v>
+      </c>
+      <c r="U8" s="105">
+        <v>1.8200000000000001E-2</v>
+      </c>
+      <c r="V8" s="104" t="s">
+        <v>38</v>
+      </c>
+      <c r="W8" s="104" t="s">
+        <v>29</v>
+      </c>
+      <c r="X8" s="104" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y8" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB8" s="104" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="103">
+        <v>11000</v>
+      </c>
+      <c r="I9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" s="102">
+        <v>1629.9</v>
+      </c>
+      <c r="Q9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="S9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="T9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="U9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="V9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="W9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="X9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB9" s="102" t="s">
         <v>27</v>
       </c>
     </row>
@@ -28560,7 +30157,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.88671875" style="3" customWidth="1"/>
@@ -28591,7 +30188,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="147" t="s">
         <v>126</v>
       </c>
@@ -28677,7 +30274,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="30" customHeight="1">
+    <row r="2" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -28763,7 +30360,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -28849,7 +30446,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -28935,7 +30532,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -29021,7 +30618,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>27</v>
       </c>
@@ -29122,7 +30719,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="11.77734375" style="3" hidden="1" customWidth="1"/>
@@ -29153,7 +30750,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="147" t="s">
         <v>154</v>
       </c>
@@ -29239,7 +30836,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="39.6" customHeight="1">
+    <row r="2" spans="1:28" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -29325,7 +30922,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="22.05" customHeight="1">
+    <row r="3" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -29411,7 +31008,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -29497,7 +31094,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -29583,7 +31180,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -29669,7 +31266,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -29755,7 +31352,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -29841,7 +31438,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -29927,7 +31524,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1">
+    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -30013,7 +31610,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="22.05" customHeight="1">
+    <row r="11" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -30099,7 +31696,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="22.05" customHeight="1">
+    <row r="12" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -30185,7 +31782,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="22.05" customHeight="1">
+    <row r="13" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -30271,7 +31868,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="22.05" customHeight="1">
+    <row r="14" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>27</v>
       </c>
@@ -30369,7 +31966,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BE450D-ABF8-4C4B-88DF-0F4B0CF61565}">
   <dimension ref="A1:AB9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" style="3" hidden="1" customWidth="1"/>
@@ -30400,7 +31997,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="149" t="s">
         <v>162</v>
       </c>
@@ -30486,7 +32083,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="46.8" customHeight="1">
+    <row r="2" spans="1:28" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -30572,7 +32169,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="23">
         <v>1</v>
       </c>
@@ -30658,7 +32255,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="23">
         <v>2</v>
       </c>
@@ -30742,7 +32339,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="23">
         <v>3</v>
       </c>
@@ -30828,7 +32425,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>27</v>
       </c>
@@ -30914,7 +32511,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="G9" s="46"/>
     </row>
   </sheetData>
@@ -30932,7 +32529,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="91" customWidth="1"/>
     <col min="2" max="2" width="9.44140625" style="1" hidden="1" customWidth="1"/>
@@ -30964,7 +32561,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="150" t="s">
         <v>179</v>
       </c>
@@ -31050,7 +32647,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="52.2" customHeight="1">
+    <row r="2" spans="1:28" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="88" t="s">
         <v>0</v>
       </c>
@@ -31136,7 +32733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="101" customFormat="1" ht="19.8" customHeight="1">
+    <row r="3" spans="1:28" s="101" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="93">
         <v>1</v>
       </c>
@@ -31216,7 +32813,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25.05" customHeight="1">
+    <row r="4" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="47">
         <v>2</v>
       </c>
@@ -31302,7 +32899,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25.05" customHeight="1">
+    <row r="5" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="47">
         <v>3</v>
       </c>
@@ -31388,7 +32985,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
+    <row r="6" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="93">
         <v>4</v>
       </c>
@@ -31474,7 +33071,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
+    <row r="7" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="93">
         <v>5</v>
       </c>
@@ -31560,7 +33157,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
+    <row r="8" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="93">
         <v>6</v>
       </c>
@@ -31646,7 +33243,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
+    <row r="9" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="93">
         <v>7</v>
       </c>
@@ -31732,7 +33329,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1">
+    <row r="10" spans="1:28" s="99" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="93">
         <v>8</v>
       </c>
@@ -31818,7 +33415,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="25.05" customHeight="1">
+    <row r="11" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="90" t="s">
         <v>27</v>
       </c>
@@ -31919,7 +33516,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="10.77734375" style="3" hidden="1" customWidth="1"/>
@@ -31951,7 +33548,7 @@
     <col min="29" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="147" t="s">
         <v>199</v>
       </c>
@@ -32037,7 +33634,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="52.8" customHeight="1">
+    <row r="2" spans="1:28" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -32123,7 +33720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" customFormat="1" ht="22.05" customHeight="1">
+    <row r="3" spans="1:28" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29">
         <v>1</v>
       </c>
@@ -32207,7 +33804,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:28" customFormat="1" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="29">
         <v>2</v>
       </c>
@@ -32291,7 +33888,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="29">
         <v>3</v>
       </c>
@@ -32377,7 +33974,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
         <v>4</v>
       </c>
@@ -32463,7 +34060,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="22.05" customHeight="1">
+    <row r="7" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="29">
         <v>5</v>
       </c>
@@ -32549,7 +34146,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="22.05" customHeight="1">
+    <row r="8" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="29">
         <v>6</v>
       </c>
@@ -32635,7 +34232,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="22.05" customHeight="1">
+    <row r="9" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>27</v>
       </c>
@@ -32721,7 +34318,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="22.05" customHeight="1"/>
+    <row r="10" spans="1:28" ht="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AB1"/>
@@ -32737,7 +34334,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.77734375" style="1" customWidth="1"/>
@@ -32768,7 +34365,7 @@
     <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" customHeight="1">
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="146" t="s">
         <v>242</v>
       </c>
@@ -32854,7 +34451,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="54" customHeight="1">
+    <row r="2" spans="1:28" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -32940,7 +34537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="47" customFormat="1" ht="22.2" customHeight="1">
+    <row r="3" spans="1:28" s="47" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="47">
         <v>1</v>
       </c>
@@ -33017,7 +34614,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="47">
         <v>2</v>
       </c>
@@ -33103,7 +34700,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="5" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="47">
         <v>3</v>
       </c>
@@ -33189,7 +34786,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="6" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="47">
         <v>4</v>
       </c>
@@ -33275,7 +34872,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="7" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>5</v>
       </c>
@@ -33361,7 +34958,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="8" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>6</v>
       </c>
@@ -33447,7 +35044,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="9" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="47">
         <v>7</v>
       </c>
@@ -33533,7 +35130,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="10" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="47">
         <v>8</v>
       </c>
@@ -33619,7 +35216,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="11" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>9</v>
       </c>
@@ -33705,7 +35302,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="12" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47">
         <v>10</v>
       </c>
@@ -33791,7 +35388,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="13" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47">
         <v>11</v>
       </c>
@@ -33871,7 +35468,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1">
+    <row r="14" spans="1:28" s="21" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>27</v>
       </c>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73743943-860C-41B4-BF0D-1317E6BFD6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C65577-A38A-45F1-BD92-549F02B7D180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="29" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="28" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051 M" sheetId="60" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6158" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6224" uniqueCount="679">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -2058,6 +2058,57 @@
   </si>
   <si>
     <t>713x2120</t>
+  </si>
+  <si>
+    <t>PRIME 050</t>
+  </si>
+  <si>
+    <t>91x225x91</t>
+  </si>
+  <si>
+    <t>219.4</t>
+  </si>
+  <si>
+    <t>0.0305</t>
+  </si>
+  <si>
+    <t>1.83</t>
+  </si>
+  <si>
+    <t>0.0424</t>
+  </si>
+  <si>
+    <t>834x1848</t>
+  </si>
+  <si>
+    <t>1016x1582</t>
+  </si>
+  <si>
+    <t>128x19x204x19x128</t>
+  </si>
+  <si>
+    <t>1.610</t>
+  </si>
+  <si>
+    <t>PCBOX EMBALAGENS LTDA.</t>
+  </si>
+  <si>
+    <t>838x1282</t>
+  </si>
+  <si>
+    <t>127x155x127</t>
+  </si>
+  <si>
+    <t>PRIME 051</t>
+  </si>
+  <si>
+    <t>11/08/2026</t>
+  </si>
+  <si>
+    <t>947x1944</t>
+  </si>
+  <si>
+    <t>102x105x102</t>
   </si>
 </sst>
 </file>
@@ -2667,24 +2718,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2708,6 +2741,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2962,88 +3013,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="153" t="s">
         <v>309</v>
       </c>
-      <c r="B1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="145" t="s">
+      <c r="B1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="153" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3866,88 +3917,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="153" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="145" t="s">
+      <c r="B1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="153" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4685,88 +4736,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="158" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="150" t="s">
+      <c r="B1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="158" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5591,88 +5642,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="155" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="147" t="s">
+      <c r="B1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="155" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7008,88 +7059,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="153" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="145" t="s">
+      <c r="B1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="153" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7558,88 +7609,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="158" t="s">
         <v>343</v>
       </c>
-      <c r="B1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="150" t="s">
+      <c r="B1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="158" t="s">
         <v>27</v>
       </c>
     </row>
@@ -8633,88 +8684,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="153" t="s">
         <v>364</v>
       </c>
-      <c r="B1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="145" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="145" t="s">
+      <c r="B1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="153" t="s">
         <v>27</v>
       </c>
     </row>
@@ -9368,88 +9419,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="155" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="147" t="s">
+      <c r="B1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="155" t="s">
         <v>27</v>
       </c>
     </row>
@@ -10360,88 +10411,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="158" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="150" t="s">
+      <c r="B1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="158" t="s">
         <v>27</v>
       </c>
     </row>
@@ -12128,88 +12179,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="158" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="150" t="s">
+      <c r="B1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="158" t="s">
         <v>27</v>
       </c>
     </row>
@@ -13120,88 +13171,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="158" t="s">
         <v>489</v>
       </c>
-      <c r="B1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="150" t="s">
+      <c r="B1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="158" t="s">
         <v>27</v>
       </c>
     </row>
@@ -15144,88 +15195,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="154" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="146" t="s">
+      <c r="B1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="154" t="s">
         <v>27</v>
       </c>
     </row>
@@ -16051,88 +16102,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="154" t="s">
         <v>493</v>
       </c>
-      <c r="B1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="146" t="s">
+      <c r="B1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="154" t="s">
         <v>27</v>
       </c>
     </row>
@@ -16536,88 +16587,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="158" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="150" t="s">
+      <c r="B1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="158" t="s">
         <v>27</v>
       </c>
     </row>
@@ -17870,88 +17921,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="159" t="s">
         <v>523</v>
       </c>
-      <c r="B1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="151" t="s">
+      <c r="B1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="159" t="s">
         <v>27</v>
       </c>
     </row>
@@ -18260,88 +18311,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="154" t="s">
         <v>539</v>
       </c>
-      <c r="B1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="146" t="s">
+      <c r="B1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="154" t="s">
         <v>27</v>
       </c>
     </row>
@@ -19252,88 +19303,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="155" t="s">
         <v>552</v>
       </c>
-      <c r="B1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="147" t="s">
+      <c r="B1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="155" t="s">
         <v>27</v>
       </c>
     </row>
@@ -19900,88 +19951,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="160" t="s">
         <v>571</v>
       </c>
-      <c r="B1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="152" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="152" t="s">
+      <c r="B1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="160" t="s">
         <v>27</v>
       </c>
     </row>
@@ -20806,88 +20857,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="155" t="s">
         <v>578</v>
       </c>
-      <c r="B1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="147" t="s">
+      <c r="B1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="155" t="s">
         <v>27</v>
       </c>
     </row>
@@ -21452,88 +21503,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="159" t="s">
         <v>581</v>
       </c>
-      <c r="B1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="151" t="s">
+      <c r="B1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="159" t="s">
         <v>27</v>
       </c>
     </row>
@@ -21928,88 +21979,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="158" t="s">
         <v>591</v>
       </c>
-      <c r="B1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="150" t="s">
+      <c r="B1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="158" t="s">
         <v>27</v>
       </c>
     </row>
@@ -22540,7 +22591,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9920A0AA-9240-4CDC-B26B-9F885FC523AF}">
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" style="1" customWidth="1"/>
@@ -22553,7 +22604,7 @@
     <col min="8" max="8" width="5.6640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="9.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="6.77734375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" style="1" customWidth="1"/>
     <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
     <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
@@ -22573,88 +22624,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="159" t="s">
         <v>609</v>
       </c>
-      <c r="B1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="151" t="s">
+      <c r="B1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="159" t="s">
         <v>27</v>
       </c>
     </row>
@@ -22744,605 +22795,777 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="159" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="153">
+    <row r="3" spans="1:28" s="151" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="145">
         <v>1</v>
       </c>
-      <c r="B3" s="154" t="s">
+      <c r="B3" s="146" t="s">
         <v>279</v>
       </c>
-      <c r="C3" s="153" t="s">
+      <c r="C3" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="153" t="s">
+      <c r="D3" s="145" t="s">
         <v>608</v>
       </c>
-      <c r="E3" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="153">
+      <c r="E3" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="145">
         <v>262117</v>
       </c>
-      <c r="G3" s="153" t="s">
+      <c r="G3" s="145" t="s">
         <v>607</v>
       </c>
-      <c r="H3" s="153">
+      <c r="H3" s="145">
         <v>200</v>
       </c>
-      <c r="I3" s="155">
+      <c r="I3" s="147">
         <v>0.79</v>
       </c>
-      <c r="J3" s="155">
+      <c r="J3" s="147">
         <v>2.1429999999999998</v>
       </c>
-      <c r="K3" s="153" t="s">
+      <c r="K3" s="145" t="s">
         <v>606</v>
       </c>
-      <c r="L3" s="155">
+      <c r="L3" s="147">
         <v>338.59399999999999</v>
       </c>
-      <c r="M3" s="156">
+      <c r="M3" s="148">
         <v>214.3</v>
       </c>
-      <c r="N3" s="157">
+      <c r="N3" s="149">
         <v>2.98E-2</v>
       </c>
-      <c r="O3" s="158">
+      <c r="O3" s="150">
         <v>1.79</v>
       </c>
-      <c r="P3" s="153">
+      <c r="P3" s="145">
         <v>116.8</v>
       </c>
-      <c r="Q3" s="153">
+      <c r="Q3" s="145">
         <v>2</v>
       </c>
-      <c r="R3" s="153">
+      <c r="R3" s="145">
         <v>1600</v>
       </c>
-      <c r="S3" s="155">
+      <c r="S3" s="147">
         <v>1.58</v>
       </c>
-      <c r="T3" s="153">
+      <c r="T3" s="145">
         <v>20</v>
       </c>
-      <c r="U3" s="157">
+      <c r="U3" s="149">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="V3" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="X3" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z3" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA3" s="153" t="s">
+      <c r="V3" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="145" t="s">
         <v>39</v>
       </c>
-      <c r="AB3" s="153" t="s">
+      <c r="AB3" s="145" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="159" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="153">
+    <row r="4" spans="1:28" s="152" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="70">
+        <v>1</v>
+      </c>
+      <c r="B4" s="71" t="s">
+        <v>672</v>
+      </c>
+      <c r="C4" s="70" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="70" t="s">
+        <v>651</v>
+      </c>
+      <c r="E4" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="70">
+        <v>262167</v>
+      </c>
+      <c r="G4" s="70" t="s">
+        <v>671</v>
+      </c>
+      <c r="H4" s="70">
+        <v>200</v>
+      </c>
+      <c r="I4" s="72">
+        <v>0.498</v>
+      </c>
+      <c r="J4" s="72">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="K4" s="70" t="s">
+        <v>670</v>
+      </c>
+      <c r="L4" s="72">
+        <v>77.787999999999997</v>
+      </c>
+      <c r="M4" s="73">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="N4" s="74">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="O4" s="75">
+        <v>0.65</v>
+      </c>
+      <c r="P4" s="70">
+        <v>26.8</v>
+      </c>
+      <c r="Q4" s="70">
         <v>2</v>
       </c>
-      <c r="B4" s="154" t="s">
+      <c r="R4" s="70">
+        <v>1200</v>
+      </c>
+      <c r="S4" s="72">
+        <v>0.996</v>
+      </c>
+      <c r="T4" s="70">
+        <v>204</v>
+      </c>
+      <c r="U4" s="74">
+        <v>0.17</v>
+      </c>
+      <c r="V4" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="70" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB4" s="70" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" s="152" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="70">
+        <v>2</v>
+      </c>
+      <c r="B5" s="71" t="s">
+        <v>672</v>
+      </c>
+      <c r="C5" s="70" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="70" t="s">
+        <v>651</v>
+      </c>
+      <c r="E5" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="70">
+        <v>262166</v>
+      </c>
+      <c r="G5" s="70" t="s">
+        <v>671</v>
+      </c>
+      <c r="H5" s="70">
+        <v>200</v>
+      </c>
+      <c r="I5" s="72">
+        <v>0.498</v>
+      </c>
+      <c r="J5" s="72">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="K5" s="70" t="s">
+        <v>670</v>
+      </c>
+      <c r="L5" s="72">
+        <v>57.868000000000002</v>
+      </c>
+      <c r="M5" s="73">
+        <v>58.1</v>
+      </c>
+      <c r="N5" s="74">
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="O5" s="75">
+        <v>0.48</v>
+      </c>
+      <c r="P5" s="70">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="70">
+        <v>2</v>
+      </c>
+      <c r="R5" s="70">
+        <v>1050</v>
+      </c>
+      <c r="S5" s="72">
+        <v>0.996</v>
+      </c>
+      <c r="T5" s="70">
+        <v>54</v>
+      </c>
+      <c r="U5" s="74">
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="V5" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="70" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5" s="70" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" s="151" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="145">
+        <v>2</v>
+      </c>
+      <c r="B6" s="146" t="s">
         <v>279</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C6" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="153" t="s">
+      <c r="D6" s="145" t="s">
         <v>383</v>
       </c>
-      <c r="E4" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="153">
+      <c r="E6" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="145">
         <v>262118</v>
       </c>
-      <c r="G4" s="153" t="s">
+      <c r="G6" s="145" t="s">
         <v>604</v>
       </c>
-      <c r="H4" s="153">
+      <c r="H6" s="145">
         <v>300</v>
       </c>
-      <c r="I4" s="155">
+      <c r="I6" s="147">
         <v>0.93300000000000005</v>
       </c>
-      <c r="J4" s="155">
+      <c r="J6" s="147">
         <v>1.8049999999999999</v>
       </c>
-      <c r="K4" s="153" t="s">
+      <c r="K6" s="145" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="155">
+      <c r="L6" s="147">
         <v>505.22</v>
       </c>
-      <c r="M4" s="156">
+      <c r="M6" s="148">
         <v>541.5</v>
       </c>
-      <c r="N4" s="157">
+      <c r="N6" s="149">
         <v>0.15040000000000001</v>
       </c>
-      <c r="O4" s="158">
+      <c r="O6" s="150">
         <v>9.0299999999999994</v>
       </c>
-      <c r="P4" s="153">
+      <c r="P6" s="145">
         <v>174.3</v>
       </c>
-      <c r="Q4" s="153">
+      <c r="Q6" s="145">
         <v>1</v>
       </c>
-      <c r="R4" s="153">
+      <c r="R6" s="145">
         <v>1000</v>
       </c>
-      <c r="S4" s="155">
+      <c r="S6" s="147">
         <v>0.93300000000000005</v>
       </c>
-      <c r="T4" s="153">
+      <c r="T6" s="145">
         <v>67</v>
       </c>
-      <c r="U4" s="157">
+      <c r="U6" s="149">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="V4" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="X4" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="153" t="s">
+      <c r="V6" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="W6" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="145" t="s">
         <v>39</v>
       </c>
-      <c r="AB4" s="153" t="s">
+      <c r="AB6" s="145" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="159" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="153">
+    <row r="7" spans="1:28" s="151" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="145">
         <v>3</v>
       </c>
-      <c r="B5" s="154" t="s">
+      <c r="B7" s="146" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="153" t="s">
+      <c r="C7" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="153" t="s">
+      <c r="D7" s="145" t="s">
         <v>583</v>
       </c>
-      <c r="E5" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="153">
+      <c r="E7" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="145">
         <v>262119</v>
       </c>
-      <c r="G5" s="153" t="s">
+      <c r="G7" s="145" t="s">
         <v>602</v>
       </c>
-      <c r="H5" s="153">
+      <c r="H7" s="145">
         <v>300</v>
       </c>
-      <c r="I5" s="155">
+      <c r="I7" s="147">
         <v>0.97799999999999998</v>
       </c>
-      <c r="J5" s="155">
+      <c r="J7" s="147">
         <v>1.347</v>
       </c>
-      <c r="K5" s="153" t="s">
+      <c r="K7" s="145" t="s">
         <v>601</v>
       </c>
-      <c r="L5" s="155">
+      <c r="L7" s="147">
         <v>395.21</v>
       </c>
-      <c r="M5" s="156">
+      <c r="M7" s="148">
         <v>404.1</v>
       </c>
-      <c r="N5" s="157">
+      <c r="N7" s="149">
         <v>0.11219999999999999</v>
       </c>
-      <c r="O5" s="158">
+      <c r="O7" s="150">
         <v>6.73</v>
       </c>
-      <c r="P5" s="153">
+      <c r="P7" s="145">
         <v>136.30000000000001</v>
       </c>
-      <c r="Q5" s="153">
+      <c r="Q7" s="145">
         <v>1</v>
       </c>
-      <c r="R5" s="153">
+      <c r="R7" s="145">
         <v>1000</v>
       </c>
-      <c r="S5" s="155">
+      <c r="S7" s="147">
         <v>0.97799999999999998</v>
       </c>
-      <c r="T5" s="153">
+      <c r="T7" s="145">
         <v>22</v>
       </c>
-      <c r="U5" s="157">
+      <c r="U7" s="149">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="V5" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="W5" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="X5" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z5" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA5" s="153" t="s">
+      <c r="V7" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="X7" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y7" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="145" t="s">
         <v>39</v>
       </c>
-      <c r="AB5" s="153" t="s">
+      <c r="AB7" s="145" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="159" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="153">
+    <row r="8" spans="1:28" s="151" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="145">
         <v>4</v>
       </c>
-      <c r="B6" s="154" t="s">
+      <c r="B8" s="146" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="153" t="s">
+      <c r="C8" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="153" t="s">
+      <c r="D8" s="145" t="s">
         <v>583</v>
       </c>
-      <c r="E6" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="153">
+      <c r="E8" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="145">
         <v>262120</v>
       </c>
-      <c r="G6" s="153" t="s">
+      <c r="G8" s="145" t="s">
         <v>599</v>
       </c>
-      <c r="H6" s="153">
+      <c r="H8" s="145">
         <v>3000</v>
       </c>
-      <c r="I6" s="155">
+      <c r="I8" s="147">
         <v>0.45600000000000002</v>
       </c>
-      <c r="J6" s="155">
+      <c r="J8" s="147">
         <v>1.5609999999999999</v>
       </c>
-      <c r="K6" s="153" t="s">
+      <c r="K8" s="145" t="s">
         <v>598</v>
       </c>
-      <c r="L6" s="155">
+      <c r="L8" s="147">
         <v>2135.4479999999999</v>
       </c>
-      <c r="M6" s="156">
+      <c r="M8" s="148">
         <v>2341.5</v>
       </c>
-      <c r="N6" s="157">
+      <c r="N8" s="149">
         <v>0.32519999999999999</v>
       </c>
-      <c r="O6" s="158">
+      <c r="O8" s="150">
         <v>19.510000000000002</v>
       </c>
-      <c r="P6" s="153">
+      <c r="P8" s="145">
         <v>736.7</v>
       </c>
-      <c r="Q6" s="153">
+      <c r="Q8" s="145">
         <v>2</v>
       </c>
-      <c r="R6" s="153">
+      <c r="R8" s="145">
         <v>950</v>
       </c>
-      <c r="S6" s="155">
+      <c r="S8" s="147">
         <v>0.91200000000000003</v>
       </c>
-      <c r="T6" s="153">
+      <c r="T8" s="145">
         <v>38</v>
       </c>
-      <c r="U6" s="157">
+      <c r="U8" s="149">
         <v>0.04</v>
       </c>
-      <c r="V6" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="W6" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="X6" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y6" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z6" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA6" s="153" t="s">
+      <c r="V8" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="W8" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="X8" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y8" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="AB6" s="153" t="s">
+      <c r="AB8" s="145" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="159" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="153">
+    <row r="9" spans="1:28" s="151" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="145">
         <v>5</v>
       </c>
-      <c r="B7" s="154" t="s">
+      <c r="B9" s="146" t="s">
         <v>156</v>
       </c>
-      <c r="C7" s="153" t="s">
+      <c r="C9" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="153" t="s">
+      <c r="D9" s="145" t="s">
         <v>583</v>
       </c>
-      <c r="E7" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="153">
+      <c r="E9" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="145">
         <v>262122</v>
       </c>
-      <c r="G7" s="153" t="s">
+      <c r="G9" s="145" t="s">
         <v>594</v>
       </c>
-      <c r="H7" s="153">
+      <c r="H9" s="145">
         <v>2500</v>
       </c>
-      <c r="I7" s="155">
+      <c r="I9" s="147">
         <v>0.46200000000000002</v>
       </c>
-      <c r="J7" s="155">
+      <c r="J9" s="147">
         <v>1.5629999999999999</v>
       </c>
-      <c r="K7" s="153" t="s">
+      <c r="K9" s="145" t="s">
         <v>596</v>
       </c>
-      <c r="L7" s="155">
+      <c r="L9" s="147">
         <v>1805.2650000000001</v>
       </c>
-      <c r="M7" s="156">
+      <c r="M9" s="148">
         <v>1953.8</v>
       </c>
-      <c r="N7" s="157">
+      <c r="N9" s="149">
         <v>0.27139999999999997</v>
       </c>
-      <c r="O7" s="158">
+      <c r="O9" s="150">
         <v>16.28</v>
       </c>
-      <c r="P7" s="153">
+      <c r="P9" s="145">
         <v>622.79999999999995</v>
       </c>
-      <c r="Q7" s="153">
+      <c r="Q9" s="145">
         <v>2</v>
       </c>
-      <c r="R7" s="153">
+      <c r="R9" s="145">
         <v>950</v>
       </c>
-      <c r="S7" s="155">
+      <c r="S9" s="147">
         <v>0.92400000000000004</v>
       </c>
-      <c r="T7" s="153">
+      <c r="T9" s="145">
         <v>26</v>
       </c>
-      <c r="U7" s="157">
+      <c r="U9" s="149">
         <v>2.7400000000000001E-2</v>
       </c>
-      <c r="V7" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="W7" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="X7" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y7" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z7" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA7" s="153" t="s">
+      <c r="V9" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="W9" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="X9" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y9" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="AB7" s="153" t="s">
+      <c r="AB9" s="145" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="159" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="153">
+    <row r="10" spans="1:28" s="151" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="145">
         <v>6</v>
       </c>
-      <c r="B8" s="154" t="s">
+      <c r="B10" s="146" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="153" t="s">
+      <c r="C10" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="153" t="s">
+      <c r="D10" s="145" t="s">
         <v>583</v>
       </c>
-      <c r="E8" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="153">
+      <c r="E10" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="145">
         <v>262121</v>
       </c>
-      <c r="G8" s="153" t="s">
+      <c r="G10" s="145" t="s">
         <v>594</v>
       </c>
-      <c r="H8" s="153">
+      <c r="H10" s="145">
         <v>2500</v>
       </c>
-      <c r="I8" s="155">
+      <c r="I10" s="147">
         <v>0.42</v>
       </c>
-      <c r="J8" s="155">
+      <c r="J10" s="147">
         <v>1.123</v>
       </c>
-      <c r="K8" s="153" t="s">
+      <c r="K10" s="145" t="s">
         <v>593</v>
       </c>
-      <c r="L8" s="155">
+      <c r="L10" s="147">
         <v>1179.1500000000001</v>
       </c>
-      <c r="M8" s="156">
+      <c r="M10" s="148">
         <v>1403.8</v>
       </c>
-      <c r="N8" s="157">
+      <c r="N10" s="149">
         <v>0.19500000000000001</v>
       </c>
-      <c r="O8" s="158">
+      <c r="O10" s="150">
         <v>11.7</v>
       </c>
-      <c r="P8" s="153">
+      <c r="P10" s="145">
         <v>406.8</v>
       </c>
-      <c r="Q8" s="153">
+      <c r="Q10" s="145">
         <v>2</v>
       </c>
-      <c r="R8" s="153">
+      <c r="R10" s="145">
         <v>900</v>
       </c>
-      <c r="S8" s="155">
+      <c r="S10" s="147">
         <v>0.84</v>
       </c>
-      <c r="T8" s="153">
+      <c r="T10" s="145">
         <v>60</v>
       </c>
-      <c r="U8" s="157">
+      <c r="U10" s="149">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="V8" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="W8" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="X8" s="153" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y8" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z8" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA8" s="153" t="s">
+      <c r="V10" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="145" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="145" t="s">
         <v>33</v>
       </c>
-      <c r="AB8" s="153" t="s">
+      <c r="AB10" s="145" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="19">
+    <row r="11" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="19">
         <v>8800</v>
       </c>
-      <c r="I9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="P9" s="19">
+      <c r="I11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="19">
         <v>2193.8000000000002</v>
       </c>
-      <c r="Q9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="S9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="T9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="U9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="V9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="W9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="X9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA9" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB9" s="19" t="s">
+      <c r="Q11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="X11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB11" s="19" t="s">
         <v>27</v>
       </c>
     </row>
@@ -23392,88 +23615,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="155" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="148" t="s">
+      <c r="B1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="156" t="s">
         <v>27</v>
       </c>
     </row>
@@ -25589,88 +25812,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="154" t="s">
         <v>632</v>
       </c>
-      <c r="B1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="146" t="s">
+      <c r="B1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="154" t="s">
         <v>27</v>
       </c>
     </row>
@@ -26975,7 +27198,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEE2B25-3AB7-403C-A289-9D2E4B6CDB55}">
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -27007,88 +27230,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="159" t="s">
         <v>649</v>
       </c>
-      <c r="B1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="151" t="s">
+      <c r="B1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="159" t="s">
         <v>27</v>
       </c>
     </row>
@@ -27186,254 +27409,252 @@
         <v>190</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="30">
+        <v>46244</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5">
+        <v>262165</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="H3" s="5">
+        <v>480</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="L3" s="7">
+        <v>178559</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="P3" s="5">
+        <v>111.8</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>2</v>
+      </c>
+      <c r="R3" s="5">
+        <v>850</v>
+      </c>
+      <c r="S3" s="7">
+        <v>0.81399999999999995</v>
+      </c>
+      <c r="T3" s="5">
         <v>36</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="5">
-        <v>262140</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>645</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1250</v>
-      </c>
-      <c r="I3" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="J3" s="7">
+      <c r="U3" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA3" s="5">
         <v>1</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="7">
-        <v>625</v>
-      </c>
-      <c r="M3" s="9">
-        <v>416.7</v>
-      </c>
-      <c r="N3" s="6">
-        <v>3.8600000000000002E-2</v>
-      </c>
-      <c r="O3" s="8">
-        <v>2.31</v>
-      </c>
-      <c r="P3" s="5">
-        <v>215.6</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>3</v>
-      </c>
-      <c r="R3" s="5">
-        <v>1550</v>
-      </c>
-      <c r="S3" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="T3" s="5">
-        <v>50</v>
-      </c>
-      <c r="U3" s="6">
-        <v>3.2300000000000002E-2</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA3" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="AB3" s="5" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" s="160" customFormat="1" x14ac:dyDescent="0.3">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="70" t="s">
-        <v>651</v>
-      </c>
-      <c r="E4" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="70">
-        <v>262164</v>
-      </c>
-      <c r="G4" s="70" t="s">
-        <v>660</v>
-      </c>
-      <c r="H4" s="70">
-        <v>500</v>
-      </c>
-      <c r="I4" s="72">
-        <v>0.69299999999999995</v>
-      </c>
-      <c r="J4" s="72">
-        <v>0.7</v>
-      </c>
-      <c r="K4" s="70" t="s">
+      <c r="D4" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="5">
+        <v>262140</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1250</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="7">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="72">
-        <v>242.55</v>
-      </c>
-      <c r="M4" s="73">
-        <v>175</v>
-      </c>
-      <c r="N4" s="74">
-        <v>2.4299999999999999E-2</v>
-      </c>
-      <c r="O4" s="75">
-        <v>1.46</v>
-      </c>
-      <c r="P4" s="70">
-        <v>83.7</v>
-      </c>
-      <c r="Q4" s="70">
-        <v>2</v>
-      </c>
-      <c r="R4" s="70">
-        <v>1450</v>
-      </c>
-      <c r="S4" s="72">
-        <v>1.3859999999999999</v>
-      </c>
-      <c r="T4" s="70">
-        <v>64</v>
-      </c>
-      <c r="U4" s="74">
-        <v>4.41E-2</v>
-      </c>
-      <c r="V4" s="70" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" s="70" t="s">
-        <v>28</v>
-      </c>
-      <c r="X4" s="70" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z4" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA4" s="70" t="s">
+      <c r="L4" s="7">
+        <v>625</v>
+      </c>
+      <c r="M4" s="9">
+        <v>416.7</v>
+      </c>
+      <c r="N4" s="6">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="O4" s="8">
+        <v>2.31</v>
+      </c>
+      <c r="P4" s="5">
+        <v>215.6</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>3</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1550</v>
+      </c>
+      <c r="S4" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="T4" s="5">
+        <v>50</v>
+      </c>
+      <c r="U4" s="6">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AB4" s="70" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AB4" s="5" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" s="152" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="5">
-        <v>262142</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>645</v>
-      </c>
-      <c r="H5" s="5">
-        <v>600</v>
-      </c>
-      <c r="I5" s="7">
-        <v>0.69</v>
-      </c>
-      <c r="J5" s="7">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5" t="s">
+      <c r="D5" s="70" t="s">
+        <v>651</v>
+      </c>
+      <c r="E5" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="70">
+        <v>262164</v>
+      </c>
+      <c r="G5" s="70" t="s">
+        <v>660</v>
+      </c>
+      <c r="H5" s="70">
+        <v>500</v>
+      </c>
+      <c r="I5" s="72">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="J5" s="72">
+        <v>0.7</v>
+      </c>
+      <c r="K5" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="7">
-        <v>414</v>
-      </c>
-      <c r="M5" s="9">
-        <v>300</v>
-      </c>
-      <c r="N5" s="6">
-        <v>4.1700000000000001E-2</v>
-      </c>
-      <c r="O5" s="8">
-        <v>2.5</v>
-      </c>
-      <c r="P5" s="5">
-        <v>142.80000000000001</v>
-      </c>
-      <c r="Q5" s="5">
+      <c r="L5" s="72">
+        <v>242.55</v>
+      </c>
+      <c r="M5" s="73">
+        <v>175</v>
+      </c>
+      <c r="N5" s="74">
+        <v>2.4299999999999999E-2</v>
+      </c>
+      <c r="O5" s="75">
+        <v>1.46</v>
+      </c>
+      <c r="P5" s="70">
+        <v>83.7</v>
+      </c>
+      <c r="Q5" s="70">
         <v>2</v>
       </c>
-      <c r="R5" s="5">
-        <v>1400</v>
-      </c>
-      <c r="S5" s="7">
-        <v>1.38</v>
-      </c>
-      <c r="T5" s="5">
-        <v>20</v>
-      </c>
-      <c r="U5" s="6">
-        <v>1.43E-2</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA5" s="5" t="s">
+      <c r="R5" s="70">
+        <v>1450</v>
+      </c>
+      <c r="S5" s="72">
+        <v>1.3859999999999999</v>
+      </c>
+      <c r="T5" s="70">
+        <v>64</v>
+      </c>
+      <c r="U5" s="74">
+        <v>4.41E-2</v>
+      </c>
+      <c r="V5" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="W5" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="AB5" s="5" t="s">
-        <v>647</v>
+      <c r="AB5" s="70" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="6" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -27453,16 +27674,16 @@
         <v>27</v>
       </c>
       <c r="F6" s="5">
-        <v>262143</v>
+        <v>262142</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>645</v>
       </c>
       <c r="H6" s="5">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I6" s="7">
-        <v>0.63</v>
+        <v>0.69</v>
       </c>
       <c r="J6" s="7">
         <v>1</v>
@@ -27471,34 +27692,34 @@
         <v>34</v>
       </c>
       <c r="L6" s="7">
-        <v>630</v>
+        <v>414</v>
       </c>
       <c r="M6" s="9">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N6" s="6">
-        <v>6.9400000000000003E-2</v>
+        <v>4.1700000000000001E-2</v>
       </c>
       <c r="O6" s="8">
-        <v>4.17</v>
+        <v>2.5</v>
       </c>
       <c r="P6" s="5">
-        <v>217.3</v>
+        <v>142.80000000000001</v>
       </c>
       <c r="Q6" s="5">
         <v>2</v>
       </c>
       <c r="R6" s="5">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="S6" s="7">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="T6" s="5">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="U6" s="6">
-        <v>3.0800000000000001E-2</v>
+        <v>1.43E-2</v>
       </c>
       <c r="V6" s="5" t="s">
         <v>28</v>
@@ -27519,7 +27740,7 @@
         <v>39</v>
       </c>
       <c r="AB6" s="5" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -27539,16 +27760,16 @@
         <v>27</v>
       </c>
       <c r="F7" s="5">
-        <v>262141</v>
+        <v>262143</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>645</v>
       </c>
       <c r="H7" s="5">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="I7" s="7">
-        <v>0.57999999999999996</v>
+        <v>0.63</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
@@ -27557,34 +27778,34 @@
         <v>34</v>
       </c>
       <c r="L7" s="7">
-        <v>725</v>
+        <v>630</v>
       </c>
       <c r="M7" s="9">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="N7" s="6">
-        <v>8.6800000000000002E-2</v>
+        <v>6.9400000000000003E-2</v>
       </c>
       <c r="O7" s="8">
-        <v>5.21</v>
+        <v>4.17</v>
       </c>
       <c r="P7" s="5">
-        <v>250.1</v>
+        <v>217.3</v>
       </c>
       <c r="Q7" s="5">
         <v>2</v>
       </c>
       <c r="R7" s="5">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="S7" s="7">
-        <v>1.1599999999999999</v>
+        <v>1.26</v>
       </c>
       <c r="T7" s="5">
         <v>40</v>
       </c>
       <c r="U7" s="6">
-        <v>3.3300000000000003E-2</v>
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="V7" s="5" t="s">
         <v>28</v>
@@ -27605,7 +27826,7 @@
         <v>39</v>
       </c>
       <c r="AB7" s="5" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -27616,7 +27837,7 @@
         <v>190</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>643</v>
+        <v>36</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>613</v>
@@ -27625,61 +27846,61 @@
         <v>27</v>
       </c>
       <c r="F8" s="5">
-        <v>262136</v>
+        <v>262141</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="H8" s="5">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="I8" s="7">
-        <v>0.52500000000000002</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="J8" s="7">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>642</v>
+        <v>34</v>
       </c>
       <c r="L8" s="7">
-        <v>606.375</v>
+        <v>725</v>
       </c>
       <c r="M8" s="9">
-        <v>577.5</v>
+        <v>625</v>
       </c>
       <c r="N8" s="6">
-        <v>8.0199999999999994E-2</v>
+        <v>8.6800000000000002E-2</v>
       </c>
       <c r="O8" s="8">
-        <v>4.8099999999999996</v>
+        <v>5.21</v>
       </c>
       <c r="P8" s="5">
-        <v>259.2</v>
+        <v>250.1</v>
       </c>
       <c r="Q8" s="5">
         <v>2</v>
       </c>
       <c r="R8" s="5">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="S8" s="7">
-        <v>1.05</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="T8" s="5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="U8" s="6">
-        <v>4.5499999999999999E-2</v>
+        <v>3.3300000000000003E-2</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>27</v>
@@ -27691,7 +27912,7 @@
         <v>39</v>
       </c>
       <c r="AB8" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -27702,7 +27923,7 @@
         <v>190</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>189</v>
+        <v>643</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>613</v>
@@ -27711,61 +27932,61 @@
         <v>27</v>
       </c>
       <c r="F9" s="5">
-        <v>262139</v>
+        <v>262136</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="H9" s="5">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="I9" s="7">
-        <v>0.8</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="J9" s="7">
-        <v>2.0499999999999998</v>
+        <v>1.05</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="L9" s="7">
-        <v>492</v>
+        <v>606.375</v>
       </c>
       <c r="M9" s="9">
-        <v>615</v>
+        <v>577.5</v>
       </c>
       <c r="N9" s="6">
-        <v>0.17080000000000001</v>
+        <v>8.0199999999999994E-2</v>
       </c>
       <c r="O9" s="8">
-        <v>10.25</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="P9" s="5">
-        <v>190.9</v>
+        <v>259.2</v>
       </c>
       <c r="Q9" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" s="5">
-        <v>850</v>
+        <v>1100</v>
       </c>
       <c r="S9" s="7">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="T9" s="5">
         <v>50</v>
       </c>
       <c r="U9" s="6">
-        <v>5.8799999999999998E-2</v>
+        <v>4.5499999999999999E-2</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="Y9" s="5" t="s">
         <v>27</v>
@@ -27777,93 +27998,93 @@
         <v>39</v>
       </c>
       <c r="AB9" s="5" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" s="152" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="71" t="s">
         <v>190</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="5">
-        <v>262137</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="H10" s="5">
-        <v>1000</v>
-      </c>
-      <c r="I10" s="7">
-        <v>0.307</v>
-      </c>
-      <c r="J10" s="7">
-        <v>0.88</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="L10" s="7">
-        <v>270.16000000000003</v>
-      </c>
-      <c r="M10" s="9">
-        <v>440</v>
-      </c>
-      <c r="N10" s="6">
-        <v>6.1100000000000002E-2</v>
-      </c>
-      <c r="O10" s="8">
-        <v>3.67</v>
-      </c>
-      <c r="P10" s="5">
-        <v>93.2</v>
-      </c>
-      <c r="Q10" s="5">
+      <c r="D10" s="70" t="s">
+        <v>676</v>
+      </c>
+      <c r="E10" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="70">
+        <v>262168</v>
+      </c>
+      <c r="G10" s="70" t="s">
+        <v>675</v>
+      </c>
+      <c r="H10" s="70">
+        <v>1500</v>
+      </c>
+      <c r="I10" s="72">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="J10" s="72">
+        <v>1.262</v>
+      </c>
+      <c r="K10" s="70" t="s">
+        <v>674</v>
+      </c>
+      <c r="L10" s="72">
+        <v>774.23699999999997</v>
+      </c>
+      <c r="M10" s="73">
+        <v>946.5</v>
+      </c>
+      <c r="N10" s="74">
+        <v>0.13150000000000001</v>
+      </c>
+      <c r="O10" s="75">
+        <v>7.89</v>
+      </c>
+      <c r="P10" s="70">
+        <v>267.10000000000002</v>
+      </c>
+      <c r="Q10" s="70">
         <v>2</v>
       </c>
-      <c r="R10" s="5">
-        <v>650</v>
-      </c>
-      <c r="S10" s="7">
-        <v>0.61399999999999999</v>
-      </c>
-      <c r="T10" s="5">
-        <v>36</v>
-      </c>
-      <c r="U10" s="6">
-        <v>5.5399999999999998E-2</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="X10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB10" s="5" t="s">
-        <v>636</v>
+      <c r="R10" s="70">
+        <v>850</v>
+      </c>
+      <c r="S10" s="72">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="T10" s="70">
+        <v>32</v>
+      </c>
+      <c r="U10" s="74">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="V10" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y10" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="70" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB10" s="70" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="11" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -27874,7 +28095,7 @@
         <v>190</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>613</v>
@@ -27883,158 +28104,416 @@
         <v>27</v>
       </c>
       <c r="F11" s="5">
+        <v>262139</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="H11" s="5">
+        <v>300</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="J11" s="7">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="L11" s="7">
+        <v>492</v>
+      </c>
+      <c r="M11" s="9">
+        <v>615</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0.17080000000000001</v>
+      </c>
+      <c r="O11" s="8">
+        <v>10.25</v>
+      </c>
+      <c r="P11" s="5">
+        <v>190.9</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>1</v>
+      </c>
+      <c r="R11" s="5">
+        <v>850</v>
+      </c>
+      <c r="S11" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="T11" s="5">
+        <v>50</v>
+      </c>
+      <c r="U11" s="6">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB11" s="5" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" s="152" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>10</v>
+      </c>
+      <c r="B12" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="70" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="70" t="s">
+        <v>676</v>
+      </c>
+      <c r="E12" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="70">
+        <v>262169</v>
+      </c>
+      <c r="G12" s="70" t="s">
+        <v>675</v>
+      </c>
+      <c r="H12" s="70">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="72">
+        <v>0.309</v>
+      </c>
+      <c r="J12" s="72">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="K12" s="70" t="s">
+        <v>678</v>
+      </c>
+      <c r="L12" s="72">
+        <v>297.25799999999998</v>
+      </c>
+      <c r="M12" s="73">
+        <v>481</v>
+      </c>
+      <c r="N12" s="74">
+        <v>6.6799999999999998E-2</v>
+      </c>
+      <c r="O12" s="75">
+        <v>4.01</v>
+      </c>
+      <c r="P12" s="70">
+        <v>102.6</v>
+      </c>
+      <c r="Q12" s="70">
+        <v>2</v>
+      </c>
+      <c r="R12" s="70">
+        <v>650</v>
+      </c>
+      <c r="S12" s="72">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="T12" s="70">
+        <v>32</v>
+      </c>
+      <c r="U12" s="74">
+        <v>4.9200000000000001E-2</v>
+      </c>
+      <c r="V12" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="W12" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="X12" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y12" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z12" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA12" s="70" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB12" s="70" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="5">
+        <v>262137</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I13" s="7">
+        <v>0.307</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="L13" s="7">
+        <v>270.16000000000003</v>
+      </c>
+      <c r="M13" s="9">
+        <v>440</v>
+      </c>
+      <c r="N13" s="6">
+        <v>6.1100000000000002E-2</v>
+      </c>
+      <c r="O13" s="8">
+        <v>3.67</v>
+      </c>
+      <c r="P13" s="5">
+        <v>93.2</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>2</v>
+      </c>
+      <c r="R13" s="5">
+        <v>650</v>
+      </c>
+      <c r="S13" s="7">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="T13" s="5">
+        <v>36</v>
+      </c>
+      <c r="U13" s="6">
+        <v>5.5399999999999998E-2</v>
+      </c>
+      <c r="V13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB13" s="5" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="5">
         <v>262138</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H14" s="5">
         <v>4000</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I14" s="7">
         <v>0.27800000000000002</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J14" s="7">
         <v>0.85</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K14" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L14" s="7">
         <v>945.2</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M14" s="9">
         <v>1700</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N14" s="6">
         <v>0.2361</v>
       </c>
-      <c r="O11" s="8">
+      <c r="O14" s="8">
         <v>14.17</v>
       </c>
-      <c r="P11" s="5">
+      <c r="P14" s="5">
         <v>326.10000000000002</v>
       </c>
-      <c r="Q11" s="5">
+      <c r="Q14" s="5">
         <v>2</v>
       </c>
-      <c r="R11" s="5">
+      <c r="R14" s="5">
         <v>600</v>
       </c>
-      <c r="S11" s="7">
+      <c r="S14" s="7">
         <v>0.55600000000000005</v>
       </c>
-      <c r="T11" s="5">
+      <c r="T14" s="5">
         <v>44</v>
       </c>
-      <c r="U11" s="6">
+      <c r="U14" s="6">
         <v>7.3300000000000004E-2</v>
       </c>
-      <c r="V11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="X11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA11" s="5" t="s">
+      <c r="V14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="X14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AB11" s="5" t="s">
+      <c r="AB14" s="5" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="19">
+    <row r="15" spans="1:28" s="21" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="19">
         <v>10500</v>
       </c>
-      <c r="I12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="O12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="P12" s="19">
+      <c r="I15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" s="19">
         <v>1695.4</v>
       </c>
-      <c r="Q12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="S12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="T12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="U12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="V12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="W12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="X12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB12" s="19" t="s">
+      <c r="Q15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="X15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB15" s="19" t="s">
         <v>27</v>
       </c>
     </row>
@@ -28082,88 +28561,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="159" t="s">
         <v>654</v>
       </c>
-      <c r="B1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="151" t="s">
+      <c r="B1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="159" t="s">
         <v>27</v>
       </c>
     </row>
@@ -28727,88 +29206,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="159" t="s">
         <v>655</v>
       </c>
-      <c r="B1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="151" t="s">
+      <c r="B1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="159" t="s">
         <v>27</v>
       </c>
     </row>
@@ -29370,88 +29849,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="159" t="s">
         <v>659</v>
       </c>
-      <c r="B1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="151" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="151" t="s">
+      <c r="B1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="159" t="s">
         <v>27</v>
       </c>
     </row>
@@ -30189,88 +30668,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="155" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="147" t="s">
+      <c r="B1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="155" t="s">
         <v>27</v>
       </c>
     </row>
@@ -30751,88 +31230,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="155" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="147" t="s">
+      <c r="B1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="155" t="s">
         <v>27</v>
       </c>
     </row>
@@ -31998,88 +32477,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="157" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="149" t="s">
+      <c r="B1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="157" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="157" t="s">
         <v>27</v>
       </c>
     </row>
@@ -32562,88 +33041,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="158" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="150" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="150" t="s">
+      <c r="B1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="158" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="158" t="s">
         <v>27</v>
       </c>
     </row>
@@ -33549,88 +34028,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="155" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="147" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="147" t="s">
+      <c r="B1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="155" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="155" t="s">
         <v>27</v>
       </c>
     </row>
@@ -34366,88 +34845,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="154" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="146" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="146" t="s">
+      <c r="B1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="154" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="154" t="s">
         <v>27</v>
       </c>
     </row>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C65577-A38A-45F1-BD92-549F02B7D180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230F5CD6-F48A-4B30-9A79-35614027E8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="28" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="18" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DR  VÔ CHICO S MIGUEL - 1051 M" sheetId="60" r:id="rId1"/>
@@ -47,6 +47,7 @@
     <sheet name="São Miguel 1097" sheetId="82" r:id="rId32"/>
     <sheet name="Tolecaixas 1099" sheetId="83" r:id="rId33"/>
     <sheet name="DR Embalagens 1100" sheetId="84" r:id="rId34"/>
+    <sheet name="ABAPEL 1105" sheetId="85" r:id="rId35"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'ABAPEL 8023 M'!$A$1:$AB$10</definedName>
@@ -72,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6224" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6323" uniqueCount="683">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -2109,6 +2110,18 @@
   </si>
   <si>
     <t>102x105x102</t>
+  </si>
+  <si>
+    <t>776x1490</t>
+  </si>
+  <si>
+    <t>108x540x108</t>
+  </si>
+  <si>
+    <t>8.132</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - ABAPEL COMERCIO DE EMBALAGENS LTDA  —  OF: 001105</t>
   </si>
 </sst>
 </file>
@@ -13138,13 +13151,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="8.77734375" style="1" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" style="1" customWidth="1"/>
@@ -15063,88 +15076,136 @@
       </c>
     </row>
     <row r="23" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="19">
+      <c r="A23" s="5">
+        <v>21</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5">
+        <v>251412</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="5">
+        <v>350</v>
+      </c>
+      <c r="I23" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="J23" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L23" s="7"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="6"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="5"/>
+      <c r="AA23" s="5"/>
+      <c r="AB23" s="5"/>
+    </row>
+    <row r="24" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="19">
         <v>34700</v>
       </c>
-      <c r="I23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="K23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="L23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="N23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="O23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="P23" s="19">
+      <c r="I24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" s="19">
         <v>7142.2</v>
       </c>
-      <c r="Q23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="S23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="T23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="U23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="V23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="W23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="X23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB23" s="19" t="s">
+      <c r="Q24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="U24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="X24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA24" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB24" s="19" t="s">
         <v>27</v>
       </c>
     </row>
@@ -30630,6 +30691,392 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF195B3-1D12-452C-933A-2BCDEAFCB384}">
+  <dimension ref="A1:AB4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="5.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6" style="1" customWidth="1"/>
+    <col min="17" max="17" width="3.21875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.88671875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="6.77734375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="7.44140625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5546875" style="1" customWidth="1"/>
+    <col min="25" max="26" width="11.77734375" style="1" customWidth="1"/>
+    <col min="27" max="27" width="2.44140625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="8.44140625" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="159" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="159" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="159" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="109">
+        <v>1</v>
+      </c>
+      <c r="B3" s="111" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="109" t="s">
+        <v>334</v>
+      </c>
+      <c r="D3" s="109" t="s">
+        <v>676</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="109">
+        <v>262170</v>
+      </c>
+      <c r="G3" s="109" t="s">
+        <v>681</v>
+      </c>
+      <c r="H3" s="109">
+        <v>1100</v>
+      </c>
+      <c r="I3" s="110">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="J3" s="110">
+        <v>1.47</v>
+      </c>
+      <c r="K3" s="109" t="s">
+        <v>680</v>
+      </c>
+      <c r="L3" s="106">
+        <v>1222.452</v>
+      </c>
+      <c r="M3" s="108">
+        <v>808.5</v>
+      </c>
+      <c r="N3" s="105">
+        <v>0.1123</v>
+      </c>
+      <c r="O3" s="107">
+        <v>6.74</v>
+      </c>
+      <c r="P3" s="104">
+        <v>421.7</v>
+      </c>
+      <c r="Q3" s="104">
+        <v>2</v>
+      </c>
+      <c r="R3" s="104">
+        <v>1550</v>
+      </c>
+      <c r="S3" s="106">
+        <v>1.512</v>
+      </c>
+      <c r="T3" s="104">
+        <v>38</v>
+      </c>
+      <c r="U3" s="105">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="V3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="104" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB3" s="104" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="103">
+        <v>1100</v>
+      </c>
+      <c r="I4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="102">
+        <v>421.7</v>
+      </c>
+      <c r="Q4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="S4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="U4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="X4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="102" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB4" s="102" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AB1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DED98A-7C54-481B-B12E-5DA15CD22C80}">
   <sheetPr>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\programação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9581C10-11BD-422C-A873-CB3C685E0496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA1475C-5471-49B3-8369-E3FBF597D6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="11" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PCBOX IPE 1065 M" sheetId="52" r:id="rId1"/>
@@ -29,8 +29,9 @@
     <sheet name="DR Embalagens 1100" sheetId="84" r:id="rId14"/>
     <sheet name="ABAPEL 1105" sheetId="85" r:id="rId15"/>
     <sheet name="FAVINCO 1108" sheetId="86" r:id="rId16"/>
+    <sheet name="FAVINCO 1109 P" sheetId="87" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3001" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3096" uniqueCount="349">
   <si>
     <t>Seq.Prod</t>
   </si>
@@ -1081,6 +1082,21 @@
   </si>
   <si>
     <t>PROGRAMAÇÃO ONDULADEIRA - ANSELMO E FILHOS LTDA.  —  OF: 001108</t>
+  </si>
+  <si>
+    <t>890x1950</t>
+  </si>
+  <si>
+    <t>205x460x205</t>
+  </si>
+  <si>
+    <t>PRIME 032</t>
+  </si>
+  <si>
+    <t>03/07/2026</t>
+  </si>
+  <si>
+    <t>PROGRAMAÇÃO ONDULADEIRA - FAVINCO  —  OF: 001109</t>
   </si>
 </sst>
 </file>
@@ -1483,13 +1499,13 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -1744,88 +1760,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="88" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="89" t="s">
+      <c r="B1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="88" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3161,88 +3177,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="90" t="s">
         <v>280</v>
       </c>
-      <c r="B1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="88" t="s">
+      <c r="B1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="90" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4582,88 +4598,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="90" t="s">
         <v>335</v>
       </c>
-      <c r="B1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA1" s="88" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="88" t="s">
+      <c r="B1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="90" t="s">
+    